--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_78F93925DADCA3680AC4056103619441800DAB63" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B494AD88-1497-48CE-B4DE-BBB56924514B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="395">
   <si>
     <t>id</t>
   </si>
@@ -1276,7 +1276,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1323,6 +1323,19 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1402,7 +1415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1491,6 +1504,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1971,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:K293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -8908,7 +8935,7 @@
       </c>
       <c r="K224" s="8"/>
     </row>
-    <row r="225" spans="1:11" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>10500014</v>
       </c>
@@ -8936,10 +8963,9 @@
       <c r="I225" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="J225" s="8"/>
       <c r="K225" s="8"/>
     </row>
-    <row r="226" spans="1:11" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>10500015</v>
       </c>
@@ -8967,10 +8993,9 @@
       <c r="I226" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="J226" s="8"/>
       <c r="K226" s="8"/>
     </row>
-    <row r="227" spans="1:11" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>10500016</v>
       </c>
@@ -8998,7 +9023,6 @@
       <c r="I227" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="J227" s="8"/>
       <c r="K227" s="8"/>
     </row>
     <row r="228" spans="1:11" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
@@ -10899,6 +10923,126 @@
         <v>392</v>
       </c>
       <c r="J289" s="33"/>
+    </row>
+    <row r="290" spans="1:10" s="36" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A290" s="36">
+        <v>20550211</v>
+      </c>
+      <c r="B290" s="37">
+        <v>105502</v>
+      </c>
+      <c r="C290" s="38">
+        <v>2055021</v>
+      </c>
+      <c r="D290" s="38">
+        <v>1</v>
+      </c>
+      <c r="E290" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="F290" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G290" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="H290" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I290" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="J290" s="41"/>
+    </row>
+    <row r="291" spans="1:10" s="36" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A291" s="36">
+        <v>20550212</v>
+      </c>
+      <c r="B291" s="37">
+        <v>105502</v>
+      </c>
+      <c r="C291" s="38">
+        <v>2055021</v>
+      </c>
+      <c r="D291" s="38">
+        <v>2</v>
+      </c>
+      <c r="E291" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F291" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G291" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="H291" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I291" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="J291" s="41"/>
+    </row>
+    <row r="292" spans="1:10" s="36" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A292" s="36">
+        <v>20550213</v>
+      </c>
+      <c r="B292" s="37">
+        <v>105502</v>
+      </c>
+      <c r="C292" s="38">
+        <v>2055021</v>
+      </c>
+      <c r="D292" s="38">
+        <v>3</v>
+      </c>
+      <c r="E292" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F292" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G292" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="H292" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I292" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="J292" s="41"/>
+    </row>
+    <row r="293" spans="1:10" s="36" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A293" s="36">
+        <v>20550214</v>
+      </c>
+      <c r="B293" s="37">
+        <v>105502</v>
+      </c>
+      <c r="C293" s="38">
+        <v>2055021</v>
+      </c>
+      <c r="D293" s="38">
+        <v>4</v>
+      </c>
+      <c r="E293" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="F293" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="G293" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="H293" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I293" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="J293" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -8125,7 +8125,7 @@
         <v>2</v>
       </c>
       <c r="E179" s="19" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F179" s="17" t="s">
         <v>20</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseRoller" sheetId="1" r:id="rId1"/>
@@ -1059,22 +1059,22 @@
     <t>4_9_6_7_8_5_8_7_8_2_10_2_9_1_3_1_5_8_7_11_2_1_5_11_3_1_1_5_1_1_4_3_9_6_3_2_1_3_9_6_1_1_7_6_3_3_5_4_3_5_9_8_3_1_6_6_3_11_4_4_8_6_9_6_11_3_2_7_8_8_7_3_6_2_3_4_9_2_10_4_1_3_10_4_3_11_4_11_3_6_10_2_5_1_4_6_11_1_3_11_4_10_3_11_1_2_9_4_3_5_9_5_6_3_8_4_7_4_3_8_3_2_10_4_5_4_5_9_9_7_7_10_3_2_10_2_7_10_3_9_5_4_11_1_8_2_3_1_1_1_5_7_4_1_4_6_3_8_8_4_1_4_1_6_9_9_9_1_5_2_11_3_3_6_11_4_3_8_11_4_4_1_11_2_9_6_5_6_7_9_7_8_9_6_10_2_9_8_5_10_4_9_2_7_4_4_5_4_1_11_4_2_10_4_9_7_3_7_2_9_3_11_3_2_6_4_11_4_4_3_9_5_5_9_7_10_2_6_4_7_6_2_5_5_7_5_5_11_3_11_4_11_1_7_5_2_4_3_11_3_1_5_8_5_4_1_11_1_8_11_3_7_10_4_7_9_10_1_7_11_4_8_7_6_7_5_10_2_10_4_2_10_2_4_7_8_8_6_6_2_5_8_4_3_9_7_3_1_2_2_5_10_3_7_6_6_6_1_1_11_2_2_8_6_1_1_3_5_6_10_2_3_8_9_2_9_10_3_9_8_1_6_10_3_8_5_5_3_8_10_3_11_2_8_9_6_6_1_10_3_10_4_9_11_2_4_6_10_2_3_2_1_8_10_4_1_9_6_4_8_7_9_8_11_3_5_1_10_4_2_6_3_2_6_7_1_9_6_1_9_3_4_1_1_10_3_10_3_1_1_11_3_10_2_3_9_6_11_4_9_8_8_8_10_3_1_2_6_1_11_1_8_9_9_2_3_6_8_10_4_8_3_11_1_2_8_3_2_3_1_2_3_5_6_7_8_3_4_1_3_7_10_2_3_10_3_10_2_3_1_11_1_9_3_2_2_5_4_11_2_2_11_3_8_10_2_3_4_9_3_3_8_10_4_3_11_3_10_4_6</t>
   </si>
   <si>
-    <t>1_2_3_5_1_1_1_2_2_2_1_3_4_1_1_3_1_1_4_2_4_4_4_5_1_1_4_1_16_3_2_3_3_1_4_2_2_4_3_3_1_1_1_1_2_1_5_2_3_3_1_2_1_4_3_3_4_2_1_1_1_5_1_16_1_3_3_1_2_2_3_1_16_3_2_1_2_16_3_1_1_1_1_1_1_1_1_1_3_5_1_1_1_16_1_16_16_3_3_2_3_3_3_3_1_4_4_1_2_3_1_4_5_1_2_1_1_1_2_2_3_5_2_1_3_4_4_1_2_2_3_1_1_4_3_2_2_2_5_1_1_1_3_3_3_5_1_1_1_2_3_1_16_5_4_4_4_3_3_1_2_1_4_3_3_3_3_1_1_2_3_3_3_1_4_2_2_2_3_1_3_3_4_4_1_1_1_3_5_1_4_16_2_2_2_4_5_2_2_2_2_2_4_3_16_2_5_3_1_4_3_1_2_2_1_3_3_2_2_4_1_3_1_4_3_2_3_1_1_1_4_1_4_5_1_1_1_2_1_5_2_2_1_1_3_2_4_2_3_2_5_3_3_3_3_4_1_1_2_1_1_1_2_5_3_1_4_2_2_2_1_2_3_3_1_2_4_2_2_1_2_4_4_2_1_2_3_1_1_5_4_1_2_2_2_3_2_2_2_5_1_1_4_3_1_1_1_1_2_2_2_1_2_1_1_1_3_4_2_2_3_2_16_3_3_3_1_1_1_1_1_4_4_3_3_3_3_1_1_2_2_5_5_1_1_5_1_2_4_1_5_1_3_1_4_16_2_3_2_2_1_1_4_5_2_2_2_1_3_2_4_4_2_2_1_1_1_3_1_4_3_1_1_3_3_2_4_2_4_2_3_4_2_2_2_3_3_5_1_1_2_2_4_4_1_5_4_2_2_4_4_2_5_1_2_2_3_2_1_1_2_2_3_16_16_1_3_3_2_3_1_2_2_2_1_2_2_3_3_2_2_2_3_1_1_3_2_1_1_1_1_1_2_3_1_3_4_1_2_5_5_4_5_3_1_4_2_2_16_16_1_4_1_1_5_2_5_16_3_3_1_4_4_2_2_3_3_1_2_3_1_3_16_16_3_2_5_2_3_5</t>
+    <t>1_2_3_5_1_1_1_2_2_2_1_3_4_1_1_3_1_1_4_2_4_4_4_5_1_1_4_1_1_3_2_3_3_1_4_2_2_4_3_3_1_1_1_1_2_1_5_2_3_3_1_2_1_4_3_3_4_2_1_1_1_5_1_1_1_3_3_1_2_2_3_1_1_3_2_1_2_1_3_1_1_1_1_1_1_1_1_1_3_5_1_1_1_1_1_1_1_3_3_2_3_3_3_3_1_4_4_1_2_3_1_4_5_1_2_1_1_1_2_2_3_5_2_1_3_4_4_1_2_2_3_1_1_4_3_2_2_2_5_1_1_1_3_3_3_5_1_1_1_2_3_1_1_5_4_4_4_3_3_1_2_1_4_3_3_3_3_1_1_2_3_3_3_1_4_2_2_2_3_1_3_3_4_4_1_1_1_3_5_1_4_1_2_2_2_4_5_2_2_2_2_2_4_3_1_2_5_3_1_4_3_1_2_2_1_3_3_2_2_4_1_3_1_4_3_2_3_1_1_1_4_1_4_5_1_1_1_2_1_5_2_2_1_1_3_2_4_2_3_2_5_3_3_3_3_4_1_1_2_1_1_1_2_5_3_1_4_2_2_2_1_2_3_3_1_2_4_2_2_1_2_4_4_2_1_2_3_1_1_5_4_1_2_2_2_3_2_2_2_5_1_1_4_3_1_1_1_1_2_2_2_1_2_1_1_1_3_4_2_2_3_2_1_3_3_3_1_1_1_1_1_4_4_3_3_3_3_1_1_2_2_5_5_1_1_5_1_2_4_1_5_1_3_1_4_1_2_3_2_2_1_1_4_5_2_2_2_1_3_2_4_4_2_2_1_1_1_3_1_4_3_1_1_3_3_2_4_2_4_2_3_4_2_2_2_3_3_5_1_1_2_2_4_4_1_5_4_2_2_4_4_2_5_1_2_2_3_2_1_1_2_2_3_1_1_1_3_3_2_3_1_2_2_2_1_2_2_3_3_2_2_2_3_1_1_3_2_1_1_1_1_1_2_3_1_3_4_1_2_5_5_4_5_3_1_4_2_2_1_1_1_4_1_1_5_2_5_1_3_3_1_4_4_2_2_3_3_1_2_3_1_3_1_1_3_2_5_2_3_5</t>
   </si>
   <si>
     <t>2_2_2_2</t>
   </si>
   <si>
-    <t>3_3_2_5_3_3_1_4_1_3_2_2_5_1_5_5_1_16_16_3_2_2_2_4_1_3_3_4_5_16_1_1_3_2_3_2_1_1_3_2_2_2_2_1_2_1_3_2_1_2_4_1_1_4_2_4_2_2_1_1_3_2_5_3_1_3_3_2_2_1_1_1_1_1_2_1_3_2_2_1_1_1_1_1_1_4_4_1_3_3_3_4_4_1_2_1_2_4_1_2_2_2_2_1_2_2_1_1_3_2_2_3_4_1_3_1_3_3_1_4_1_2_2_4_3_4_2_3_2_3_1_3_3_2_2_1_1_5_4_3_1_2_1_1_3_2_1_1_5_5_4_3_3_3_1_4_1_3_3_1_2_4_1_2_2_3_3_1_1_3_16_2_1_3_1_1_2_4_1_2_3_2_4_4_2_2_2_1_3_1_3_1_2_1_16_4_1_2_2_2_2_1_3_3_4_2_3_5_1_1_1_1_1_4_1_2_1_5_5_1_4_1_2_3_2_3_3_4_3_3_4_4_3_1_3_3_4_5_3_2_1_3_2_3_2_1_2_1_4_2_1_3_2_3_3_4_1_3_3_3_4_3_3_1_2_2_2_3_2_1_1_2_3_3_1_1_4_3_3_4_16_1_2_2_2_2_2_3_2_1_3_1_4_1_1_2_4_3_5_2_1_5_2_1_1_1_2_4_3_1_4_1_4_3_2_1_4_3_5_2_1_3_3_5_3_1_1_2_3_3_1_3_1_1_1_1_3_3_1_2_4_2_1_1_2_4_4_5_1_1_1_2_2_3_2_2_1_1_1_1_2_1_2_4_4_4_1_3_2_4_1_1_1_4_1_1_2_1_1_3_1_1_1_4_1_1_4_4_1_16_1_4_2_1_3_4_1_2_4_2_4_3_1_1_1_2_3_1_2_1_5_1_1_4_1_2_2_2_5_4_16_2_2_1_1_2_4_1_1_3_1_2_3_2_2_1_3_3_3_3_1_1_16_1_2_5_3_4_1_1_1_2_1_2_1_5_2_4_1_1_2_2_2_1_1_1_1_2_1_3_1_1_1_2_1_2_3_2_1_5_5_1_5_16_4_2_2_5_4_4_5_3_1_3_3_5_1_16_1_2</t>
+    <t>3_3_2_5_3_3_1_4_1_3_2_2_5_1_5_5_1_1_1_3_2_2_2_4_1_3_3_4_5_1_1_1_3_2_3_2_1_1_3_2_2_2_2_1_2_1_3_2_1_2_4_1_1_4_2_4_2_2_1_1_3_2_5_3_1_3_3_2_2_1_1_1_1_1_2_1_3_2_2_1_1_1_1_1_1_4_4_1_3_3_3_4_4_1_2_1_2_4_1_2_2_2_2_1_2_2_1_1_3_2_2_3_4_1_3_1_3_3_1_4_1_2_2_4_3_4_2_3_2_3_1_3_3_2_2_1_1_5_4_3_1_2_1_1_3_2_1_1_5_5_4_3_3_3_1_4_1_3_3_1_2_4_1_2_2_3_3_1_1_3_1_2_1_3_1_1_2_4_1_2_3_2_4_4_2_2_2_1_3_1_3_1_2_1_1_4_1_2_2_2_2_1_3_3_4_2_3_5_1_1_1_1_1_4_1_2_1_5_5_1_4_1_2_3_2_3_3_4_3_3_4_4_3_1_3_3_4_5_3_2_1_3_2_3_2_1_2_1_4_2_1_3_2_3_3_4_1_3_3_3_4_3_3_1_2_2_2_3_2_1_1_2_3_3_1_1_4_3_3_4_1_1_2_2_2_2_2_3_2_1_3_1_4_1_1_2_4_3_5_2_1_5_2_1_1_1_2_4_3_1_4_1_4_3_2_1_4_3_5_2_1_3_3_5_3_1_1_2_3_3_1_3_1_1_1_1_3_3_1_2_4_2_1_1_2_4_4_5_1_1_1_2_2_3_2_2_1_1_1_1_2_1_2_4_4_4_1_3_2_4_1_1_1_4_1_1_2_1_1_3_1_1_1_4_1_1_4_4_1_1_1_4_2_1_3_4_1_2_4_2_4_3_1_1_1_2_3_1_2_1_5_1_1_4_1_2_2_2_5_4_1_2_2_1_1_2_4_1_1_3_1_2_3_2_2_1_3_3_3_3_1_1_1_1_2_5_3_4_1_1_1_2_1_2_1_5_2_4_1_1_2_2_2_1_1_1_1_2_1_3_1_1_1_2_1_2_3_2_1_5_5_1_5_1_4_2_2_5_4_4_5_3_1_3_3_5_1_1_1_2</t>
   </si>
   <si>
     <t>3_3_3_3</t>
   </si>
   <si>
-    <t>3_3_1_4_4_1_1_1_5_1_16_4_3_2_2_2_4_3_4_1_3_3_5_1_1_1_16_1_1_2_3_3_1_4_4_3_3_4_5_1_1_1_4_1_16_16_5_4_3_4_4_3_1_1_1_5_4_1_1_4_1_1_2_2_2_5_4_3_3_3_5_4_2_2_1_2_1_1_1_3_2_1_3_1_1_2_2_3_4_1_1_1_3_3_4_4_1_1_1_5_1_5_4_2_3_1_3_1_3_2_1_2_1_1_2_4_4_2_4_4_3_4_16_16_1_1_4_2_1_3_16_2_2_2_5_1_1_4_3_3_3_4_4_3_3_1_1_5_3_3_1_1_1_2_3_3_5_2_2_2_1_3_4_2_3_1_2_1_1_2_4_3_4_2_2_4_4_4_1_3_1_1_3_2_1_2_2_1_3_4_1_2_2_4_2_3_3_2_3_4_3_1_3_2_2_3_3_16_3_4_2_2_1_2_4_4_2_4_3_5_2_4_1_2_2_3_3_1_1_4_2_2_4_2_2_3_2_3_3_2_1_2_4_1_3_2_1_1_4_3_3_3_5_1_4_1_2_2_4_3_4_4_1_5_1_2_5_4_1_5_2_2_1_1_3_1_2_3_5_2_2_3_1_4_1_1_1_4_3_1_2_2_1_4_16_1_3_4_4_2_2_2_1_3_3_1_2_2_1_3_2_2_2_3_2_1_5_4_2_4_3_4_4_3_3_3_1_4_1_1_2_2_2_1_2_5_4_2_1_1_1_1_1_4_2_2_1_1_4_3_3_5_4_1_3_4_2_2_1_1_2_1_1_4_2_3_2_2_2_3_3_1_1_2_1_2_3_2_1_4_1_1_5_5_1_1_3_3_1_3_4_3_1_3_1_1_1_2_2_2_4_1_2_3_3_1_1_1_1_1_3_1_3_2_2_1_1_2_1_5_2_3_1_2_1_1_3_2_3_1_1_3_4_1_2_4_3_3_5_3_1_3_2_5_4_2_3_1_1_5_5_1_3_16_4_3_1_3_2_3_2_2_2_1_2_2_2_2_3_3_3_3_1_3_4_1_2_4_3_1_2_5_2_1_1_2_16_16_3_1_1_1_16_2_3_1_2_2_1_1</t>
-  </si>
-  <si>
-    <t>1_1_1_1_1_1_1_2_2_4_1_3_2_2_1_2_2_4_2_1_2_3_3_3_3_1_2_1_2_1_2_1_5_3_3_16_2_1_4_5_4_4_2_2_4_4_4_3_1_2_1_2_2_1_1_2_2_1_1_2_2_2_1_1_1_1_4_2_2_5_2_1_2_4_2_1_3_3_4_1_1_2_1_2_3_1_1_1_4_1_4_4_3_1_1_1_1_1_1_1_1_3_2_4_16_2_2_1_5_2_3_1_1_4_5_3_4_3_3_2_3_1_2_1_3_2_16_3_2_1_4_3_4_1_2_2_2_2_1_2_2_2_2_4_1_16_16_1_1_2_2_2_3_3_1_1_3_1_1_1_1_1_2_1_1_1_1_3_3_5_5_4_5_3_3_3_3_1_1_2_3_1_1_4_5_3_1_2_2_16_2_1_2_2_1_2_4_1_2_5_2_2_2_5_4_1_1_2_4_2_1_1_16_1_5_5_2_3_5_2_3_1_1_3_2_4_1_2_1_1_1_5_5_4_4_1_2_5_5_5_1_3_2_4_2_2_3_5_1_1_4_2_2_1_5_3_3_3_4_2_2_3_1_3_1_16_1_4_2_1_3_2_1_3_3_1_3_1_4_2_16_2_2_5_2_1_4_16_2_3_1_1_2_3_4_1_1_3_1_16_2_5_1_2_1_3_2_5_2_1_1_16_5_2_2_3_16_1_16_5_2_4_4_2_4_1_1_1_1_1_2_1_1_1_1_2_2_2_1_1_1_2_2_2_2_1_4_2_1_1_4_1_5_5_5_4_5_4_2_4_2_4_2_1_3_4_2_3_2_1_3_3_3_1_2_2_2_2_2_1_3_1_2_1_2_2_1_2_16_3_1_2_1_3_5_1_1_1_3_2_4_2_5_4_1_2_1_5_1_1_3_2_2_1_1_1_2_2_2_2_3_3_2_5_1_2_2_2_1_1_1_4_1_3_1_4_2_2_5_2_1_3_1_4_2_5_4_4_3_3_3_2_3_1_1_1_2_1_4_1_3_2_1_2_1_3_2_4_4_3_1_4_1_3_5_3_2_3_4_1_3_2_4_4_4_1_3_2_1_3_2_3_3_3_4_1_5_2_5_1</t>
+    <t>3_3_1_4_4_1_1_1_5_1_1_4_3_2_2_2_4_3_4_1_3_3_5_1_1_1_1_1_1_2_3_3_1_4_4_3_3_4_5_1_1_1_4_1_1_1_5_4_3_4_4_3_1_1_1_5_4_1_1_4_1_1_2_2_2_5_4_3_3_3_5_4_2_2_1_2_1_1_1_3_2_1_3_1_1_2_2_3_4_1_1_1_3_3_4_4_1_1_1_5_1_5_4_2_3_1_3_1_3_2_1_2_1_1_2_4_4_2_4_4_3_4_1_1_1_1_4_2_1_3_1_2_2_2_5_1_1_4_3_3_3_4_4_3_3_1_1_5_3_3_1_1_1_2_3_3_5_2_2_2_1_3_4_2_3_1_2_1_1_2_4_3_4_2_2_4_4_4_1_3_1_1_3_2_1_2_2_1_3_4_1_2_2_4_2_3_3_2_3_4_3_1_3_2_2_3_3_1_3_4_2_2_1_2_4_4_2_4_3_5_2_4_1_2_2_3_3_1_1_4_2_2_4_2_2_3_2_3_3_2_1_2_4_1_3_2_1_1_4_3_3_3_5_1_4_1_2_2_4_3_4_4_1_5_1_2_5_4_1_5_2_2_1_1_3_1_2_3_5_2_2_3_1_4_1_1_1_4_3_1_2_2_1_4_1_1_3_4_4_2_2_2_1_3_3_1_2_2_1_3_2_2_2_3_2_1_5_4_2_4_3_4_4_3_3_3_1_4_1_1_2_2_2_1_2_5_4_2_1_1_1_1_1_4_2_2_1_1_4_3_3_5_4_1_3_4_2_2_1_1_2_1_1_4_2_3_2_2_2_3_3_1_1_2_1_2_3_2_1_4_1_1_5_5_1_1_3_3_1_3_4_3_1_3_1_1_1_2_2_2_4_1_2_3_3_1_1_1_1_1_3_1_3_2_2_1_1_2_1_5_2_3_1_2_1_1_3_2_3_1_1_3_4_1_2_4_3_3_5_3_1_3_2_5_4_2_3_1_1_5_5_1_3_1_4_3_1_3_2_3_2_2_2_1_2_2_2_2_3_3_3_3_1_3_4_1_2_4_3_1_2_5_2_1_1_2_1_1_3_1_1_1_1_2_3_1_2_2_1_1</t>
+  </si>
+  <si>
+    <t>1_1_1_1_1_1_1_2_2_4_1_3_2_2_1_2_2_4_2_1_2_3_3_3_3_1_2_1_2_1_2_1_5_3_3_1_2_1_4_5_4_4_2_2_4_4_4_3_1_2_1_2_2_1_1_2_2_1_1_2_2_2_1_1_1_1_4_2_2_5_2_1_2_4_2_1_3_3_4_1_1_2_1_2_3_1_1_1_4_1_4_4_3_1_1_1_1_1_1_1_1_3_2_4_1_2_2_1_5_2_3_1_1_4_5_3_4_3_3_2_3_1_2_1_3_2_1_3_2_1_4_3_4_1_2_2_2_2_1_2_2_2_2_4_1_1_1_1_1_2_2_2_3_3_1_1_3_1_1_1_1_1_2_1_1_1_1_3_3_5_5_4_5_3_3_3_3_1_1_2_3_1_1_4_5_3_1_2_2_1_2_1_2_2_1_2_4_1_2_5_2_2_2_5_4_1_1_2_4_2_1_1_1_1_5_5_2_3_5_2_3_1_1_3_2_4_1_2_1_1_1_5_5_4_4_1_2_5_5_5_1_3_2_4_2_2_3_5_1_1_4_2_2_1_5_3_3_3_4_2_2_3_1_3_1_1_1_4_2_1_3_2_1_3_3_1_3_1_4_2_1_2_2_5_2_1_4_1_2_3_1_1_2_3_4_1_1_3_1_1_2_5_1_2_1_3_2_5_2_1_1_1_5_2_2_3_1_1_1_5_2_4_4_2_4_1_1_1_1_1_2_1_1_1_1_2_2_2_1_1_1_2_2_2_2_1_4_2_1_1_4_1_5_5_5_4_5_4_2_4_2_4_2_1_3_4_2_3_2_1_3_3_3_1_2_2_2_2_2_1_3_1_2_1_2_2_1_2_1_3_1_2_1_3_5_1_1_1_3_2_4_2_5_4_1_2_1_5_1_1_3_2_2_1_1_1_2_2_2_2_3_3_2_5_1_2_2_2_1_1_1_4_1_3_1_4_2_2_5_2_1_3_1_4_2_5_4_4_3_3_3_2_3_1_1_1_2_1_4_1_3_2_1_2_1_3_2_4_4_3_1_4_1_3_5_3_2_3_4_1_3_2_4_4_4_1_3_2_1_3_2_3_3_3_4_1_5_2_5_1</t>
   </si>
   <si>
     <t>6_7_6_10_7_7_9_6_7_6_6_6_6_7_7_7_7_7_8_6_7_8_6_9_6_8_7_6_8_6_6_10_7_6_7_9_9_10_9_8_9_8_6_8_8_6_9_6_10_10_6_6_7_6_17_8_8_8_9_6_6_6_6_8_6_6_9_8_7_7_6_6_6_8_7_7_6_7_7_7_10_10_7_8_17_6_9_9_6_9_9_9_6_8_6_6_17_6_6_7_7_6_7_7_7_6_9_8_7_6_6_8_8_7_10_6_10_8_8_9_8_7_6_6_6_7_7_6_6_9_7_8_9_9_17_8_7_7_9_7_6_6_10_9_10_8_7_7_8_7_6_6_9_9_6_8_9_9_6_8_6_6_6_9_6_7_9_7_6_6_6_10_6_17_7_7_6_9_8_7_7_6_6_9_9_6_6_10_6_7_9_6_6_7_7_7_6_17_9_8_8_8_8_9_8_6_7_8_6_9_10_8_8_8_8_8_8_7_8_9_6_6_6_7_7_7_7_7_9_6_8_17_8_9_7_6_6_7_7_6_8_7_6_7_7_6_6_8_8_6_9_7_8_6_7_7_6_10_6_6_6_8_6_9_6_10_7_9_6_8_8_8_6_9_9_6_7_7_8_6_6_10_6_6_8_7_7_6_6_6_8_8_6_6_6_6_6_8_7_6_6_6_6_7_7_6_10_10_8_7_6_6_9_7_7_8_7_8_9_7_8_17_17_6_6_6_8_7_7_9_9_6_7_7_8_8_7_7_17_7_7_6_7_7_7_10_9_9_7_7_7_10_8_10_6_6_10_6_9_10_6_7_10_7_8_8_8_8_8_8_6_6_6_6_8_6_6_17_7_7_7_6_6_9_9_6_6_6_9_6_9_6_6_7_7_9_17_7_8_6_9_7_10_10_10_7_7_17_10_6_9_7_6_7_7_6_6_9_6_8_10_7_7_10_6_17_6_6_7_9_9_9_9_9_9_6_9_7_6_6_6_9_17_7_17_7_9_8_7_9_8_6_7_17_9_7_6_8_8_7_6_6_8_7_6_6_6_6_7_8_9_10_6_6_10_8_10_9_8_7_10_6_6_6_6_8_9_9_9_9_9_9_9_17_6_17_9_7_6_6</t>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -8764,13 +8764,13 @@
     <row r="200" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A200" s="5">
         <f t="shared" si="8"/>
-        <v>20160022</v>
+        <v>20160012</v>
       </c>
       <c r="B200" s="6">
         <v>101600</v>
       </c>
       <c r="C200" s="34">
-        <v>2016002</v>
+        <v>2016001</v>
       </c>
       <c r="D200" s="34">
         <v>2</v>
@@ -8795,13 +8795,13 @@
     <row r="201" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A201" s="5">
         <f t="shared" si="8"/>
-        <v>20160033</v>
+        <v>20160013</v>
       </c>
       <c r="B201" s="6">
         <v>101600</v>
       </c>
       <c r="C201" s="34">
-        <v>2016003</v>
+        <v>2016001</v>
       </c>
       <c r="D201" s="34">
         <v>3</v>
@@ -8826,13 +8826,13 @@
     <row r="202" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A202" s="5">
         <f t="shared" si="8"/>
-        <v>20160044</v>
+        <v>20160014</v>
       </c>
       <c r="B202" s="6">
         <v>101600</v>
       </c>
       <c r="C202" s="34">
-        <v>2016004</v>
+        <v>2016001</v>
       </c>
       <c r="D202" s="34">
         <v>4</v>
@@ -8857,13 +8857,13 @@
     <row r="203" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A203" s="5">
         <f t="shared" si="8"/>
-        <v>20160055</v>
+        <v>20160015</v>
       </c>
       <c r="B203" s="6">
         <v>101600</v>
       </c>
       <c r="C203" s="34">
-        <v>2016005</v>
+        <v>2016001</v>
       </c>
       <c r="D203" s="34">
         <v>5</v>
@@ -8888,13 +8888,13 @@
     <row r="204" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A204" s="5">
         <f t="shared" si="8"/>
-        <v>20160066</v>
+        <v>20160016</v>
       </c>
       <c r="B204" s="6">
         <v>101600</v>
       </c>
       <c r="C204" s="34">
-        <v>2016006</v>
+        <v>2016001</v>
       </c>
       <c r="D204" s="34">
         <v>6</v>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="428">
   <si>
     <t>id</t>
   </si>
@@ -1077,52 +1077,52 @@
     <t>1_1_1_1_1_1_1_2_2_4_1_3_2_2_1_2_2_4_2_1_2_3_3_3_3_1_2_1_2_1_2_1_5_3_3_1_2_1_4_5_4_4_2_2_4_4_4_3_1_2_1_2_2_1_1_2_2_1_1_2_2_2_1_1_1_1_4_2_2_5_2_1_2_4_2_1_3_3_4_1_1_2_1_2_3_1_1_1_4_1_4_4_3_1_1_1_1_1_1_1_1_3_2_4_1_2_2_1_5_2_3_1_1_4_5_3_4_3_3_2_3_1_2_1_3_2_1_3_2_1_4_3_4_1_2_2_2_2_1_2_2_2_2_4_1_1_1_1_1_2_2_2_3_3_1_1_3_1_1_1_1_1_2_1_1_1_1_3_3_5_5_4_5_3_3_3_3_1_1_2_3_1_1_4_5_3_1_2_2_1_2_1_2_2_1_2_4_1_2_5_2_2_2_5_4_1_1_2_4_2_1_1_1_1_5_5_2_3_5_2_3_1_1_3_2_4_1_2_1_1_1_5_5_4_4_1_2_5_5_5_1_3_2_4_2_2_3_5_1_1_4_2_2_1_5_3_3_3_4_2_2_3_1_3_1_1_1_4_2_1_3_2_1_3_3_1_3_1_4_2_1_2_2_5_2_1_4_1_2_3_1_1_2_3_4_1_1_3_1_1_2_5_1_2_1_3_2_5_2_1_1_1_5_2_2_3_1_1_1_5_2_4_4_2_4_1_1_1_1_1_2_1_1_1_1_2_2_2_1_1_1_2_2_2_2_1_4_2_1_1_4_1_5_5_5_4_5_4_2_4_2_4_2_1_3_4_2_3_2_1_3_3_3_1_2_2_2_2_2_1_3_1_2_1_2_2_1_2_1_3_1_2_1_3_5_1_1_1_3_2_4_2_5_4_1_2_1_5_1_1_3_2_2_1_1_1_2_2_2_2_3_3_2_5_1_2_2_2_1_1_1_4_1_3_1_4_2_2_5_2_1_3_1_4_2_5_4_4_3_3_3_2_3_1_1_1_2_1_4_1_3_2_1_2_1_3_2_4_4_3_1_4_1_3_5_3_2_3_4_1_3_2_4_4_4_1_3_2_1_3_2_3_3_3_4_1_5_2_5_1</t>
   </si>
   <si>
-    <t>6_7_6_10_7_7_9_6_7_6_6_6_6_7_7_7_7_7_8_6_7_8_6_9_6_8_7_6_8_6_6_10_7_6_7_9_9_10_9_8_9_8_6_8_8_6_9_6_10_10_6_6_7_6_17_8_8_8_9_6_6_6_6_8_6_6_9_8_7_7_6_6_6_8_7_7_6_7_7_7_10_10_7_8_17_6_9_9_6_9_9_9_6_8_6_6_17_6_6_7_7_6_7_7_7_6_9_8_7_6_6_8_8_7_10_6_10_8_8_9_8_7_6_6_6_7_7_6_6_9_7_8_9_9_17_8_7_7_9_7_6_6_10_9_10_8_7_7_8_7_6_6_9_9_6_8_9_9_6_8_6_6_6_9_6_7_9_7_6_6_6_10_6_17_7_7_6_9_8_7_7_6_6_9_9_6_6_10_6_7_9_6_6_7_7_7_6_17_9_8_8_8_8_9_8_6_7_8_6_9_10_8_8_8_8_8_8_7_8_9_6_6_6_7_7_7_7_7_9_6_8_17_8_9_7_6_6_7_7_6_8_7_6_7_7_6_6_8_8_6_9_7_8_6_7_7_6_10_6_6_6_8_6_9_6_10_7_9_6_8_8_8_6_9_9_6_7_7_8_6_6_10_6_6_8_7_7_6_6_6_8_8_6_6_6_6_6_8_7_6_6_6_6_7_7_6_10_10_8_7_6_6_9_7_7_8_7_8_9_7_8_17_17_6_6_6_8_7_7_9_9_6_7_7_8_8_7_7_17_7_7_6_7_7_7_10_9_9_7_7_7_10_8_10_6_6_10_6_9_10_6_7_10_7_8_8_8_8_8_8_6_6_6_6_8_6_6_17_7_7_7_6_6_9_9_6_6_6_9_6_9_6_6_7_7_9_17_7_8_6_9_7_10_10_10_7_7_17_10_6_9_7_6_7_7_6_6_9_6_8_10_7_7_10_6_17_6_6_7_9_9_9_9_9_9_6_9_7_6_6_6_9_17_7_17_7_9_8_7_9_8_6_7_17_9_7_6_8_8_7_6_6_8_7_6_6_6_6_7_8_9_10_6_6_10_8_10_9_8_7_10_6_6_6_6_8_9_9_9_9_9_9_9_17_6_17_9_7_6_6</t>
-  </si>
-  <si>
-    <t>6_6_9_7_9_8_8_7_10_8_8_9_9_7_7_10_8_6_9_6_17_7_9_6_8_7_17_7_10_6_8_9_6_7_7_6_6_7_7_8_9_6_6_9_6_6_7_8_7_7_7_9_7_6_6_6_7_8_6_7_8_7_7_9_6_6_17_7_17_9_7_7_8_6_6_6_6_6_7_7_6_17_8_6_7_9_7_6_8_10_6_6_9_10_7_8_9_7_9_10_8_7_6_6_9_9_6_6_6_8_8_6_7_6_6_6_6_6_8_9_9_9_6_6_6_8_6_6_9_8_8_8_8_8_7_7_6_10_8_9_17_8_7_6_6_6_6_8_7_9_7_17_6_9_10_7_6_7_7_7_9_6_6_6_6_7_8_9_8_8_7_10_10_10_7_6_10_10_9_6_6_8_6_7_7_6_8_7_6_9_6_6_6_9_6_8_7_8_6_6_6_9_9_8_7_7_7_7_17_8_7_9_7_10_6_7_7_7_6_8_7_7_7_6_6_6_7_7_8_8_10_6_9_9_9_7_7_7_8_6_8_6_8_8_8_8_6_7_7_10_10_6_6_9_6_9_6_6_8_7_8_8_6_7_7_7_7_8_8_8_6_6_6_8_7_7_6_6_10_10_6_9_10_17_17_17_8_8_8_8_6_6_6_6_6_8_7_6_8_8_8_9_8_9_6_7_8_6_7_7_7_7_6_8_8_10_6_7_6_6_6_7_6_7_7_8_8_7_10_7_7_7_6_6_7_7_6_7_9_7_6_6_6_10_10_10_7_7_7_7_6_7_7_8_8_17_7_6_8_8_6_7_7_6_8_7_6_6_7_8_8_8_6_7_7_6_8_7_6_8_7_6_7_6_8_7_6_6_6_6_7_8_6_8_6_6_8_8_9_7_8_7_8_7_6_6_6_7_7_9_7_7_6_7_7_6_17_7_7_8_6_6_6_9_9_10_8_6_6_9_7_7_7_9_6_6_10_10_7_8_9_6_10_17_17_9_8_8_7_17_17_7_7_7_7_10_6_6_6_8_10_7_6_8_9_10_6_6_17_9_7_6_7_6_6_6_6_17_17_8_8_8_6_7_7_9_10_6_17_6_7_9_7_6_6_6_8_6_9_9</t>
-  </si>
-  <si>
-    <t>7_6_6_10_8_8_6_6_9_9_9_10_7_7_9_7_7_7_10_9_9_6_8_7_7_10_6_10_6_6_6_7_7_17_9_6_6_6_7_9_6_7_7_7_6_6_6_6_7_6_8_6_6_8_9_8_8_7_7_7_9_9_6_6_6_17_6_7_6_6_7_8_6_8_6_8_6_8_8_10_7_7_7_6_7_7_7_6_9_6_10_6_6_8_8_9_8_8_10_6_6_8_9_6_6_7_17_17_7_6_10_7_9_6_7_7_7_8_8_6_6_6_6_8_8_6_8_8_6_8_9_8_6_9_6_6_6_7_10_10_6_7_7_6_9_6_9_9_17_7_7_6_8_8_6_10_10_7_8_6_8_17_17_7_10_8_8_6_8_6_6_6_7_6_9_6_8_8_8_8_9_8_8_9_7_6_8_6_6_7_7_6_8_8_8_6_8_6_6_6_6_6_7_6_7_6_8_6_9_17_6_8_6_6_6_7_7_7_9_8_7_6_6_7_7_10_10_10_6_7_17_7_7_8_6_6_6_8_7_8_7_6_7_7_7_6_6_8_7_7_9_7_6_7_17_17_8_6_7_6_9_6_8_7_7_7_6_6_7_6_8_6_9_9_6_10_7_7_6_6_6_17_17_10_10_8_8_17_9_9_9_6_7_8_8_6_7_6_6_7_8_9_10_10_6_8_8_17_9_8_8_10_10_10_10_8_8_8_10_7_6_6_6_7_8_6_6_7_7_7_10_7_6_6_8_17_6_8_8_7_8_6_6_6_7_7_8_6_6_6_6_9_9_6_9_6_6_7_7_9_8_6_8_7_6_7_6_6_7_6_6_7_6_8_7_10_8_9_9_9_8_6_9_9_6_8_17_6_9_7_6_6_7_10_7_7_7_7_6_6_8_7_8_6_7_10_6_6_6_6_6_17_6_8_8_8_6_7_8_6_6_6_6_8_6_9_7_6_8_6_6_6_6_7_9_9_7_7_9_8_6_9_8_17_6_6_7_7_8_6_6_6_6_6_8_9_7_7_7_6_9_8_6_6_8_8_8_6_6_7_6_17_7_8_6_9_8_8_8_7_6_6_6_6_7_6_9_7_8_9_10_10_7_6_17_8_8_7_6_8</t>
-  </si>
-  <si>
-    <t>7_8_6_7_7_10_9_8_7_6_6_9_10_6_8_6_7_10_9_8_6_8_6_8_6_8_10_9_8_9_9_9_9_6_8_9_9_9_9_8_6_7_9_6_6_7_6_6_6_6_6_6_8_7_10_8_10_10_8_8_7_7_8_8_8_7_8_6_6_7_6_6_8_8_6_6_7_8_7_6_7_6_6_17_6_7_7_8_9_6_8_8_8_7_10_6_7_8_6_7_7_6_6_6_6_7_9_6_8_6_6_17_8_8_7_17_7_9_17_7_10_10_8_7_6_8_8_8_6_6_6_8_9_17_8_7_9_6_8_6_7_9_9_7_7_8_6_6_6_6_6_6_6_6_6_6_10_7_8_6_7_7_6_7_6_6_10_7_9_9_7_10_10_8_7_6_7_7_6_9_7_6_10_10_6_8_9_7_8_9_9_6_6_6_8_9_6_7_6_7_17_8_8_6_6_7_9_9_7_6_6_9_6_6_6_6_7_7_6_7_9_6_7_6_10_6_6_6_10_10_8_7_8_6_8_8_6_7_7_7_7_6_6_6_8_9_6_7_7_17_7_8_8_9_17_7_8_6_10_8_9_8_7_7_6_6_9_10_10_6_6_6_7_8_7_7_7_8_6_6_6_6_8_8_6_6_6_7_7_7_7_6_6_7_7_7_7_7_6_8_9_8_7_9_6_6_7_10_6_8_8_8_6_7_6_6_6_6_6_6_6_8_9_6_6_6_8_9_6_7_6_6_6_6_6_6_8_7_7_7_7_7_10_7_7_7_9_6_6_6_6_6_8_8_8_8_7_7_17_7_9_8_8_7_6_7_9_6_7_9_7_17_7_7_6_8_6_8_17_8_6_9_10_8_6_7_9_9_10_17_9_9_6_6_6_6_8_9_9_6_8_9_6_6_7_17_6_8_6_6_7_8_9_8_8_6_6_7_6_6_7_6_6_7_6_7_9_7_6_6_9_8_9_9_6_6_7_8_8_6_9_7_6_6_6_6_6_6_6_6_7_7_6_6_7_9_8_8_8_6_6_8_9_9_9_7_9_9_7_8_9_7_7_7_8_7_9_8_8_7_6_7_7_8_8_8_7_8_6_6_17_10_6_8_9_6_6_7_17_7</t>
-  </si>
-  <si>
-    <t>9_8_8_6_6_6_17_8_6_7_6_9_8_6_6_10_7_6_9_8_8_9_7_8_10_10_6_6_6_7_8_8_10_6_7_7_6_17_7_7_8_6_7_6_7_7_8_8_9_6_7_6_8_8_8_8_8_6_6_8_7_6_8_6_10_6_6_8_6_8_10_6_9_7_9_7_6_6_7_7_8_7_7_7_6_6_6_6_6_6_8_10_7_7_7_8_6_6_7_8_6_6_17_6_6_10_7_7_8_8_8_9_6_10_6_8_6_8_8_8_6_7_8_6_7_9_6_6_7_8_8_8_7_6_6_6_6_7_7_7_6_17_10_6_6_9_9_6_8_6_7_7_6_17_6_7_7_7_6_6_9_9_17_6_8_8_8_6_10_8_8_9_17_9_6_7_7_6_6_6_6_9_6_9_9_7_10_6_8_6_6_9_9_9_6_9_6_6_6_7_7_8_6_9_6_6_7_7_9_8_7_6_9_6_6_8_6_7_6_7_6_8_7_6_7_9_7_8_9_9_8_8_6_7_8_8_10_7_7_6_8_8_6_10_8_7_8_7_6_6_7_6_7_7_8_6_6_6_7_6_8_6_7_7_7_8_6_7_8_9_8_9_9_7_6_8_8_7_8_6_9_6_6_8_9_9_8_7_7_10_6_9_8_8_8_7_9_6_6_8_8_8_7_6_7_7_9_8_7_6_6_6_8_8_7_7_6_9_10_7_10_10_10_7_6_6_6_7_7_7_7_7_6_8_7_8_17_6_6_6_8_7_10_6_7_17_7_6_8_7_7_6_7_9_7_6_8_6_6_6_6_8_7_7_9_8_9_9_7_8_10_6_8_9_7_7_7_7_7_7_6_7_9_6_7_7_6_9_7_6_6_6_9_10_8_8_7_10_6_8_7_7_7_6_7_9_6_8_8_8_9_8_6_6_6_8_8_8_9_7_6_8_9_10_6_7_10_8_8_6_8_7_6_9_6_7_7_7_9_6_7_8_7_8_9_10_7_6_8_9_7_8_6_7_9_8_8_8_6_6_6_7_6_6_9_6_7_6_6_6_6_9_8_8_8_8_6_17_17_8_6_10_6_9_7_9_9_6_9_6_8_7_6_6_8_6_8_8_9_6</t>
+    <t>6_7_6_10_7_7_9_6_7_6_6_6_6_7_7_7_7_7_8_6_7_8_6_9_6_8_7_6_8_6_6_10_7_6_7_9_9_10_9_8_9_8_6_8_8_6_9_6_10_10_6_6_7_6_6_8_8_8_9_6_6_6_6_8_6_6_9_8_7_7_6_6_6_8_7_7_6_7_7_7_10_10_7_8_6_6_9_9_6_9_9_9_6_8_6_6_6_6_6_7_7_6_7_7_7_6_9_8_7_6_6_8_8_7_10_6_10_8_8_9_8_7_6_6_6_7_7_6_6_9_7_8_9_9_6_8_7_7_9_7_6_6_10_9_10_8_7_7_8_7_6_6_9_9_6_8_9_9_6_8_6_6_6_9_6_7_9_7_6_6_6_10_6_6_7_7_6_9_8_7_7_6_6_9_9_6_6_10_6_7_9_6_6_7_7_7_6_6_9_8_8_8_8_9_8_6_7_8_6_9_10_8_8_8_8_8_8_7_8_9_6_6_6_7_7_7_7_7_9_6_8_6_8_9_7_6_6_7_7_6_8_7_6_7_7_6_6_8_8_6_9_7_8_6_7_7_6_10_6_6_6_8_6_9_6_10_7_9_6_8_8_8_6_9_9_6_7_7_8_6_6_10_6_6_8_7_7_6_6_6_8_8_6_6_6_6_6_8_7_6_6_6_6_7_7_6_10_10_8_7_6_6_9_7_7_8_7_8_9_7_8_6_6_6_6_6_8_7_7_9_9_6_7_7_8_8_7_7_6_7_7_6_7_7_7_10_9_9_7_7_7_10_8_10_6_6_10_6_9_10_6_7_10_7_8_8_8_8_8_8_6_6_6_6_8_6_6_6_7_7_7_6_6_9_9_6_6_6_9_6_9_6_6_7_7_9_6_7_8_6_9_7_10_10_10_7_7_6_10_6_9_7_6_7_7_6_6_9_6_8_10_7_7_10_6_6_6_6_7_9_9_9_9_9_9_6_9_7_6_6_6_9_6_7_6_7_9_8_7_9_8_6_7_6_9_7_6_8_8_7_6_6_8_7_6_6_6_6_7_8_9_10_6_6_10_8_10_9_8_7_10_6_6_6_6_8_9_9_9_9_9_9_9_6_6_6_9_7_6_6</t>
+  </si>
+  <si>
+    <t>6_6_9_7_9_8_8_7_10_8_8_9_9_7_7_10_8_6_9_6_6_7_9_6_8_7_6_7_10_6_8_9_6_7_7_6_6_7_7_8_9_6_6_9_6_6_7_8_7_7_7_9_7_6_6_6_7_8_6_7_8_7_7_9_6_6_6_7_6_9_7_7_8_6_6_6_6_6_7_7_6_6_8_6_7_9_7_6_8_10_6_6_9_10_7_8_9_7_9_10_8_7_6_6_9_9_6_6_6_8_8_6_7_6_6_6_6_6_8_9_9_9_6_6_6_8_6_6_9_8_8_8_8_8_7_7_6_10_8_9_6_8_7_6_6_6_6_8_7_9_7_6_6_9_10_7_6_7_7_7_9_6_6_6_6_7_8_9_8_8_7_10_10_10_7_6_10_10_9_6_6_8_6_7_7_6_8_7_6_9_6_6_6_9_6_8_7_8_6_6_6_9_9_8_7_7_7_7_6_8_7_9_7_10_6_7_7_7_6_8_7_7_7_6_6_6_7_7_8_8_10_6_9_9_9_7_7_7_8_6_8_6_8_8_8_8_6_7_7_10_10_6_6_9_6_9_6_6_8_7_8_8_6_7_7_7_7_8_8_8_6_6_6_8_7_7_6_6_10_10_6_9_10_6_6_6_8_8_8_8_6_6_6_6_6_8_7_6_8_8_8_9_8_9_6_7_8_6_7_7_7_7_6_8_8_10_6_7_6_6_6_7_6_7_7_8_8_7_10_7_7_7_6_6_7_7_6_7_9_7_6_6_6_10_10_10_7_7_7_7_6_7_7_8_8_6_7_6_8_8_6_7_7_6_8_7_6_6_7_8_8_8_6_7_7_6_8_7_6_8_7_6_7_6_8_7_6_6_6_6_7_8_6_8_6_6_8_8_9_7_8_7_8_7_6_6_6_7_7_9_7_7_6_7_7_6_6_7_7_8_6_6_6_9_9_10_8_6_6_9_7_7_7_9_6_6_10_10_7_8_9_6_10_6_6_9_8_8_7_6_6_7_7_7_7_10_6_6_6_8_10_7_6_8_9_10_6_6_6_9_7_6_7_6_6_6_6_6_6_8_8_8_6_7_7_9_10_6_6_6_7_9_7_6_6_6_8_6_9_9</t>
+  </si>
+  <si>
+    <t>7_6_6_10_8_8_6_6_9_9_9_10_7_7_9_7_7_7_10_9_9_6_8_7_7_10_6_10_6_6_6_7_7_6_9_6_6_6_7_9_6_7_7_7_6_6_6_6_7_6_8_6_6_8_9_8_8_7_7_7_9_9_6_6_6_6_6_7_6_6_7_8_6_8_6_8_6_8_8_10_7_7_7_6_7_7_7_6_9_6_10_6_6_8_8_9_8_8_10_6_6_8_9_6_6_7_6_6_7_6_10_7_9_6_7_7_7_8_8_6_6_6_6_8_8_6_8_8_6_8_9_8_6_9_6_6_6_7_10_10_6_7_7_6_9_6_9_9_6_7_7_6_8_8_6_10_10_7_8_6_8_6_6_7_10_8_8_6_8_6_6_6_7_6_9_6_8_8_8_8_9_8_8_9_7_6_8_6_6_7_7_6_8_8_8_6_8_6_6_6_6_6_7_6_7_6_8_6_9_6_6_8_6_6_6_7_7_7_9_8_7_6_6_7_7_10_10_10_6_7_6_7_7_8_6_6_6_8_7_8_7_6_7_7_7_6_6_8_7_7_9_7_6_7_6_6_8_6_7_6_9_6_8_7_7_7_6_6_7_6_8_6_9_9_6_10_7_7_6_6_6_6_6_10_10_8_8_6_9_9_9_6_7_8_8_6_7_6_6_7_8_9_10_10_6_8_8_6_9_8_8_10_10_10_10_8_8_8_10_7_6_6_6_7_8_6_6_7_7_7_10_7_6_6_8_6_6_8_8_7_8_6_6_6_7_7_8_6_6_6_6_9_9_6_9_6_6_7_7_9_8_6_8_7_6_7_6_6_7_6_6_7_6_8_7_10_8_9_9_9_8_6_9_9_6_8_6_6_9_7_6_6_7_10_7_7_7_7_6_6_8_7_8_6_7_10_6_6_6_6_6_6_6_8_8_8_6_7_8_6_6_6_6_8_6_9_7_6_8_6_6_6_6_7_9_9_7_7_9_8_6_9_8_6_6_6_7_7_8_6_6_6_6_6_8_9_7_7_7_6_9_8_6_6_8_8_8_6_6_7_6_6_7_8_6_9_8_8_8_7_6_6_6_6_7_6_9_7_8_9_10_10_7_6_6_8_8_7_6_8</t>
+  </si>
+  <si>
+    <t>7_8_6_7_7_10_9_8_7_6_6_9_10_6_8_6_7_10_9_8_6_8_6_8_6_8_10_9_8_9_9_9_9_6_8_9_9_9_9_8_6_7_9_6_6_7_6_6_6_6_6_6_8_7_10_8_10_10_8_8_7_7_8_8_8_7_8_6_6_7_6_6_8_8_6_6_7_8_7_6_7_6_6_6_6_7_7_8_9_6_8_8_8_7_10_6_7_8_6_7_7_6_6_6_6_7_9_6_8_6_6_6_8_8_7_6_7_9_6_7_10_10_8_7_6_8_8_8_6_6_6_8_9_6_8_7_9_6_8_6_7_9_9_7_7_8_6_6_6_6_6_6_6_6_6_6_10_7_8_6_7_7_6_7_6_6_10_7_9_9_7_10_10_8_7_6_7_7_6_9_7_6_10_10_6_8_9_7_8_9_9_6_6_6_8_9_6_7_6_7_6_8_8_6_6_7_9_9_7_6_6_9_6_6_6_6_7_7_6_7_9_6_7_6_10_6_6_6_10_10_8_7_8_6_8_8_6_7_7_7_7_6_6_6_8_9_6_7_7_6_7_8_8_9_6_7_8_6_10_8_9_8_7_7_6_6_9_10_10_6_6_6_7_8_7_7_7_8_6_6_6_6_8_8_6_6_6_7_7_7_7_6_6_7_7_7_7_7_6_8_9_8_7_9_6_6_7_10_6_8_8_8_6_7_6_6_6_6_6_6_6_8_9_6_6_6_8_9_6_7_6_6_6_6_6_6_8_7_7_7_7_7_10_7_7_7_9_6_6_6_6_6_8_8_8_8_7_7_6_7_9_8_8_7_6_7_9_6_7_9_7_6_7_7_6_8_6_8_6_8_6_9_10_8_6_7_9_9_10_6_9_9_6_6_6_6_8_9_9_6_8_9_6_6_7_6_6_8_6_6_7_8_9_8_8_6_6_7_6_6_7_6_6_7_6_7_9_7_6_6_9_8_9_9_6_6_7_8_8_6_9_7_6_6_6_6_6_6_6_6_7_7_6_6_7_9_8_8_8_6_6_8_9_9_9_7_9_9_7_8_9_7_7_7_8_7_9_8_8_7_6_7_7_8_8_8_7_8_6_6_6_10_6_8_9_6_6_7_6_7</t>
+  </si>
+  <si>
+    <t>9_8_8_6_6_6_6_8_6_7_6_9_8_6_6_10_7_6_9_8_8_9_7_8_10_10_6_6_6_7_8_8_10_6_7_7_6_6_7_7_8_6_7_6_7_7_8_8_9_6_7_6_8_8_8_8_8_6_6_8_7_6_8_6_10_6_6_8_6_8_10_6_9_7_9_7_6_6_7_7_8_7_7_7_6_6_6_6_6_6_8_10_7_7_7_8_6_6_7_8_6_6_6_6_6_10_7_7_8_8_8_9_6_10_6_8_6_8_8_8_6_7_8_6_7_9_6_6_7_8_8_8_7_6_6_6_6_7_7_7_6_6_10_6_6_9_9_6_8_6_7_7_6_6_6_7_7_7_6_6_9_9_6_6_8_8_8_6_10_8_8_9_6_9_6_7_7_6_6_6_6_9_6_9_9_7_10_6_8_6_6_9_9_9_6_9_6_6_6_7_7_8_6_9_6_6_7_7_9_8_7_6_9_6_6_8_6_7_6_7_6_8_7_6_7_9_7_8_9_9_8_8_6_7_8_8_10_7_7_6_8_8_6_10_8_7_8_7_6_6_7_6_7_7_8_6_6_6_7_6_8_6_7_7_7_8_6_7_8_9_8_9_9_7_6_8_8_7_8_6_9_6_6_8_9_9_8_7_7_10_6_9_8_8_8_7_9_6_6_8_8_8_7_6_7_7_9_8_7_6_6_6_8_8_7_7_6_9_10_7_10_10_10_7_6_6_6_7_7_7_7_7_6_8_7_8_6_6_6_6_8_7_10_6_7_6_7_6_8_7_7_6_7_9_7_6_8_6_6_6_6_8_7_7_9_8_9_9_7_8_10_6_8_9_7_7_7_7_7_7_6_7_9_6_7_7_6_9_7_6_6_6_9_10_8_8_7_10_6_8_7_7_7_6_7_9_6_8_8_8_9_8_6_6_6_8_8_8_9_7_6_8_9_10_6_7_10_8_8_6_8_7_6_9_6_7_7_7_9_6_7_8_7_8_9_10_7_6_8_9_7_8_6_7_9_8_8_8_6_6_6_7_6_6_9_6_7_6_6_6_6_9_8_8_8_8_6_6_6_8_6_10_6_9_7_9_9_6_9_6_8_7_6_6_8_6_8_8_9_6</t>
   </si>
   <si>
     <t>1_1_1_1_1_1</t>
   </si>
   <si>
-    <t>11_11_11_13_12_11_11_12_12_11_11_11_12_15_11_12_13_14_12_11_11_11_11_13_13_12_12_12_12_11_11_12_13_12_14_13_13_18_14_14_12_13_12_11_12_13_12_14_18_18_18_12_11_11_11_11_13_15_15_11_12_12_14_11_11_13_11_13_11_11_11_11_11_13_11_11_13_12_13_14_14_15_12_12_14_12_11_11_13_11_13_13_12_11_15_11_13_12_11_15_11_11_12_12_14_12_15_11_13_13_18_11_11_14_12_11_14_11_12_14_14_11_11_13_14_11_11_11_11_11_13_14_11_13_14_11_11_11_11_11_13_11_12_13_12_12_12_14_14_11_13_14_12_18_11_13_18_18_12_11_13_12_18_13_12_13_11_13_12_12_14_11_12_12_13_14_11_14_13_12_11_11_14_12_12_18_15_15_12_13_11_18_12_11_13_15_12_13_11_11_15_15_11_12_11_12_11_11_12_14_11_12_11_12_11_15_12_12_14_13_14_14_15_11_11_12_13_11_12_14_11_12_12_11_12_13_14_13_11_13_11_11_12_11_12_11_11_11_13_12_11_13_12_11_12_13_14_12_13_12_13_12_14_12_13_11_18_12_13_12_11_14_18_18_11_12_12_12_11_13_12_11_11_12_11_15_12_11_11_11_14_12_12_13_11_18_18_11_11_13_12_11_11_11_11_11_11_13_13_12_13_11_11_11_11_11_11_12_12_11_12_12_11_14_12_14_18_13_13_12_11_12_12_11_11_12_13_12_14_13_11_12_11_14_14_11_15_13_13_13_12_12_12_12_14_12_11_18_13_11_14_11_11_12_14_13_13_12_13_11_12_18_11_15_15_13_15_15_11_13_13_11_13_13_11_12_12_11_11_13_12_11_14_11_11_11_13_13_15_14_11_13_14_14_15_15_14_14_12_12_12_11_14_14_13_11_15_11_18_11_13_11_11_11_13_13_13_12_11_14_12_18_11_12_12_11_11_14_13_11_11_14_12_11_12_12_11_12_11_11_15_15_12_13_14_11_11_12_11_13_14_13_13_14_11_13_14_15_12_15_11_13_11_12_11_13_11_12_12_18_14_14_12_11_12_12_11_12_14_12_11_11_13_11_11_11_12_15_12_11</t>
+    <t>11_11_11_13_12_11_11_12_12_11_11_11_12_15_11_12_13_14_12_11_11_11_11_13_13_12_12_12_12_11_11_12_13_12_14_13_13_11_14_14_12_13_12_11_12_13_12_14_11_11_11_12_11_11_11_11_13_15_15_11_12_12_14_11_11_13_11_13_11_11_11_11_11_13_11_11_13_12_13_14_14_15_12_12_14_12_11_11_13_11_13_13_12_11_15_11_13_12_11_15_11_11_12_12_14_12_15_11_13_13_11_11_11_14_12_11_14_11_12_14_14_11_11_13_14_11_11_11_11_11_13_14_11_13_14_11_11_11_11_11_13_11_12_13_12_12_12_14_14_11_13_14_12_11_11_13_11_11_12_11_13_12_11_13_12_13_11_13_12_12_14_11_12_12_13_14_11_14_13_12_11_11_14_12_12_11_15_15_12_13_11_11_12_11_13_15_12_13_11_11_15_15_11_12_11_12_11_11_12_14_11_12_11_12_11_15_12_12_14_13_14_14_15_11_11_12_13_11_12_14_11_12_12_11_12_13_14_13_11_13_11_11_12_11_12_11_11_11_13_12_11_13_12_11_12_13_14_12_13_12_13_12_14_12_13_11_11_12_13_12_11_14_11_11_11_12_12_12_11_13_12_11_11_12_11_15_12_11_11_11_14_12_12_13_11_11_11_11_11_13_12_11_11_11_11_11_11_13_13_12_13_11_11_11_11_11_11_12_12_11_12_12_11_14_12_14_11_13_13_12_11_12_12_11_11_12_13_12_14_13_11_12_11_14_14_11_15_13_13_13_12_12_12_12_14_12_11_11_13_11_14_11_11_12_14_13_13_12_13_11_12_11_11_15_15_13_15_15_11_13_13_11_13_13_11_12_12_11_11_13_12_11_14_11_11_11_13_13_15_14_11_13_14_14_15_15_14_14_12_12_12_11_14_14_13_11_15_11_11_11_13_11_11_11_13_13_13_12_11_14_12_11_11_12_12_11_11_14_13_11_11_14_12_11_12_12_11_12_11_11_15_15_12_13_14_11_11_12_11_13_14_13_13_14_11_13_14_15_12_15_11_13_11_12_11_13_11_12_12_11_14_14_12_11_12_12_11_12_14_12_11_11_13_11_11_11_12_15_12_11</t>
   </si>
   <si>
     <t>2_2_2_2_2_2</t>
   </si>
   <si>
-    <t>11_12_13_11_11_13_11_18_12_12_11_11_13_11_12_11_11_13_11_18_11_11_11_12_18_11_18_13_13_13_11_11_13_15_12_12_11_11_13_15_15_12_13_11_11_14_11_11_11_11_11_11_12_11_12_13_14_12_11_13_13_18_11_13_13_13_11_12_12_15_11_11_11_11_13_13_13_12_11_14_12_12_18_18_14_11_13_15_11_11_13_13_11_13_15_12_12_11_11_13_13_14_13_12_12_11_11_12_12_12_12_13_14_15_15_12_12_12_15_15_11_11_13_11_11_12_12_12_14_13_12_13_15_12_12_13_13_13_12_12_12_11_11_14_11_11_14_15_12_11_18_11_13_12_11_12_12_13_11_13_11_12_13_11_12_14_12_12_13_11_13_13_14_12_11_13_11_11_14_12_13_12_14_13_13_12_12_11_11_15_13_13_13_12_11_11_12_11_11_18_11_13_14_12_14_15_12_14_11_11_13_13_12_12_13_12_14_14_11_12_13_14_14_11_13_11_13_13_13_18_12_11_11_14_12_11_14_11_12_11_11_12_13_15_15_14_14_12_12_18_12_11_11_11_14_14_11_13_12_12_12_14_11_14_12_12_13_11_12_11_11_11_11_11_11_11_12_11_11_11_13_13_18_13_13_13_13_14_14_14_13_12_12_12_12_15_12_13_11_13_13_13_13_12_13_12_11_11_14_14_14_13_15_12_13_12_13_11_13_14_11_11_11_15_11_14_14_11_13_13_13_12_12_15_14_13_13_11_13_11_11_14_12_13_13_13_18_13_15_12_11_11_11_12_12_15_11_14_13_11_14_14_14_13_14_14_13_11_11_15_11_12_12_12_11_11_12_15_13_11_14_18_11_13_12_13_11_11_11_13_11_18_11_12_12_11_13_18_11_11_12_12_11_12_15_14_11_12_14_15_11_11_13_13_12_15_14_13_11_11_11_13_13_13_11_13_18_18_11_12_11_11_12_11_18_13_11_12_11_12_14_12_11_18_14_13_12_12_11_12_15_15_11_11_12_11_11_11_15_11_11_12_11_11_13_12_12_13_11_18_11_13_11_11_14_11_14_12_14_13_12_12_12_13_11_11_11_11_12_13_11_11_11_14_12_12_13_12_13_13</t>
+    <t>11_12_13_11_11_13_11_11_12_12_11_11_13_11_12_11_11_13_11_11_11_11_11_12_11_11_11_13_13_13_11_11_13_15_12_12_11_11_13_15_15_12_13_11_11_14_11_11_11_11_11_11_12_11_12_13_14_12_11_13_13_11_11_13_13_13_11_12_12_15_11_11_11_11_13_13_13_12_11_14_12_12_11_11_14_11_13_15_11_11_13_13_11_13_15_12_12_11_11_13_13_14_13_12_12_11_11_12_12_12_12_13_14_15_15_12_12_12_15_15_11_11_13_11_11_12_12_12_14_13_12_13_15_12_12_13_13_13_12_12_12_11_11_14_11_11_14_15_12_11_11_11_13_12_11_12_12_13_11_13_11_12_13_11_12_14_12_12_13_11_13_13_14_12_11_13_11_11_14_12_13_12_14_13_13_12_12_11_11_15_13_13_13_12_11_11_12_11_11_11_11_13_14_12_14_15_12_14_11_11_13_13_12_12_13_12_14_14_11_12_13_14_14_11_13_11_13_13_13_11_12_11_11_14_12_11_14_11_12_11_11_12_13_15_15_14_14_12_12_11_12_11_11_11_14_14_11_13_12_12_12_14_11_14_12_12_13_11_12_11_11_11_11_11_11_11_12_11_11_11_13_13_11_13_13_13_13_14_14_14_13_12_12_12_12_15_12_13_11_13_13_13_13_12_13_12_11_11_14_14_14_13_15_12_13_12_13_11_13_14_11_11_11_15_11_14_14_11_13_13_13_12_12_15_14_13_13_11_13_11_11_14_12_13_13_13_11_13_15_12_11_11_11_12_12_15_11_14_13_11_14_14_14_13_14_14_13_11_11_15_11_12_12_12_11_11_12_15_13_11_14_11_11_13_12_13_11_11_11_13_11_11_11_12_12_11_13_11_11_11_12_12_11_12_15_14_11_12_14_15_11_11_13_13_12_15_14_13_11_11_11_13_13_13_11_13_11_11_11_12_11_11_12_11_11_13_11_12_11_12_14_12_11_11_14_13_12_12_11_12_15_15_11_11_12_11_11_11_15_11_11_12_11_11_13_12_12_13_11_11_11_13_11_11_14_11_14_12_14_13_12_12_12_13_11_11_11_11_12_13_11_11_11_14_12_12_13_12_13_13</t>
   </si>
   <si>
     <t>3_3_3_3_3_3</t>
   </si>
   <si>
-    <t>15_11_11_14_13_13_13_12_12_13_12_12_14_13_12_11_13_11_13_14_12_15_15_12_14_12_12_13_12_11_11_13_12_13_13_13_18_12_14_12_13_11_11_11_12_12_11_13_11_11_11_13_11_15_11_12_14_11_12_12_13_14_12_12_11_13_12_13_11_12_15_11_12_13_13_14_12_13_13_12_14_12_15_11_12_12_14_12_13_11_13_11_11_11_12_14_11_11_15_12_11_11_11_14_13_12_13_14_11_13_14_14_11_12_15_12_12_11_13_11_15_13_12_12_11_11_13_11_18_11_11_12_13_15_15_12_12_13_18_12_12_11_11_11_15_11_11_11_11_11_14_11_12_12_11_11_11_11_11_11_15_15_11_11_12_11_12_11_13_12_11_13_13_11_11_11_15_11_14_13_13_15_15_11_15_12_12_15_11_13_14_13_13_14_11_13_13_12_15_13_13_13_14_13_12_13_11_15_13_11_11_12_14_13_13_11_14_12_12_13_12_11_11_18_11_12_12_15_12_13_11_11_13_12_14_15_13_13_13_14_12_11_13_12_11_11_12_14_12_11_12_12_14_14_11_12_12_11_11_13_11_13_13_11_13_13_12_12_12_12_11_13_13_13_14_14_11_14_11_11_15_15_15_15_11_12_15_13_11_18_11_12_12_11_13_11_11_12_11_13_12_12_11_14_11_11_13_11_15_11_14_13_11_13_15_11_11_14_14_11_12_12_11_12_11_11_14_12_14_14_12_11_12_11_11_13_12_12_11_12_12_14_13_11_14_15_13_14_11_11_14_12_13_12_13_11_11_13_13_12_14_11_18_12_18_11_12_14_14_12_11_11_11_12_13_13_13_14_14_11_11_13_11_13_13_13_14_11_11_13_11_11_13_12_12_12_15_13_14_12_12_13_13_14_14_14_11_12_15_13_11_11_11_13_11_13_12_12_12_12_14_11_18_18_11_13_15_11_12_12_12_13_11_13_12_12_11_12_13_11_11_14_14_14_13_13_12_13_12_14_13_14_11_14_13_11_15_13_12_13_13_11_11_14_15_13_11_11_11_12_12_13_12_12_12_12_14_13_15_15_12_11_11_14_14_11_11_15_13_12_12_14_11_12_11_11_11_14_12_11</t>
+    <t>15_11_11_14_13_13_13_12_12_13_12_12_14_13_12_11_13_11_13_14_12_15_15_12_14_12_12_13_12_11_11_13_12_13_13_13_11_12_14_12_13_11_11_11_12_12_11_13_11_11_11_13_11_15_11_12_14_11_12_12_13_14_12_12_11_13_12_13_11_12_15_11_12_13_13_14_12_13_13_12_14_12_15_11_12_12_14_12_13_11_13_11_11_11_12_14_11_11_15_12_11_11_11_14_13_12_13_14_11_13_14_14_11_12_15_12_12_11_13_11_15_13_12_12_11_11_13_11_11_11_11_12_13_15_15_12_12_13_11_12_12_11_11_11_15_11_11_11_11_11_14_11_12_12_11_11_11_11_11_11_15_15_11_11_12_11_12_11_13_12_11_13_13_11_11_11_15_11_14_13_13_15_15_11_15_12_12_15_11_13_14_13_13_14_11_13_13_12_15_13_13_13_14_13_12_13_11_15_13_11_11_12_14_13_13_11_14_12_12_13_12_11_11_11_11_12_12_15_12_13_11_11_13_12_14_15_13_13_13_14_12_11_13_12_11_11_12_14_12_11_12_12_14_14_11_12_12_11_11_13_11_13_13_11_13_13_12_12_12_12_11_13_13_13_14_14_11_14_11_11_15_15_15_15_11_12_15_13_11_11_11_12_12_11_13_11_11_12_11_13_12_12_11_14_11_11_13_11_15_11_14_13_11_13_15_11_11_14_14_11_12_12_11_12_11_11_14_12_14_14_12_11_12_11_11_13_12_12_11_12_12_14_13_11_14_15_13_14_11_11_14_12_13_12_13_11_11_13_13_12_14_11_11_12_11_11_12_14_14_12_11_11_11_12_13_13_13_14_14_11_11_13_11_13_13_13_14_11_11_13_11_11_13_12_12_12_15_13_14_12_12_13_13_14_14_14_11_12_15_13_11_11_11_13_11_13_12_12_12_12_14_11_11_11_11_13_15_11_12_12_12_13_11_13_12_12_11_12_13_11_11_14_14_14_13_13_12_13_12_14_13_14_11_14_13_11_15_13_12_13_13_11_11_14_15_13_11_11_11_12_12_13_12_12_12_12_14_13_15_15_12_11_11_14_14_11_11_15_13_12_12_14_11_12_11_11_11_14_12_11</t>
   </si>
   <si>
     <t>4_4_4_4_4_4</t>
   </si>
   <si>
-    <t>13_13_15_12_11_12_12_12_12_11_11_11_12_11_13_11_12_14_11_12_12_13_15_15_14_11_11_13_14_12_12_11_12_13_11_11_14_14_12_13_13_14_14_14_15_14_12_11_15_12_12_14_12_12_12_11_18_11_14_13_14_12_11_11_12_12_14_12_11_12_13_14_15_12_11_11_13_15_14_15_11_13_12_11_12_11_11_11_12_14_11_11_13_12_12_12_12_13_14_14_14_12_13_11_11_11_15_14_13_14_11_12_12_12_14_13_13_11_13_15_15_15_11_11_14_15_11_15_11_11_12_14_13_13_14_12_11_11_11_11_12_11_11_18_12_14_13_13_15_11_11_11_11_14_13_11_11_18_18_13_11_13_12_13_13_12_11_12_13_11_11_14_11_13_13_12_14_14_11_12_11_12_11_11_13_13_15_11_11_14_14_15_12_12_18_12_11_13_13_13_13_11_14_14_11_18_14_11_11_13_12_12_11_13_12_13_11_13_13_12_14_11_14_13_13_12_12_12_12_14_18_12_13_13_12_12_12_14_13_13_11_11_14_14_11_11_11_12_12_13_14_12_12_11_11_11_12_11_11_14_12_11_14_12_14_11_11_12_12_12_11_12_11_12_11_11_14_12_11_13_11_13_11_12_12_12_12_12_14_12_11_15_11_14_13_11_12_12_11_11_11_11_11_11_12_11_11_15_11_12_11_11_11_13_13_11_11_12_14_12_11_11_11_13_14_14_11_12_12_11_11_11_13_11_14_12_11_12_11_18_18_13_12_12_11_11_11_14_13_11_11_14_11_15_15_15_12_11_11_12_13_11_11_11_14_11_13_12_11_14_18_12_12_12_11_14_12_12_12_15_12_14_18_13_11_12_12_12_15_14_14_14_13_12_12_15_15_14_14_12_12_18_13_11_11_11_18_11_12_11_11_13_11_18_15_14_14_12_11_11_13_11_13_18_11_13_11_11_11_11_13_13_13_11_11_11_14_12_12_12_18_12_11_11_13_12_11_12_12_14_11_14_14_14_12_18_11_12_11_14_11_11_11_11_15_12_12_11_14_13_11_11_11_11_11_14_14_13_11_13_11_12_12_11_11_12_13_14_12_13_12_13_14_14_13_13_11_13_15_12</t>
+    <t>13_13_15_12_11_12_12_12_12_11_11_11_12_11_13_11_12_14_11_12_12_13_15_15_14_11_11_13_14_12_12_11_12_13_11_11_14_14_12_13_13_14_14_14_15_14_12_11_15_12_12_14_12_12_12_11_11_11_14_13_14_12_11_11_12_12_14_12_11_12_13_14_15_12_11_11_13_15_14_15_11_13_12_11_12_11_11_11_12_14_11_11_13_12_12_12_12_13_14_14_14_12_13_11_11_11_15_14_13_14_11_12_12_12_14_13_13_11_13_15_15_15_11_11_14_15_11_15_11_11_12_14_13_13_14_12_11_11_11_11_12_11_11_11_12_14_13_13_15_11_11_11_11_14_13_11_11_11_11_13_11_13_12_13_13_12_11_12_13_11_11_14_11_13_13_12_14_14_11_12_11_12_11_11_13_13_15_11_11_14_14_15_12_12_11_12_11_13_13_13_13_11_14_14_11_11_14_11_11_13_12_12_11_13_12_13_11_13_13_12_14_11_14_13_13_12_12_12_12_14_11_12_13_13_12_12_12_14_13_13_11_11_14_14_11_11_11_12_12_13_14_12_12_11_11_11_12_11_11_14_12_11_14_12_14_11_11_12_12_12_11_12_11_12_11_11_14_12_11_13_11_13_11_12_12_12_12_12_14_12_11_15_11_14_13_11_12_12_11_11_11_11_11_11_12_11_11_15_11_12_11_11_11_13_13_11_11_12_14_12_11_11_11_13_14_14_11_12_12_11_11_11_13_11_14_12_11_12_11_11_11_13_12_12_11_11_11_14_13_11_11_14_11_15_15_15_12_11_11_12_13_11_11_11_14_11_13_12_11_14_11_12_12_12_11_14_12_12_12_15_12_14_11_13_11_12_12_12_15_14_14_14_13_12_12_15_15_14_14_12_12_11_13_11_11_11_11_11_12_11_11_13_11_11_15_14_14_12_11_11_13_11_13_11_11_13_11_11_11_11_13_13_13_11_11_11_14_12_12_12_11_12_11_11_13_12_11_12_12_14_11_14_14_14_12_11_11_12_11_14_11_11_11_11_15_12_12_11_14_13_11_11_11_11_11_14_14_13_11_13_11_12_12_11_11_12_13_14_12_13_12_13_14_14_13_13_11_13_15_12</t>
   </si>
   <si>
     <t>5_5_5_5_5_5</t>
   </si>
   <si>
-    <t>12_11_14_11_11_11_12_11_12_12_12_12_11_11_12_12_13_12_12_13_13_15_15_12_12_12_15_11_13_11_18_11_13_15_15_11_12_11_11_12_11_13_11_12_11_14_11_11_18_15_11_11_13_12_18_18_18_11_13_11_11_11_15_13_13_13_11_11_12_11_14_18_11_13_12_11_13_12_11_11_12_11_13_14_11_12_14_13_13_11_13_13_12_11_11_11_14_11_12_13_15_12_13_11_11_11_15_13_11_12_12_14_13_14_12_12_14_13_15_15_15_11_11_11_11_12_12_11_13_12_12_13_14_11_13_11_13_13_11_12_13_11_15_13_15_12_18_14_11_11_12_11_11_11_11_14_13_11_13_14_14_15_11_11_11_18_13_11_11_11_13_15_12_11_13_13_11_13_13_11_11_11_11_11_13_15_13_11_12_11_12_12_11_13_11_11_13_13_11_13_13_14_12_14_12_12_11_18_11_12_11_11_11_13_12_12_12_11_11_12_11_12_12_11_13_13_12_13_14_13_11_12_13_14_11_11_11_13_14_13_13_14_14_12_12_12_13_13_14_14_14_11_13_18_13_14_12_12_11_18_15_13_15_13_13_12_12_14_12_14_14_13_14_11_13_11_15_11_11_13_12_11_11_13_12_13_12_14_14_13_11_13_11_11_12_11_12_14_14_12_12_11_12_11_12_13_12_11_12_12_13_13_11_12_13_15_13_18_12_12_14_12_12_18_14_18_11_14_11_12_12_12_12_12_12_11_13_13_13_11_12_12_12_11_12_13_13_13_11_11_11_11_13_12_12_12_15_11_11_11_11_18_14_14_14_12_11_14_18_12_13_11_11_11_18_12_11_11_11_11_11_12_12_13_15_13_14_11_12_12_11_13_11_11_15_13_12_14_12_12_11_15_13_11_12_11_11_18_14_15_15_13_11_11_11_12_12_11_13_13_14_13_13_11_12_13_11_11_13_13_15_15_11_11_11_11_11_12_12_12_13_11_11_11_13_12_12_12_12_13_11_15_13_13_13_11_12_12_11_11_18_11_11_12_12_13_11_13_11_13_13_12_14_14_13_13_12_18_14_14_14_12_14_14_11_13_13_11_11_11_13_13_12_11_11_11_11_11_13_12</t>
-  </si>
-  <si>
-    <t>11_12_11_12_15_11_12_11_13_11_11_12_12_11_11_15_14_12_15_12_12_15_11_12_11_11_12_18_18_11_11_11_14_14_14_12_11_11_12_13_13_11_14_11_12_12_11_12_12_15_14_12_11_11_18_14_12_12_12_14_13_12_11_18_14_11_11_15_12_13_15_15_11_11_12_11_11_12_13_11_11_11_12_11_13_14_12_18_18_11_14_13_11_13_13_12_13_13_12_12_12_12_12_14_14_14_11_13_13_11_11_11_11_12_13_14_13_11_13_13_12_13_11_11_15_12_15_15_13_14_12_11_18_12_12_11_13_11_11_11_14_13_13_13_13_12_12_12_12_11_11_11_11_11_11_14_12_12_11_12_11_11_11_12_11_13_11_12_14_12_15_15_11_12_15_13_12_13_18_12_15_15_13_12_14_11_12_11_12_11_11_11_14_11_13_13_13_13_13_13_15_11_11_13_18_11_11_11_11_13_12_14_12_12_12_11_12_11_11_11_14_13_11_13_12_11_11_15_13_13_13_11_13_11_12_14_12_11_14_12_12_12_12_14_12_18_13_11_11_11_13_12_12_12_12_13_13_12_12_12_11_12_11_13_15_14_11_11_13_13_11_12_14_11_11_11_11_11_14_18_11_11_12_13_11_13_14_11_11_13_14_13_12_13_12_12_11_12_11_11_13_12_12_15_15_12_15_14_11_11_15_14_11_13_13_13_11_12_12_12_11_12_11_12_12_13_13_11_11_12_12_15_13_12_14_11_11_12_18_11_13_11_13_12_15_14_12_14_12_15_11_12_12_12_11_14_13_11_11_11_11_11_11_12_13_13_15_13_11_13_11_14_13_13_13_11_13_12_13_13_13_18_11_13_14_12_12_12_11_12_15_12_14_11_14_14_14_14_14_14_11_11_14_12_14_14_12_12_12_11_12_11_12_12_12_12_13_13_12_12_15_11_11_14_11_14_12_14_14_11_12_12_11_11_13_12_13_11_11_12_13_13_12_12_11_13_13_13_11_11_12_12_12_14_18_13_13_12_13_15_12_13_12_15_14_13_11_11_15_14_14_12_11_11_13_15_11_13_14_15_13_13_14_14_13_13_13_11_11_12_18_12_13_13_12_12_11_14_11_18</t>
+    <t>12_11_14_11_11_11_12_11_12_12_12_12_11_11_12_12_13_12_12_13_13_15_15_12_12_12_15_11_13_11_11_11_13_15_15_11_12_11_11_12_11_13_11_12_11_14_11_11_11_15_11_11_13_12_11_11_11_11_13_11_11_11_15_13_13_13_11_11_12_11_14_11_11_13_12_11_13_12_11_11_12_11_13_14_11_12_14_13_13_11_13_13_12_11_11_11_14_11_12_13_15_12_13_11_11_11_15_13_11_12_12_14_13_14_12_12_14_13_15_15_15_11_11_11_11_12_12_11_13_12_12_13_14_11_13_11_13_13_11_12_13_11_15_13_15_12_11_14_11_11_12_11_11_11_11_14_13_11_13_14_14_15_11_11_11_11_13_11_11_11_13_15_12_11_13_13_11_13_13_11_11_11_11_11_13_15_13_11_12_11_12_12_11_13_11_11_13_13_11_13_13_14_12_14_12_12_11_11_11_12_11_11_11_13_12_12_12_11_11_12_11_12_12_11_13_13_12_13_14_13_11_12_13_14_11_11_11_13_14_13_13_14_14_12_12_12_13_13_14_14_14_11_13_11_13_14_12_12_11_11_15_13_15_13_13_12_12_14_12_14_14_13_14_11_13_11_15_11_11_13_12_11_11_13_12_13_12_14_14_13_11_13_11_11_12_11_12_14_14_12_12_11_12_11_12_13_12_11_12_12_13_13_11_12_13_15_13_11_12_12_14_12_12_11_14_11_11_14_11_12_12_12_12_12_12_11_13_13_13_11_12_12_12_11_12_13_13_13_11_11_11_11_13_12_12_12_15_11_11_11_11_11_14_14_14_12_11_14_11_12_13_11_11_11_11_12_11_11_11_11_11_12_12_13_15_13_14_11_12_12_11_13_11_11_15_13_12_14_12_12_11_15_13_11_12_11_11_11_14_15_15_13_11_11_11_12_12_11_13_13_14_13_13_11_12_13_11_11_13_13_15_15_11_11_11_11_11_12_12_12_13_11_11_11_13_12_12_12_12_13_11_15_13_13_13_11_12_12_11_11_11_11_11_12_12_13_11_13_11_13_13_12_14_14_13_13_12_11_14_14_14_12_14_14_11_13_13_11_11_11_13_13_12_11_11_11_11_11_13_12</t>
+  </si>
+  <si>
+    <t>11_12_11_12_15_11_12_11_13_11_11_12_12_11_11_15_14_12_15_12_12_15_11_12_11_11_12_11_11_11_11_11_14_14_14_12_11_11_12_13_13_11_14_11_12_12_11_12_12_15_14_12_11_11_11_14_12_12_12_14_13_12_11_11_14_11_11_15_12_13_15_15_11_11_12_11_11_12_13_11_11_11_12_11_13_14_12_11_11_11_14_13_11_13_13_12_13_13_12_12_12_12_12_14_14_14_11_13_13_11_11_11_11_12_13_14_13_11_13_13_12_13_11_11_15_12_15_15_13_14_12_11_11_12_12_11_13_11_11_11_14_13_13_13_13_12_12_12_12_11_11_11_11_11_11_14_12_12_11_12_11_11_11_12_11_13_11_12_14_12_15_15_11_12_15_13_12_13_11_12_15_15_13_12_14_11_12_11_12_11_11_11_14_11_13_13_13_13_13_13_15_11_11_13_11_11_11_11_11_13_12_14_12_12_12_11_12_11_11_11_14_13_11_13_12_11_11_15_13_13_13_11_13_11_12_14_12_11_14_12_12_12_12_14_12_11_13_11_11_11_13_12_12_12_12_13_13_12_12_12_11_12_11_13_15_14_11_11_13_13_11_12_14_11_11_11_11_11_14_11_11_11_12_13_11_13_14_11_11_13_14_13_12_13_12_12_11_12_11_11_13_12_12_15_15_12_15_14_11_11_15_14_11_13_13_13_11_12_12_12_11_12_11_12_12_13_13_11_11_12_12_15_13_12_14_11_11_12_11_11_13_11_13_12_15_14_12_14_12_15_11_12_12_12_11_14_13_11_11_11_11_11_11_12_13_13_15_13_11_13_11_14_13_13_13_11_13_12_13_13_13_11_11_13_14_12_12_12_11_12_15_12_14_11_14_14_14_14_14_14_11_11_14_12_14_14_12_12_12_11_12_11_12_12_12_12_13_13_12_12_15_11_11_14_11_14_12_14_14_11_12_12_11_11_13_12_13_11_11_12_13_13_12_12_11_13_13_13_11_11_12_12_12_14_11_13_13_12_13_15_12_13_12_15_14_13_11_11_15_14_14_12_11_11_13_15_11_13_14_15_13_13_14_14_13_13_13_11_11_12_11_12_13_13_12_12_11_14_11_11</t>
   </si>
   <si>
     <t>6_5_9_2_5_7_7_7_1_1_5_4_9_3_5_7_6_6_8_8_8_6_6_6_1_4_2_2_1_3_3_5_1_6_1_3_2_5_7_6_5_8_1_1_1_4_4_4_2_1_1_1_1_6_5_1_2_2_2_2_6_2_2_2_7_5_7_1_1_2_4_4_3_1_1_3_9_3_7_7_5_3_2_5_7_1_1_3_3_3_5_1_4_3_5_1_2_1_9_7_7_1_3_2_2_5_4_3_9_8_10_4_6_2_2_4_4_4_3_4_2_3_1_1_1_2_5_3_1_8_3_10_5_3_4_5_1_3_9_8_4_1_5_4_2_2_2_2_1_2_7_5_7_7_2_5_5_1_2_6_2_2_2_2_4_10_10_5_4_6_6_10_3_8_8_3_6_5_4_1_5_4_4_7_1_6_8_4_5_5_6_1_8_7_8_6_6_2_3_3_10_6_6_2_4_6_3_3_6_3_4_6_6_1_3_4_1_7_3_4_2_5_2_2_8_3_3_7_5_3_4_4_4_9_9_1_6_7_3_7_2_3_3_2_4_4_4_4_2_7_1_6_3_3_3_3_9_3_6_3_1_9_6_5_6_3_3_2_4_3_1_8_5_5_5_5_7_9_7_9_7_8_7_7_8_3_4_2_2_5_4_4_4_2_2_5_5_8_5_4_1_10_1_5_2_5_1_1_1_2_5_1_8_5_3_1_4_1_1_9_4_2_1_1_9_1_1_7_5_1_3_6_4_4_4_7_5_3_1_2_4_2_3_7_6_3_4_7_3_3_2_3_1_1_1_1_1_1_1_1_6_1_6_6_1_2_2_3_2_6_9_2_1_4_4_2_1_6_2_7_8_4_9_4_1_2_2_6_1_1_9_2_4_4_4_7_5_5_8_3_3_6_2_7_1_9_5_7_2_6_2_2_8_3_8_1_6_7_2_1_9_3_5_3_5_2_4_4_8_7_10_2_2_1_1_4_3_4_6_5_8_2_5_7_4_8_5_2_1_1_7_7_7_3_7_2_5_4_4_4_7_4_4_9_3_2_6_6_6_3_7_6_5_3_6_4_3_8_5_1_9_8_7_7_2_8_8_8_6_3_6_5_5_3_4_2_2_2_8_2</t>
@@ -1167,10 +1167,64 @@
     <t>5_6_2_10_3_8_10_2_10_1_5_2_5_7_8_2_5_8_2_1_1_7_1_2_8_8_8_8_8_4_5_6_3_5_6_4_5_10_4_10_1_6_6_6_10_3_7_8_8_5_9_6_7_2_7_5_7_10_2_7_1_5_9_10_2_6_6_8_2_9_6_5_3_3_9_3_7_1_4_8_10_4_10_4_1_7_5_2_9_5_7_7_5_2_7_2_4_3_2_9_9_6_3_3_7_1_5_8_5_4_8_1_9_9_5_1_3_3_5_7_4_10_2_1_7_2_9_6_3_8_4_5_9_3_7_1_7_3_10_4_1_2_5_3_1_8_5_5_4_6_7_9_8_5_10_1_5_9_7_6_9_6_6_3_6_4_9_1_3_6_3_6_3_10_1_10_3_9_10_4_9_4_9_5_3_6_5_5_8_9_6_8_4_5_5_8_9_6_10_4_2_8_7_8_10_1_1_3_5_1_7_9_10_4_6_3_7_7_3_10_2_7_4_4_10_3_9_7_3_4_1_8_4_10_2_3_4_10_1_9_6_1_9_8_3_5_3_4_1_4_10_3_5_4_9_2_1_9_1_3_2_1_8_2_4_2_1_3_2_7_4_10_2_8_4_1_7_10_3_4_3_7_2_8_7_7_1_9_6_2_5_1_4_6_3_10_2_7_1_8_2_5_5_9_8_3_8_6_1_8_4_8_1_3_1_1_3_1_8_7_1_10_2_10_2_8_4_5_7_10_2_2_9_10_4_3_1_9_7_10_3_5_6_10_1_5_8_7_6_3_4_7_6_1_9_4_4_2_5_7_5_7_1_8_2_6_1_6_10_4_2_10_3_5_8_10_3_4_7_7_10_2_5_1_10_3_7_9_10_2_8_3_6_1_3_1_4_1_1_7_5_2_3_7_9_6_10_3_2_4_3_8_5_1_3_10_3_1_8_2_4_3_5_3_7_4_6_6_8_8_4_9_9_7_8_1_1_2_1_10_1_9_3_10_2_6_7_1_5_9_1_6_1_5_8_10_1_3_2_8_8_4_1_10_1_7_1_9_9_8_10_3_9_5_9_4_4_5_2_9_6_3_3_4_3_10_4_5_9_6_2_3_2_2_8_2_2_1_2_3</t>
   </si>
   <si>
-    <t>1_5_5_8_2_2_1_1_7_1_3_1_6_3_1_4_1_3_7_4_3_1_8_6_1_6_1_7_7_8_5_2_4_4_1_1_3_8_1_3_7_3_3_5_2_2_5_7_3_1_6_4_4_3_5_3_5_5_3_1_2_1_5_5_5_7_8_1_8_2_5_5_2_7_3_3_1_5_7_8_2_8_6_6_8_4_1_6_3_1_2_3_3_1_1_1_4_5_2_3_5_2_8_3_4_2_3_1_1_2_4_7_1_1_8_5_5_2_6_5_2_1_1_6_3_3_3_5_4_4_5_3_4_7_2_4_4_7_3_1_4_4_5_8_3_7_8_4_2_4_1_6_1_6_3_1_1_2_8_2_2_1_8_4_4_5_2_2_6_5_2_1_5_1_7_7_1_7_3_2_3_3_4_5_2_6_1_3_5_3_8_5_4_5_2_3_3_2_1_4_3_7_2_7_5_1_7_1_1_2_7_4_5_3_1_5_2_8_5_5_7_1_1_5_4_2_7_1_2_2_5_6_2_1_4_5_4_4_8_1_3_4_1_5_1_1_6_1_6_3_2_1_5_7_1_1_2_2_8_2_5_4_7_3_3_6_2_6_2_7_2_3_3_1_5_4_4_1_4_5_1_2_1_1_1_1_7_6_2_2_1_5_2_1_1_5_1_3_6_8_3_6_4_8_1_4_1_1_1_1_4_5_5_1_1_3_2_1_6_3_1_1_8_3_3_5_3_3_2_3_2_1_3_1_1_2_2_5_1_7_8_8_5_2_5_2_2_1_7_2_3_3_3_2_3_3_4_7_1_1_1_1_6_2_8_3_4_4_3_2_3_3_5_5_5_2_5_3_4_7_6_1_4_4_5_2_1_1_5_7_7_4_1_2_2_7_2_1_7_8_6_5_3_1_3_8_7_1_2_2_3_5_6_6_4_1_4_6_1_2_3_2_5_5_1_1_5_2_1_5_3_2_5_3_3_2_3_4_4_2_4_1_5_3_4_6_3_4_7_5_1_5_1_1_1_1_1_6_7_2_8_2_3_4_2_8_1_2_1_4_1_6_3_3_1_8_1_7_8_8_2_1_2_2_2_2_4_4_5_3_1_6_3_2_6_5_8_4_4_7</t>
-  </si>
-  <si>
-    <t>4_1_6_3_7_2_4_9_7_2_8_2_15_4_8_5_15_7_6_4_2_4_9_7_1_1_1_4_2_4_1_3_6_15_4_2_1_3_9_9_6_6_3_9_3_2_1_9_2_4_15_6_6_3_7_6_8_7_4_6_9_3_2_15_4_6_1_2_8_1_2_15_6_4_2_4_1_8_6_2_2_4_3_2_3_1_5_6_1_5_1_4_1_9_1_2_4_6_6_15_2_15_3_2_1_6_1_3_4_15_5_2_4_1_7_9_8_3_4_2_1_4_3_2_8_9_6_9_15_2_1_4_4_7_5_4_9_2_1_15_4_4_1_1_2_2_2_9_5_3_15_7_1_1_2_4_3_9_2_1_7_2_7_8_3_8_2_8_2_3_4_8_2_4_1_9_9_1_2_4_9_7_1_4_5_9_6_1_1_1_2_8_5_15_3_2_7_7_4_8_4_1_2_2_3_2_2_4_3_8_9_2_2_2_2_2_9_1_9_2_3_4_6_9_8_1_2_7_4_3_8_2_7_3_2_6_15_4_2_2_9_8_3_1_4_4_9_9_3_3_1_4_5_3_1_15_4_1_3_4_4_7_9_6_15_6_8_8_1_1_7_1_4_5_3_1_3_4_2_4_2_9_4_2_1_8_8_1_9_6_4_4_3_1_8_3_1_3_15_6_3_7_9_4_1_5_4_9_8_7_2_3_3_2_2_6_3_4_4_6_1_3_1_15_3_8_3_5_3_1_7_2_5_8_15_5_9_15_2_8_4_4_5_8_7_6_8_6_3_15_4_8_1_9_4_5_2_7_6_1_8_7_8_7_7_2_1_3_7_2_3_8_2_9_2_6_15_4_6_2_2_6_1_3_9_3_1_6_5_1_6_1_2_15_4_4_8_1_9_2_5_1_4_4_9_3_6_1_1_1_8_2_2_4_5_1_2_15_6_9_6_2_2_3_1_4_5_2_1_3_7_1_1_15_6_6_8_7_1_4_1_1_1_6_8_4_1_8_9_5_3_15_4_6_3_1_5_8_4_3_7_4_4_1_6_15_7_6_8_3_2_9_7_3_1_15_6_3_1_1_3_6_9_3_3_4_6_8_4_8_1_3_5_1_8_3_2_2_5_1</t>
+    <t>1_5_2_8_6_4_8_7_3_6_1_3_5_7_5_8_1_1_7_2_4_5_5_4_4_2_1_2_1_4_4_1_2_9_4_6_7_1_2_2_6_2_6_6_3_3_3_6_2_5_8_2_2_4_4_4_3_6_1_2_8_8_6_1_6_2_2_5_5_5_5_7_7_7_2_2_9_9_5_2_2_4_3_3_3_5_7_5_4_4_7_7_7_7_5_6_3_3_3_2_1_1_5_5_5_1_5_3_3_3_4_8_2_3_3_6_6_1_2_2_8_3_1_1_1_1_9_4_2_2_7_5_4_4_9_9_2_5_2_3_1_2_2_2_8_9_2_1_1_2_1_5_2_3_6_2_9_9_6_1_5_5_3_4_5_3_3_3_3_2_3_4_2_9_6_2_1_4_2_8_2_9_2_2_2_4_1_2_6_6_6_6_4_4_8_3_3_5_5_3_4_3_2_2_3_1_1_9_9_4_8_7_8_3_7_7_6_8_8_4_8_1_4_1_1_3_4_2_2_2_5_3_3_4_1_1_4_1_8_9_5_9_5_6_6_1_4_8_1_5_3_6_5_3_4_5_4_4_1_4_8_1_1_5_8_5_2_7_2_6_4_7_7_3_1_8_8_3_3_6_2_5_1_1_3_1_4_6_4_3_4_8_9_3_5_5_9_4_4_1_4_8_6_1_5_2_5_7_3_3_1_6_4_5_7_5_5_2_8_6_2_5_3_3_4_1_2_1_2_2_2_8_4_5_7_2_1_6_6_3_9_6_8_5_2_7_5_1_6_4_4_3_3_1_3_8_9_9_9_5_1_1_1_3_1_4_8_8_1_3_8_2_2_7_5_5_4_3_5_5_4_5_1_2_8_2_8_4_6_6_6_6_3_2_8_7_2_8_6_2_2_8_7_4_2_2_4_3_7_4_5_7_1_5_3_2_2_6_2_2_2_2_7_3_2_3_3_5_1_7_4_4_8_2_2_6_1_1_8_3_4_2_2_4_2_7_1_1_1_3_2_2_3_1_9_2_5_3_2_4_7_2_4_2_8_4_3_3_3_6_5_1_6_1_5_5_1_5_4_9_2_8_4_4_1_8_1_1_8_1_2_6_6_3_4_6_5_9_5_2</t>
+  </si>
+  <si>
+    <t>8_6_6_3_3_1_2_5_5_5_2_2_2_2_1_1_4_2_3_1_1_4_6_4_1_6_2_2_7_6_1_1_1_4_6_3_1_9_7_4_4_3_3_3_1_1_4_2_5_3_3_2_6_5_4_9_1_6_5_2_9_1_3_3_8_9_1_5_3_6_7_3_4_8_1_9_3_3_1_2_4_5_5_1_2_1_2_5_1_7_9_7_4_4_3_3_3_2_7_7_9_7_3_6_4_1_2_6_2_3_3_2_2_6_4_8_8_8_3_1_1_6_3_9_5_4_2_3_6_9_2_2_4_4_6_2_3_8_2_7_8_1_2_7_5_4_8_4_2_5_1_4_7_1_8_1_8_5_5_8_1_7_8_4_6_4_3_4_1_5_7_1_6_8_8_4_2_1_6_1_1_3_3_8_8_8_3_3_3_7_7_4_1_3_7_5_2_2_1_7_2_1_4_2_5_1_6_4_5_4_8_4_5_8_1_1_5_7_2_8_8_6_1_6_5_7_2_1_2_3_2_3_2_3_5_3_2_7_2_2_4_7_4_3_3_7_7_7_8_5_4_6_9_4_5_2_9_9_5_4_4_5_6_2_2_5_4_8_4_5_2_6_6_6_8_5_1_2_1_2_4_2_7_1_4_1_6_9_8_5_3_2_7_1_4_2_9_6_5_2_1_2_2_5_1_3_4_5_5_3_5_3_3_4_4_7_6_5_4_9_5_5_1_2_4_3_3_2_1_2_1_5_1_4_8_3_1_1_5_5_4_2_3_3_1_1_5_4_6_2_6_2_2_2_2_2_2_7_2_5_5_2_2_6_5_1_2_2_2_2_4_4_2_6_7_6_6_7_2_5_1_5_1_4_2_8_8_5_2_8_2_1_1_4_6_2_6_6_2_2_7_2_4_5_4_8_3_1_1_1_4_4_4_6_6_3_3_2_8_9_7_3_4_6_8_8_5_9_4_6_8_1_1_6_4_2_2_2_4_4_3_3_4_7_2_1_4_1_3_2_2_7_6_3_1_4_2_3_7_5_8_8_8_4_1_5_6_1_1_1_4_9_1_1_6_6_1_5_1_3_3_1_6_5_1_1_2_6_6_1_5_7_9_1_8_7_6_1_1_5</t>
+  </si>
+  <si>
+    <t>3_6_5_1_4_3_5_4_1_1_1_1_2_9_4_3_2_6_6_7_4_4_1_5_7_4_1_1_9_5_8_6_5_4_2_6_8_2_5_2_8_1_2_6_6_6_9_2_2_1_1_5_3_1_5_1_7_9_1_2_1_6_5_7_4_2_4_4_3_1_1_3_1_4_4_1_1_1_6_3_2_2_2_1_2_8_8_2_5_7_8_8_3_2_1_3_5_2_5_4_1_9_9_3_2_8_5_2_2_4_4_5_1_2_8_8_8_8_4_1_9_2_2_4_5_1_1_4_8_2_5_5_1_1_4_1_4_1_3_3_2_1_8_1_1_2_6_2_8_8_3_1_3_7_2_2_2_2_1_3_9_5_1_2_2_5_5_3_5_4_5_2_5_5_6_5_4_5_7_5_3_4_2_8_5_5_1_9_8_3_1_7_3_9_9_7_2_5_7_7_1_1_5_2_8_8_5_6_8_2_6_4_2_2_5_5_5_4_2_5_1_8_7_9_7_9_8_8_2_2_9_4_1_2_4_2_2_6_4_6_7_8_1_7_1_8_6_1_1_4_4_8_8_5_8_2_8_4_2_6_2_9_7_5_6_3_7_1_4_3_5_4_4_4_7_1_8_8_3_2_6_8_2_6_1_5_1_3_9_1_3_8_7_2_3_9_4_1_3_8_1_3_9_8_7_1_1_5_4_1_2_4_5_5_9_1_2_4_1_6_8_8_1_6_4_2_6_4_7_8_2_1_9_2_7_1_1_1_9_4_1_1_1_1_1_5_2_2_3_4_8_8_2_2_3_3_3_7_2_1_3_3_3_3_8_8_8_9_5_5_6_4_4_1_8_3_9_1_7_3_2_1_8_8_3_5_5_7_5_2_7_1_7_3_1_5_5_2_4_1_8_8_4_4_7_5_8_3_1_1_1_6_1_9_7_4_6_6_3_1_2_3_3_5_2_9_4_4_4_5_3_2_5_5_5_2_2_3_7_1_7_6_8_6_6_3_3_3_7_2_5_3_9_9_8_1_2_1_5_4_2_2_4_6_4_1_4_7_9_1_4_5_2_4_7_9_5_4_1_3_9_6_6_6_1_7_1_1_1_6_6_6_1_4_3_3_1_6_1_1</t>
+  </si>
+  <si>
+    <t>7_1_4_4_9_9_8_2_6_4_6_4_4_3_4_4_4_6_2_1_8_3_3_2_8_3_7_1_2_5_1_3_3_3_3_3_4_4_4_2_2_5_1_2_4_7_7_1_1_8_8_2_6_2_4_1_6_8_1_7_9_5_6_2_4_7_1_2_1_9_1_8_1_6_9_7_6_6_1_8_2_8_5_2_4_5_8_5_7_2_8_2_1_6_1_1_6_6_4_7_1_7_1_2_2_2_4_6_2_1_1_4_3_7_5_4_3_3_1_3_1_4_7_3_6_5_5_4_4_3_6_9_3_3_8_1_5_4_3_6_7_7_6_1_8_6_6_7_3_1_4_7_2_3_7_4_4_3_7_3_6_7_2_1_4_1_1_1_3_3_7_1_3_2_4_5_4_7_2_2_3_6_2_5_2_8_2_1_6_1_4_7_5_5_2_2_6_2_6_1_1_1_2_1_1_9_7_3_4_9_7_9_4_3_4_4_7_7_7_3_6_7_2_1_1_5_1_8_8_8_5_1_6_6_2_4_3_9_1_6_1_2_3_2_1_1_2_3_2_4_6_2_1_1_6_1_1_3_9_3_2_5_2_1_6_2_5_4_2_9_6_8_8_5_1_3_1_6_9_3_1_1_1_1_2_1_1_4_5_4_4_6_6_2_2_2_7_6_6_6_3_3_3_1_3_5_4_5_2_1_6_1_1_6_6_1_7_7_4_4_7_7_8_1_3_5_8_5_4_1_3_5_7_5_2_1_3_7_7_1_2_2_4_4_5_5_6_6_4_8_8_1_4_7_2_7_1_2_4_2_3_9_2_3_3_1_4_5_1_2_3_4_1_8_4_7_4_7_8_5_6_6_1_6_6_2_6_3_8_2_3_4_1_9_9_3_6_2_5_2_2_5_6_6_7_3_9_1_2_9_1_2_2_6_2_4_4_6_6_6_1_4_9_5_8_3_4_7_3_9_2_8_3_7_3_4_2_4_4_6_1_5_3_3_7_5_7_3_3_7_4_6_6_7_6_1_5_6_8_3_3_3_4_1_4_8_3_2_1_2_4_2_1_4_2_6_9_5_2_3_3_4_8_2_3_1_7_8_2_6_2_4_2_9_1_2_7_9_5_3</t>
+  </si>
+  <si>
+    <t>2_8_8_1_1_2_3_9_9_4_2_4_1_7_9_4_1_3_7_2_4_7_2_7_7_7_9_6_6_5_3_4_3_2_1_4_7_3_2_1_1_3_3_3_1_2_4_2_5_3_1_8_1_2_6_2_2_6_2_1_1_5_5_1_3_9_4_4_9_3_3_5_4_8_8_7_2_7_6_3_8_7_5_7_7_2_8_3_5_4_8_8_4_4_4_8_7_2_3_6_5_3_3_5_2_6_2_5_3_2_4_2_6_6_5_6_2_2_9_3_3_1_2_2_9_4_4_4_4_8_8_3_7_5_6_8_2_3_7_8_8_2_3_1_5_5_2_2_2_4_9_7_4_1_1_3_2_8_6_5_4_4_5_1_5_9_7_5_1_7_7_2_2_4_3_2_2_6_4_3_2_2_8_1_3_3_7_2_7_6_4_4_5_5_2_2_2_1_3_7_3_2_3_2_2_6_3_9_3_4_2_2_2_6_3_3_1_1_1_9_2_2_5_1_1_1_8_3_5_4_4_4_1_7_6_2_3_6_2_9_4_5_8_1_1_5_7_7_8_3_5_9_5_4_4_6_8_2_4_6_3_5_4_2_7_2_6_3_6_2_5_5_2_2_2_9_1_9_9_7_8_5_5_4_1_4_2_1_2_1_7_6_3_1_1_1_9_1_3_6_1_5_9_2_1_6_8_8_8_8_8_7_1_2_5_5_2_5_3_4_4_4_3_1_1_5_3_5_6_4_5_3_8_8_7_4_4_5_5_5_6_2_4_3_8_6_7_7_8_4_7_7_7_7_7_6_9_9_1_3_1_4_2_4_9_1_4_1_1_4_7_2_5_8_2_6_6_1_2_2_5_5_7_3_4_5_2_5_4_3_7_3_6_1_4_9_3_5_3_8_7_3_3_5_2_2_2_2_4_4_8_2_1_4_2_7_2_5_4_4_2_3_6_3_4_7_7_5_5_4_2_7_4_3_3_2_1_4_1_5_3_4_5_2_8_8_8_6_1_1_4_3_2_1_1_6_1_5_1_9_2_5_3_7_6_1_4_1_6_2_8_7_9_1_3_1_6_2_6_2_4_4_4_8_6_1_2_1_8_5_2_6_6_2_3_5_2_5_2_4</t>
+  </si>
+  <si>
+    <t>5_3_6_2_2_8_3_8_3_4_7_3_6_3_1_7_8_3_6_5_3_3_3_3_2_4_6_3_8_3_5_6_8_3_6_2_7_7_1_1_6_8_8_2_4_3_6_4_3_6_2_2_7_5_2_3_8_2_3_1_7_5_1_1_1_4_6_6_2_7_7_4_1_6_3_3_3_3_5_1_4_4_7_3_2_1_8_3_4_2_8_4_4_4_2_3_5_3_3_7_7_5_3_4_1_1_1_5_5_4_4_5_4_6_1_2_1_1_6_1_1_1_6_8_4_1_1_1_4_4_1_8_6_3_6_2_2_4_2_6_6_1_1_6_7_7_7_5_1_8_5_2_2_1_4_2_2_3_8_7_3_4_2_6_1_2_7_6_6_1_2_1_4_6_1_7_7_6_4_3_3_4_6_7_7_4_1_7_7_1_6_3_2_3_6_8_2_3_6_2_4_3_7_4_2_2_3_4_5_7_7_2_4_6_3_4_1_5_4_2_2_6_4_2_6_7_6_6_5_2_7_5_5_4_4_2_1_4_2_2_6_2_3_4_3_7_6_2_2_4_7_2_5_5_5_6_6_8_6_5_2_2_8_8_4_7_4_5_5_2_8_8_8_7_8_1_3_7_6_1_1_4_7_5_2_4_6_1_1_4_6_1_2_2_4_5_2_2_4_1_1_3_2_8_3_1_6_1_1_1_6_4_5_4_3_3_7_3_6_7_2_6_1_2_7_6_2_3_2_3_1_1_7_1_5_7_1_2_3_6_4_6_6_4_6_4_5_1_5_3_4_2_6_2_2_2_6_2_4_7_7_5_8_3_3_4_4_7_1_2_4_2_2_1_5_8_8_5_4_7_6_4_8_2_1_3_7_1_6_1_7_4_7_2_5_8_2_4_1_6_5_7_3_2_7_1_2_7_6_4_3_8_7_7_2_4_3_8_5_2_5_4_4_2_1_2_3_2_3_7_1_1_1_3_5_5_5_4_4_2_5_3_6_7_2_5_2_5_5_4_1_2_3_1_4_3_4_4_6_5_1_1_2_2_3_2_2_5_1_6_7_7_7_2_3_2_2_2_4_1_1_6_8_3_4_8_1_1_1_2_7_2_5_4_4_3_3_1_1_5</t>
+  </si>
+  <si>
+    <t>6_8_2_2_6_1_5_2_7_2_4_4_4_1_3_3_1_9_2_1_3_1_4_2_4_1_3_2_2_3_6_7_1_2_3_2_5_8_7_8_5_2_7_7_5_8_1_7_1_3_2_2_3_4_6_3_1_2_5_4_10_6_5_1_3_1_4_6_6_4_1_3_1_7_4_4_4_3_4_7_4_8_1_1_6_4_6_1_2_4_1_1_4_2_6_10_5_8_1_7_6_2_5_3_2_5_9_5_1_2_8_6_4_5_7_3_10_8_10_4_9_7_1_4_2_4_10_6_3_7_7_7_1_5_9_1_7_5_7_6_1_3_10_1_9_6_4_8_7_1_4_5_9_4_2_6_9_1_7_3_3_2_2_5_8_7_1_6_5_3_7_2_3_5_2_6_4_3_4_3_2_3_4_4_1_10_8_4_4_8_5_3_9_3_4_8_4_2_10_4_4_8_8_2_2_1_2_2_7_7_8_3_9_1_3_7_5_2_3_3_2_1_2_7_1_4_3_3_8_5_5_10_5_1_9_4_2_10_8_4_8_4_7_1_2_7_1_7_1_4_2_10_6_10_6_4_2_2_4_2_3_6_3_2_7_2_6_8_7_2_2_1_6_3_4_5_5_5_2_1_1_1_4_2_4_2_2_3_1_1_6_3_4_9_1_7_4_4_1_3_2_1_3_3_5_2_2_1_1_7_10_8_3_2_10_6_2_1_4_1_4_7_7_2_2_4_2_3_3_1_6_1_3_1_2_1_1_8_1_2_3_1_3_2_9_3_8_3_6_10_8_1_2_8_10_7_4_10_2_10_8_4_1_8_3_2_2_4_3_1_5_2_7_1_3_4_6_6_5_3_1_7_3_1_4_3_10_8_1_3_4_5_1_4_1_1_3_3_5_6_7_3_9_3_4_5_8_2_3_5_1_6_3_7_2_4_5_3_2_6_6_8_3_3_5_4_5_6_2_10_5_2_7_1_8_3_2_5_1_2_5_1_10_6_5_4_2_7_3_1_3_6_5_4_1_3_2_6_4_6_3_3_3_1_1_2_3_7_5_1_7_10_8_3_2_4_3_3_4_4_2_3_4_10_8_5_1_3_6_4_1_4_5_3_3_3_1_5_7_1</t>
+  </si>
+  <si>
+    <t>3_1_5_6_2_4_4_8_5_5_5_4_3_6_4_2_1_6_7_4_4_3_3_5_8_5_4_7_5_5_1_1_1_6_3_1_6_4_2_5_7_2_3_1_3_1_6_2_3_8_4_6_3_1_3_6_6_3_5_3_1_1_1_6_4_6_5_6_2_2_7_4_1_2_2_1_6_6_3_5_1_7_3_3_3_5_3_2_2_8_2_1_1_2_1_2_2_3_3_4_4_3_5_5_1_5_6_1_2_7_4_1_4_3_1_2_2_2_8_8_3_3_1_1_4_1_1_1_7_1_6_7_6_7_4_1_1_5_4_1_4_3_2_1_3_2_4_4_5_8_3_1_3_4_6_4_4_8_5_2_8_2_2_3_4_3_3_4_4_5_3_1_4_4_4_3_6_2_5_6_4_1_7_5_1_3_6_1_4_7_4_7_4_5_6_2_4_1_8_7_5_3_4_3_1_1_5_3_4_5_4_4_4_2_7_5_4_2_5_3_1_2_1_5_5_5_4_1_3_1_5_5_3_7_7_4_1_1_2_5_4_5_5_3_1_2_2_3_5_4_2_3_5_4_1_3_3_4_2_6_3_7_5_5_1_1_4_6_7_5_3_6_1_4_4_6_6_6_2_8_4_7_4_4_8_2_2_4_5_3_5_3_3_3_7_2_4_4_4_7_1_4_4_2_2_2_1_2_5_8_4_1_6_1_7_2_4_1_6_2_8_8_6_5_1_1_6_6_6_1_4_4_7_5_1_4_7_3_2_6_4_2_2_1_7_3_1_4_6_1_6_1_5_2_2_6_3_2_1_2_4_7_3_3_7_1_1_2_1_6_8_2_5_7_2_7_4_4_7_4_5_3_3_6_6_3_4_1_1_3_1_2_2_1_2_5_2_1_1_1_1_8_3_3_4_4_6_7_3_4_2_8_8_7_8_4_4_2_1_8_2_2_3_6_7_4_5_2_3_1_8_6_2_6_3_3_3_6_2_8_8_6_1_2_3_2_2_5_6_5_5_2_7_3_3_8_2_2_2_2_5_5_7_7_5_7_8_8_5_4_6_7_5_5_5_6_1_1_4_1_2_1_2_2_1_1_1_7_7_3_5_5_4_6_4_5_3_5_3_4</t>
+  </si>
+  <si>
+    <t>3_2_4_6_4_8_4_4_2_5_2_1_7_5_6_1_2_4_5_4_1_1_3_2_4_2_4_5_5_4_1_9_2_3_3_5_2_1_5_2_3_8_3_3_3_4_2_5_6_7_4_3_3_9_3_4_5_1_3_2_7_1_8_1_4_3_7_6_4_3_5_3_5_2_7_10_8_6_9_5_2_6_1_2_1_10_6_3_3_6_3_3_7_1_2_2_3_4_7_2_3_3_4_1_8_2_2_3_6_7_2_7_3_2_4_2_2_2_2_9_7_4_1_2_8_2_6_7_3_5_5_8_7_1_5_2_10_8_5_4_2_4_8_2_4_4_9_6_5_8_6_5_4_5_1_1_1_3_9_2_6_1_5_5_9_1_2_2_4_10_4_3_1_5_3_2_4_3_3_7_5_6_2_6_2_4_6_6_2_5_10_8_6_1_2_2_6_6_2_4_3_3_6_2_3_4_4_8_2_4_6_2_2_9_1_5_7_2_2_4_1_1_6_3_5_7_6_2_6_8_10_8_6_2_4_4_2_4_9_8_7_2_5_3_5_1_2_6_1_5_5_4_2_5_1_1_5_2_5_1_10_7_6_6_6_6_1_7_6_3_1_2_3_3_6_1_3_4_1_5_6_1_6_3_4_1_3_1_4_4_6_10_8_4_4_4_3_1_7_1_2_2_9_2_6_2_2_1_8_3_2_4_5_2_2_6_6_7_5_5_5_10_6_9_7_9_7_2_1_2_8_2_1_1_1_6_1_5_9_2_4_1_1_4_5_3_3_5_4_2_1_2_8_1_2_5_3_8_1_1_7_1_2_4_9_5_3_8_4_6_4_8_6_4_6_4_5_3_8_8_6_5_2_8_8_3_7_2_5_4_6_5_10_4_6_1_4_10_8_2_8_6_7_5_2_2_4_6_4_3_1_8_2_3_8_6_2_8_1_8_3_5_3_6_1_3_2_5_7_5_1_1_2_2_2_8_4_9_2_4_5_1_6_2_3_4_9_3_6_3_7_6_4_3_10_8_2_3_5_4_4_4_5_1_7_5_4_3_4_10_8_7_4_5_9_2_6_5_3_1_9_10_7_5_1_5_6_1_3_7_10_7_1_4_9_7_8_4_2_1</t>
+  </si>
+  <si>
+    <t>4_3_7_2_2_2_2_5_2_2_2_2_8_5_3_8_5_5_2_5_5_1_5_2_4_4_1_6_6_5_4_1_5_5_4_7_2_7_2_1_4_6_2_2_2_2_2_1_5_7_6_5_2_2_1_3_6_3_2_8_7_6_4_4_4_4_5_7_7_2_2_6_3_4_1_4_1_4_3_5_2_2_8_5_1_1_5_8_1_1_3_4_5_6_6_6_3_5_3_8_2_2_3_4_1_6_4_1_1_1_3_6_5_2_8_6_6_6_2_8_3_7_2_2_2_6_7_3_5_2_2_6_8_8_3_6_7_5_5_4_8_8_2_1_1_5_6_4_7_8_3_1_3_3_6_7_5_3_4_5_2_5_7_8_5_6_6_7_1_8_3_4_3_2_8_7_6_2_6_2_2_8_1_6_5_2_4_1_1_1_1_4_2_2_2_3_2_8_4_3_4_1_2_1_2_6_6_7_7_7_4_2_2_5_2_1_7_6_6_2_2_1_2_6_6_4_1_3_7_6_3_4_3_3_1_1_1_8_7_5_8_2_6_1_1_8_3_3_2_5_3_1_2_1_8_3_7_4_4_3_6_6_7_4_5_3_3_5_5_3_5_5_5_2_5_2_6_5_2_4_2_5_1_3_6_6_7_1_8_5_5_5_3_4_6_1_8_6_6_3_3_1_2_7_2_2_2_4_4_7_3_4_4_3_5_5_5_2_6_6_6_1_4_2_3_5_1_7_6_5_1_4_1_1_2_7_4_1_4_2_4_3_7_1_1_7_2_1_1_6_5_6_2_2_7_1_5_5_2_5_3_3_6_5_1_3_1_5_6_1_7_7_5_6_2_2_3_1_2_7_7_3_5_1_5_5_4_8_8_5_5_2_1_6_1_8_3_3_5_8_8_8_3_4_6_4_5_5_5_5_7_5_5_2_8_1_1_1_7_3_4_3_5_2_5_3_3_2_2_2_8_2_1_3_4_5_2_5_4_8_3_2_3_3_6_7_1_6_6_6_1_1_1_4_5_5_6_3_1_6_4_8_8_2_2_8_3_2_2_2_4_4_2_6_8_4_5_5_4_8_1_3_6_3_1_1_3_4_5_2_6_6_7_2_7_2_3_6_4_7</t>
+  </si>
+  <si>
+    <t>4_4_7_2_9_2_8_3_2_5_8_2_3_7_2_3_2_7_1_9_5_3_2_10_2_3_9_5_5_2_9_4_6_9_8_3_5_2_1_3_4_6_3_8_3_2_6_6_2_4_7_2_5_2_5_4_10_8_10_7_3_1_6_4_7_1_4_5_3_4_2_1_7_7_7_1_1_3_1_9_7_7_2_2_4_1_5_4_10_8_4_7_3_4_7_7_4_4_2_6_3_8_3_9_1_8_5_6_5_1_6_1_9_1_7_7_6_1_1_10_8_5_7_1_7_8_2_8_3_2_3_9_8_8_1_10_4_5_5_6_3_5_1_1_6_4_2_6_4_1_5_4_4_4_5_10_8_3_1_1_7_1_6_1_5_10_7_4_6_9_8_1_2_2_1_4_3_2_5_6_2_10_4_5_1_4_4_2_1_2_3_6_1_3_6_3_2_5_7_4_1_9_3_3_9_5_3_6_3_7_3_1_2_1_7_9_3_3_7_1_3_7_5_7_5_2_8_3_3_2_6_1_5_4_3_10_5_2_1_2_1_4_5_10_7_2_2_6_6_1_4_7_6_2_3_3_6_5_3_2_4_3_8_3_5_7_1_2_10_5_5_7_3_2_3_4_10_8_1_6_10_6_2_9_2_2_9_2_1_5_1_2_7_2_2_3_10_5_4_10_7_3_4_10_6_2_5_2_7_9_6_2_2_10_8_8_2_1_10_5_2_5_1_3_8_2_2_3_9_3_4_8_2_6_1_1_5_5_9_2_6_1_3_5_4_4_8_1_3_6_2_3_4_7_2_4_8_7_2_7_2_2_7_6_4_4_2_6_1_10_6_7_6_1_2_2_4_4_9_4_1_3_7_9_6_6_3_3_9_5_4_1_8_2_1_8_3_1_8_2_7_9_10_8_3_1_4_5_8_1_5_8_3_2_3_10_8_2_4_1_9_7_3_3_8_9_4_2_7_2_3_1_9_6_3_7_3_8_9_7_6_4_5_4_1_1_8_2_5_4_1_8_7_3_4_7_1_9_8_2_9_9_1_8_2_9_3_2_6_3_1_6_4_2_2_10_7_1_4_10_8_6_2_7_7_3_2_1_1_1_1_1_2_2_10_5_1_2_7_5</t>
+  </si>
+  <si>
+    <t>4_4_4_5_1_6_8_8_2_2_1_1_4_8_1_2_2_7_5_3_4_7_5_2_7_3_3_4_6_3_3_3_1_1_1_2_3_1_7_1_3_2_4_5_3_7_2_2_6_3_1_3_1_4_7_6_6_1_8_2_6_2_2_1_1_5_3_4_8_6_6_1_3_1_5_1_4_1_3_1_1_3_4_5_7_1_3_4_2_3_2_2_5_1_2_2_7_1_7_3_3_6_6_3_6_8_1_2_4_1_2_2_2_1_1_8_2_2_2_1_5_5_1_1_5_7_2_1_1_6_5_6_2_4_7_1_4_4_3_1_8_2_7_6_2_6_3_3_4_1_6_6_3_3_4_7_2_7_1_1_1_2_5_7_2_2_6_4_3_3_2_1_8_7_5_2_5_5_7_6_8_5_8_3_2_7_1_5_2_5_7_6_4_6_6_6_6_1_5_6_3_3_5_7_7_8_3_2_4_3_3_7_7_7_4_5_7_4_4_6_5_5_5_8_8_4_5_4_2_2_7_5_2_4_4_2_6_2_2_4_4_6_2_7_7_6_3_6_6_2_6_4_3_1_5_5_5_3_1_5_3_6_5_1_1_8_7_5_3_2_2_1_1_3_7_5_6_4_5_3_7_2_3_5_5_6_6_2_2_7_3_4_2_2_3_3_4_8_7_1_6_6_6_1_2_1_6_4_1_1_2_2_1_1_1_2_8_4_5_3_2_7_6_6_6_1_8_6_1_4_3_3_3_5_3_1_5_2_7_3_2_2_2_4_1_6_6_3_7_1_3_1_1_2_4_1_5_2_6_1_3_4_2_3_3_2_5_4_6_1_2_6_7_8_7_2_3_4_7_7_3_3_3_6_2_6_1_4_5_8_7_7_4_3_1_7_7_2_5_2_4_1_4_7_7_2_3_3_6_1_1_4_4_4_4_5_5_4_1_6_1_1_2_6_2_5_6_2_1_4_2_8_4_7_3_3_1_8_4_4_4_4_8_1_5_6_1_2_6_2_4_4_2_5_6_6_7_7_6_1_5_4_5_5_1_3_3_4_1_1_1_6_5_5_8_6_2_4_2_6_3_3_6_4_8_3_8_2_2_1_2_8_1_4_4_7_5_5_1_7</t>
+  </si>
+  <si>
+    <t>1_8_2_9_4_1_3_1_3_1_5_4_9_2_4_3_5_3_4_9_1_7_4_6_1_6_2_1_2_5_3_8_2_2_4_1_8_5_4_6_4_10_8_5_2_6_7_3_5_6_2_2_9_1_2_5_2_1_3_7_3_3_1_2_7_1_6_10_8_5_4_4_6_8_9_3_5_1_7_4_8_2_4_1_9_8_7_4_2_1_1_4_7_6_4_1_5_9_7_8_3_8_2_7_3_10_6_3_7_3_1_4_10_6_7_1_8_4_4_9_1_3_8_6_10_5_4_1_3_2_3_6_7_4_1_5_10_8_4_3_7_8_2_8_7_2_5_1_8_2_9_2_1_1_1_3_6_3_8_6_5_3_4_5_2_6_6_7_5_3_4_8_5_5_1_4_8_4_2_9_5_1_1_4_10_8_4_3_3_5_2_2_6_1_1_6_2_4_8_10_6_3_6_1_8_2_4_2_3_2_3_2_6_7_6_6_7_2_5_10_5_3_1_1_5_8_4_8_1_8_9_3_2_6_10_7_3_7_3_8_1_10_4_2_2_2_5_3_2_3_1_6_7_9_4_2_1_9_5_5_4_8_2_5_4_4_2_7_5_2_4_7_6_3_8_2_4_5_6_5_5_10_8_7_8_4_8_9_5_2_8_5_3_1_9_7_3_4_7_6_2_4_3_2_1_4_3_3_1_3_7_1_6_3_5_4_6_4_7_8_4_6_4_1_3_8_3_9_6_2_7_4_1_3_4_1_2_2_2_1_3_5_1_2_4_6_2_5_5_7_1_1_3_2_1_1_1_1_6_4_1_1_3_3_3_3_5_3_10_5_10_3_7_1_7_9_2_1_2_1_1_1_7_5_2_5_2_2_6_7_7_3_8_1_5_1_2_2_4_7_4_2_5_10_6_3_7_3_2_5_9_7_9_7_8_1_2_2_5_6_3_8_4_3_2_5_9_4_3_1_6_1_1_7_1_2_1_7_1_6_7_3_1_3_5_2_7_5_1_5_10_8_4_7_4_8_9_7_10_1_6_2_5_6_1_5_3_4_3_6_4_8_2_7_1_2_5_3_6_6_2_9_2_3_4_3_4_6_4_3_7_3_5_10_7_6_3_6_3_6</t>
+  </si>
+  <si>
+    <t>1_7_2_1_2_2_3_5_7_7_6_6_5_2_1_4_1_8_3_6_3_3_3_4_5_4_3_7_7_2_6_6_5_2_8_6_7_7_7_7_3_4_4_1_7_2_6_6_4_4_3_8_8_1_2_8_2_1_3_3_2_4_4_8_1_2_7_7_4_4_6_6_4_2_2_5_2_2_3_2_2_2_1_2_8_1_3_1_7_4_4_2_6_3_3_4_2_8_8_2_6_8_6_1_1_8_4_2_3_3_6_7_1_4_3_1_1_1_3_4_2_2_4_3_5_5_1_1_3_3_1_2_1_1_4_7_7_8_8_8_2_4_2_3_1_6_7_4_4_2_6_3_4_7_5_3_2_2_2_2_4_6_6_5_2_2_1_3_3_1_2_4_4_6_4_2_1_2_6_3_7_3_1_1_6_1_6_1_4_1_7_2_4_1_1_4_4_6_2_6_6_1_1_1_7_7_7_4_4_5_1_6_7_2_1_5_7_3_4_6_2_2_3_4_1_6_5_8_8_6_5_4_3_4_4_6_6_4_3_1_3_4_7_3_3_2_3_1_3_6_4_4_7_5_4_4_2_2_6_3_4_3_5_3_1_2_1_1_7_8_8_1_1_7_1_3_4_1_3_2_1_7_7_6_5_4_5_4_8_6_4_4_5_5_6_1_1_1_4_7_7_7_6_6_5_3_2_6_1_8_2_2_4_4_1_4_1_1_1_2_6_3_2_1_7_1_5_6_2_1_1_4_7_3_7_4_1_1_3_1_6_6_5_5_5_6_6_5_4_1_7_2_3_6_5_5_3_5_5_3_3_3_8_6_1_3_6_2_3_5_2_7_1_3_4_8_5_4_6_8_3_2_1_6_7_2_2_4_2_4_1_4_4_6_2_2_7_5_4_8_5_5_1_5_6_1_1_4_2_2_7_1_1_8_7_4_1_5_8_5_5_1_7_7_5_8_6_6_1_2_2_2_4_1_2_7_1_1_6_2_2_1_1_3_5_7_5_1_3_8_2_8_6_1_5_4_5_1_7_2_5_1_3_3_7_7_1_2_5_1_5_8_2_5_3_2_3_2_1_7_1_4_3_4_6_1_6_4_4_4_7_5_4_6_1_2_1_3_7_2</t>
+  </si>
+  <si>
+    <t>2_5_6_1_3_9_3_6_7_2_4_6_6_1_8_1_2_3_5_3_7_1_4_1_4_2_4_6_3_2_7_7_3_2_8_2_1_2_1_9_6_7_2_10_8_4_3_6_6_6_5_4_7_7_5_1_6_10_8_10_6_4_4_1_4_3_6_5_3_2_3_4_6_1_6_3_3_6_6_10_8_4_3_2_4_3_7_7_3_1_3_6_1_3_8_1_3_1_6_7_5_3_2_6_6_1_6_6_5_3_9_2_4_6_3_8_6_3_2_2_6_10_8_4_1_4_1_1_8_3_8_7_4_5_6_2_7_4_7_8_8_6_2_2_3_5_7_2_6_3_1_6_9_1_1_9_4_6_5_4_4_10_7_2_8_6_8_3_8_1_9_5_1_4_2_9_7_7_7_7_3_3_4_3_1_6_2_1_10_4_2_2_1_6_4_3_2_8_8_2_1_6_3_6_4_4_5_1_1_4_10_2_4_6_3_8_2_8_10_8_2_7_3_6_6_5_1_6_9_4_1_4_6_10_8_5_7_5_1_5_2_6_2_4_6_2_5_3_5_3_1_1_5_9_3_8_8_5_4_2_6_2_3_4_5_10_6_1_2_5_7_4_8_2_2_3_5_4_3_3_3_8_8_5_2_4_5_8_2_3_1_2_3_10_3_7_5_1_6_4_9_10_3_3_1_10_6_8_8_3_2_8_6_5_3_6_6_2_4_1_4_2_10_6_6_10_8_10_6_3_2_6_3_10_8_6_2_1_1_3_10_4_6_6_7_1_2_1_7_6_1_5_3_2_6_2_4_9_1_3_2_10_3_5_6_4_7_4_2_7_6_1_8_6_3_3_4_6_9_8_6_4_5_6_1_1_6_5_2_1_7_2_3_8_7_6_1_1_7_7_6_6_7_1_7_1_1_2_6_1_2_8_4_9_4_2_3_2_6_8_7_1_4_10_6_1_3_8_5_2_8_4_4_7_7_2_2_7_2_3_7_3_2_2_5_7_2_5_3_3_3_1_6_6_3_3_1_3_2_3_4_2_3_1_3_1_3_5_2_10_2_1_8_1_7_4_6_9_3_6_4_8_3_8_5_2_3_6_2_7_3_2_2_2_6_6_7_9_7_8</t>
+  </si>
+  <si>
+    <t>2_2_3_7_1_5_5_4_2_1_7_4_4_5_5_5_1_6_6_1_1_3_7_3_2_1_3_3_5_6_1_3_6_2_5_7_7_8_2_6_1_1_3_4_5_3_5_4_2_1_2_5_2_1_1_5_5_6_5_6_2_2_7_1_2_4_4_6_4_3_6_1_7_7_5_1_5_5_6_3_5_2_4_3_3_5_5_2_2_2_3_8_1_2_3_6_4_2_2_7_7_7_1_1_1_6_5_1_4_4_7_3_8_5_2_1_3_3_4_3_1_7_2_1_3_2_1_5_7_2_3_2_3_3_1_6_6_2_2_1_3_2_2_1_1_7_3_5_5_2_1_1_8_2_5_4_3_1_8_4_1_4_2_4_7_1_1_4_2_6_6_2_4_1_1_5_3_6_1_1_6_5_2_5_7_1_1_7_3_1_2_4_6_4_7_6_6_1_1_3_3_3_3_3_1_2_2_1_1_5_7_2_8_4_2_6_6_6_4_5_4_4_4_5_2_8_4_7_3_6_6_2_6_5_2_2_1_1_3_1_5_3_3_3_8_4_4_8_8_4_4_6_5_3_5_2_3_3_7_8_1_2_6_3_1_7_3_8_5_8_2_8_8_6_4_3_5_4_6_3_3_2_7_5_1_3_1_6_4_4_8_4_1_3_5_2_5_6_8_4_3_4_2_2_3_3_3_3_6_2_4_4_8_6_1_5_7_2_6_1_5_6_7_3_6_4_4_2_8_3_1_7_2_2_5_1_6_5_3_6_5_1_3_4_4_6_5_4_3_1_6_7_7_6_6_8_8_2_1_1_8_8_1_2_3_1_8_8_3_6_6_4_1_3_7_1_3_3_1_2_1_2_2_8_1_4_4_6_1_8_8_7_8_5_5_4_2_1_1_4_4_6_3_2_5_6_4_2_3_3_7_7_1_2_4_2_2_2_4_6_6_7_8_1_1_1_1_1_2_3_8_7_3_3_1_5_4_1_1_3_3_1_3_1_2_4_6_4_6_4_2_6_5_5_1_3_7_5_3_6_6_4_4_5_4_3_3_4_4_6_1_8_7_1_6_3_1_3_6_5_2_3_3_3_8_5_4_2_4_1_3_4_2_1_2_3_6_6_1_7</t>
+  </si>
+  <si>
+    <t>1_1_1_1_1_1_1</t>
+  </si>
+  <si>
+    <t>10_2_1_3_4_6_1_1_1_7_1_9_6_15_10_8_8_4_6_6_5_10_3_4_9_10_3_12_12_10_5_6_10_5_5_2_11_4_7_3_9_9_5_4_8_5_8_5_5_3_6_8_3_15_7_4_10_9_6_6_15_10_10_6_6_6_2_6_5_7_9_11_5_3_4_3_11_6_6_2_2_1_1_7_7_10_8_12_3_6_3_12_12_12_11_4_9_7_9_8_10_3_9_7_1_5_1_4_3_3_1_6_3_10_1_5_12_9_9_4_4_10_5_2_2_5_14_5_3_1_6_5_12_6_5_5_6_6_12_10_5_5_9_4_11_10_6_12_11_11_4_8_12_6_7_7_3_3_6_1_3_3_9_15_6_4_8_2_12_12_1_13_1_7_6_6_2_5_5_12_1_1_1_6_13_7_3_1_13_13_10_4_6_6_8_11_2_7_4_11_8_1_4_4_3_13_7_1_6_3_6_2_5_8_2_11_2_6_5_5_9_2_6_2_7_6_10_14_1_7_6_3_3_3_1_5_3_1_3_10_1_10_12_3_8_1_14_7_6_6_6_8_7_8_8_10_7_2_3_7_14_8_8_1_7_4_4_4_6_14_5_2_4_12_2_2_2_3_2_1_4_7_10_7_7_12_10_2_2_11_6_7_7_9_2_2_7_1_1_7_3_3_3_5_5_6_5_5_12_4_7_11_11_3_7_6_12_11_12_8_5_8_2_3_6_14_14_8_5_2_3_1_2_11_4_3_5_5_12_8_3_1_1_1_7_7_6_11_8_6_2_3_6_5_5_6_1_1_1_8_5_2_7_10_2_8_3_5_1_1_8_4_2_2_6_8_4_1_1_4_3_1_3_8_10_9_6_5_5_1_10_5_15_5_8_8_6_10_11_8_8_8_3_8_2_10_10_8_3_5_7_7_7_12_7_8_1_9_5_6_6_3_3_8_6_2_8_6_6_2_1_12_6_9_8_9_14_14_1_1_3_15_2_14_4_13_10_6_6_11_9_9_1_1_4_15_5_4_4_4_5_5_1_8_5_6_6_13_2_2_6_6_5_3_8_15_1_9_8_5_3_14_4_8_2_5_3_3_4_4_1_5_4_3_3_14_4_2_4_5</t>
+  </si>
+  <si>
+    <t>5_3_4_5_3_2_3_5_3_6_5_4_1_6_5_3_3_1_5_3_2_5_1_5_5_6_5_4_3_1_2_3_1_3_3_5_2_2_1_4_4_5_4_6_3_4_2_2_1_2_1_2_4_1_2_2_4_5_3_5_1_2_5_1_3_1_4_6_3_1_5_1_2_1_3_1_6_5_2_6_1_5_5_2_6_2_5_3_6_6_4_2_3_2_2_3_2_4_2_5_1_5_2_6_2_5_5_3_4_5_3_3_6_5_1_1_1_1_1_1_4_1_5_1_1_6_1_6_4_6_5_2_5_6_2_1_1_3_5_4_3_1_3_2_2_2_4_2_5_1_3_6_7_4_4_5_4_3_1_2_2_6_6_1_2_5_2_4_2_4_4_5_4_3_5_3_6_2_1_1_5_5_2_1_2_3_1_2_1_1_7_2_3_1_1_3_3_2_3_6_5_4_3_4_2_3_3_3_2_1_1_6_2_2_2_1_1_2_3_3_3_1_2_5_6_1_3_6_7_1_1_1_2_6_4_2_1_1_7_2_3_2_6_4_3_3_2_2_1_3_5_4_3_2_4_1_3_2_3_3_1_1_3_2_1_2_2_5_1_4_1_7_4_2_3_1_2_1_4_2_1_5_3_1_2_5_7_1_3_5_1_4_4_1_4_1_2_7_1_6_2_3_1_2_6_2_1_6_1_3_5_6_1_7_2_4_2_4_2_4_5_2_1_5_4_3_4_3_2_2_5_4_6_7_6_4_5_2_5_3_4_3_3_1_2_2_4_5_5_6_1_1_2_3_5_6_1_2_5_3_1_6_3_5_3_1_7_1_5_7_3_3_3_1_1_5_1_5_2_5_1_2_3_3_1_1_1_2_1_3_1_4_2_3_2_7_2_1_2_1_4_1_7_1_3_2_3_2_6_2_7_3_5_7_1_3_1_3_5_6_6_5_5_5_7_3_1_5_1_5_1_5_4_5_5_3_3_2_1_1_2_2_4_3_2_2_3_5_4_5_1_2_4_3_5_4_6_3_4_1_2_3_1_5_3_6_1_1_1_4_7_3_1_1_1_2_1_5_5_1_1_2_2_1_3_3_3_7_2_2_5_2_3_2_2_3_1_3_5_4</t>
+  </si>
+  <si>
+    <t>2_2_2_2_2_2_2</t>
   </si>
   <si>
     <t>6_1_6_15_15_15_8_4_4_14_2_9_6_7_9_6_8_5_10_12_5_7_12_10_2_7_13_5_2_2_2_12_5_11_11_9_5_5_6_6_8_7_9_2_1_12_2_3_4_4_4_2_1_1_6_10_2_2_6_10_1_13_1_12_12_14_3_3_15_8_11_2_2_3_3_2_5_9_4_3_2_2_10_5_5_12_4_4_3_3_6_6_4_4_4_7_7_2_15_10_10_5_10_1_1_2_2_2_5_5_5_3_3_1_10_3_3_6_2_7_3_1_6_9_11_11_6_6_10_4_1_3_7_7_1_6_4_6_10_2_14_10_11_8_11_1_1_8_8_1_9_9_9_10_7_2_13_2_5_9_9_9_10_8_5_5_10_9_3_12_11_8_7_5_1_2_9_8_1_1_4_15_1_5_3_8_8_8_7_6_5_7_7_11_9_2_3_5_12_12_6_11_4_10_10_6_5_2_5_10_2_2_3_4_2_4_9_9_9_12_13_10_6_1_2_6_1_11_3_3_8_1_10_3_2_5_10_3_1_12_12_14_14_14_7_7_3_12_7_2_10_13_1_9_1_7_6_5_11_8_14_1_10_14_14_6_9_6_12_6_1_1_1_13_3_8_7_1_8_8_5_5_3_5_5_10_4_12_12_1_3_4_8_4_10_7_8_7_7_5_2_10_2_2_9_15_15_8_9_1_2_4_2_4_2_10_7_1_6_5_7_13_13_5_5_3_6_4_5_2_4_4_9_13_6_6_2_7_7_8_1_13_1_4_7_6_6_3_9_8_6_7_7_4_10_8_13_13_6_3_1_3_14_1_1_6_6_4_4_2_4_7_7_4_3_9_2_1_8_8_8_8_8_8_4_2_10_5_6_2_2_5_7_3_10_6_9_8_9_4_2_2_6_8_3_14_3_4_6_1_14_9_2_5_8_3_5_6_10_1_9_2_10_12_5_8_6_6_8_4_9_6_2_3_12_3_1_4_9_5_7_2_2_15_1_6_2_12_6_11_1_1_4_4_6_4_6_14_7_11_2_9_6_3_5_1_12_12_2_4_8_7_8_8_12_1_4_10_2_12_3_1_1_4_8_3_4_9_11_7_8_6_3_5_9_13_7_1_7_2</t>
@@ -1179,54 +1233,42 @@
     <t>1_5_1_10_4_5_4_7_7_3_3_6_14_5_6_3_13_4_6_2_4_1_11_2_1_4_11_5_5_12_6_9_9_14_5_7_1_5_11_1_9_14_2_7_5_6_6_6_7_11_4_4_1_8_2_6_15_7_14_6_6_11_5_9_6_8_3_2_7_3_8_1_12_6_13_6_8_2_2_2_2_10_5_5_2_14_3_1_13_4_3_12_7_12_7_4_3_6_7_7_14_7_15_3_6_14_5_5_15_4_5_1_11_3_3_7_3_1_14_4_6_15_2_13_7_3_6_6_6_1_2_8_8_5_6_1_2_7_13_7_8_9_1_6_13_5_8_3_6_2_8_6_3_2_1_13_7_6_4_3_12_2_3_13_7_1_2_8_6_11_3_8_4_6_6_4_9_1_7_15_4_3_5_1_1_4_1_2_12_2_5_3_6_5_1_10_7_13_6_6_6_4_13_7_3_11_4_15_6_5_11_7_9_2_8_13_3_2_15_2_6_1_2_12_5_11_3_1_1_5_6_13_1_15_6_2_13_7_4_13_5_2_8_9_6_2_6_8_2_7_2_3_3_12_4_6_1_12_6_6_7_4_3_14_6_15_5_3_14_3_6_3_2_6_10_5_5_5_4_7_12_6_6_2_1_11_3_12_7_8_8_9_1_3_15_6_10_5_2_5_4_3_1_3_12_4_10_6_1_2_14_6_5_5_8_6_11_5_9_3_10_3_1_3_5_4_3_14_4_12_3_2_3_3_2_8_11_2_2_3_14_6_5_2_2_13_7_4_8_10_1_8_13_7_15_6_2_1_2_1_4_2_4_12_3_4_3_3_7_1_3_2_4_2_4_15_7_2_11_7_6_5_1_2_4_12_2_2_6_2_2_12_4_11_1_11_7_2_14_2_11_3_5_3_13_3_6_5_8_6_7_4_1_4_13_1_15_7_3_2_2_12_3_2_4_14_6_7_7_9_13_6_5_5_1_11_4_11_4_7_15_7_6_1_2_8_13_2_3_5_5_4_7_2_4_6_1_4_3_9_5_6_2_6_8_4_4_2_11_4_5_1_15_6_12_4_6_12_5_1_8_14_5_2_7_9_6_12_7_11_5_15_5_6_6_15_7_8_12_6</t>
   </si>
   <si>
+    <t>3_3_3_3_3_3_3</t>
+  </si>
+  <si>
     <t>3_8_12_11_7_7_1_5_5_1_5_5_6_7_5_1_5_3_4_1_2_2_10_6_2_4_11_4_14_9_10_2_7_3_10_13_3_5_15_2_9_7_2_12_2_8_12_6_8_3_10_9_3_3_3_9_4_8_9_5_3_4_4_4_1_6_3_9_7_1_2_2_12_11_3_6_12_2_5_11_9_12_6_13_2_2_5_5_4_3_3_4_4_4_8_7_9_10_7_7_9_1_5_15_4_10_10_7_5_6_6_5_2_5_6_6_10_1_6_12_10_10_12_7_8_12_12_1_8_4_7_2_2_5_15_3_9_2_4_12_5_8_11_2_4_6_3_12_14_13_8_9_3_12_3_3_10_7_2_6_6_6_5_4_9_6_4_10_11_1_13_13_13_5_2_14_12_5_4_9_9_1_1_3_7_7_7_7_7_2_5_9_1_6_6_4_9_8_13_9_5_5_1_5_10_10_10_9_2_4_3_1_6_5_12_5_7_5_5_2_1_8_2_3_8_4_11_12_5_2_4_1_11_11_4_6_6_2_6_6_4_8_13_8_5_5_2_3_10_5_4_2_9_10_10_10_1_2_9_9_5_1_10_3_9_6_6_3_1_2_2_6_12_11_10_9_14_7_12_4_10_3_14_3_6_1_1_12_6_1_1_1_11_2_4_7_3_2_7_1_2_5_12_5_7_4_4_4_8_2_5_8_8_10_10_1_4_5_2_7_4_4_10_10_4_3_1_3_12_12_8_1_1_3_2_13_3_10_1_1_6_2_5_7_10_5_7_9_3_5_14_10_1_3_7_1_1_14_1_5_3_13_9_1_3_10_3_5_5_3_11_6_2_4_6_4_2_3_14_2_2_15_10_14_3_8_6_6_4_7_3_2_8_6_4_4_3_6_4_2_15_11_5_1_1_6_5_10_2_1_10_8_9_11_11_8_6_6_2_7_10_5_1_8_11_7_8_12_4_14_2_9_9_11_6_4_12_15_15_5_1_9_3_2_7_5_6_3_5_3_8_10_2_5_8_5_5_7_3_4_12_9_10_1_7_4_3_6_6_6_6_9_5_5_10_12_12_7_6_6_5_5_3_5_2_11_6_5_6_5_7_12_7_9_13_7_4_2_2_6</t>
   </si>
   <si>
     <t>13_6_14_5_2_3_13_1_1_9_4_6_12_5_8_10_5_7_5_14_7_7_6_4_12_5_2_1_1_3_11_7_4_1_7_6_5_13_4_4_11_5_2_4_6_4_4_8_3_8_4_7_14_5_6_8_3_10_3_13_2_3_10_5_3_2_15_4_10_5_8_3_12_3_14_5_8_4_1_15_5_4_6_2_8_6_7_2_10_6_15_7_4_4_14_4_6_10_5_2_5_3_6_5_5_8_11_2_11_5_5_3_1_2_6_8_3_13_6_4_15_4_14_4_3_8_12_7_7_14_5_1_6_2_8_4_7_2_7_14_5_13_2_3_8_3_6_13_3_12_6_2_12_6_9_13_4_9_2_4_2_5_6_1_8_1_10_1_2_11_6_8_12_7_1_9_8_6_1_13_4_5_15_7_10_3_5_2_7_1_2_6_15_6_3_3_12_7_4_6_14_3_3_7_12_6_6_1_11_3_5_5_3_3_8_1_1_3_13_7_1_4_2_8_12_6_15_6_1_4_13_5_6_6_15_1_14_4_6_1_7_9_13_1_7_3_9_11_6_4_3_9_15_7_15_5_5_11_2_3_2_8_8_7_8_6_8_11_6_3_1_5_2_3_3_3_8_14_6_4_13_7_6_6_7_10_7_7_4_7_11_7_1_1_3_10_5_15_7_1_13_6_9_11_7_15_7_8_2_3_2_8_11_5_2_1_7_7_3_1_2_7_6_2_4_13_3_6_10_7_5_6_9_1_2_8_12_4_11_5_6_3_6_14_6_3_15_7_15_7_5_10_6_6_1_5_7_9_2_13_5_2_2_13_4_13_4_13_7_2_7_11_2_2_6_2_3_3_10_7_9_9_2_8_4_11_6_14_5_7_1_1_13_5_12_7_3_6_8_4_3_14_2_2_5_10_6_13_6_3_8_1_11_4_14_7_6_15_7_3_8_8_6_12_2_11_3_14_4_8_4_14_7_5_5_14_6_12_6_15_6_5_15_4_7_3_3_3_13_5_13_1_1_10_6_10_7_1_2_3_14_4_14_4_5_10_5_2_4_11_5_4_7_12_3_11_4_5_6_9_2_5_14_3_15_3_5_1_9_1_2_12_6_3_9_15_1_15_6_6</t>
   </si>
   <si>
+    <t>4_4_4_4_4_4_4</t>
+  </si>
+  <si>
     <t>6_1_5_5_1_11_5_4_5_1_1_12_8_10_2_8_8_15_12_3_5_3_2_5_8_7_8_2_3_5_5_5_3_4_14_9_2_7_7_4_3_3_4_4_6_3_3_9_3_3_9_5_5_3_10_10_3_5_5_8_7_2_8_7_2_4_10_10_6_6_1_1_6_10_1_10_8_3_11_4_2_5_10_13_11_2_7_8_8_2_1_2_5_10_1_3_9_10_8_8_5_5_4_4_2_5_4_10_3_2_3_7_5_6_6_4_2_1_5_9_12_12_10_11_4_3_1_12_15_2_3_3_6_8_6_4_1_5_4_2_9_3_3_6_5_8_1_6_6_1_2_4_14_6_11_3_6_6_3_9_3_7_8_5_14_8_2_2_12_5_5_3_8_5_8_5_8_8_1_8_5_8_3_3_5_8_1_10_9_2_3_8_2_6_6_3_2_4_8_10_1_14_2_11_2_3_5_6_6_6_1_5_2_9_3_3_2_5_7_5_7_5_1_8_4_5_2_2_8_6_5_2_4_4_4_3_7_10_13_7_1_2_5_2_8_2_9_4_9_9_9_11_11_1_1_5_8_10_7_8_15_11_5_5_11_4_1_2_3_1_9_2_2_2_13_13_9_8_3_1_1_8_1_12_2_2_7_10_3_6_3_6_14_13_13_1_1_1_4_7_2_6_9_7_1_1_14_5_14_5_3_14_10_4_15_1_14_6_9_13_2_8_9_14_14_14_9_7_8_3_8_5_7_8_1_1_8_6_7_2_8_8_1_11_6_6_1_1_6_1_10_1_4_13_2_2_6_6_3_6_3_3_5_8_3_3_7_8_8_7_5_1_8_3_9_5_11_2_7_10_6_2_10_2_3_2_15_6_6_11_2_13_4_7_7_7_14_8_2_4_4_3_4_1_4_9_8_9_9_12_4_1_13_10_7_12_13_13_3_4_6_4_10_2_1_3_7_2_2_4_2_15_3_3_5_2_6_5_6_6_4_4_4_12_4_5_1_7_13_1_8_8_14_5_13_3_3_3_3_2_3_10_10_10_15_1_6_10_1_7_7_7_8_5_7_7_4_3_5_3_1_3_9_7_4_9_1_3_12_3_7_2_10_10_2_7_9_8_9_9</t>
   </si>
   <si>
     <t>8_4_11_6_1_8_5_3_10_3_4_7_1_5_1_12_6_13_6_13_4_8_7_11_5_4_2_14_4_7_4_15_3_1_9_1_6_8_5_3_7_7_1_4_10_6_7_12_3_2_9_14_5_2_5_12_6_10_2_9_6_9_9_1_4_15_5_3_1_5_4_2_1_12_3_12_5_5_2_6_2_7_4_11_4_12_7_11_4_1_1_3_11_7_6_8_2_8_9_13_7_5_15_7_6_11_4_8_3_5_3_2_15_6_6_7_3_11_6_5_1_7_2_1_1_5_9_12_6_8_2_5_2_6_10_4_1_11_7_4_10_2_8_10_2_14_4_15_7_11_7_7_3_11_6_11_1_9_13_5_6_14_6_5_4_13_4_8_8_14_5_14_3_3_6_10_6_8_5_4_12_4_15_5_1_2_3_4_5_13_6_10_4_4_15_7_15_6_4_15_5_5_4_5_1_7_3_1_13_4_12_4_5_14_6_3_12_5_2_5_3_13_1_14_2_1_12_6_3_11_5_3_3_3_7_1_8_10_4_3_1_12_6_11_5_15_4_5_5_7_5_5_15_3_12_5_2_2_11_6_1_10_5_10_6_7_3_2_4_7_14_5_3_4_2_12_5_15_4_1_2_13_4_4_5_13_1_1_2_3_15_5_6_1_3_13_4_8_12_4_9_11_1_2_14_5_5_10_7_2_15_5_12_3_12_7_8_4_14_3_3_8_1_2_9_3_5_3_11_6_1_1_5_8_6_8_10_3_1_11_2_5_4_1_9_12_6_1_1_2_3_6_5_3_9_11_4_4_14_7_4_13_7_2_5_9_1_1_4_1_3_13_6_13_6_1_10_7_7_15_5_1_13_3_7_8_13_2_11_5_2_1_4_2_4_7_1_2_1_5_5_6_1_1_7_15_2_8_10_5_13_2_11_4_4_6_7_13_3_1_13_6_1_15_6_3_2_3_14_5_12_3_6_7_1_8_2_14_4_4_15_7_6_3_6_15_5_2_3_1_11_5_6_14_4_4_7_1_5_6_6_2_11_6_14_4_4_6_5_13_4_2_4_2_1_10_5_8_2_14_6_1_3_3_2_14_6_8_5_2_13_6_10_6_11_6_2_13_6_3</t>
   </si>
   <si>
+    <t>5_5_5_5_5_5_5</t>
+  </si>
+  <si>
     <t>5_8_14_8_1_8_8_8_5_6_8_11_11_10_5_9_10_2_5_6_1_5_7_7_3_7_8_1_5_4_4_4_3_7_7_5_15_2_9_7_5_1_6_1_6_1_3_3_2_5_6_6_7_3_8_5_6_2_2_2_1_1_8_8_3_9_2_2_4_4_6_6_15_14_5_5_5_4_4_1_1_6_3_11_6_4_8_8_2_1_3_1_3_14_2_14_5_2_9_9_11_11_1_8_1_1_6_5_10_10_5_5_9_1_2_4_9_13_2_7_9_2_2_2_3_3_8_10_10_8_15_7_1_3_3_6_1_1_7_7_3_7_7_5_2_9_11_9_8_7_1_1_6_9_4_3_6_6_5_1_5_11_14_9_5_4_1_2_8_4_15_5_9_3_3_12_5_6_2_1_1_3_11_7_10_8_5_3_7_4_13_1_9_10_2_6_8_2_5_7_8_14_5_14_5_9_4_4_4_2_2_1_4_3_7_7_1_11_2_10_1_1_1_14_5_10_5_1_3_2_8_11_1_5_5_5_11_4_7_9_1_10_1_5_9_9_3_3_14_2_1_3_3_3_3_11_9_9_2_2_1_5_6_1_12_2_5_5_3_5_3_8_1_10_10_9_8_7_1_5_9_10_3_14_7_7_5_5_7_4_5_9_5_9_6_12_7_6_12_13_8_5_5_6_6_4_8_1_8_5_4_13_2_4_8_7_1_11_5_14_12_1_3_6_6_6_6_10_3_8_8_8_8_10_4_6_7_5_2_1_3_9_9_2_4_3_1_14_5_8_8_13_1_11_8_3_3_2_1_7_1_6_6_8_8_8_5_5_5_3_3_3_6_4_10_3_1_3_6_3_12_4_2_2_7_2_1_15_15_7_5_7_6_6_4_4_9_6_14_8_5_2_5_5_6_10_5_9_5_6_4_2_10_14_8_10_2_13_11_1_3_5_11_5_2_15_3_3_5_10_3_3_15_15_10_3_2_2_12_5_10_4_8_8_9_4_4_6_11_14_4_9_8_7_7_4_11_1_2_5_13_13_4_9_7_10_10_4_12_9_9_3_8_3_6_1_1_6_3_1_1_7_10_10_10_14_5_9_4_5_3_10_14_5_6_3_9_1_5_5</t>
   </si>
   <si>
     <t>9_5_1_12_3_7_5_12_5_6_6_2_4_1_6_12_1_6_14_2_8_1_5_13_5_14_4_6_1_4_7_7_2_2_12_5_6_10_6_5_2_3_4_6_4_11_1_14_5_8_8_3_9_2_3_8_14_3_8_6_11_5_11_5_1_4_2_8_9_1_10_6_5_2_7_1_5_12_7_3_2_14_6_12_6_1_9_12_1_10_6_12_3_4_1_8_5_6_6_9_2_7_2_6_13_4_5_13_4_6_5_13_7_7_6_1_10_6_4_2_2_8_2_13_7_8_1_7_5_1_2_13_4_1_15_6_5_9_6_13_6_4_10_4_9_12_5_10_5_3_7_3_7_4_2_11_1_10_4_7_14_5_13_3_4_2_9_6_8_15_6_15_5_12_3_11_2_1_6_13_3_1_4_1_1_15_2_6_11_6_10_6_15_5_1_3_12_6_11_7_2_12_7_3_3_6_14_4_10_6_12_6_1_9_2_13_5_15_7_9_7_1_6_8_12_4_6_2_4_1_2_13_4_1_5_9_2_3_3_3_15_4_13_7_9_6_1_1_14_5_8_6_9_3_14_6_1_10_7_2_3_5_4_4_4_5_1_1_7_15_5_5_2_8_4_7_5_7_8_11_5_2_7_12_6_14_6_6_15_5_4_6_4_7_10_3_15_4_1_12_7_1_10_2_8_9_6_2_11_3_4_7_3_1_3_13_4_3_1_14_7_9_3_13_4_15_7_7_9_10_6_3_14_5_1_6_11_2_4_1_12_6_5_8_3_2_13_2_7_4_3_8_4_14_7_14_1_2_10_6_15_2_1_4_8_8_2_11_5_14_5_5_12_1_9_9_14_3_1_12_4_4_15_1_4_10_3_12_7_6_6_1_13_6_6_2_5_2_3_4_13_3_1_2_3_10_6_1_9_13_6_2_6_8_1_13_5_5_6_12_3_2_15_2_11_5_15_6_3_3_3_10_4_8_15_4_7_14_7_7_5_10_5_1_15_2_7_2_14_7_9_7_6_8_8_15_6_8_3_1_2_14_6_4_11_2_4_4_7_6_15_1_10_6_1_4_11_6_11_4_3_7_1_8_8_8_11_1_6_2_7_15_3_12_6_6_4_6_3_4</t>
   </si>
   <si>
+    <t>6_6_6_6_6_6_6</t>
+  </si>
+  <si>
     <t>5_1_12_7_6_5_4_2_9_7_7_1_1_1_1_1_4_1_6_4_3_1_3_3_1_1_7_13_7_13_13_14_3_6_14_5_3_3_2_11_3_13_7_9_6_15_10_10_10_6_13_3_4_5_8_3_5_5_2_12_9_15_3_5_9_1_12_2_7_13_8_1_3_4_11_5_5_4_1_5_7_9_7_5_8_3_7_6_13_2_2_7_4_3_3_12_10_4_12_8_8_6_14_3_5_1_2_4_5_3_14_5_5_6_5_5_5_2_2_4_7_8_1_6_6_6_6_5_5_1_8_1_1_11_7_6_6_10_1_10_4_5_1_15_8_1_4_11_6_9_9_2_2_5_12_7_7_7_10_1_1_2_11_8_8_7_6_1_14_11_12_5_4_14_9_2_6_10_6_8_2_11_9_12_3_3_12_12_6_11_11_11_10_7_3_3_6_7_2_3_1_1_2_12_3_11_9_4_4_8_9_3_9_3_1_3_12_5_4_10_1_8_3_1_7_7_2_1_3_10_10_4_3_8_14_6_3_13_10_15_13_10_4_9_5_5_5_9_2_7_1_5_8_5_7_6_3_9_7_5_2_2_6_3_1_8_10_8_9_12_8_8_14_14_11_11_2_2_5_6_2_2_9_1_9_6_8_5_14_10_13_13_10_6_1_1_1_14_6_2_3_4_14_4_1_6_3_2_5_3_10_4_4_1_1_12_10_3_3_5_3_1_8_7_12_11_12_2_8_7_7_3_6_4_5_4_9_1_13_7_2_9_14_14_14_9_14_10_9_10_1_3_10_8_9_15_1_1_8_10_3_6_1_8_3_2_12_2_7_1_15_6_5_13_11_14_5_3_10_13_9_11_1_3_4_3_6_1_1_9_3_8_11_1_7_8_4_1_10_2_9_12_6_10_10_9_1_12_6_5_5_1_1_3_3_14_10_10_10_5_2_3_4_10_8_3_3_5_1_11_11_3_3_3_1_6_4_14_7_13_12_8_5_9_4_6_2_2_6_6_14_9_12_3_6_10_10_1_14_7_7_3_3_4_2_5_14_13_6_3_9_11_3_3_9_13_14_7_5_5_6_1_4_4_9_11_1_10_10_1_14_3_6_9_5_3_6_12_1_5</t>
   </si>
   <si>
     <t>8_14_4_8_8_2_2_14_2_6_9_7_4_11_7_1_7_12_4_9_7_2_2_7_10_5_1_6_11_5_3_1_10_6_1_5_7_13_6_10_5_11_6_4_9_11_6_10_5_1_14_5_3_1_11_3_2_15_6_7_1_3_2_13_3_1_7_6_5_11_2_3_1_6_3_13_7_12_4_6_4_5_3_6_9_1_2_5_4_5_15_6_13_5_2_7_11_6_1_10_1_6_9_11_7_5_3_4_2_13_6_14_6_7_1_4_8_8_2_8_4_13_1_5_1_15_7_1_5_14_5_2_1_7_6_14_7_1_8_5_7_8_2_8_10_3_13_6_9_2_2_10_7_13_7_15_6_3_2_4_8_14_1_14_5_8_9_2_12_5_5_1_13_3_4_7_6_2_15_6_13_6_2_1_3_14_6_2_1_7_7_6_8_2_3_6_3_7_1_8_3_5_6_13_7_9_9_5_9_8_4_1_3_2_9_11_6_4_1_3_2_7_14_3_7_6_1_3_6_2_4_6_1_6_2_5_11_7_14_6_4_11_5_11_7_5_2_10_5_1_6_9_4_10_5_5_1_6_8_2_6_5_2_13_6_12_6_1_3_11_7_12_5_1_6_1_2_4_2_7_9_6_3_9_6_10_5_3_6_5_9_5_3_9_9_5_15_6_14_3_1_6_5_3_15_3_13_6_15_3_15_6_15_2_4_1_10_4_13_6_2_1_3_1_10_7_1_7_1_9_12_4_5_2_12_4_10_5_13_6_4_3_10_7_1_5_7_3_15_2_9_11_3_2_15_5_3_3_5_3_13_6_1_4_1_11_5_3_12_7_11_5_5_13_6_6_14_4_7_7_8_5_4_2_1_2_7_2_1_5_11_5_5_4_4_9_1_11_3_8_7_3_1_13_1_12_3_8_6_2_4_15_1_6_3_8_3_15_7_1_15_7_4_12_2_2_13_6_13_7_2_9_10_3_1_5_1_2_12_3_4_3_9_9_3_11_7_14_7_3_3_14_2_2_1_10_7_10_5_7_10_5_11_5_15_3_3_14_2_2_4_8_1_2_1_2_9_4_5_8_3_9_14_6_15_5_1_5_4_2_4_2_10_5_14_7_15_4_7_5</t>
   </si>
   <si>
-    <t>1_1_1_1_1_1_1</t>
-  </si>
-  <si>
-    <t>10_2_1_3_4_6_1_1_1_7_1_9_6_15_10_8_8_4_6_6_5_10_3_4_9_10_3_12_12_10_5_6_10_5_5_2_11_4_7_3_9_9_5_4_8_5_8_5_5_3_6_8_3_15_7_4_10_9_6_6_15_10_10_6_6_6_2_6_5_7_9_11_5_3_4_3_11_6_6_2_2_1_1_7_7_10_8_12_3_6_3_12_12_12_11_4_9_7_9_8_10_3_9_7_1_5_1_4_3_3_1_6_3_10_1_5_12_9_9_4_4_10_5_2_2_5_14_5_3_1_6_5_12_6_5_5_6_6_12_10_5_5_9_4_11_10_6_12_11_11_4_8_12_6_7_7_3_3_6_1_3_3_9_15_6_4_8_2_12_12_1_13_1_7_6_6_2_5_5_12_1_1_1_6_13_7_3_1_13_13_10_4_6_6_8_11_2_7_4_11_8_1_4_4_3_13_7_1_6_3_6_2_5_8_2_11_2_6_5_5_9_2_6_2_7_6_10_14_1_7_6_3_3_3_1_5_3_1_3_10_1_10_12_3_8_1_14_7_6_6_6_8_7_8_8_10_7_2_3_7_14_8_8_1_7_4_4_4_6_14_5_2_4_12_2_2_2_3_2_1_4_7_10_7_7_12_10_2_2_11_6_7_7_9_2_2_7_1_1_7_3_3_3_5_5_6_5_5_12_4_7_11_11_3_7_6_12_11_12_8_5_8_2_3_6_14_14_8_5_2_3_1_2_11_4_3_5_5_12_8_3_1_1_1_7_7_6_11_8_6_2_3_6_5_5_6_1_1_1_8_5_2_7_10_2_8_3_5_1_1_8_4_2_2_6_8_4_1_1_4_3_1_3_8_10_9_6_5_5_1_10_5_15_5_8_8_6_10_11_8_8_8_3_8_2_10_10_8_3_5_7_7_7_12_7_8_1_9_5_6_6_3_3_8_6_2_8_6_6_2_1_12_6_9_8_9_14_14_1_1_3_15_2_14_4_13_10_6_6_11_9_9_1_1_4_15_5_4_4_4_5_5_1_8_5_6_6_13_2_2_6_6_5_3_8_15_1_9_8_5_3_14_4_8_2_5_3_3_4_4_1_5_4_3_3_14_4_2_4_5</t>
-  </si>
-  <si>
-    <t>5_3_4_5_3_2_3_5_3_6_5_4_1_6_5_3_3_1_5_3_2_5_1_5_5_6_5_4_3_1_2_3_1_3_3_5_2_2_1_4_4_5_4_6_3_4_2_2_1_2_1_2_4_1_2_2_4_5_3_5_1_2_5_1_3_1_4_6_3_1_5_1_2_1_3_1_6_5_2_6_1_5_5_2_6_2_5_3_6_6_4_2_3_2_2_3_2_4_2_5_1_5_2_6_2_5_5_3_4_5_3_3_6_5_1_1_1_1_1_1_4_1_5_1_1_6_1_6_4_6_5_2_5_6_2_1_1_3_5_4_3_1_3_2_2_2_4_2_5_1_3_6_7_4_4_5_4_3_1_2_2_6_6_1_2_5_2_4_2_4_4_5_4_3_5_3_6_2_1_1_5_5_2_1_2_3_1_2_1_1_7_2_3_1_1_3_3_2_3_6_5_4_3_4_2_3_3_3_2_1_1_6_2_2_2_1_1_2_3_3_3_1_2_5_6_1_3_6_7_1_1_1_2_6_4_2_1_1_7_2_3_2_6_4_3_3_2_2_1_3_5_4_3_2_4_1_3_2_3_3_1_1_3_2_1_2_2_5_1_4_1_7_4_2_3_1_2_1_4_2_1_5_3_1_2_5_7_1_3_5_1_4_4_1_4_1_2_7_1_6_2_3_1_2_6_2_1_6_1_3_5_6_1_7_2_4_2_4_2_4_5_2_1_5_4_3_4_3_2_2_5_4_6_7_6_4_5_2_5_3_4_3_3_1_2_2_4_5_5_6_1_1_2_3_5_6_1_2_5_3_1_6_3_5_3_1_7_1_5_7_3_3_3_1_1_5_1_5_2_5_1_2_3_3_1_1_1_2_1_3_1_4_2_3_2_7_2_1_2_1_4_1_7_1_3_2_3_2_6_2_7_3_5_7_1_3_1_3_5_6_6_5_5_5_7_3_1_5_1_5_1_5_4_5_5_3_3_2_1_1_2_2_4_3_2_2_3_5_4_5_1_2_4_3_5_4_6_3_4_1_2_3_1_5_3_6_1_1_1_4_7_3_1_1_1_2_1_5_5_1_1_2_2_1_3_3_3_7_2_2_5_2_3_2_2_3_1_3_5_4</t>
-  </si>
-  <si>
-    <t>2_2_2_2_2_2_2</t>
-  </si>
-  <si>
-    <t>3_3_3_3_3_3_3</t>
-  </si>
-  <si>
-    <t>4_4_4_4_4_4_4</t>
-  </si>
-  <si>
-    <t>5_5_5_5_5_5_5</t>
-  </si>
-  <si>
-    <t>6_6_6_6_6_6_6</t>
-  </si>
-  <si>
     <t>7_7_7_7_7_7_7</t>
   </si>
   <si>
@@ -1285,6 +1327,42 @@
   </si>
   <si>
     <t>2_1_5_8_2_9_3_9_2_5_3_9_3_1_5_1_2_3_8_1_8_9_8_11_2_1_5_5_11_5_5_2_2_5_8_6_11_6_1_5_11_6_9_10_7_3_8_2_3_2_4_1_1_11_5_7_6_3_7_5_2_6_1_4_2_1_9_1_6_2_9_3_4_7_6_4_2_1_5_4_2_4_6_1_6_8_7_3_6_3_4_7_3_6_11_5_4_7_2_8_8_2_5_8_9_4_5_8_2_4_2_6_6_8_3_3_6_6_6_2_10_4_4_1_1_2_4_1_3_9_4_6_2_4_4_9_3_7_9_1_2_7_7_1_9_7_9_11_6_2_10_3_6_2_3_2_4_2_6_7_4_7_8_3_6_5_2_6_2_10_5_6_8_2_8_1_10_7_9_5_3_7_2_9_11_3_3_8_6_5_7_1_2_6_11_1_1_8_10_6_10_5_9_9_6_3_1_1_2_4_1_6_7_11_5_5_2_7_1_2_7_2_4_8_8_1_6_5_3_9_10_4_11_7_5_1_2_8_3_8_6_5_5_2_2_7_9_2_4_7_4_6_5_1_5_1_4_3_3_3_6_7_8_6_5_1_6_5_9_7_2_4_9_3_5_4_6_3_11_1_5_3_3_10_4_6_4_9_3_2_3_5_5_1_6_2_4_3_2_7_4_3_1_8_6_3_4_8_8_4_1_3_1_4_6_3_7_2_9_10_3_1_6_11_5_4_3_2_7_6_3_9_2_7_11_3_8_4_8_3_6_7_7_11_2_4_3_10_3_4_5_5_2_5_4_8_9_2_4_3_1_8_9_2_8_8_9_7_1_5_2_5_8_4_7_6_5_2_5_3_4_6_1_8_9_5_11_5_2_3_2_1_4_1_1_6_2_1_4_1_1_8_7_2_4_1_1_2_6_9_5_2_6_6_6_4_4_2_2_6_7_11_2_7_10_7_5_5_5_8_3_8_7_9_3_11_3_3_1_2_1_4_2_1_1_6_2_7_5_1_2_7_2_6_1_4_2_4_5_8_9_9_2_3_7_8_1_6_9_4_2_5_5_9_3_6_6_6_2_1_4_6_3_2_4_2_1_9_1_9_6_6_3_7_7_1_1_2_9_3</t>
+  </si>
+  <si>
+    <t>7_2_2_1_2_2_7_3_2_8_10_7_2_10_1_6_2_1_2_7_7_5_1_1_2_2_1_4_2_9_9_2_11_11_4_4_6_11_11_9_7_3_9_3_5_1_7_6_6_7_9_8_8_2_3_2_2_2_2_1_5_5_3_7_2_3_1_1_3_7_10_8_9_1_1_3_6_5_8_5_8_7_1_1_6_9_1_3_9_2_3_5_4_4_3_5_5_5_4_10_3_5_1_8_3_4_2_6_1_4_2_3_3_2_3_2_1_7_7_5_1_4_9_9_5_11_1_4_1_3_3_2_4_6_8_2_10_2_8_2_2_5_2_7_5_7_3_2_4_2_8_6_6_3_2_10_5_4_6_9_5_2_2_2_8_5_7_5_1_5_3_9_2_4_7_11_7_3_6_6_11_11_7_8_11_11_8_8_10_7_7_8_5_5_8_2_8_2_8_1_1_6_1_3_9_3_1_8_5_3_1_9_5_9_10_8_6_4_5_1_7_7_7_6_10_7_4_2_1_1_8_2_5_5_1_3_6_6_6_5_5_1_1_4_5_5_9_8_1_8_7_3_3_5_2_7_8_7_11_4_10_4_1_2_5_1_2_4_4_5_3_7_8_1_1_9_3_1_3_3_3_9_4_11_11_6_10_10_4_7_7_5_5_8_7_2_5_5_2_5_4_4_1_8_5_1_6_2_10_5_11_3_2_3_8_2_2_6_10_8_3_4_1_3_6_7_6_8_5_8_6_8_7_7_7_5_8_9_8_5_6_10_8_6_3_5_6_1_5_10_3_11_5_8_10_10_1_4_8_4_4_6_1_5_3_8_1_3_2_2_7_8_5_10_10_10_5_4_10_4_1_10_4_1_10_5_10_1_7_7_7_7_7_6_5_11_11_7_6_2_5_5_3_3_4_1_9_8_1_1_1_2_6_2_4_9_2_8_8_10_10_10_8_5_1_1_2_7_7_7_11_4_6_6_8_10_5_6_1_8_2_6_3_1_3_8_3_4_3_4_1_5_8_3_10_4_1_10_2_5_7_1_2_8_3_5_1_1_2_9_9_5_4_2_2_10_7_8_5_5_8_8_1_5_8_8_9_5_5_6_4_6_4_3_3_7_7_8_10_7</t>
+  </si>
+  <si>
+    <t>3_5_4_5_7_5_3_3_11_1_2_11_3_10_3_9_6_11_2_7_8_11_3_1_9_11_4_1_3_1_4_5_8_4_9_8_5_3_9_9_2_1_6_5_4_9_9_11_4_3_7_2_10_3_3_5_10_2_5_10_4_9_5_3_1_10_2_3_2_6_7_8_1_11_2_7_3_8_10_1_6_11_2_6_4_9_8_11_3_6_6_4_11_3_3_7_2_1_3_10_4_8_9_1_8_11_2_9_1_10_4_8_10_3_8_7_2_7_4_5_11_3_3_5_2_7_11_3_5_3_5_6_2_1_8_6_8_9_10_2_8_7_7_10_3_10_2_10_2_4_7_5_9_1_3_2_1_4_11_1_6_6_9_7_7_1_7_10_4_4_9_10_3_10_4_1_1_6_2_4_4_8_3_7_1_10_3_9_3_4_7_2_7_2_1_11_2_8_9_10_3_1_3_4_10_4_3_8_10_4_8_5_9_1_11_1_6_2_8_3_1_2_2_9_3_7_4_2_3_11_2_8_11_3_3_4_1_9_1_7_3_3_10_3_8_5_10_3_5_10_2_9_4_8_3_5_4_1_3_8_2_5_8_7_9_4_1_10_2_10_4_6_10_3_11_2_8_1_1_10_3_1_1_3_10_3_4_9_2_9_7_11_3_11_3_1_4_2_2_3_1_2_1_7_4_2_11_3_2_1_3_3_9_1_4_9_2_5_10_1_2_2_4_9_9_4_6_10_3_2_1_6_3_8_2_6_3_1_10_4_1_2_1_10_2_7_5_5_11_4_5_7_1_4_2_3_4_1_2_10_2_9_6_8_5_1_6_3_9_10_4_10_3_5_10_3_10_3_11_3_11_2_7_10_3_6_8_6_2_7_9_3_9_6_8_9_5_4_8_11_3_10_3_11_3_7_7_5_8_5_3_10_3_8_7_8_2_6_4_8_6_1_9_6_6_4_8_4_4_11_3_7_3_7_10_1_4_11_3_5_9_10_3_2_3_11_4_1_3_8_8_11_4_5_2_5_2_6_8_4_3_2_11_3_4_7_1_2_11_4_11_4_3_6_9_3_6_4_1_6_5_3_8_10_2_5_5_9_7_9_8_3_9_6_7_9_9_6_5_4</t>
+  </si>
+  <si>
+    <t>3_7_7_7_7_11_11_1_3_2_10_7_5_2_5_1_3_5_9_1_9_5_5_3_9_5_5_8_11_11_10_7_1_11_4_1_9_6_4_7_2_1_11_7_2_2_11_2_1_2_7_7_7_7_2_4_8_4_2_3_3_2_3_8_2_8_8_8_1_1_10_11_10_10_1_11_1_2_10_10_9_3_2_11_1_3_8_8_8_4_6_1_1_3_3_9_3_2_9_7_3_7_3_5_4_8_3_4_8_2_8_8_5_8_2_3_5_1_1_2_6_7_1_1_11_10_7_2_2_1_7_8_5_2_3_6_1_8_10_7_4_4_5_3_3_3_8_8_9_3_6_11_6_1_7_11_3_6_10_9_4_1_7_6_5_3_1_2_2_4_2_5_9_9_1_6_6_10_3_1_3_1_3_8_11_7_4_3_3_2_6_1_5_4_2_6_1_4_5_6_3_3_11_10_2_7_2_5_3_7_6_3_1_2_3_1_8_2_10_10_10_1_4_4_5_2_9_3_6_5_3_9_6_5_3_2_2_2_2_3_7_1_7_9_3_2_3_7_5_4_2_6_7_9_4_6_10_1_7_2_3_3_7_11_8_8_1_7_4_3_1_1_10_7_7_7_8_4_5_5_1_1_7_7_1_1_2_3_8_4_4_10_2_10_10_3_6_6_6_1_2_2_3_2_2_5_3_3_5_3_8_3_8_3_3_10_1_4_5_11_11_2_9_7_4_11_3_7_3_2_1_2_2_7_7_2_2_4_3_2_3_3_2_7_4_7_7_5_5_3_2_2_3_8_1_11_6_10_2_4_9_6_6_7_1_3_2_5_9_8_8_1_1_1_4_3_3_4_5_4_1_6_2_7_7_1_10_10_5_2_5_8_9_5_3_8_5_3_3_4_4_7_5_1_1_1_5_9_7_2_2_1_4_10_4_4_2_8_7_5_3_1_2_5_7_7_3_8_8_8_1_10_10_1_1_2_6_3_3_1_4_3_3_10_3_5_7_8_4_3_4_8_7_1_7_7_3_2_2_2_4_9_9_1_1_2_3_5_7_5_3_7_2_5_8_8_2_1_1_8_6_2_6_3_1_11_2_8_6_2_2_4_10_11_11_7_2_3_2_2</t>
+  </si>
+  <si>
+    <t>3_10_3_6_4_2_11_2_5_7_8_11_4_10_4_2_9_9_10_3_11_3_8_1_7_4_4_5_7_11_2_2_6_11_1_4_3_10_3_6_9_6_9_11_3_11_2_4_9_2_4_11_2_9_7_8_5_3_5_10_4_7_3_8_9_7_1_1_2_2_11_4_4_8_9_3_8_8_3_10_4_8_6_1_9_3_1_1_7_6_7_3_11_2_1_10_4_6_1_2_1_2_2_3_7_2_10_2_1_4_2_6_3_1_10_4_8_10_2_6_1_5_5_11_3_5_3_9_5_11_1_10_4_8_11_3_1_5_6_5_9_4_2_6_6_11_4_8_4_5_3_11_3_2_6_1_7_10_2_8_6_10_3_1_10_4_11_4_6_5_7_9_7_5_1_2_4_3_1_4_2_9_3_7_6_1_9_4_11_2_10_4_9_11_2_6_2_2_6_2_1_6_9_1_3_8_2_11_3_4_9_5_7_7_4_8_8_3_2_7_3_11_1_4_6_5_11_4_9_6_9_8_9_4_9_2_1_9_2_3_4_4_11_2_10_4_4_6_5_6_7_4_1_8_2_9_2_1_5_10_2_4_10_2_3_7_5_8_5_10_3_1_9_8_5_11_2_9_10_2_5_9_9_7_8_5_8_7_9_8_10_2_3_5_5_8_1_11_3_9_6_5_10_3_4_11_4_1_4_7_5_6_4_4_7_6_8_7_6_11_3_5_10_3_5_6_5_10_4_1_6_8_9_5_2_3_8_1_4_5_9_7_4_2_10_4_3_8_6_7_4_4_8_5_6_4_3_2_3_2_2_11_1_9_1_10_2_11_3_10_1_7_11_4_6_3_6_9_2_8_7_3_3_6_10_2_11_2_6_11_2_5_7_3_6_6_3_11_2_7_7_4_4_9_2_11_4_3_11_2_10_4_9_3_7_7_8_1_4_5_7_5_6_4_4_6_9_6_8_11_3_7_2_8_8_4_6_3_11_4_1_10_4_1_11_4_10_3_3_4_9_6_4_3_4_11_3_1_2_10_4_9_4_11_3_11_2_6_11_4_6_11_1_1_4_11_3_8_8_7_3_9_1_6_9_1_9_11_4_10_1_3_4_6_11_3_9_9_5_5</t>
+  </si>
+  <si>
+    <t>3_2_5_3_7_1_11_11_11_7_2_4_6_3_6_5_4_3_3_1_6_5_5_4_2_3_3_7_2_9_8_8_5_1_1_6_6_3_5_8_1_8_8_2_7_3_11_7_11_3_2_2_1_2_2_5_5_11_1_7_10_6_1_1_7_2_10_3_1_2_3_7_4_5_8_11_5_1_1_2_2_3_1_6_8_9_1_6_6_1_9_1_4_7_3_3_3_2_1_3_9_3_6_8_3_5_2_2_2_11_5_1_10_4_6_5_4_9_1_9_2_2_3_4_5_6_1_5_7_5_7_5_9_3_4_3_5_5_2_2_5_5_9_2_3_1_4_6_10_5_2_4_1_4_3_11_11_2_8_7_7_6_5_5_3_4_4_8_4_8_2_6_7_10_6_5_2_2_5_3_2_2_11_7_7_7_6_1_3_8_3_5_4_11_9_9_5_10_3_7_4_4_9_9_8_1_4_1_1_9_7_7_7_1_8_8_8_6_1_1_2_1_5_5_3_3_2_4_10_4_4_6_10_10_1_2_2_10_9_2_5_4_1_11_8_2_8_3_10_3_5_5_5_7_3_6_6_5_2_1_2_7_9_5_9_9_4_4_7_3_9_1_9_2_3_4_4_8_7_1_1_3_6_2_3_4_4_2_11_5_5_4_7_1_7_7_3_1_3_5_3_9_1_4_4_4_2_6_3_11_7_7_7_1_7_6_6_6_6_10_2_6_6_6_7_3_10_6_3_2_11_6_2_5_6_2_5_7_6_11_9_7_1_1_1_4_5_10_1_2_9_3_5_2_4_1_1_8_1_5_5_4_7_6_2_9_5_2_3_10_5_4_5_2_6_4_9_10_10_6_9_2_2_3_9_6_7_2_5_4_4_7_3_1_4_3_8_3_6_9_5_3_6_3_9_9_5_5_4_2_5_3_2_8_5_8_7_5_3_10_7_2_10_4_2_8_8_8_10_7_3_1_3_2_2_3_8_4_4_4_7_8_8_7_6_6_2_2_5_10_8_7_7_2_5_7_1_5_1_3_10_3_2_2_2_3_5_3_3_2_5_2_5_6_6_8_8_4_5_11_11_7_1_6_6_4_6_7_1_4_8_9_2_3_2_3_4_4_7_8</t>
+  </si>
+  <si>
+    <t>2_10_4_5_4_11_1_4_11_3_5_7_9_8_10_3_9_2_11_1_1_3_4_10_1_2_1_3_4_2_2_4_10_1_5_4_3_6_3_6_7_5_6_1_5_9_5_9_5_6_4_4_1_3_2_1_8_3_1_2_10_3_1_8_10_3_9_10_3_1_3_4_4_11_1_11_2_2_7_3_6_8_9_4_2_6_7_4_1_11_4_4_9_1_5_11_4_4_3_4_6_2_8_3_8_11_3_11_1_6_1_11_3_10_1_2_2_1_5_1_6_4_6_6_9_3_3_8_11_4_9_2_9_10_3_2_10_3_4_7_4_8_9_7_8_7_6_5_9_9_3_5_2_11_4_10_4_10_3_11_2_3_2_9_6_10_4_6_10_3_2_6_8_6_6_3_11_4_1_7_1_6_6_1_7_6_6_3_5_6_11_3_6_5_11_4_6_5_8_11_1_1_11_4_2_6_5_3_9_5_2_7_1_9_11_4_3_2_6_8_3_2_9_1_6_2_7_7_7_4_5_1_2_1_1_7_1_5_8_8_6_11_2_6_3_10_2_7_8_2_11_3_1_9_2_11_4_3_11_2_11_4_3_5_6_5_1_8_11_2_1_5_1_2_7_9_6_9_10_2_4_8_9_1_8_11_4_6_10_2_2_8_8_6_9_7_5_7_4_10_4_1_3_6_4_9_8_8_9_3_11_1_10_1_3_9_10_2_2_4_5_3_5_6_10_3_4_3_3_1_10_3_6_5_3_10_2_1_5_7_5_2_11_3_2_5_1_4_5_11_4_1_9_1_4_7_11_3_3_3_7_9_1_11_4_5_4_10_2_8_5_9_8_11_3_1_6_4_4_6_2_5_1_10_3_7_3_9_2_5_4_4_6_2_11_3_8_10_2_7_3_10_2_2_2_4_11_3_10_3_5_4_9_3_3_6_1_10_2_5_1_11_2_11_4_2_10_4_10_4_1_4_7_3_4_4_5_1_9_4_8_1_11_4_6_8_2_10_3_4_1_3_1_1_8_2_1_10_4_5_7_4_6_5_9_3_3_5_11_3_10_3_4_10_3_1_5_4_10_2_6_9_3_1_10_3_6_6_2_6_4_9_2_6_8_10_3_4_8_2</t>
+  </si>
+  <si>
+    <t>2_3_2_2_3_7_2_1_2_9_9_9_1_2_8_8_6_5_3_4_8_2_8_5_7_8_4_2_2_2_2_2_7_5_5_5_3_8_1_6_10_2_8_9_5_3_2_8_8_3_1_1_4_6_4_6_6_1_3_9_1_3_4_4_4_2_7_2_10_4_8_1_2_11_3_7_7_8_1_3_7_9_2_3_3_6_6_2_2_7_9_5_6_9_1_9_3_8_1_10_2_10_4_5_6_5_1_2_2_2_5_1_10_3_2_11_11_5_1_3_5_10_4_2_7_7_6_6_5_10_4_11_4_1_1_5_1_9_3_10_8_3_2_9_3_1_4_1_3_3_2_4_4_10_10_6_6_7_4_10_4_7_1_5_9_10_4_1_5_7_4_10_8_3_10_5_2_5_5_9_4_2_2_9_5_2_2_6_6_6_2_2_10_3_4_5_5_10_11_3_5_7_3_3_9_1_5_3_4_8_2_2_6_2_2_2_2_10_5_6_4_3_7_6_6_6_2_2_9_2_2_2_5_8_10_7_11_3_4_2_2_2_2_2_1_1_4_3_1_10_5_3_4_9_3_4_9_5_11_11_8_4_5_9_7_6_3_6_2_6_4_9_9_3_8_8_9_6_4_3_4_4_4_10_4_5_11_6_10_3_1_6_11_7_8_4_3_7_2_2_3_4_7_9_1_1_7_7_4_11_1_1_11_11_2_5_1_1_8_1_2_3_1_8_5_4_8_6_7_3_9_9_5_8_2_7_4_4_4_3_2_3_8_10_5_1_6_1_3_6_5_10_6_10_10_3_6_6_6_5_5_1_10_10_3_1_2_6_6_10_7_7_3_1_9_3_3_2_5_8_7_7_2_9_4_4_10_1_3_1_3_3_7_8_5_8_8_4_10_5_2_6_4_4_1_2_1_9_3_9_9_2_5_6_9_10_6_7_8_2_9_2_3_3_5_7_7_1_4_9_9_7_2_7_10_10_3_1_11_6_10_10_10_1_5_6_5_2_5_2_2_4_4_3_6_2_9_7_1_1_8_4_1_1_9_9_1_3_5_2_2_9_1_4_4_1_1_1_9_4_7_2_2_7_6_1_2_2_9_6_4_6_7_1_1_9_1_11_5_4</t>
+  </si>
+  <si>
+    <t>4_9_8_6_3_3_10_3_5_4_2_5_1_1_8_1_7_3_6_8_1_3_7_9_10_4_4_5_4_5_3_1_4_3_9_6_8_8_1_2_4_10_2_5_8_7_11_1_7_9_8_9_3_5_8_5_10_4_1_8_9_9_3_6_7_11_4_8_10_2_9_3_10_4_5_3_10_3_5_7_3_11_3_4_5_8_5_10_3_9_10_4_7_10_3_2_6_7_2_1_1_7_8_6_7_3_8_9_3_1_5_1_5_3_5_4_6_9_8_6_9_3_7_1_9_7_5_7_10_4_7_2_5_2_9_2_11_2_11_3_3_5_8_5_8_1_2_5_5_7_1_7_7_8_1_9_4_11_3_11_2_11_4_4_10_3_6_7_3_6_10_2_10_2_8_1_2_5_8_1_8_4_3_6_7_9_4_8_3_7_9_11_3_4_7_10_1_2_3_6_4_5_11_3_10_4_8_7_1_6_10_3_6_6_2_10_3_1_3_1_11_3_10_3_3_11_4_7_2_9_9_7_2_3_4_7_5_6_3_6_5_6_6_3_4_11_3_5_10_1_9_2_3_8_1_10_4_9_8_4_10_4_9_2_6_10_4_7_5_1_5_4_11_2_2_6_4_7_4_8_5_3_9_7_3_8_8_2_5_1_7_3_2_11_4_5_3_10_2_3_2_9_6_4_3_2_11_4_10_3_2_9_10_1_4_11_3_3_6_4_4_4_9_6_1_8_4_2_4_2_6_6_8_8_5_10_3_3_6_2_3_6_8_8_1_10_4_6_3_1_10_2_6_6_7_1_11_3_6_7_7_8_7_1_6_8_3_6_11_3_6_1_11_3_5_6_5_10_2_10_2_11_4_4_1_3_6_11_3_8_1_1_3_10_4_5_5_9_1_9_6_7_7_5_11_3_11_4_9_4_6_2_3_1_8_11_3_9_3_3_1_6_1_5_6_4_3_6_8_8_11_3_2_7_10_4_10_2_6_4_1_10_4_2_5_4_7_3_11_3_4_10_3_10_3_1_9_2_2_7_3_11_2_1_8_4_1_3_10_4_2_7_2_7_9_6_5_6_10_3_9_3_2_5_9_4_11_2_1_9_6_9_6_7_11_2_8_5_4_3</t>
+  </si>
+  <si>
+    <t>9_9_4_2_5_11_2_3_3_10_7_7_9_11_1_1_4_6_3_3_5_2_9_11_4_9_9_1_6_2_5_1_3_8_5_5_9_9_4_9_10_4_9_2_2_4_3_9_7_7_11_11_7_5_2_1_1_7_8_2_2_10_2_10_7_2_2_1_8_5_6_6_3_11_8_5_5_11_2_2_1_5_2_2_5_5_5_9_3_3_3_4_6_11_7_2_10_8_8_7_8_6_7_4_5_4_3_3_2_4_2_2_3_5_1_1_3_9_3_8_3_9_5_5_1_10_4_3_8_1_10_3_3_9_4_10_10_11_1_5_1_2_8_8_7_3_7_9_8_10_1_2_5_8_7_7_2_2_11_3_2_5_3_3_7_7_2_1_9_4_3_5_5_11_3_2_4_6_4_4_4_11_1_5_4_8_5_11_7_5_5_8_5_5_5_1_11_11_5_7_7_6_7_3_1_2_2_5_5_2_8_9_8_4_4_9_2_1_6_10_10_8_8_8_2_2_5_3_10_1_1_8_4_2_6_5_5_7_3_9_4_2_6_7_3_3_3_7_3_1_5_11_2_4_7_3_6_3_9_6_9_4_1_5_1_1_8_1_9_5_5_7_8_4_2_2_9_4_4_11_7_2_9_6_8_2_4_10_10_10_6_2_7_5_3_6_5_6_8_8_3_9_5_5_6_6_5_2_1_7_7_7_5_3_9_5_5_7_4_2_6_8_4_2_6_5_6_7_5_5_1_10_3_7_5_6_8_9_11_8_10_10_10_6_6_10_10_9_9_10_10_5_2_3_3_4_4_2_1_6_5_7_4_3_6_1_8_5_1_8_3_4_9_1_7_7_1_11_7_10_1_10_6_10_4_5_7_1_4_9_3_3_4_4_4_3_11_4_4_4_9_4_2_6_7_5_3_6_1_5_5_5_4_1_3_3_2_5_6_1_8_8_4_1_2_2_5_5_3_3_6_6_2_6_8_5_1_1_3_3_5_9_6_9_6_8_10_8_3_9_5_9_3_7_4_7_8_3_1_3_1_1_3_6_1_8_2_4_7_7_1_7_6_6_6_6_6_8_2_9_2_7_1_2_2_3_7_6_8_8_10_2_5_6_5_4_4_4_3_9</t>
+  </si>
+  <si>
+    <t>11_3_5_9_2_5_8_8_8_4_1_2_7_10_2_2_1_6_11_1_11_3_11_4_10_4_6_3_3_2_1_3_5_11_1_10_3_10_2_6_8_8_2_2_4_8_7_1_8_7_3_9_11_4_10_1_5_2_11_3_3_10_2_1_2_11_2_5_4_3_4_5_1_7_9_11_4_1_2_5_3_5_6_8_6_6_4_5_8_8_3_9_4_9_1_11_1_8_7_3_8_6_8_11_3_10_3_7_2_1_7_5_5_10_3_4_5_3_4_7_2_5_9_10_3_11_1_11_4_11_2_10_3_6_11_3_11_2_2_2_5_10_4_10_3_4_10_3_6_6_1_9_11_3_7_7_7_8_6_4_5_6_1_9_10_3_10_3_4_5_9_3_8_1_6_4_5_9_5_1_7_4_8_8_1_5_4_2_10_4_10_2_2_9_9_1_1_7_10_4_7_1_1_4_7_9_8_6_6_10_1_11_2_5_1_2_8_7_10_3_7_5_2_2_1_5_5_6_9_2_7_9_3_7_9_9_10_3_8_7_9_1_8_5_5_6_3_3_1_7_1_1_8_11_3_5_11_2_11_3_6_5_2_9_10_4_8_3_1_2_11_3_11_4_10_4_3_9_1_4_11_2_11_3_10_2_7_1_7_5_6_8_7_7_5_3_10_3_10_3_7_9_3_7_11_2_1_10_3_11_4_2_11_2_6_11_2_3_1_1_7_8_11_3_1_10_2_7_11_3_7_10_1_5_4_8_4_5_10_2_6_9_2_4_10_3_6_8_3_8_8_4_4_10_3_7_6_10_2_9_7_5_4_8_8_5_2_4_9_8_3_10_2_1_1_1_3_10_2_7_3_6_5_5_7_10_3_10_2_7_1_5_2_4_4_2_9_9_6_7_6_5_3_2_6_7_8_7_10_2_5_7_3_7_4_10_1_4_6_3_10_2_7_9_3_4_6_11_1_11_1_2_10_2_3_11_4_11_2_11_2_4_11_3_8_10_3_6_7_10_3_3_2_8_2_5_1_5_7_1_10_3_10_1_5_1_8_2_8_3_1_9_6_7_1_2_8_9_8_7_5_11_3_7_10_2_5_8_4_8_5_8_4_8_8_9_3_8_4_1</t>
+  </si>
+  <si>
+    <t>5_1_10_10_6_2_7_3_2_8_8_8_2_2_7_1_8_8_11_8_7_1_4_3_6_6_3_9_6_5_4_1_7_6_5_7_8_1_3_10_1_2_3_3_5_2_2_2_3_3_2_10_3_3_8_1_5_5_6_2_9_11_2_3_5_11_10_5_8_3_3_3_3_8_4_1_5_1_4_10_8_3_9_9_4_4_4_5_9_3_10_9_5_10_10_3_2_2_4_4_10_2_2_2_7_6_2_1_5_7_9_2_5_2_11_5_8_9_6_6_1_4_2_7_10_5_1_8_2_7_2_6_4_3_2_1_7_7_2_4_5_9_5_7_9_3_3_9_6_9_7_2_2_3_3_1_5_5_7_2_2_3_3_3_3_7_3_6_5_4_5_5_4_10_3_1_1_9_1_3_3_3_6_6_5_3_7_7_2_4_9_2_2_4_1_1_3_4_1_4_1_5_1_3_2_2_2_5_5_5_7_11_6_3_1_2_3_7_2_7_1_3_7_5_7_3_3_3_9_11_1_4_11_4_11_4_6_7_1_5_5_2_8_8_3_3_10_1_2_6_7_3_1_3_8_2_6_8_5_4_5_4_1_1_2_3_1_10_10_4_4_6_9_9_5_11_5_6_9_7_5_1_1_3_3_3_2_3_5_4_5_4_10_8_7_5_2_3_4_2_2_9_2_8_1_5_4_7_7_1_9_3_3_6_6_3_1_3_6_3_7_9_5_1_6_1_4_5_10_10_5_4_1_7_8_9_4_3_1_1_1_2_7_6_3_5_5_6_8_6_5_3_1_1_10_10_6_2_1_8_7_4_5_5_2_6_1_9_7_3_6_3_2_4_6_9_11_5_3_3_7_5_8_10_1_4_4_2_5_7_10_3_3_7_6_8_8_7_6_5_1_7_9_9_5_1_1_4_2_5_1_7_7_6_11_5_6_1_5_3_5_1_6_2_5_4_2_6_6_11_6_2_10_4_11_9_9_9_7_5_10_3_5_5_8_9_9_11_10_11_6_6_7_10_3_3_5_5_11_3_3_1_4_8_9_4_5_2_2_8_7_1_3_4_4_7_3_3_2_9_7_7_9_5_4_6_11_5_5_9_7_6_2_5_5_2_5_3_3_7</t>
+  </si>
+  <si>
+    <t>9_7_9_3_10_2_6_3_7_3_8_5_7_7_4_5_7_3_7_2_8_1_2_2_3_8_4_8_1_3_6_5_3_11_3_2_11_4_10_3_7_5_3_3_3_1_8_8_1_6_8_11_2_6_11_4_11_2_4_3_9_2_10_4_5_2_5_7_10_3_8_6_6_3_8_1_1_6_5_8_6_4_3_6_10_3_3_1_9_9_11_3_11_4_1_3_8_1_11_3_7_9_9_6_2_3_5_3_10_3_3_1_2_7_5_8_3_5_9_6_2_7_9_10_1_1_2_5_11_1_11_1_8_2_11_3_10_3_5_7_6_10_3_9_3_5_1_9_7_1_1_8_7_7_5_11_3_5_3_11_2_7_10_4_10_3_8_1_1_11_2_2_11_3_8_5_7_8_4_11_3_9_7_3_3_2_2_9_7_7_3_11_3_4_6_9_5_11_2_7_8_2_3_9_10_1_4_9_11_3_10_3_7_6_5_5_4_4_7_3_8_6_9_5_1_11_3_6_11_2_7_2_1_5_3_4_2_7_1_2_1_9_2_5_1_2_3_1_9_2_1_4_11_3_10_3_3_10_4_2_7_4_7_3_11_4_1_8_8_4_10_3_7_2_6_4_10_2_7_10_3_2_8_8_10_2_5_7_1_11_3_11_3_8_2_2_4_1_6_10_1_2_9_1_2_8_7_1_1_9_10_4_7_8_3_4_3_9_5_3_5_6_8_11_2_3_6_1_6_4_1_9_8_10_1_2_4_10_3_11_3_9_9_5_6_11_2_7_1_5_7_5_4_1_6_6_4_8_2_7_6_7_3_8_8_2_10_3_10_3_11_2_5_4_7_8_8_3_11_4_10_3_2_10_4_10_3_6_8_9_1_9_3_5_2_10_1_5_10_4_6_3_11_4_7_4_4_10_3_2_10_3_1_8_8_5_4_5_1_7_7_1_3_5_7_10_2_6_6_2_10_2_1_4_10_4_2_2_1_6_11_1_9_4_7_8_5_7_10_3_11_2_10_4_4_8_7_8_5_11_4_6_5_9_6_1_4_10_4_6_4_10_4_7_2_4_8_7_9_2_2_11_2_7_2_4_4_7_10_2_6_4_11_2_5_4_1_8_3_1</t>
   </si>
 </sst>
 </file>
@@ -2597,7 +2675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K303"/>
+  <dimension ref="A1:K309"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -8764,13 +8842,13 @@
     <row r="200" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A200" s="5">
         <f t="shared" si="8"/>
-        <v>20160022</v>
+        <v>20160012</v>
       </c>
       <c r="B200" s="6">
         <v>101600</v>
       </c>
       <c r="C200" s="34">
-        <v>2016002</v>
+        <v>2016001</v>
       </c>
       <c r="D200" s="34">
         <v>2</v>
@@ -8795,13 +8873,13 @@
     <row r="201" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A201" s="5">
         <f t="shared" si="8"/>
-        <v>20160033</v>
+        <v>20160013</v>
       </c>
       <c r="B201" s="6">
         <v>101600</v>
       </c>
       <c r="C201" s="34">
-        <v>2016003</v>
+        <v>2016001</v>
       </c>
       <c r="D201" s="34">
         <v>3</v>
@@ -8826,13 +8904,13 @@
     <row r="202" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A202" s="5">
         <f t="shared" si="8"/>
-        <v>20160044</v>
+        <v>20160014</v>
       </c>
       <c r="B202" s="6">
         <v>101600</v>
       </c>
       <c r="C202" s="34">
-        <v>2016004</v>
+        <v>2016001</v>
       </c>
       <c r="D202" s="34">
         <v>4</v>
@@ -8857,13 +8935,13 @@
     <row r="203" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A203" s="5">
         <f t="shared" si="8"/>
-        <v>20160055</v>
+        <v>20160015</v>
       </c>
       <c r="B203" s="6">
         <v>101600</v>
       </c>
       <c r="C203" s="34">
-        <v>2016005</v>
+        <v>2016001</v>
       </c>
       <c r="D203" s="34">
         <v>5</v>
@@ -8888,13 +8966,13 @@
     <row r="204" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A204" s="5">
         <f t="shared" si="8"/>
-        <v>20160066</v>
+        <v>20160016</v>
       </c>
       <c r="B204" s="6">
         <v>101600</v>
       </c>
       <c r="C204" s="34">
-        <v>2016006</v>
+        <v>2016001</v>
       </c>
       <c r="D204" s="34">
         <v>6</v>
@@ -10565,13 +10643,13 @@
         <v>20</v>
       </c>
       <c r="G258" s="7" t="s">
-        <v>45</v>
+        <v>362</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>46</v>
+        <v>362</v>
       </c>
       <c r="J258" s="38"/>
       <c r="K258" s="38"/>
@@ -10596,13 +10674,13 @@
         <v>20</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>48</v>
+        <v>363</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>49</v>
+        <v>363</v>
       </c>
       <c r="J259" s="38"/>
       <c r="K259" s="38"/>
@@ -10627,13 +10705,13 @@
         <v>20</v>
       </c>
       <c r="G260" s="7" t="s">
-        <v>51</v>
+        <v>364</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>52</v>
+        <v>364</v>
       </c>
       <c r="J260" s="38"/>
       <c r="K260" s="38"/>
@@ -10658,13 +10736,13 @@
         <v>20</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>54</v>
+        <v>365</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>55</v>
+        <v>365</v>
       </c>
       <c r="J261" s="38"/>
       <c r="K261" s="38"/>
@@ -10689,13 +10767,13 @@
         <v>20</v>
       </c>
       <c r="G262" s="7" t="s">
-        <v>57</v>
+        <v>366</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>58</v>
+        <v>366</v>
       </c>
       <c r="J262" s="38"/>
       <c r="K262" s="38"/>
@@ -10720,13 +10798,13 @@
         <v>20</v>
       </c>
       <c r="G263" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I263" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K263" s="9"/>
     </row>
@@ -10750,13 +10828,13 @@
         <v>20</v>
       </c>
       <c r="G264" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I264" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K264" s="9"/>
     </row>
@@ -10780,13 +10858,13 @@
         <v>20</v>
       </c>
       <c r="G265" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I265" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K265" s="9"/>
     </row>
@@ -10810,13 +10888,13 @@
         <v>20</v>
       </c>
       <c r="G266" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I266" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K266" s="9"/>
     </row>
@@ -10840,13 +10918,13 @@
         <v>20</v>
       </c>
       <c r="G267" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I267" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K267" s="9"/>
     </row>
@@ -10870,13 +10948,13 @@
         <v>20</v>
       </c>
       <c r="G268" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I268" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K268" s="9"/>
     </row>
@@ -10894,19 +10972,19 @@
         <v>1</v>
       </c>
       <c r="E269" s="19" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G269" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I269" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J269" s="33"/>
       <c r="K269" s="33"/>
@@ -10925,19 +11003,19 @@
         <v>2</v>
       </c>
       <c r="E270" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G270" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I270" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="J270" s="33"/>
       <c r="K270" s="33"/>
@@ -10956,19 +11034,19 @@
         <v>3</v>
       </c>
       <c r="E271" s="19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G271" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I271" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="J271" s="33"/>
       <c r="K271" s="33"/>
@@ -10987,19 +11065,19 @@
         <v>4</v>
       </c>
       <c r="E272" s="19" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G272" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I272" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="J272" s="33"/>
       <c r="K272" s="33"/>
@@ -11018,19 +11096,19 @@
         <v>5</v>
       </c>
       <c r="E273" s="19" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G273" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I273" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="J273" s="33"/>
       <c r="K273" s="33"/>
@@ -11049,19 +11127,19 @@
         <v>6</v>
       </c>
       <c r="E274" s="19" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G274" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I274" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="J274" s="33"/>
       <c r="K274" s="33"/>
@@ -11080,19 +11158,19 @@
         <v>7</v>
       </c>
       <c r="E275" s="19" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="F275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I275" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="J275" s="33"/>
       <c r="K275" s="33"/>
@@ -11117,13 +11195,13 @@
         <v>20</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="J276" s="33"/>
     </row>
@@ -11147,13 +11225,13 @@
         <v>20</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="J277" s="33"/>
     </row>
@@ -11177,13 +11255,13 @@
         <v>20</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="J278" s="33"/>
     </row>
@@ -11201,19 +11279,19 @@
         <v>4</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="J279" s="33"/>
     </row>
@@ -11237,13 +11315,13 @@
         <v>20</v>
       </c>
       <c r="G280" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I280" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="J280" s="33"/>
       <c r="K280" s="33"/>
@@ -11268,13 +11346,13 @@
         <v>20</v>
       </c>
       <c r="G281" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I281" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="J281" s="33"/>
       <c r="K281" s="33"/>
@@ -11299,13 +11377,13 @@
         <v>20</v>
       </c>
       <c r="G282" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I282" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="J282" s="33"/>
       <c r="K282" s="33"/>
@@ -11330,13 +11408,13 @@
         <v>20</v>
       </c>
       <c r="G283" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I283" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="J283" s="33"/>
       <c r="K283" s="33"/>
@@ -11361,13 +11439,13 @@
         <v>20</v>
       </c>
       <c r="G284" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I284" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="J284" s="33"/>
       <c r="K284" s="33"/>
@@ -11392,13 +11470,13 @@
         <v>20</v>
       </c>
       <c r="G285" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I285" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="J285" s="33"/>
       <c r="K285" s="33"/>
@@ -11423,13 +11501,13 @@
         <v>20</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="J286" s="33"/>
     </row>
@@ -11453,13 +11531,13 @@
         <v>20</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I287" s="5" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="J287" s="33"/>
     </row>
@@ -11483,13 +11561,13 @@
         <v>20</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="J288" s="33"/>
     </row>
@@ -11507,19 +11585,19 @@
         <v>4</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="J289" s="33"/>
     </row>
@@ -11543,13 +11621,13 @@
         <v>20</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I290" s="5" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="J290" s="33"/>
     </row>
@@ -11573,13 +11651,13 @@
         <v>20</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="J291" s="33"/>
     </row>
@@ -11603,13 +11681,13 @@
         <v>20</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I292" s="5" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="J292" s="33"/>
     </row>
@@ -11627,19 +11705,19 @@
         <v>4</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I293" s="5" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="J293" s="33"/>
     </row>
@@ -11657,19 +11735,19 @@
         <v>1</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="F294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G294" s="39" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="H294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I294" s="39" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="J294" s="40"/>
       <c r="K294" s="40"/>
@@ -11688,7 +11766,7 @@
         <v>2</v>
       </c>
       <c r="E295" s="34" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F295" s="35" t="s">
         <v>20</v>
@@ -11719,7 +11797,7 @@
         <v>3</v>
       </c>
       <c r="E296" s="34" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="F296" s="35" t="s">
         <v>20</v>
@@ -11812,19 +11890,19 @@
         <v>1</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="F299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G299" s="39" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="H299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I299" s="39" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="J299" s="40"/>
       <c r="K299" s="40"/>
@@ -11843,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="E300" s="34" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="F300" s="35" t="s">
         <v>20</v>
@@ -11873,7 +11951,7 @@
         <v>3</v>
       </c>
       <c r="E301" s="34" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="F301" s="35" t="s">
         <v>20</v>
@@ -11948,6 +12026,192 @@
         <v>264</v>
       </c>
       <c r="J303" s="41"/>
+    </row>
+    <row r="304" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A304" s="5">
+        <f t="shared" ref="A304:A309" si="10">C304*10+D304</f>
+        <v>20190011</v>
+      </c>
+      <c r="B304" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C304" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D304" s="32">
+        <v>1</v>
+      </c>
+      <c r="E304" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="F304" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G304" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="H304" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I304" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="J304" s="41"/>
+    </row>
+    <row r="305" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A305" s="5">
+        <f t="shared" si="10"/>
+        <v>20190012</v>
+      </c>
+      <c r="B305" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C305" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D305" s="32">
+        <v>2</v>
+      </c>
+      <c r="E305" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="F305" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G305" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="H305" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I305" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="J305" s="41"/>
+    </row>
+    <row r="306" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A306" s="5">
+        <f t="shared" si="10"/>
+        <v>20190013</v>
+      </c>
+      <c r="B306" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C306" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D306" s="32">
+        <v>3</v>
+      </c>
+      <c r="E306" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="F306" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G306" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="H306" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I306" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="J306" s="41"/>
+    </row>
+    <row r="307" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A307" s="5">
+        <f t="shared" si="10"/>
+        <v>20190014</v>
+      </c>
+      <c r="B307" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C307" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D307" s="32">
+        <v>4</v>
+      </c>
+      <c r="E307" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="F307" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G307" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="H307" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I307" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="J307" s="41"/>
+    </row>
+    <row r="308" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A308" s="5">
+        <f t="shared" si="10"/>
+        <v>20190015</v>
+      </c>
+      <c r="B308" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C308" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D308" s="32">
+        <v>5</v>
+      </c>
+      <c r="E308" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="F308" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G308" s="39" t="s">
+        <v>424</v>
+      </c>
+      <c r="H308" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I308" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="J308" s="41"/>
+    </row>
+    <row r="309" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A309" s="5">
+        <f t="shared" si="10"/>
+        <v>20190016</v>
+      </c>
+      <c r="B309" s="31">
+        <v>101900</v>
+      </c>
+      <c r="C309" s="32">
+        <v>2019001</v>
+      </c>
+      <c r="D309" s="32">
+        <v>6</v>
+      </c>
+      <c r="E309" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="F309" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G309" s="39" t="s">
+        <v>426</v>
+      </c>
+      <c r="H309" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I309" s="39" t="s">
+        <v>427</v>
+      </c>
+      <c r="J309" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="450">
   <si>
     <t>id</t>
   </si>
@@ -1167,18 +1167,33 @@
     <t>5_6_2_10_3_8_10_2_10_1_5_2_5_7_8_2_5_8_2_1_1_7_1_2_8_8_8_8_8_4_5_6_3_5_6_4_5_10_4_10_1_6_6_6_10_3_7_8_8_5_9_6_7_2_7_5_7_10_2_7_1_5_9_10_2_6_6_8_2_9_6_5_3_3_9_3_7_1_4_8_10_4_10_4_1_7_5_2_9_5_7_7_5_2_7_2_4_3_2_9_9_6_3_3_7_1_5_8_5_4_8_1_9_9_5_1_3_3_5_7_4_10_2_1_7_2_9_6_3_8_4_5_9_3_7_1_7_3_10_4_1_2_5_3_1_8_5_5_4_6_7_9_8_5_10_1_5_9_7_6_9_6_6_3_6_4_9_1_3_6_3_6_3_10_1_10_3_9_10_4_9_4_9_5_3_6_5_5_8_9_6_8_4_5_5_8_9_6_10_4_2_8_7_8_10_1_1_3_5_1_7_9_10_4_6_3_7_7_3_10_2_7_4_4_10_3_9_7_3_4_1_8_4_10_2_3_4_10_1_9_6_1_9_8_3_5_3_4_1_4_10_3_5_4_9_2_1_9_1_3_2_1_8_2_4_2_1_3_2_7_4_10_2_8_4_1_7_10_3_4_3_7_2_8_7_7_1_9_6_2_5_1_4_6_3_10_2_7_1_8_2_5_5_9_8_3_8_6_1_8_4_8_1_3_1_1_3_1_8_7_1_10_2_10_2_8_4_5_7_10_2_2_9_10_4_3_1_9_7_10_3_5_6_10_1_5_8_7_6_3_4_7_6_1_9_4_4_2_5_7_5_7_1_8_2_6_1_6_10_4_2_10_3_5_8_10_3_4_7_7_10_2_5_1_10_3_7_9_10_2_8_3_6_1_3_1_4_1_1_7_5_2_3_7_9_6_10_3_2_4_3_8_5_1_3_10_3_1_8_2_4_3_5_3_7_4_6_6_8_8_4_9_9_7_8_1_1_2_1_10_1_9_3_10_2_6_7_1_5_9_1_6_1_5_8_10_1_3_2_8_8_4_1_10_1_7_1_9_9_8_10_3_9_5_9_4_4_5_2_9_6_3_3_4_3_10_4_5_9_6_2_3_2_2_8_2_2_1_2_3</t>
   </si>
   <si>
+    <t>7_7_6_7_3_4_5_3_3_1_3_5_5_4_4_4_2_4_4_2_6_6_4_3_1_4_3_1_8_4_1_4_1_5_5_5_1_3_3_6_5_2_2_5_7_1_7_4_4_4_4_6_6_3_5_2_1_1_1_7_8_1_5_5_2_3_4_3_2_7_4_4_1_1_3_6_2_7_2_3_1_6_4_6_6_1_4_4_4_8_5_2_4_4_1_6_5_3_1_7_2_2_2_1_1_1_3_3_3_7_5_1_1_1_3_7_1_5_8_8_8_1_5_3_2_6_3_2_5_6_7_4_4_5_3_3_6_7_5_4_2_2_5_6_1_5_3_1_1_3_1_5_4_5_5_7_2_3_4_4_3_6_1_3_3_3_2_2_1_6_3_5_4_6_1_4_6_3_6_5_1_5_1_7_7_7_1_6_2_2_3_4_4_3_7_2_1_5_5_2_6_8_6_2_2_6_2_1_5_7_3_2_4_9_3_3_6_2_8_2_2_2_3_3_3_4_6_7_1_5_5_5_2_3_1_4_6_8_1_7_2_8_5_5_1_4_4_5_1_1_2_6_3_4_2_3_4_1_7_2_6_1_2_2_3_1_5_5_4_5_1_1_1_8_2_3_5_3_3_3_9_6_2_4_3_4_1_6_1_8_7_2_3_6_7_7_5_2_5_2_3_1_2_7_1_3_1_5_7_7_3_1_2_2_4_5_4_2_2_2_2_2_4_4_2_2_5_6_3_1_6_5_9_7_6_9_6_7_5_3_5_3_5_5_5_8_2_2_5_5_6_6_1_4_1_8_1_4_4_1_6_5_1_8_1_1_1_7_2_2_2_4_4_2_2_6_4_7_3_8_8_6_5_1_5_4_2_2_4_5_5_6_3_5_1_6_4_4_1_2_2_2_2_1_2_7_1_4_2_7_1_2_6_6_1_9_1_1_5_7_2_6_6_5_5_1_5_2_7_2_2_2_3_3_9_9_8_8_1_1_2_7_3_4_4_8_7_2_4_1_3_3_2_3_6_1_1_4_9_1_8_1_3_5_8_3_3_6_4_4_4_7_1_6_6_2_4_1_1_1_4_4_4_2_7_1_1_8_3_9_1_1_6_5_4_2_2_4_1_2</t>
+  </si>
+  <si>
     <t>1_5_2_8_6_4_8_7_3_6_1_3_5_7_5_8_1_1_7_2_4_5_5_4_4_2_1_2_1_4_4_1_2_9_4_6_7_1_2_2_6_2_6_6_3_3_3_6_2_5_8_2_2_4_4_4_3_6_1_2_8_8_6_1_6_2_2_5_5_5_5_7_7_7_2_2_9_9_5_2_2_4_3_3_3_5_7_5_4_4_7_7_7_7_5_6_3_3_3_2_1_1_5_5_5_1_5_3_3_3_4_8_2_3_3_6_6_1_2_2_8_3_1_1_1_1_9_4_2_2_7_5_4_4_9_9_2_5_2_3_1_2_2_2_8_9_2_1_1_2_1_5_2_3_6_2_9_9_6_1_5_5_3_4_5_3_3_3_3_2_3_4_2_9_6_2_1_4_2_8_2_9_2_2_2_4_1_2_6_6_6_6_4_4_8_3_3_5_5_3_4_3_2_2_3_1_1_9_9_4_8_7_8_3_7_7_6_8_8_4_8_1_4_1_1_3_4_2_2_2_5_3_3_4_1_1_4_1_8_9_5_9_5_6_6_1_4_8_1_5_3_6_5_3_4_5_4_4_1_4_8_1_1_5_8_5_2_7_2_6_4_7_7_3_1_8_8_3_3_6_2_5_1_1_3_1_4_6_4_3_4_8_9_3_5_5_9_4_4_1_4_8_6_1_5_2_5_7_3_3_1_6_4_5_7_5_5_2_8_6_2_5_3_3_4_1_2_1_2_2_2_8_4_5_7_2_1_6_6_3_9_6_8_5_2_7_5_1_6_4_4_3_3_1_3_8_9_9_9_5_1_1_1_3_1_4_8_8_1_3_8_2_2_7_5_5_4_3_5_5_4_5_1_2_8_2_8_4_6_6_6_6_3_2_8_7_2_8_6_2_2_8_7_4_2_2_4_3_7_4_5_7_1_5_3_2_2_6_2_2_2_2_7_3_2_3_3_5_1_7_4_4_8_2_2_6_1_1_8_3_4_2_2_4_2_7_1_1_1_3_2_2_3_1_9_2_5_3_2_4_7_2_4_2_8_4_3_3_3_6_5_1_6_1_5_5_1_5_4_9_2_8_4_4_1_8_1_1_8_1_2_6_6_3_4_6_5_9_5_2</t>
   </si>
   <si>
+    <t>3_1_2_4_2_4_2_8_5_2_1_2_7_8_5_4_7_2_8_4_2_5_1_3_4_6_7_4_1_1_1_1_4_4_7_3_6_6_5_4_4_2_2_5_5_2_6_4_4_1_3_6_3_1_6_7_1_8_5_5_1_8_3_4_2_1_8_5_5_5_5_2_3_3_3_3_1_4_9_7_3_6_6_6_6_3_3_1_2_1_4_1_6_2_5_6_5_5_4_3_4_5_5_3_1_5_3_3_3_4_4_5_5_3_3_4_7_2_3_3_1_1_6_4_4_5_4_2_4_2_7_8_8_6_3_4_6_4_4_4_1_1_5_2_5_5_4_2_3_2_1_2_3_3_1_2_5_1_1_2_1_4_6_2_6_5_1_6_6_4_7_2_8_4_4_3_3_3_3_4_6_1_1_6_2_1_1_3_5_6_2_9_4_2_5_8_1_1_2_8_3_1_4_6_7_6_1_6_5_3_1_2_7_2_1_3_2_4_4_6_1_1_2_3_3_5_4_5_1_6_3_4_5_6_2_4_7_2_1_1_2_9_4_1_1_5_3_3_1_4_1_5_2_8_4_7_1_1_8_2_5_2_6_7_2_3_3_2_1_4_3_8_3_3_5_4_2_9_9_4_5_4_1_4_3_7_4_1_2_1_3_2_2_4_3_3_2_4_8_2_6_8_7_1_2_5_5_3_2_2_4_9_3_5_1_8_6_5_3_6_3_9_2_4_4_4_6_6_3_7_7_7_1_1_2_2_2_1_1_1_6_5_5_5_5_6_1_1_1_2_6_9_1_1_5_6_3_3_3_2_2_5_1_1_1_4_4_7_5_5_2_9_5_2_5_5_7_5_6_6_2_2_2_2_8_5_3_5_5_3_2_8_1_2_1_5_1_1_1_1_1_5_2_3_3_6_5_3_2_2_4_1_1_4_1_2_5_5_7_5_7_7_7_7_6_7_6_2_2_3_6_5_2_7_2_2_5_4_1_3_8_8_1_7_2_4_1_1_5_1_6_4_6_6_5_1_2_5_1_1_1_2_4_6_3_1_3_1_2_3_1_3_4_1_1_1_5_4_9_4_5_8_8_8_4_3_4_8_3_6_2_7_2_6_4_5_9_4_3_1</t>
+  </si>
+  <si>
     <t>8_6_6_3_3_1_2_5_5_5_2_2_2_2_1_1_4_2_3_1_1_4_6_4_1_6_2_2_7_6_1_1_1_4_6_3_1_9_7_4_4_3_3_3_1_1_4_2_5_3_3_2_6_5_4_9_1_6_5_2_9_1_3_3_8_9_1_5_3_6_7_3_4_8_1_9_3_3_1_2_4_5_5_1_2_1_2_5_1_7_9_7_4_4_3_3_3_2_7_7_9_7_3_6_4_1_2_6_2_3_3_2_2_6_4_8_8_8_3_1_1_6_3_9_5_4_2_3_6_9_2_2_4_4_6_2_3_8_2_7_8_1_2_7_5_4_8_4_2_5_1_4_7_1_8_1_8_5_5_8_1_7_8_4_6_4_3_4_1_5_7_1_6_8_8_4_2_1_6_1_1_3_3_8_8_8_3_3_3_7_7_4_1_3_7_5_2_2_1_7_2_1_4_2_5_1_6_4_5_4_8_4_5_8_1_1_5_7_2_8_8_6_1_6_5_7_2_1_2_3_2_3_2_3_5_3_2_7_2_2_4_7_4_3_3_7_7_7_8_5_4_6_9_4_5_2_9_9_5_4_4_5_6_2_2_5_4_8_4_5_2_6_6_6_8_5_1_2_1_2_4_2_7_1_4_1_6_9_8_5_3_2_7_1_4_2_9_6_5_2_1_2_2_5_1_3_4_5_5_3_5_3_3_4_4_7_6_5_4_9_5_5_1_2_4_3_3_2_1_2_1_5_1_4_8_3_1_1_5_5_4_2_3_3_1_1_5_4_6_2_6_2_2_2_2_2_2_7_2_5_5_2_2_6_5_1_2_2_2_2_4_4_2_6_7_6_6_7_2_5_1_5_1_4_2_8_8_5_2_8_2_1_1_4_6_2_6_6_2_2_7_2_4_5_4_8_3_1_1_1_4_4_4_6_6_3_3_2_8_9_7_3_4_6_8_8_5_9_4_6_8_1_1_6_4_2_2_2_4_4_3_3_4_7_2_1_4_1_3_2_2_7_6_3_1_4_2_3_7_5_8_8_8_4_1_5_6_1_1_1_4_9_1_1_6_6_1_5_1_3_3_1_6_5_1_1_2_6_6_1_5_7_9_1_8_7_6_1_1_5</t>
   </si>
   <si>
+    <t>7_8_5_4_5_5_8_2_3_1_1_1_7_3_4_9_9_7_2_4_3_1_7_7_4_9_3_1_1_1_6_6_1_2_9_2_7_2_4_1_1_5_3_6_4_2_3_3_2_6_3_2_7_5_2_3_7_6_2_2_5_2_2_3_1_1_1_7_1_4_3_8_2_1_1_2_2_4_1_2_3_3_3_1_1_6_2_6_3_5_5_2_8_2_3_3_6_2_5_6_3_7_7_8_1_1_2_9_2_4_3_3_1_7_2_6_6_3_7_4_7_3_6_8_2_6_1_6_6_2_1_4_2_3_5_9_4_7_3_6_7_4_6_2_7_4_5_6_6_5_9_1_2_7_9_9_9_5_3_3_6_5_5_6_4_2_3_5_3_6_7_7_8_2_3_1_2_5_4_7_3_5_6_3_1_4_1_2_1_4_7_2_9_2_5_5_7_3_3_4_4_2_3_5_1_1_5_6_6_1_6_1_4_4_1_4_4_4_2_5_6_4_4_1_8_6_1_1_7_4_1_7_2_2_8_5_5_5_1_1_4_3_1_1_2_1_1_5_4_5_7_4_6_3_2_2_3_5_2_3_1_9_2_2_7_5_5_6_3_8_3_1_4_6_2_6_1_5_3_5_2_3_2_2_2_3_3_1_8_2_7_2_2_5_2_2_4_2_1_6_2_5_8_7_2_1_3_7_2_2_2_7_4_7_8_1_2_3_7_8_8_7_7_7_3_3_6_4_4_3_2_2_1_2_3_3_5_2_5_5_7_2_2_2_2_4_3_3_7_6_3_2_2_4_5_5_5_3_5_7_1_2_1_7_6_7_7_7_7_2_1_9_4_1_1_2_3_3_5_6_2_5_7_1_5_5_3_2_7_6_2_4_5_6_1_6_2_4_2_3_6_4_4_7_2_5_7_8_6_4_6_6_1_3_1_1_7_3_5_1_1_3_2_7_7_5_8_5_7_2_2_2_1_5_7_7_8_9_9_2_3_6_8_4_9_6_3_1_1_1_1_8_4_4_1_3_5_4_2_5_5_5_6_6_2_4_4_7_4_3_6_2_6_1_6_2_2_6_3_1_8_5_6_1_1_1_3_6_2_5_2_2_7_2_6_4_5_1_4_7</t>
+  </si>
+  <si>
     <t>3_6_5_1_4_3_5_4_1_1_1_1_2_9_4_3_2_6_6_7_4_4_1_5_7_4_1_1_9_5_8_6_5_4_2_6_8_2_5_2_8_1_2_6_6_6_9_2_2_1_1_5_3_1_5_1_7_9_1_2_1_6_5_7_4_2_4_4_3_1_1_3_1_4_4_1_1_1_6_3_2_2_2_1_2_8_8_2_5_7_8_8_3_2_1_3_5_2_5_4_1_9_9_3_2_8_5_2_2_4_4_5_1_2_8_8_8_8_4_1_9_2_2_4_5_1_1_4_8_2_5_5_1_1_4_1_4_1_3_3_2_1_8_1_1_2_6_2_8_8_3_1_3_7_2_2_2_2_1_3_9_5_1_2_2_5_5_3_5_4_5_2_5_5_6_5_4_5_7_5_3_4_2_8_5_5_1_9_8_3_1_7_3_9_9_7_2_5_7_7_1_1_5_2_8_8_5_6_8_2_6_4_2_2_5_5_5_4_2_5_1_8_7_9_7_9_8_8_2_2_9_4_1_2_4_2_2_6_4_6_7_8_1_7_1_8_6_1_1_4_4_8_8_5_8_2_8_4_2_6_2_9_7_5_6_3_7_1_4_3_5_4_4_4_7_1_8_8_3_2_6_8_2_6_1_5_1_3_9_1_3_8_7_2_3_9_4_1_3_8_1_3_9_8_7_1_1_5_4_1_2_4_5_5_9_1_2_4_1_6_8_8_1_6_4_2_6_4_7_8_2_1_9_2_7_1_1_1_9_4_1_1_1_1_1_5_2_2_3_4_8_8_2_2_3_3_3_7_2_1_3_3_3_3_8_8_8_9_5_5_6_4_4_1_8_3_9_1_7_3_2_1_8_8_3_5_5_7_5_2_7_1_7_3_1_5_5_2_4_1_8_8_4_4_7_5_8_3_1_1_1_6_1_9_7_4_6_6_3_1_2_3_3_5_2_9_4_4_4_5_3_2_5_5_5_2_2_3_7_1_7_6_8_6_6_3_3_3_7_2_5_3_9_9_8_1_2_1_5_4_2_2_4_6_4_1_4_7_9_1_4_5_2_4_7_9_5_4_1_3_9_6_6_6_1_7_1_1_1_6_6_6_1_4_3_3_1_6_1_1</t>
   </si>
   <si>
+    <t>4_2_2_3_4_6_2_3_7_5_1_3_3_3_3_2_1_3_9_9_5_4_1_7_5_3_6_4_2_8_6_4_7_3_3_1_5_3_7_2_7_3_3_7_1_3_1_3_2_2_5_2_4_6_5_3_2_4_2_4_1_7_3_8_2_6_8_3_1_6_2_5_1_2_3_2_4_2_9_1_4_2_8_6_3_8_1_1_3_4_9_4_1_5_4_6_4_1_1_8_6_1_7_6_4_6_3_2_2_9_2_5_1_1_1_2_1_6_3_3_1_6_8_9_6_6_2_2_2_2_6_3_6_5_4_2_2_4_3_4_1_1_2_2_1_6_1_7_1_1_1_1_7_7_7_4_5_6_6_5_9_1_6_7_1_3_8_4_4_4_4_3_1_4_7_6_6_4_8_1_3_3_7_6_6_8_3_4_1_1_1_3_9_9_6_5_3_3_3_3_9_6_3_4_2_5_3_5_4_2_5_7_7_1_4_4_5_7_6_5_5_3_3_7_3_4_2_1_3_4_3_3_2_4_8_7_8_4_4_6_4_6_3_1_6_6_4_1_2_7_7_1_1_1_1_2_2_2_4_7_7_3_6_5_3_2_4_4_3_5_5_6_2_8_6_1_1_2_4_6_1_1_1_9_1_3_2_4_2_8_7_1_2_5_1_3_2_5_4_2_5_4_6_2_1_7_6_3_5_6_1_1_7_2_9_3_8_2_3_7_7_3_7_8_4_4_4_6_3_4_7_4_8_3_4_2_2_8_4_5_1_7_2_2_1_3_1_6_3_3_4_4_1_1_1_2_3_4_3_4_2_2_3_3_1_2_2_1_2_5_6_5_2_6_4_9_9_6_2_3_3_2_1_1_2_2_2_2_5_5_5_4_5_5_1_3_6_1_7_4_6_8_1_1_3_2_3_9_9_5_1_1_2_4_1_3_7_5_1_3_2_3_6_2_3_2_7_3_3_3_6_2_2_6_6_1_6_1_2_2_5_5_1_6_5_6_3_3_6_3_3_4_3_1_1_4_3_1_5_1_5_3_3_4_4_1_2_2_5_1_2_9_1_2_7_8_4_4_2_2_2_2_3_6_6_5_8_8_5_8_5_4_4_1_2_1_5_2_1_1</t>
+  </si>
+  <si>
     <t>7_1_4_4_9_9_8_2_6_4_6_4_4_3_4_4_4_6_2_1_8_3_3_2_8_3_7_1_2_5_1_3_3_3_3_3_4_4_4_2_2_5_1_2_4_7_7_1_1_8_8_2_6_2_4_1_6_8_1_7_9_5_6_2_4_7_1_2_1_9_1_8_1_6_9_7_6_6_1_8_2_8_5_2_4_5_8_5_7_2_8_2_1_6_1_1_6_6_4_7_1_7_1_2_2_2_4_6_2_1_1_4_3_7_5_4_3_3_1_3_1_4_7_3_6_5_5_4_4_3_6_9_3_3_8_1_5_4_3_6_7_7_6_1_8_6_6_7_3_1_4_7_2_3_7_4_4_3_7_3_6_7_2_1_4_1_1_1_3_3_7_1_3_2_4_5_4_7_2_2_3_6_2_5_2_8_2_1_6_1_4_7_5_5_2_2_6_2_6_1_1_1_2_1_1_9_7_3_4_9_7_9_4_3_4_4_7_7_7_3_6_7_2_1_1_5_1_8_8_8_5_1_6_6_2_4_3_9_1_6_1_2_3_2_1_1_2_3_2_4_6_2_1_1_6_1_1_3_9_3_2_5_2_1_6_2_5_4_2_9_6_8_8_5_1_3_1_6_9_3_1_1_1_1_2_1_1_4_5_4_4_6_6_2_2_2_7_6_6_6_3_3_3_1_3_5_4_5_2_1_6_1_1_6_6_1_7_7_4_4_7_7_8_1_3_5_8_5_4_1_3_5_7_5_2_1_3_7_7_1_2_2_4_4_5_5_6_6_4_8_8_1_4_7_2_7_1_2_4_2_3_9_2_3_3_1_4_5_1_2_3_4_1_8_4_7_4_7_8_5_6_6_1_6_6_2_6_3_8_2_3_4_1_9_9_3_6_2_5_2_2_5_6_6_7_3_9_1_2_9_1_2_2_6_2_4_4_6_6_6_1_4_9_5_8_3_4_7_3_9_2_8_3_7_3_4_2_4_4_6_1_5_3_3_7_5_7_3_3_7_4_6_6_7_6_1_5_6_8_3_3_3_4_1_4_8_3_2_1_2_4_2_1_4_2_6_9_5_2_3_3_4_8_2_3_1_7_8_2_6_2_4_2_9_1_2_7_9_5_3</t>
   </si>
   <si>
+    <t>2_2_1_1_3_1_2_3_8_6_7_1_1_2_2_6_3_1_6_6_1_4_8_4_4_2_1_5_5_1_4_6_2_6_6_5_7_7_7_4_1_4_1_4_1_2_7_2_2_2_2_2_5_8_8_4_2_8_3_4_1_2_8_4_6_6_1_6_3_2_6_2_1_6_5_6_6_9_1_4_4_6_2_3_1_6_6_7_2_8_4_7_1_4_3_5_4_4_3_1_1_3_3_6_4_3_3_2_3_3_3_4_4_7_3_2_7_3_6_1_2_1_5_2_4_5_4_7_7_7_4_2_1_1_2_2_5_2_5_6_1_7_2_7_4_1_1_3_4_2_4_9_6_7_4_5_4_6_6_1_4_1_1_2_1_6_6_1_6_3_3_8_9_3_1_3_4_6_1_4_7_3_7_2_8_5_2_2_1_1_2_2_6_3_1_3_7_7_2_1_8_8_1_3_1_1_2_4_6_4_3_4_7_8_6_1_1_2_7_2_7_5_5_5_2_5_7_6_1_6_5_5_2_7_3_7_2_4_2_8_2_6_6_5_2_4_6_9_5_3_7_4_4_5_4_7_8_8_7_6_6_9_5_2_2_2_7_7_3_4_4_4_1_1_8_2_7_6_4_6_4_7_3_4_4_4_8_1_1_4_4_1_4_9_5_5_2_2_6_1_6_1_2_4_2_6_8_7_1_4_2_9_5_2_9_2_2_1_3_4_6_8_5_5_7_5_2_7_6_4_6_3_7_3_3_8_7_3_8_4_1_7_4_5_4_8_1_3_4_4_1_5_5_5_3_1_1_4_1_8_2_3_5_1_5_3_6_6_6_2_4_5_5_2_1_1_1_1_5_5_1_8_8_6_4_2_1_2_1_7_7_1_5_8_7_7_7_3_5_3_7_6_3_3_2_6_3_7_1_1_4_1_2_6_6_6_5_4_8_6_2_3_4_6_4_3_1_4_7_6_5_8_5_7_1_2_6_7_1_3_6_1_3_5_4_5_4_4_2_3_1_2_5_4_1_6_5_2_8_2_3_6_3_1_5_3_5_5_5_2_2_2_1_3_5_6_2_1_1_6_4_5_7_2_6_6_6_1_1_3_3_4_4_4_1_4_3_2_4_8</t>
+  </si>
+  <si>
     <t>2_8_8_1_1_2_3_9_9_4_2_4_1_7_9_4_1_3_7_2_4_7_2_7_7_7_9_6_6_5_3_4_3_2_1_4_7_3_2_1_1_3_3_3_1_2_4_2_5_3_1_8_1_2_6_2_2_6_2_1_1_5_5_1_3_9_4_4_9_3_3_5_4_8_8_7_2_7_6_3_8_7_5_7_7_2_8_3_5_4_8_8_4_4_4_8_7_2_3_6_5_3_3_5_2_6_2_5_3_2_4_2_6_6_5_6_2_2_9_3_3_1_2_2_9_4_4_4_4_8_8_3_7_5_6_8_2_3_7_8_8_2_3_1_5_5_2_2_2_4_9_7_4_1_1_3_2_8_6_5_4_4_5_1_5_9_7_5_1_7_7_2_2_4_3_2_2_6_4_3_2_2_8_1_3_3_7_2_7_6_4_4_5_5_2_2_2_1_3_7_3_2_3_2_2_6_3_9_3_4_2_2_2_6_3_3_1_1_1_9_2_2_5_1_1_1_8_3_5_4_4_4_1_7_6_2_3_6_2_9_4_5_8_1_1_5_7_7_8_3_5_9_5_4_4_6_8_2_4_6_3_5_4_2_7_2_6_3_6_2_5_5_2_2_2_9_1_9_9_7_8_5_5_4_1_4_2_1_2_1_7_6_3_1_1_1_9_1_3_6_1_5_9_2_1_6_8_8_8_8_8_7_1_2_5_5_2_5_3_4_4_4_3_1_1_5_3_5_6_4_5_3_8_8_7_4_4_5_5_5_6_2_4_3_8_6_7_7_8_4_7_7_7_7_7_6_9_9_1_3_1_4_2_4_9_1_4_1_1_4_7_2_5_8_2_6_6_1_2_2_5_5_7_3_4_5_2_5_4_3_7_3_6_1_4_9_3_5_3_8_7_3_3_5_2_2_2_2_4_4_8_2_1_4_2_7_2_5_4_4_2_3_6_3_4_7_7_5_5_4_2_7_4_3_3_2_1_4_1_5_3_4_5_2_8_8_8_6_1_1_4_3_2_1_1_6_1_5_1_9_2_5_3_7_6_1_4_1_6_2_8_7_9_1_3_1_6_2_6_2_4_4_4_8_6_1_2_1_8_5_2_6_6_2_3_5_2_5_2_4</t>
   </si>
   <si>
@@ -1302,10 +1317,7 @@
     <t>10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_10_11_12_13_14_15_13_12</t>
   </si>
   <si>
-    <t>3_1_5_8_4_5_10_10_1_4_7_1_4_3_2_1_6_3_4_9_10_5_2_3_1_1_2_7_7_3_5_5_8_5_4_8_8_2_9_2_7_7_3_8_8_10_3_10_4_1_7_4_10_1_5_5_4_2_2_6_4_4_8_3_2_1_5_3_6_6_9_8_8_4_3_2_6_5_6_9_2_11_7_2_2_1_3_2_3_6_4_2_5_7_2_3_1_1_8_3_11_11_5_7_9_4_4_11_4_2_8_1_2_4_7_1_1_2_3_10_4_4_2_1_3_8_2_4_2_4_2_2_2_2_1_8_4_2_1_5_1_4_1_6_3_2_5_6_6_5_10_9_11_1_1_5_11_2_5_9_1_5_3_6_1_4_1_4_7_6_1_2_7_4_11_4_5_11_8_9_4_5_4_4_6_5_5_3_2_8_10_5_1_11_4_11_10_7_3_2_3_3_7_7_7_7_1_10_4_2_4_8_8_9_9_4_3_4_1_11_7_6_3_11_11_5_2_5_10_10_9_9_1_8_2_10_6_7_7_7_7_11_6_5_2_6_2_6_6_5_5_5_1_4_1_4_1_4_4_7_3_5_3_7_3_5_1_7_4_7_7_9_2_2_2_2_3_2_1_5_10_10_1_3_1_1_7_3_2_2_6_5_5_7_7_7_3_11_6_10_11_6_2_5_2_2_2_3_3_4_9_5_6_10_2_7_2_7_7_3_6_9_11_11_3_3_5_1_5_1_2_1_6_6_10_3_7_5_9_4_8_2_8_2_11_11_2_1_7_5_6_6_6_6_3_3_3_5_8_5_9_9_5_5_7_6_1_5_7_5_9_4_6_1_6_4_6_6_6_6_8_7_1_1_2_1_5_9_7_5_5_11_4_5_6_6_1_5_3_2_2_2_3_5_9_3_5_10_2_3_5_3_3_11_3_7_5_7_7_11_4_11_10_10_10_6_8_5_5_5_3_3_5_5_6_1_1_3_4_1_7_7_11_4_6_3_3_7_2_2_8_3_3_2_9_9_5_5_3_5_5_10_9_11_11_1_1_3_3_1_2_1_3_3_5_2_5_2_3_3_1_9_7_10_4_4_4_7_1_3_1_10_9_4_1_7_1_1_1_6</t>
-  </si>
-  <si>
-    <t>7_1_1_5_6_1_3_10_5_9_1_4_9_3_5_3_5_1_8_1_4_1_2_2_3_7_7_4_5_7_1_5_6_11_6_3_5_5_4_5_2_6_7_3_4_7_1_7_7_5_3_2_5_11_6_3_1_1_10_6_4_2_6_2_3_4_10_6_8_7_9_1_1_8_8_8_9_9_8_2_7_4_5_6_7_5_1_1_2_3_2_6_5_3_4_4_5_3_5_4_8_7_11_5_3_6_5_5_3_3_11_5_5_5_5_7_1_6_1_1_1_1_8_4_1_5_7_10_6_1_8_6_1_3_6_1_2_3_2_2_1_6_5_7_11_7_2_9_3_5_5_3_4_1_8_9_11_3_2_1_5_4_5_2_5_5_2_6_1_1_9_4_5_4_2_4_3_1_4_7_5_4_1_8_1_2_10_4_8_4_2_6_6_6_3_8_7_10_6_6_11_6_2_1_11_2_2_4_1_4_1_4_6_6_6_3_3_1_11_5_1_9_7_2_8_6_5_8_11_5_11_1_11_2_3_3_1_4_8_8_6_6_7_5_2_6_3_5_3_10_6_3_6_3_1_2_1_8_8_7_7_4_9_5_5_1_5_8_3_5_9_8_5_10_6_1_9_4_8_10_7_10_1_4_1_2_2_5_4_1_5_1_4_2_1_3_4_1_5_5_5_9_7_6_4_3_3_5_1_9_2_4_3_6_2_11_6_11_6_4_10_4_9_4_1_5_9_3_11_2_7_3_1_4_7_5_1_8_5_3_2_8_1_5_6_8_4_4_2_3_3_10_7_7_2_1_7_2_1_6_2_8_2_1_6_9_4_8_1_2_7_7_10_3_1_5_5_1_4_10_7_8_1_9_2_1_2_8_1_2_2_3_6_4_2_10_4_11_6_8_4_6_3_1_2_4_2_3_3_5_5_3_5_3_5_9_2_7_8_6_6_1_8_1_8_2_3_4_2_3_9_3_4_6_11_3_7_6_5_11_7_7_5_2_9_1_3_5_1_4_2_4_9_4_1_4_3_1_2_6_2_9_2_3_4_9_3_5_6_1_3_4_3_9_2_4_2_6_1_2_2_8_5_3_4_3_11_7_8_3_11_6_9_2_8_7_4_6_2_1</t>
+    <t>3_7_7_5_3_3_4_6_5_4_2_6_6_2_4_2_2_2_2_5_8_8_5_3_6_4_4_8_1_5_1_1_10_6_1_3_9_11_7_1_1_10_10_9_9_1_1_3_7_4_2_5_2_2_2_9_3_2_4_1_8_3_7_1_8_8_6_6_2_4_6_2_10_4_4_5_1_7_7_11_1_7_1_10_6_4_4_4_4_11_5_4_2_8_1_2_6_3_10_2_3_2_2_7_6_3_2_5_1_8_1_2_5_7_3_8_8_8_4_8_2_2_2_7_7_5_5_7_4_3_1_10_8_6_7_7_4_3_1_2_3_8_4_3_10_2_1_1_8_4_2_7_7_3_9_9_5_2_1_1_3_5_3_5_5_1_5_9_11_8_3_5_6_2_6_1_2_1_10_3_3_5_2_6_2_3_9_3_3_2_6_10_10_10_7_10_9_7_7_5_1_1_4_5_2_4_8_2_2_5_1_1_9_7_7_1_8_6_7_7_5_2_4_4_8_5_6_6_1_3_2_5_5_5_7_7_8_2_6_4_4_2_4_7_1_2_1_1_4_4_2_8_5_5_6_11_3_7_6_1_1_7_8_9_9_9_5_4_10_8_1_4_3_11_4_8_1_5_11_2_8_1_7_4_7_3_8_8_2_4_1_1_3_11_11_6_5_2_5_4_8_3_3_1_2_3_4_6_1_2_6_3_3_1_6_1_6_3_6_1_10_10_5_2_9_8_3_4_10_3_2_3_5_1_6_9_5_10_2_5_4_9_9_3_3_2_3_3_7_5_1_3_1_4_3_5_11_3_9_9_7_5_7_1_8_8_1_2_5_3_4_1_1_1_6_7_4_1_6_6_1_6_2_2_5_5_1_3_2_2_1_6_9_9_1_2_6_1_4_2_2_3_3_1_6_8_5_5_1_2_5_5_1_2_6_6_10_10_3_3_1_8_4_4_1_5_1_3_2_1_2_7_7_3_8_8_5_10_1_1_6_3_2_1_2_8_5_3_7_1_2_1_1_10_4_8_4_4_3_3_8_1_5_7_2_5_5_9_2_11_5_1_1_1_1_5_8_8_4_3_1_8_3_8_2_5_2_6_9_5_2_1_7_6_5_5_4_10_10_3</t>
   </si>
   <si>
     <t>1_1_1</t>
@@ -1363,6 +1375,60 @@
   </si>
   <si>
     <t>9_7_9_3_10_2_6_3_7_3_8_5_7_7_4_5_7_3_7_2_8_1_2_2_3_8_4_8_1_3_6_5_3_11_3_2_11_4_10_3_7_5_3_3_3_1_8_8_1_6_8_11_2_6_11_4_11_2_4_3_9_2_10_4_5_2_5_7_10_3_8_6_6_3_8_1_1_6_5_8_6_4_3_6_10_3_3_1_9_9_11_3_11_4_1_3_8_1_11_3_7_9_9_6_2_3_5_3_10_3_3_1_2_7_5_8_3_5_9_6_2_7_9_10_1_1_2_5_11_1_11_1_8_2_11_3_10_3_5_7_6_10_3_9_3_5_1_9_7_1_1_8_7_7_5_11_3_5_3_11_2_7_10_4_10_3_8_1_1_11_2_2_11_3_8_5_7_8_4_11_3_9_7_3_3_2_2_9_7_7_3_11_3_4_6_9_5_11_2_7_8_2_3_9_10_1_4_9_11_3_10_3_7_6_5_5_4_4_7_3_8_6_9_5_1_11_3_6_11_2_7_2_1_5_3_4_2_7_1_2_1_9_2_5_1_2_3_1_9_2_1_4_11_3_10_3_3_10_4_2_7_4_7_3_11_4_1_8_8_4_10_3_7_2_6_4_10_2_7_10_3_2_8_8_10_2_5_7_1_11_3_11_3_8_2_2_4_1_6_10_1_2_9_1_2_8_7_1_1_9_10_4_7_8_3_4_3_9_5_3_5_6_8_11_2_3_6_1_6_4_1_9_8_10_1_2_4_10_3_11_3_9_9_5_6_11_2_7_1_5_7_5_4_1_6_6_4_8_2_7_6_7_3_8_8_2_10_3_10_3_11_2_5_4_7_8_8_3_11_4_10_3_2_10_4_10_3_6_8_9_1_9_3_5_2_10_1_5_10_4_6_3_11_4_7_4_4_10_3_2_10_3_1_8_8_5_4_5_1_7_7_1_3_5_7_10_2_6_6_2_10_2_1_4_10_4_2_2_1_6_11_1_9_4_7_8_5_7_10_3_11_2_10_4_4_8_7_8_5_11_4_6_5_9_6_1_4_10_4_6_4_10_4_7_2_4_8_7_9_2_2_11_2_7_2_4_4_7_10_2_6_4_11_2_5_4_1_8_3_1</t>
+  </si>
+  <si>
+    <t>1_4_1_1_2_3_1_4_2_2_5_3_2_1_1_3_4_1_4_2_2_3_1_1_1_2_2_3_1_3_3_5_1_3_1_4_1_3_2_3_1_2_1_1_1_3_4_1_1_3_3_1_1_4_2_2_1_2_4_1_1_4_2_4_2_4_1_1_4_2_4_1_1_5_4_4_1_1_3_3_1_4_3_3_3_2_1_3_2_1_4_4_1_3_2_2_4_3_1_3_3_4_4_2_1_4_1_1_3_3_3_1_2_1_4_1_4_1_2_1_3_3_4_4_3_3_2_2_2_1_3_2_1_1_4_1_2_1_2_2_4_1_2_3_4_5_1_1_4_1_2_5_2_1_1_1_1_1_2_5_3_3_1_3_5_2_4_2_5_5_4_1_2_4_2_2_4_3_3_1_3_2_4_4_2_4_4_2_1_5_4_1_2_1_4_3_3_4_1_1_2_2_2_2_1_1_1_5_1_1_1_2_1_5_1_1_1_1_3_3_2_1_1_1_1_2_1_1_3_3_2_1_1_2_1_2_2_1_4_3_3_2_3_4_2_5_1_5_5_2_1_1_3_2_5_2_2_1_1_1_1_4_1_1_3_3_3_1_5_3_4_1_3_2_3_1_1_5_3_5_2_3_3_3_1_4_1_1_2_3_2_2_4_1_1_3_2_4_1_3_3_1_1_1_1_2_1_3_2_3_1_4_4_1_5_5_5_1_3_4_3_1_2_3_5_5_2_1_1_4_1_4_3_1_3_4_3_3_4_1_1_1_1_4_2_2_4_2_1_4_1_2_2_1_2_1_4_1_1_4_4_4_2_1_3_2_1_1_1_2_5_1_2_2_4_1_2_1_1_3_3_2_2_4_2_2_3_1_1_1_1_4_1_3_1_4_3_4_1_3_1_2_4_1_1_5_1_1_4_1_1_2_5_5_5_5_1_1_2_3_1_3_1_1_1_4_1_2_1_1_1_2_1_1_3_1_3_2_1_1_1_2_1_2_1_4_1_5_1_1_1_1_4_1_4_3_1_1_2_1_1_2_4_1_2_2_2_1_1_2_1_2_1_1_4_2_2_3_1_1_2_2_1_1_3_4_2_1_2_3_1_2_2_1_1_1_4_1_1_2</t>
+  </si>
+  <si>
+    <t>2_3_1_2_1_3_4_3_1_2_1_5_5_5_4_2_3_2_2_1_3_1_1_1_1_4_5_1_3_4_4_3_3_2_5_5_5_2_1_1_3_2_3_5_3_5_2_1_2_2_2_1_4_1_2_2_2_2_2_5_2_1_1_1_2_2_4_3_3_1_2_3_2_3_3_4_5_2_3_3_2_2_1_1_4_1_3_1_4_2_2_3_1_1_2_4_4_3_3_1_3_5_4_4_2_3_5_2_1_5_4_3_4_5_4_1_1_1_1_4_2_1_1_2_2_2_5_4_5_2_3_2_3_1_3_1_2_1_5_4_4_2_2_3_2_5_1_3_1_3_5_5_2_5_4_1_2_3_1_2_5_1_4_5_4_1_2_3_3_5_5_2_3_4_5_2_4_2_2_1_1_5_1_1_1_3_1_1_5_4_3_2_4_4_2_1_3_4_2_1_3_1_1_1_5_4_2_2_2_2_1_4_1_3_4_3_1_5_4_3_4_4_2_3_3_1_4_5_2_5_2_4_2_2_2_1_1_3_3_2_5_2_2_5_3_5_1_5_4_3_3_4_2_2_3_4_1_5_3_3_1_4_3_3_3_1_2_3_4_5_2_1_2_1_2_4_1_1_5_2_1_1_2_1_4_5_1_2_4_3_2_1_2_1_4_2_2_2_3_2_4_1_1_2_1_2_5_2_5_1_1_1_4_4_5_3_2_3_2_4_3_3_5_1_2_1_5_2_3_3_3_2_3_3_1_4_5_3_1_2_5_2_2_3_3_1_1_1_4_4_2_2_4_2_3_4_1_2_1_2_1_5_4_2_1_3_2_1_4_4_4_2_2_5_4_4_1_1_2_1_2_4_3_1_4_1_1_5_1_5_1_2_3_2_1_2_2_4_3_5_5_1_2_2_1_3_1_4_4_5_1_1_1_4_2_1_3_4_1_2_4_5_4_3_4_4_5_4_5_4_2_5_5_2_1_3_2_2_3_4_2_1_2_2_5_4_3_4_1_5_1_2_5_2_3_5_5_4_5_2_3_5_2_4_1_3_2_4_3_1_1_4_2_4_5_1_1_2_2_3_3_5_2_4_1_1_3_2_4_2_5_4_4_1_5_3_1_3_4_2</t>
+  </si>
+  <si>
+    <t>1_1_2_1_2_2_2_4_2_4_1_3_2_2_2_3_1_2_2_5_3_3_3_4_3_2_2_1_5_3_2_5_5_2_1_2_5_2_2_3_2_1_2_1_1_2_5_4_2_2_1_4_2_1_2_2_2_1_1_2_1_2_2_2_1_1_2_2_1_1_3_1_3_1_3_2_2_1_5_4_1_1_3_3_1_3_4_3_1_1_2_1_4_4_4_1_2_2_4_2_1_1_1_3_2_2_2_2_1_1_4_4_2_1_1_5_2_2_2_3_2_1_1_2_2_2_2_1_2_4_4_4_3_2_2_3_3_2_5_2_2_2_3_2_4_3_2_1_1_2_2_2_3_1_4_1_2_1_1_1_4_1_1_5_1_3_5_1_3_3_1_3_4_4_2_3_1_5_1_1_1_3_4_4_3_3_2_1_4_4_3_1_3_2_1_2_4_5_2_3_3_2_2_3_3_2_2_1_1_4_1_1_1_2_3_3_3_3_3_2_3_2_1_4_2_2_3_1_2_1_5_5_3_2_2_1_1_4_1_1_1_5_1_3_2_2_3_3_2_2_1_1_1_1_1_1_1_1_3_3_1_1_3_2_2_1_1_4_4_2_4_4_3_4_1_4_2_1_1_3_1_2_4_5_1_2_1_3_3_1_1_2_1_3_2_1_5_2_4_1_1_1_1_2_2_1_2_2_4_1_2_2_2_1_1_3_2_1_1_3_3_1_1_2_4_3_1_4_3_1_3_5_3_4_1_1_4_2_3_3_3_5_1_1_2_2_3_5_3_1_1_1_2_1_1_1_2_4_3_2_2_1_3_1_3_2_2_2_1_1_2_1_2_1_4_4_4_3_5_2_3_1_2_1_3_3_1_4_5_5_5_3_2_3_4_4_2_3_2_5_5_2_1_2_1_2_1_2_2_1_4_2_4_4_1_1_1_3_2_1_4_2_4_3_1_3_1_3_4_2_1_1_3_1_5_3_2_1_1_3_2_1_2_3_3_2_2_1_1_3_3_3_2_1_1_2_2_1_3_2_2_2_2_1_3_1_5_5_1_1_5_2_3_1_1_3_1_1_2_3_4_4_3_2_3_3_4_4_3_1_5_1_2_1_1_2_1_3_1_4</t>
+  </si>
+  <si>
+    <t>2_2_1_1_3_4_2_1_3_3_1_4_2_3_3_2_2_5_2_2_3_4_3_2_1_5_3_4_3_3_2_5_1_1_5_3_3_3_3_1_1_2_1_5_1_5_2_1_1_5_1_2_2_1_3_1_3_5_4_3_1_1_5_4_3_3_4_1_4_2_1_1_5_5_3_1_3_2_5_2_5_4_1_5_5_2_5_4_1_1_3_5_3_1_3_2_4_3_3_3_4_1_3_2_3_2_2_1_2_2_1_5_1_2_4_3_1_1_1_3_3_3_5_2_3_1_5_5_4_5_5_1_4_4_3_3_4_4_4_2_5_3_2_1_1_4_1_3_3_3_3_5_1_2_1_4_1_3_4_2_5_1_2_1_1_1_1_3_4_4_5_1_5_2_1_2_1_3_3_3_5_4_4_2_3_1_2_3_1_5_1_5_1_3_5_5_3_3_5_3_4_5_5_3_1_2_2_3_5_3_2_4_2_5_2_3_4_1_1_2_4_3_4_1_2_2_4_2_3_4_3_5_3_3_1_1_3_1_3_1_1_1_3_2_3_2_1_4_1_5_4_3_1_5_5_4_4_2_1_2_4_4_3_1_1_1_5_2_1_2_5_2_4_4_4_3_5_2_5_5_5_2_4_4_4_2_4_5_5_2_3_3_3_3_2_1_4_3_1_2_1_4_1_2_2_2_1_5_3_5_2_2_3_1_3_3_2_2_1_1_3_5_1_5_4_4_3_3_4_5_4_4_4_3_1_4_4_3_5_4_2_1_4_2_4_5_1_2_4_2_2_1_5_5_2_1_5_4_3_4_4_5_5_2_2_5_2_2_2_1_5_2_2_2_1_5_3_4_4_2_2_4_3_2_2_5_4_1_2_1_5_5_5_1_5_4_3_2_3_2_3_4_3_2_1_1_2_1_1_2_3_2_1_4_1_1_3_5_2_2_2_1_5_2_2_5_2_5_4_1_1_3_4_1_3_1_1_5_5_5_5_3_1_2_4_2_4_1_2_3_3_1_2_3_3_3_2_2_5_4_3_4_2_4_3_4_4_4_5_2_2_4_2_1_1_1_2_2_4_4_1_2_1_3_2_1_3_3_4_3_2_3_3_3_4_4_2_3_5_3</t>
+  </si>
+  <si>
+    <t>3_1_2_3_1_2_1_1_2_3_3_1_1_1_2_2_4_2_1_1_2_2_1_2_1_5_1_1_1_3_3_4_4_5_3_3_3_5_3_3_2_1_5_3_3_3_4_1_3_4_4_4_4_1_2_2_2_1_4_4_1_2_1_1_1_3_4_2_5_5_3_1_3_3_5_3_2_4_3_4_4_2_5_3_2_1_3_1_2_2_2_1_4_2_3_2_5_3_4_1_1_1_1_1_1_2_1_2_1_1_5_1_1_3_1_3_3_3_1_1_1_4_2_2_2_3_3_1_1_3_4_2_2_2_5_1_1_3_1_4_3_1_1_2_3_3_1_2_3_1_3_2_1_1_2_3_3_2_2_3_5_5_5_1_1_4_2_5_2_4_1_4_4_3_3_2_1_1_4_4_1_1_2_2_2_1_1_3_1_2_1_1_1_1_3_1_1_1_2_2_3_2_5_5_3_2_2_1_1_4_3_3_2_2_3_3_2_1_4_2_2_4_1_1_3_2_1_2_1_4_1_4_5_2_1_1_4_1_4_3_1_2_2_4_1_5_1_3_3_3_4_4_2_2_1_3_3_2_2_3_2_1_2_2_5_1_1_3_3_3_3_4_3_3_1_3_1_3_1_2_2_4_1_2_2_4_4_4_1_3_3_3_1_2_3_2_1_2_3_2_3_4_2_3_3_3_1_1_2_1_1_1_3_1_2_2_1_2_2_2_1_1_5_1_2_5_1_3_2_2_1_3_1_2_1_1_1_2_1_2_4_1_2_1_2_3_1_1_3_3_1_1_4_3_1_1_2_5_2_4_1_1_1_2_2_5_2_3_2_1_3_3_3_1_5_1_1_1_2_3_3_3_1_3_3_1_3_3_1_1_2_2_3_4_4_4_5_4_1_2_2_1_1_4_4_1_5_3_1_4_1_3_3_4_5_1_2_4_1_1_1_1_1_1_2_4_5_2_1_5_1_1_1_1_3_2_1_1_2_3_1_3_4_5_2_2_2_3_1_1_2_1_2_1_3_2_2_1_3_1_2_2_2_2_2_1_4_1_4_4_3_1_1_2_1_5_5_2_2_3_1_1_4_1_1_1_3_1_3_3_1_1_4_5_5_4_3_2_1_1</t>
+  </si>
+  <si>
+    <t>4_3_1_4_1_2_2_1_2_3_5_5_5_3_4_5_3_1_4_1_4_2_2_3_5_4_5_5_1_2_5_1_5_2_2_2_2_5_3_5_5_1_2_1_1_3_5_4_1_5_5_3_1_4_3_2_4_2_2_3_5_4_2_5_3_2_3_5_1_2_5_5_2_4_2_2_1_1_2_3_5_1_2_5_3_2_4_4_2_5_4_4_2_2_3_17_8_3_2_3_4_1_2_4_3_5_5_4_5_5_3_4_4_4_1_1_3_5_2_1_5_3_2_1_2_4_3_2_1_5_2_4_5_5_2_4_1_5_2_1_2_5_1_1_1_4_1_1_4_17_17_17_4_5_4_1_4_4_1_4_2_2_2_5_5_1_4_1_5_3_2_4_1_2_4_1_1_5_2_2_4_1_4_5_1_4_3_2_3_5_2_3_1_1_5_3_3_4_5_4_3_2_2_1_4_3_3_4_5_2_5_2_3_2_5_3_4_4_3_2_1_3_2_4_3_17_7_5_1_4_3_5_4_2_2_5_4_2_3_2_5_4_4_2_2_3_4_3_5_1_1_5_1_5_1_5_2_1_1_2_5_1_1_3_4_1_4_1_4_1_5_2_4_1_2_3_1_4_2_2_2_5_1_1_5_4_1_3_1_1_1_4_5_2_1_5_4_2_2_3_3_5_4_2_3_2_3_4_2_2_2_4_3_2_4_5_2_3_3_5_1_5_2_1_1_5_3_1_3_5_5_3_4_4_17_7_2_1_5_5_4_3_5_5_2_3_4_1_5_5_1_2_5_3_3_3_2_1_1_1_4_5_1_2_1_2_1_2_1_3_3_5_3_5_1_1_3_5_5_3_4_5_5_5_4_4_1_1_5_4_1_5_5_3_2_1_4_4_3_3_1_2_5_5_2_2_1_2_5_4_4_5_3_3_2_4_2_2_1_3_3_1_1_2_2_3_4_3_2_2_3_1_3_2_3_4_5_5_1_4_5_4_1_4_1_5_2_2_1_4_4_3_5_2_4_4_3_2_1_1_4_2_3_1_5_4_4_3_3_3_3_2_4_5_4_4_4_3_2_5_3_4_1_4_1_3_3_4_2_3_1_4_2_2_1_1_4_3_1_1</t>
+  </si>
+  <si>
+    <t>1_4_1_3_2_1_2_1_3_2_1_1_1_1_3_4_4_3_3_3_3_3_4_3_5_5_1_2_1_1_1_4_3_3_1_1_3_1_2_1_1_1_5_5_4_3_1_1_3_1_2_2_2_3_1_3_2_2_2_2_3_3_1_3_3_3_3_3_3_2_2_3_3_4_3_2_5_5_3_1_4_2_2_1_1_1_1_2_4_4_2_4_2_1_1_5_1_2_1_2_3_2_5_3_1_2_2_1_3_3_2_2_2_2_1_1_1_1_3_3_4_2_2_4_3_1_3_3_3_1_3_4_3_2_2_4_1_2_4_3_3_1_2_4_1_4_1_1_3_2_2_2_2_2_1_3_1_1_2_2_2_4_2_2_1_1_1_3_1_1_2_1_3_3_1_1_4_1_5_4_1_1_1_2_2_4_2_2_2_2_3_5_5_5_3_3_3_4_2_4_2_4_4_3_1_1_1_2_3_3_2_3_3_1_1_2_4_4_2_1_1_5_3_3_2_1_2_1_3_2_3_2_1_2_3_4_4_1_2_4_1_1_2_1_1_3_2_1_1_5_4_2_1_3_2_2_3_1_5_2_1_3_5_3_2_2_4_4_1_2_2_1_2_1_2_4_1_3_4_2_1_1_3_3_1_1_2_4_1_4_5_2_2_4_1_3_3_1_1_2_5_2_2_1_3_4_1_3_1_5_3_2_1_1_2_4_3_5_1_5_1_2_1_1_5_2_1_1_1_2_2_2_2_1_5_1_4_2_2_1_1_1_5_1_5_2_5_1_2_1_3_3_5_2_2_3_2_2_1_1_1_1_1_3_1_3_1_1_3_1_1_1_1_2_2_3_2_3_1_1_2_1_1_3_1_2_2_2_1_1_1_1_2_1_5_4_4_2_3_3_2_1_2_2_2_2_4_1_5_2_1_2_4_5_4_1_4_2_2_2_2_4_1_2_3_2_2_1_1_4_4_5_4_2_1_1_1_1_1_2_3_2_1_3_4_4_1_1_1_1_2_2_2_1_2_1_3_1_3_1_1_4_2_1_4_2_2_2_1_3_4_4_4_1_4_1_1_3_1_3_3_2_4_3_5_2_3_1_2_3_1_2_1_3_1_2_3_2_1_3</t>
+  </si>
+  <si>
+    <t>6_10_8_8_8_10_9_6_9_9_8_8_6_8_7_9_9_6_6_9_8_7_6_8_10_6_8_7_7_9_7_8_7_6_8_9_6_7_10_8_8_8_8_10_10_9_10_6_6_8_10_6_8_7_7_9_7_7_10_9_6_6_7_7_7_8_9_7_8_6_7_6_8_9_8_8_10_9_9_9_10_8_7_10_6_6_8_6_9_6_10_7_10_6_7_9_7_6_9_10_6_8_10_10_10_6_6_6_8_8_7_7_9_8_9_7_6_10_6_10_10_8_8_8_9_6_8_8_8_6_6_8_6_6_6_9_9_6_8_7_6_6_8_6_6_7_6_10_10_8_7_8_9_9_6_10_7_7_6_6_6_9_7_7_6_7_6_6_10_9_6_9_9_10_6_9_9_6_9_8_8_8_7_8_7_9_7_9_6_6_9_8_6_10_8_7_6_10_10_8_6_6_8_7_7_8_7_7_8_10_10_6_6_10_7_10_8_6_8_10_10_10_9_9_10_7_9_8_7_7_6_8_8_7_9_9_8_7_6_6_9_6_8_6_6_6_9_10_7_7_8_8_7_8_10_8_8_8_10_6_10_6_7_7_6_7_7_6_8_8_7_9_9_9_9_9_10_6_6_8_10_7_9_8_6_7_6_6_10_8_7_8_10_6_9_6_6_7_7_6_6_7_6_9_9_10_8_9_9_7_7_9_6_6_7_10_10_7_8_8_9_8_7_7_9_8_6_9_9_7_8_7_6_9_7_8_7_9_7_6_7_7_9_6_9_8_6_6_10_10_6_8_6_6_6_6_6_7_9_9_9_10_6_6_10_9_9_9_6_9_7_6_9_9_8_6_9_9_7_8_7_8_7_7_7_7_6_6_8_7_9_7_9_6_6_10_9_8_6_10_9_8_7_8_10_10_8_8_7_7_7_7_6_6_10_10_10_9_6_6_6_6_7_7_8_9_9_7_6_9_10_7_7_7_8_8_6_7_9_8_7_8_8_6_10_7_8_10_10_7_8_7_8_8_6_8_7_9_7_6_7_7_7_8_6_7_7_8_8_9_6_6_8_6_8_6_10_7_9_9_9_9_7_8_6_6_9_7_7_8_6_10_7_7_7_6_6_9_6_9</t>
+  </si>
+  <si>
+    <t>9_8_9_7_8_10_7_10_7_7_6_10_8_6_7_10_6_8_6_9_7_9_7_7_7_7_9_6_7_9_8_6_10_9_6_9_7_7_8_8_7_7_7_10_10_6_10_6_8_9_7_9_8_8_8_8_7_7_9_6_6_6_7_7_7_8_6_8_8_7_8_8_9_7_7_8_7_8_6_7_6_8_8_6_7_10_10_8_6_6_9_6_6_6_6_6_9_8_6_8_6_6_8_9_9_7_6_9_10_8_6_6_8_9_6_6_8_7_9_6_6_9_8_8_6_6_8_6_6_6_7_6_8_9_6_6_8_7_7_7_6_6_6_6_6_7_6_10_6_9_6_6_6_10_7_10_9_8_6_8_8_8_9_9_9_8_8_7_9_8_9_6_6_10_6_7_7_10_6_7_8_8_10_9_6_6_6_7_6_10_8_6_10_7_6_10_8_7_7_7_7_9_8_6_6_7_8_9_10_10_7_9_8_10_10_8_8_7_8_8_6_8_7_6_8_9_7_7_8_10_7_6_10_7_8_6_7_7_8_6_8_8_8_7_6_8_7_8_8_9_9_8_10_8_6_10_6_6_6_6_7_9_7_8_6_7_8_10_6_10_8_6_6_7_7_8_8_9_7_7_8_10_6_8_10_7_8_6_6_6_10_8_6_6_6_10_9_9_7_6_7_9_9_10_9_9_7_6_7_10_9_7_7_6_9_6_6_9_7_10_6_7_9_10_8_7_6_10_10_9_9_9_7_7_7_10_10_6_7_6_7_8_6_6_6_8_10_6_9_6_9_9_8_9_9_9_10_8_6_8_7_7_8_7_7_7_8_7_7_10_6_8_8_6_6_8_8_8_8_6_8_7_7_10_7_6_8_6_10_10_8_8_8_6_8_8_8_10_6_6_6_9_8_7_6_6_6_6_6_9_9_9_8_6_6_8_6_6_7_7_7_7_7_7_7_6_8_6_8_9_7_8_7_9_9_9_7_6_6_6_7_10_8_8_6_6_7_7_7_7_6_10_9_7_7_9_9_10_6_6_10_7_6_9_8_6_6_8_7_7_7_6_6_6_9_9_6_6_6_7_6_6_8_7_6_9_6_9_7_8_8_7_7_7_6_7_10_10_8_8</t>
+  </si>
+  <si>
+    <t>8_8_8_7_8_6_9_8_7_8_9_6_8_8_6_6_7_10_8_8_8_8_9_6_8_8_9_7_7_6_10_6_9_6_6_10_6_6_8_10_9_7_6_7_7_6_7_7_7_10_6_8_6_10_6_8_9_9_10_6_8_8_8_10_8_10_8_6_7_7_7_7_8_9_8_9_6_8_10_9_6_7_9_8_8_10_9_8_9_8_10_10_7_8_7_9_9_7_7_9_8_7_7_9_7_7_6_8_7_9_8_7_7_6_6_6_9_8_10_6_8_7_7_7_9_6_8_6_7_7_6_6_7_6_6_6_8_9_7_7_6_6_6_7_7_7_7_7_10_6_7_8_8_8_6_6_7_7_9_9_6_9_9_8_10_7_8_8_8_9_8_7_6_6_7_7_7_10_6_6_6_7_7_6_7_8_10_8_6_8_6_6_9_8_8_8_8_9_10_9_6_9_9_7_7_8_7_6_8_8_9_6_8_8_6_9_8_10_9_7_7_6_9_8_7_10_9_6_8_6_6_6_9_9_6_7_9_9_7_9_6_8_7_8_9_8_8_7_8_8_10_10_6_8_7_7_6_6_10_10_8_10_8_10_6_6_6_6_6_6_8_9_6_6_6_7_8_9_6_9_10_10_6_8_6_6_6_8_6_10_6_6_6_6_10_6_7_6_6_6_8_8_7_7_10_9_7_7_7_7_8_9_8_10_8_8_6_9_6_7_9_9_9_7_9_6_6_8_8_9_6_7_6_9_9_6_7_6_8_10_8_8_9_10_10_10_6_6_8_9_7_7_8_8_10_6_7_6_6_9_7_7_6_8_10_10_8_10_10_6_7_8_10_6_6_9_7_6_6_10_10_7_6_6_8_8_8_8_7_10_10_9_8_7_9_10_7_9_7_6_6_8_6_8_9_8_9_8_9_7_8_8_8_10_6_8_8_9_6_10_8_7_7_8_7_8_6_6_8_9_10_8_7_6_7_7_6_6_6_8_7_9_6_6_10_8_9_9_8_7_6_7_7_6_10_6_6_8_8_6_8_9_10_10_8_6_7_10_8_10_9_7_9_8_7_7_7_7_7_7_10_7_8_10_8_9_10_10_6_6_6_6_6_7_8_9_9_9_7_10</t>
+  </si>
+  <si>
+    <t>7_6_6_7_7_9_8_8_8_7_8_6_6_7_7_10_7_7_8_6_6_10_8_8_6_7_7_7_6_6_7_9_9_8_8_8_8_8_6_8_8_9_8_6_6_6_6_6_9_8_6_7_8_6_6_10_7_6_7_8_7_6_9_8_6_8_8_7_6_6_9_6_8_7_8_6_6_9_7_7_6_9_8_7_7_9_10_9_7_9_7_6_9_7_7_9_9_6_7_8_9_10_7_9_7_7_8_9_7_10_7_8_8_8_6_8_10_6_8_7_8_10_8_7_7_8_7_9_8_8_9_7_7_9_9_7_6_10_10_6_10_9_6_6_7_7_7_8_8_9_8_6_7_8_7_8_6_9_9_9_6_7_8_8_9_10_8_6_6_10_10_10_10_6_6_7_8_9_8_8_8_7_6_6_6_9_7_10_9_6_6_6_6_9_6_9_6_8_8_7_6_7_10_8_8_7_7_10_7_7_7_9_6_6_8_8_7_7_7_9_8_6_10_7_6_7_7_10_6_6_9_6_6_10_7_6_6_8_8_8_9_6_6_8_10_10_9_6_6_9_8_7_7_7_7_9_8_9_9_10_10_7_6_6_9_10_8_10_6_6_6_6_8_7_8_8_8_9_8_7_7_7_8_10_8_7_10_6_6_7_9_7_8_6_6_6_6_6_6_7_6_9_7_9_7_10_10_7_8_6_6_8_7_8_9_7_6_6_6_9_8_6_8_8_9_9_9_9_7_8_6_6_9_7_7_6_8_6_9_7_8_10_6_10_6_9_6_7_7_9_6_6_6_7_9_9_8_8_10_10_6_8_9_7_10_10_7_7_8_6_6_6_6_6_6_8_7_6_9_6_6_9_9_9_9_6_10_8_9_7_8_10_6_7_7_8_6_8_10_8_9_6_9_6_6_8_8_7_6_9_8_6_8_6_8_9_6_9_6_8_7_6_7_10_7_7_6_10_10_6_9_8_7_10_8_8_8_10_7_10_6_6_6_10_10_10_8_7_6_8_6_6_9_10_9_9_8_9_8_6_7_9_8_7_6_6_7_8_7_6_9_6_10_6_10_8_8_7_9_7_7_7_9_9_9_9_6_8_8_10_7_7_9_7_8_6_6_7_10_9</t>
+  </si>
+  <si>
+    <t>8_8_10_6_8_10_6_6_6_8_6_7_6_7_7_6_6_7_7_7_7_7_7_9_8_7_8_9_9_9_9_7_10_10_7_10_6_6_6_10_10_8_7_8_8_9_9_7_7_8_8_7_6_6_7_7_7_10_6_6_7_7_9_9_6_10_8_7_10_9_9_6_6_6_7_7_7_6_10_6_7_6_10_7_7_10_10_10_7_6_9_7_7_7_7_7_8_9_6_6_10_10_9_7_7_8_8_8_6_9_7_8_8_8_7_10_9_6_6_10_7_7_7_6_9_7_9_7_7_8_8_6_7_9_10_9_6_7_6_6_6_10_7_6_6_8_6_7_9_6_6_7_7_8_10_6_10_6_8_6_6_6_8_9_8_9_6_6_7_7_6_7_8_6_7_9_10_10_9_8_7_7_6_8_8_7_7_7_8_6_6_10_6_6_8_10_6_7_7_6_6_9_9_8_7_7_9_7_7_6_6_6_7_6_10_8_8_8_6_8_7_10_10_9_6_8_9_9_6_7_8_6_6_10_6_6_7_9_6_6_7_8_7_7_6_6_6_6_7_7_7_6_6_6_8_8_6_6_7_8_7_6_9_6_9_9_7_7_6_6_9_6_6_7_8_7_9_10_7_7_7_6_8_6_10_7_6_8_6_8_9_9_8_8_9_9_8_10_6_9_6_8_8_7_8_9_7_6_9_6_8_7_8_6_8_7_8_8_6_6_7_6_7_9_9_9_6_6_8_6_8_8_8_10_8_8_9_10_7_7_7_8_8_9_8_7_7_8_7_7_6_10_6_8_6_9_9_7_10_8_7_7_6_10_7_7_7_7_6_7_9_9_8_6_6_7_6_6_9_10_8_6_7_6_6_7_8_9_8_8_7_6_8_8_6_8_9_9_8_9_6_7_7_7_10_8_8_8_7_6_9_9_8_6_10_10_7_8_7_9_8_8_7_8_10_7_9_8_6_7_6_8_6_10_9_7_7_8_8_7_9_7_9_9_6_6_6_9_9_9_6_6_8_8_8_6_7_6_8_6_6_7_6_6_6_8_8_10_8_7_8_7_10_6_6_7_10_6_6_8_7_9_8_9_10_6_9_10_6_7_6_7_10_8_6_7_7_8_8_6</t>
+  </si>
+  <si>
+    <t>13_13_15_15_12_12_13_14_11_15_13_13_11_13_11_11_11_11_13_12_11_14_13_12_11_11_13_11_14_12_14_13_15_11_12_14_11_14_12_13_14_11_11_11_12_14_14_11_13_11_13_11_12_13_13_13_13_12_15_11_11_11_14_11_11_14_15_11_11_11_12_12_12_13_12_15_11_12_12_14_13_13_13_11_11_11_13_11_11_14_11_12_12_12_11_11_12_12_14_14_11_13_14_15_14_13_12_11_11_11_14_12_13_11_11_14_14_11_14_12_14_12_12_11_11_12_11_13_12_11_11_12_13_12_11_11_13_11_15_15_12_12_13_15_15_13_13_15_11_12_13_11_13_15_14_11_13_12_12_13_12_11_11_11_11_15_15_12_14_14_11_13_14_14_14_13_11_14_14_13_13_15_11_11_13_11_13_11_11_11_13_12_12_11_14_12_12_12_12_12_13_13_12_13_14_11_13_12_15_12_12_11_13_13_11_12_14_11_11_12_11_12_12_15_14_13_12_14_11_14_14_13_13_14_14_13_15_15_11_12_11_13_11_13_13_12_14_11_12_12_11_13_15_12_12_11_13_14_13_15_13_11_11_11_13_11_11_12_11_14_11_14_15_13_13_13_13_14_11_13_13_12_15_12_12_12_12_15_14_12_13_11_11_11_11_12_12_12_11_11_11_12_11_13_11_11_11_14_13_12_14_12_14_12_11_13_11_15_12_12_15_15_14_15_11_15_11_15_11_11_13_11_13_13_13_13_13_13_13_12_14_11_13_12_13_13_13_11_12_15_11_13_11_14_14_15_15_13_11_13_13_11_14_14_13_12_15_14_12_12_12_13_13_11_14_13_13_13_13_12_12_12_11_13_11_12_13_11_11_14_13_13_13_14_11_11_13_12_11_15_13_13_12_11_13_13_13_12_14_11_15_13_15_11_11_12_14_14_11_13_13_13_12_14_15_13_13_13_15_13_13_11_11_13_14_13_11_12_12_14_12_12_12_12_12_13_14_11_13_13_14_13_12_14_15_14_13_12_15_12_12_11_14_11_13_12_12_11_11_11_11_13_14_13_14_11_11_15_14_14_13_15_11_11_15_14_14_14_12_11_11_11_15_14_12_11_11_15_11_11</t>
+  </si>
+  <si>
+    <t>12_11_11_11_15_13_14_14_12_13_14_14_11_15_15_14_14_13_11_12_12_13_12_11_13_11_15_12_12_12_11_12_11_11_14_11_11_13_13_11_11_12_12_15_15_14_11_14_12_12_12_13_13_11_12_11_14_12_14_14_15_11_12_14_13_11_11_11_13_11_14_15_12_13_12_14_14_11_12_12_11_13_12_15_11_11_11_15_12_11_12_12_14_11_14_14_12_15_15_11_11_12_14_14_12_11_15_15_13_14_13_13_14_14_14_14_15_14_12_13_15_13_13_12_13_13_13_13_11_15_11_11_11_15_15_15_14_11_11_15_12_11_14_15_14_14_11_13_15_12_11_13_13_12_15_11_11_11_11_15_11_12_13_11_14_14_12_12_14_13_14_14_14_14_12_11_11_11_15_12_15_15_15_13_11_13_14_14_14_11_14_11_12_13_11_13_11_14_11_15_12_11_12_12_13_12_11_13_12_11_13_11_14_12_15_15_11_14_14_14_14_12_12_14_14_11_12_12_15_11_11_12_11_11_11_12_11_15_11_13_15_13_14_12_12_13_13_11_13_13_14_11_11_11_14_15_12_12_13_13_14_12_14_11_12_12_15_11_14_13_12_12_11_14_12_14_13_13_12_11_11_12_12_13_15_12_13_14_12_12_11_11_11_12_14_14_14_14_12_11_11_14_14_11_13_13_11_14_11_11_12_13_13_13_11_12_14_11_12_11_14_14_12_11_13_15_14_12_11_12_13_13_13_13_13_14_14_11_12_13_13_13_13_11_11_13_11_12_12_13_14_14_15_11_12_13_15_11_11_11_13_13_11_14_13_13_11_15_13_14_12_12_11_12_12_11_13_15_14_13_11_13_13_15_15_15_11_11_11_11_12_12_14_12_12_11_12_12_12_12_12_11_11_12_12_11_12_14_13_13_13_12_11_12_13_11_13_13_12_14_11_13_15_15_12_12_13_15_14_11_11_15_13_13_15_12_12_11_11_15_14_11_11_13_11_12_15_13_14_13_11_13_14_11_11_14_15_15_14_13_13_14_14_14_14_11_11_11_11_11_14_12_13_13_12_11_15_14_15_14_13_12_11_11_13_12_11_11_12_14_15_12_12_11_11_15_14_14_12_13</t>
+  </si>
+  <si>
+    <t>11_13_11_14_13_13_11_13_14_12_11_14_12_12_11_12_11_12_12_12_11_11_12_12_13_12_12_12_12_14_12_15_11_14_14_13_15_11_11_11_14_13_12_13_11_13_15_11_11_13_13_13_15_15_11_12_11_15_12_12_11_14_14_12_12_12_14_14_11_11_11_15_11_15_11_15_15_14_13_15_13_11_14_12_12_15_11_11_11_11_15_11_11_11_12_11_13_14_15_14_11_13_14_13_13_14_13_12_13_15_15_15_15_13_12_12_13_14_11_13_13_12_11_11_12_13_11_13_11_14_15_12_13_14_14_14_11_11_14_11_11_11_14_14_15_15_12_11_14_13_12_12_11_15_14_13_14_13_15_15_15_11_15_15_14_11_11_12_12_15_13_14_14_11_15_15_12_12_13_13_15_13_13_11_11_14_15_13_14_11_15_12_11_12_11_12_13_12_12_13_12_12_12_15_11_15_14_14_14_14_13_15_15_11_13_12_13_14_14_14_12_13_13_14_13_13_12_15_14_11_12_14_12_12_15_12_11_11_15_15_13_15_13_12_15_12_15_14_12_15_15_13_13_11_12_12_12_11_15_15_15_14_11_11_11_14_15_12_13_14_13_14_12_13_11_11_13_15_11_14_12_11_15_14_12_11_13_13_13_13_13_11_11_12_13_11_15_13_13_13_12_14_11_14_14_11_13_12_11_13_11_11_13_12_14_11_12_14_15_13_13_13_13_13_14_11_12_13_15_11_14_11_14_11_13_13_12_12_12_12_12_13_13_11_14_13_13_12_13_12_11_14_14_15_13_14_11_14_11_14_11_13_13_13_14_13_13_15_11_13_13_13_13_15_11_11_14_13_11_13_12_13_15_13_14_13_15_11_12_15_15_11_11_11_14_14_11_13_14_15_12_13_15_13_15_12_13_11_11_12_12_12_15_11_14_12_13_15_13_11_12_11_11_11_14_11_11_11_11_15_13_12_12_13_13_11_14_14_14_11_14_15_14_12_14_14_14_12_13_14_12_12_13_14_15_15_15_11_12_12_15_15_14_14_11_11_11_13_13_12_15_12_15_14_12_11_14_13_13_13_14_12_14_11_12_11_11_13_13_13_13_13_13_12_11_11_11_14_14_11</t>
+  </si>
+  <si>
+    <t>14_11_14_11_15_12_13_14_13_14_11_12_15_12_12_11_13_11_11_14_15_14_11_12_14_15_11_11_11_12_12_11_13_13_13_11_13_14_13_12_12_14_11_15_15_12_15_11_13_13_13_13_11_14_15_15_13_13_12_11_13_11_15_13_15_14_14_12_12_11_13_11_11_13_13_12_12_12_14_14_13_14_11_11_14_11_13_11_12_14_12_11_11_13_14_11_13_11_11_11_13_11_15_14_14_11_11_11_11_14_11_15_13_13_11_11_13_14_11_11_15_11_13_11_12_14_12_11_11_14_11_14_12_14_13_11_11_12_13_15_13_11_12_12_11_12_14_14_12_11_11_11_12_14_14_14_13_11_14_14_11_13_11_11_15_14_12_12_11_11_12_12_12_13_11_15_13_12_12_11_12_11_13_13_14_12_15_14_12_11_14_13_11_14_12_15_13_14_15_12_13_12_15_12_11_11_14_13_13_13_13_15_15_15_13_11_15_13_12_12_13_11_13_11_12_13_11_15_15_11_15_14_11_13_12_13_11_13_11_12_14_12_12_14_12_13_11_14_14_12_13_14_14_13_14_14_11_11_11_12_14_12_14_12_15_11_12_12_13_11_12_12_11_11_11_13_13_13_12_15_14_15_15_12_13_15_14_11_13_11_12_11_14_14_12_12_12_11_13_12_12_13_12_11_13_13_15_15_11_11_14_14_11_14_12_13_13_12_14_11_14_12_11_11_12_12_14_13_11_15_15_13_13_13_12_11_11_14_11_11_15_15_14_13_12_12_12_12_13_11_11_14_11_12_13_11_11_11_13_11_11_14_13_13_13_13_11_13_13_12_12_12_14_13_12_11_13_14_11_12_12_11_11_11_11_12_11_14_15_14_11_11_14_14_12_12_13_11_12_15_14_11_11_11_13_14_13_12_13_14_14_11_12_12_11_11_12_14_14_11_11_11_12_13_11_11_11_11_11_14_13_11_11_12_13_14_11_14_13_13_13_13_11_11_15_13_13_11_15_15_15_12_15_13_12_14_14_14_12_11_11_12_11_14_14_11_15_15_11_13_15_11_12_13_14_11_13_15_11_11_15_14_14_14_14_15_15_14_12_13_13_11_14_11_11_11_11_12_13_13</t>
+  </si>
+  <si>
+    <t>13_13_14_13_13_11_14_15_11_11_13_11_13_12_14_14_13_12_11_14_12_12_12_12_11_11_13_15_11_12_13_15_14_13_13_11_13_11_14_13_12_13_13_13_13_13_11_12_13_11_11_14_13_11_11_11_11_11_13_12_13_13_12_12_11_14_12_12_13_13_12_11_11_14_12_12_11_11_11_12_13_12_11_11_14_13_12_12_11_13_12_13_13_13_11_12_11_13_12_12_13_14_15_12_11_13_15_13_14_12_15_15_11_11_12_14_12_12_13_14_14_14_11_14_11_11_11_11_13_12_13_13_12_15_11_13_14_13_12_13_14_14_13_12_14_14_13_11_12_12_12_11_14_11_13_13_15_11_12_11_15_14_11_13_12_11_11_11_12_12_15_11_13_11_11_11_11_11_13_11_11_12_11_13_12_12_13_11_11_11_15_12_12_12_12_12_11_12_12_12_12_15_13_15_12_11_15_11_14_13_15_11_15_11_11_11_12_12_11_12_11_12_14_11_11_12_13_13_14_12_14_11_11_11_14_11_11_12_13_13_12_12_15_12_12_12_12_11_12_15_15_13_13_14_11_11_14_14_12_12_13_15_15_11_12_15_15_15_12_11_11_11_15_12_14_12_11_14_14_12_13_14_14_11_13_11_12_12_12_11_13_12_13_15_12_11_11_15_11_11_11_13_13_14_13_12_13_15_11_11_11_12_13_13_13_12_14_14_13_12_15_15_13_12_11_12_12_15_12_12_14_12_15_13_11_12_12_11_11_11_11_11_14_11_11_13_15_11_11_12_13_12_14_12_13_12_14_15_12_15_11_14_12_11_14_11_11_11_11_13_14_12_12_12_14_13_11_14_11_15_13_13_11_12_15_14_12_11_11_11_13_12_15_15_13_13_11_14_12_12_15_11_15_11_15_15_14_11_13_11_14_12_12_11_14_14_14_11_14_11_11_14_12_14_15_11_12_14_13_13_15_15_14_15_13_13_13_12_12_12_15_15_15_11_13_11_14_13_13_12_13_14_12_13_13_11_13_13_13_13_12_15_12_15_13_11_15_11_11_13_11_13_14_12_12_14_13_11_12_13_15_15_15_12_11_11_11_14_11_13_15_14_12_13_14_14_13_13_11_12</t>
+  </si>
+  <si>
+    <t>12_15_11_12_11_14_11_13_13_13_13_13_13_13_13_13_12_11_12_12_13_13_11_13_13_13_13_14_14_13_13_12_11_11_12_12_14_15_14_11_11_11_12_13_12_13_13_14_11_11_14_14_13_11_11_15_13_14_15_12_12_12_13_13_11_15_14_11_14_15_13_12_11_11_13_11_11_12_12_12_11_13_11_14_12_13_15_13_11_11_11_11_12_12_11_12_12_12_14_12_12_13_13_15_14_13_11_12_11_15_15_11_12_12_13_13_13_13_11_11_12_12_12_14_14_12_11_12_13_13_15_11_11_11_11_13_12_14_14_12_14_13_13_12_15_15_14_14_11_15_11_14_11_12_13_14_14_11_11_12_13_12_14_13_13_11_15_15_15_13_12_15_12_15_13_15_11_15_13_13_12_13_14_11_12_13_14_14_11_15_12_13_11_11_12_12_14_12_13_13_13_14_14_11_12_15_11_11_11_15_11_11_12_13_14_12_12_12_11_15_11_14_14_13_14_12_11_13_15_11_13_11_15_14_11_12_14_14_13_13_11_15_15_12_12_15_12_12_13_11_14_11_13_12_12_15_11_13_11_13_13_13_12_11_12_11_15_13_14_11_11_11_12_11_12_13_14_13_14_13_11_15_15_15_13_15_12_11_13_14_12_12_15_11_11_13_11_11_13_11_11_13_11_13_15_13_14_13_13_15_12_15_15_11_11_11_11_11_13_13_13_11_12_12_12_13_13_14_12_11_11_13_13_11_14_14_13_11_13_14_11_13_13_11_11_13_12_12_13_14_11_11_12_11_11_11_11_11_14_13_14_14_13_11_11_11_15_15_14_14_12_15_14_12_11_15_14_14_15_12_15_13_11_12_13_12_13_11_12_12_13_13_11_14_13_12_14_14_12_13_15_15_15_14_12_13_13_12_12_12_11_13_13_11_11_13_13_12_14_11_13_15_13_11_14_14_12_12_14_14_15_14_14_14_15_11_12_11_14_13_11_15_12_12_13_11_11_12_14_14_13_14_15_14_11_11_13_12_11_12_12_15_12_15_11_13_11_13_12_12_14_11_12_12_15_15_13_13_14_12_11_14_13_13_14_15_14_12_11_15_12_15_11_15_15_12_12_14_14_13</t>
   </si>
 </sst>
 </file>
@@ -2675,7 +2741,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K309"/>
+  <dimension ref="A1:K324"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375"/>
@@ -10649,7 +10715,7 @@
         <v>20</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J258" s="38"/>
       <c r="K258" s="38"/>
@@ -10674,13 +10740,13 @@
         <v>20</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J259" s="38"/>
       <c r="K259" s="38"/>
@@ -10705,13 +10771,13 @@
         <v>20</v>
       </c>
       <c r="G260" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J260" s="38"/>
       <c r="K260" s="38"/>
@@ -10736,13 +10802,13 @@
         <v>20</v>
       </c>
       <c r="G261" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J261" s="38"/>
       <c r="K261" s="38"/>
@@ -10767,13 +10833,13 @@
         <v>20</v>
       </c>
       <c r="G262" s="7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J262" s="38"/>
       <c r="K262" s="38"/>
@@ -10798,13 +10864,13 @@
         <v>20</v>
       </c>
       <c r="G263" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I263" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="K263" s="9"/>
     </row>
@@ -10828,13 +10894,13 @@
         <v>20</v>
       </c>
       <c r="G264" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I264" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K264" s="9"/>
     </row>
@@ -10858,13 +10924,13 @@
         <v>20</v>
       </c>
       <c r="G265" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I265" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K265" s="9"/>
     </row>
@@ -10888,13 +10954,13 @@
         <v>20</v>
       </c>
       <c r="G266" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I266" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K266" s="9"/>
     </row>
@@ -10918,13 +10984,13 @@
         <v>20</v>
       </c>
       <c r="G267" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I267" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K267" s="9"/>
     </row>
@@ -10948,13 +11014,13 @@
         <v>20</v>
       </c>
       <c r="G268" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I268" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K268" s="9"/>
     </row>
@@ -10972,19 +11038,19 @@
         <v>1</v>
       </c>
       <c r="E269" s="19" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G269" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I269" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J269" s="33"/>
       <c r="K269" s="33"/>
@@ -11003,19 +11069,19 @@
         <v>2</v>
       </c>
       <c r="E270" s="19" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G270" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I270" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J270" s="33"/>
       <c r="K270" s="33"/>
@@ -11034,19 +11100,19 @@
         <v>3</v>
       </c>
       <c r="E271" s="19" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G271" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I271" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J271" s="33"/>
       <c r="K271" s="33"/>
@@ -11065,19 +11131,19 @@
         <v>4</v>
       </c>
       <c r="E272" s="19" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G272" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I272" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J272" s="33"/>
       <c r="K272" s="33"/>
@@ -11096,19 +11162,19 @@
         <v>5</v>
       </c>
       <c r="E273" s="19" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G273" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I273" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J273" s="33"/>
       <c r="K273" s="33"/>
@@ -11127,19 +11193,19 @@
         <v>6</v>
       </c>
       <c r="E274" s="19" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G274" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I274" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J274" s="33"/>
       <c r="K274" s="33"/>
@@ -11158,19 +11224,19 @@
         <v>7</v>
       </c>
       <c r="E275" s="19" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I275" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J275" s="33"/>
       <c r="K275" s="33"/>
@@ -11195,13 +11261,13 @@
         <v>20</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J276" s="33"/>
     </row>
@@ -11225,13 +11291,13 @@
         <v>20</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J277" s="33"/>
     </row>
@@ -11255,13 +11321,13 @@
         <v>20</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J278" s="33"/>
     </row>
@@ -11279,19 +11345,19 @@
         <v>4</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J279" s="33"/>
     </row>
@@ -11315,13 +11381,13 @@
         <v>20</v>
       </c>
       <c r="G280" t="s">
-        <v>407</v>
+        <v>194</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I280" t="s">
-        <v>408</v>
+        <v>194</v>
       </c>
       <c r="J280" s="33"/>
       <c r="K280" s="33"/>
@@ -11346,13 +11412,13 @@
         <v>20</v>
       </c>
       <c r="G281" t="s">
-        <v>382</v>
+        <v>182</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I281" t="s">
-        <v>383</v>
+        <v>182</v>
       </c>
       <c r="J281" s="33"/>
       <c r="K281" s="33"/>
@@ -11377,13 +11443,13 @@
         <v>20</v>
       </c>
       <c r="G282" t="s">
-        <v>385</v>
+        <v>185</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I282" t="s">
-        <v>386</v>
+        <v>185</v>
       </c>
       <c r="J282" s="33"/>
       <c r="K282" s="33"/>
@@ -11408,13 +11474,13 @@
         <v>20</v>
       </c>
       <c r="G283" t="s">
-        <v>388</v>
+        <v>188</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I283" t="s">
-        <v>389</v>
+        <v>188</v>
       </c>
       <c r="J283" s="33"/>
       <c r="K283" s="33"/>
@@ -11439,13 +11505,13 @@
         <v>20</v>
       </c>
       <c r="G284" t="s">
-        <v>391</v>
+        <v>191</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I284" t="s">
-        <v>392</v>
+        <v>191</v>
       </c>
       <c r="J284" s="33"/>
       <c r="K284" s="33"/>
@@ -11470,13 +11536,13 @@
         <v>20</v>
       </c>
       <c r="G285" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I285" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="J285" s="33"/>
       <c r="K285" s="33"/>
@@ -11501,13 +11567,13 @@
         <v>20</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J286" s="33"/>
     </row>
@@ -11531,13 +11597,13 @@
         <v>20</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I287" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J287" s="33"/>
     </row>
@@ -11561,13 +11627,13 @@
         <v>20</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J288" s="33"/>
     </row>
@@ -11585,19 +11651,19 @@
         <v>4</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J289" s="33"/>
     </row>
@@ -11621,13 +11687,13 @@
         <v>20</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I290" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J290" s="33"/>
     </row>
@@ -11651,13 +11717,13 @@
         <v>20</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J291" s="33"/>
     </row>
@@ -11681,13 +11747,13 @@
         <v>20</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I292" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J292" s="33"/>
     </row>
@@ -11705,19 +11771,19 @@
         <v>4</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I293" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="J293" s="33"/>
     </row>
@@ -11735,19 +11801,19 @@
         <v>1</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G294" s="39" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I294" s="39" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="J294" s="40"/>
       <c r="K294" s="40"/>
@@ -11766,7 +11832,7 @@
         <v>2</v>
       </c>
       <c r="E295" s="34" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F295" s="35" t="s">
         <v>20</v>
@@ -11797,7 +11863,7 @@
         <v>3</v>
       </c>
       <c r="E296" s="34" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F296" s="35" t="s">
         <v>20</v>
@@ -11890,19 +11956,19 @@
         <v>1</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G299" s="39" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I299" s="39" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J299" s="40"/>
       <c r="K299" s="40"/>
@@ -11921,7 +11987,7 @@
         <v>2</v>
       </c>
       <c r="E300" s="34" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F300" s="35" t="s">
         <v>20</v>
@@ -11951,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="E301" s="34" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F301" s="35" t="s">
         <v>20</v>
@@ -12048,13 +12114,13 @@
         <v>20</v>
       </c>
       <c r="G304" s="39" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H304" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I304" s="39" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J304" s="41"/>
     </row>
@@ -12079,13 +12145,13 @@
         <v>20</v>
       </c>
       <c r="G305" s="39" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H305" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I305" s="39" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J305" s="41"/>
     </row>
@@ -12110,13 +12176,13 @@
         <v>20</v>
       </c>
       <c r="G306" s="39" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H306" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I306" s="39" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J306" s="41"/>
     </row>
@@ -12141,13 +12207,13 @@
         <v>20</v>
       </c>
       <c r="G307" s="39" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H307" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I307" s="39" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J307" s="41"/>
     </row>
@@ -12172,13 +12238,13 @@
         <v>20</v>
       </c>
       <c r="G308" s="39" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="H308" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I308" s="39" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J308" s="41"/>
     </row>
@@ -12203,15 +12269,450 @@
         <v>20</v>
       </c>
       <c r="G309" s="39" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="H309" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I309" s="39" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="J309" s="41"/>
+    </row>
+    <row r="310" ht="16.5" spans="1:10">
+      <c r="A310" s="6">
+        <v>10520011</v>
+      </c>
+      <c r="B310" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C310" s="19">
+        <v>2052001</v>
+      </c>
+      <c r="D310" s="19">
+        <v>1</v>
+      </c>
+      <c r="E310" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F310" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G310" t="s">
+        <v>432</v>
+      </c>
+      <c r="H310" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I310" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="311" ht="16.5" spans="1:10">
+      <c r="A311" s="6">
+        <v>10520012</v>
+      </c>
+      <c r="B311" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C311" s="19">
+        <v>2052001</v>
+      </c>
+      <c r="D311" s="19">
+        <v>2</v>
+      </c>
+      <c r="E311" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="F311" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G311" t="s">
+        <v>434</v>
+      </c>
+      <c r="H311" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I311" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="312" ht="16.5" spans="1:10">
+      <c r="A312" s="6">
+        <v>10520013</v>
+      </c>
+      <c r="B312" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C312" s="19">
+        <v>2052001</v>
+      </c>
+      <c r="D312" s="19">
+        <v>3</v>
+      </c>
+      <c r="E312" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F312" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G312" t="s">
+        <v>436</v>
+      </c>
+      <c r="H312" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I312" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="313" ht="16.5" spans="1:10">
+      <c r="A313" s="6">
+        <v>10520014</v>
+      </c>
+      <c r="B313" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C313" s="19">
+        <v>2052001</v>
+      </c>
+      <c r="D313" s="19">
+        <v>4</v>
+      </c>
+      <c r="E313" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F313" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G313" t="s">
+        <v>438</v>
+      </c>
+      <c r="H313" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I313" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="314" ht="16.5" spans="1:10">
+      <c r="A314" s="6">
+        <v>10520015</v>
+      </c>
+      <c r="B314" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C314" s="19">
+        <v>2052002</v>
+      </c>
+      <c r="D314" s="19">
+        <v>1</v>
+      </c>
+      <c r="E314" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="F314" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G314" t="s">
+        <v>439</v>
+      </c>
+      <c r="H314" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I314" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="315" ht="16.5" spans="1:10">
+      <c r="A315" s="6">
+        <v>10520016</v>
+      </c>
+      <c r="B315" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C315" s="19">
+        <v>2052002</v>
+      </c>
+      <c r="D315" s="19">
+        <v>2</v>
+      </c>
+      <c r="E315" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="F315" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G315" t="s">
+        <v>440</v>
+      </c>
+      <c r="H315" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I315" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="316" ht="16.5" spans="1:10">
+      <c r="A316" s="6">
+        <v>10520017</v>
+      </c>
+      <c r="B316" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C316" s="19">
+        <v>2052002</v>
+      </c>
+      <c r="D316" s="19">
+        <v>3</v>
+      </c>
+      <c r="E316" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F316" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G316" t="s">
+        <v>441</v>
+      </c>
+      <c r="H316" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I316" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="317" ht="16.5" spans="1:10">
+      <c r="A317" s="6">
+        <v>10520018</v>
+      </c>
+      <c r="B317" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C317" s="19">
+        <v>2052002</v>
+      </c>
+      <c r="D317" s="19">
+        <v>4</v>
+      </c>
+      <c r="E317" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="F317" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G317" t="s">
+        <v>442</v>
+      </c>
+      <c r="H317" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I317" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="318" ht="16.5" spans="1:10">
+      <c r="A318" s="6">
+        <v>10520019</v>
+      </c>
+      <c r="B318" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C318" s="19">
+        <v>2052002</v>
+      </c>
+      <c r="D318" s="19">
+        <v>5</v>
+      </c>
+      <c r="E318" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F318" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G318" t="s">
+        <v>443</v>
+      </c>
+      <c r="H318" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I318" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="319" ht="16.5" spans="1:10">
+      <c r="A319" s="6">
+        <v>10520020</v>
+      </c>
+      <c r="B319" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C319" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D319" s="19">
+        <v>1</v>
+      </c>
+      <c r="E319" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="F319" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G319" t="s">
+        <v>444</v>
+      </c>
+      <c r="H319" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I319" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="320" ht="16.5" spans="1:10">
+      <c r="A320" s="6">
+        <v>10520021</v>
+      </c>
+      <c r="B320" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C320" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D320" s="19">
+        <v>2</v>
+      </c>
+      <c r="E320" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F320" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G320" t="s">
+        <v>445</v>
+      </c>
+      <c r="H320" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I320" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="321" ht="16.5" spans="1:9">
+      <c r="A321" s="6">
+        <v>10520022</v>
+      </c>
+      <c r="B321" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C321" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D321" s="19">
+        <v>3</v>
+      </c>
+      <c r="E321" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="F321" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G321" t="s">
+        <v>446</v>
+      </c>
+      <c r="H321" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I321" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="322" ht="16.5" spans="1:9">
+      <c r="A322" s="6">
+        <v>10520023</v>
+      </c>
+      <c r="B322" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C322" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D322" s="19">
+        <v>4</v>
+      </c>
+      <c r="E322" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="F322" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G322" t="s">
+        <v>447</v>
+      </c>
+      <c r="H322" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I322" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="323" ht="16.5" spans="1:9">
+      <c r="A323" s="6">
+        <v>10520024</v>
+      </c>
+      <c r="B323" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C323" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D323" s="19">
+        <v>5</v>
+      </c>
+      <c r="E323" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="F323" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G323" t="s">
+        <v>448</v>
+      </c>
+      <c r="H323" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I323" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="324" ht="16.5" spans="1:9">
+      <c r="A324" s="6">
+        <v>10520025</v>
+      </c>
+      <c r="B324" s="6">
+        <v>105200</v>
+      </c>
+      <c r="C324" s="19">
+        <v>2052003</v>
+      </c>
+      <c r="D324" s="19">
+        <v>6</v>
+      </c>
+      <c r="E324" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F324" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G324" t="s">
+        <v>449</v>
+      </c>
+      <c r="H324" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I324" t="s">
+        <v>449</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseRoller.xlsx
+++ b/slots/resources/sample/BaseRoller.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -79,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="407">
   <si>
     <t>id</t>
   </si>
@@ -804,31 +809,31 @@
     <t>2_1_6_2_2_2_2_1_9_6_2_8_7_9_5_1_3_4_5_3_4_7_5_2_6_4_2_1_4_8_6_2_7_7_5_7_9_7_4_8_6_5_2_3_10_5_1_4_9_3_10_4_7_9_2_4_3_7_1_7_4_5_6_10_6_10_7_10_1_1_6_6_2_1_3_2_1_5_2_10_5_5_7_10_6_3_4_2_2_6_3_6_9_7_2_3_8_5_2_2_1_4_3_6_5_4_8_2_7_6_10_7_5_2_9_6_4_2_1_5_4_8_2_6_4_4_3_1_3_8_6_2_5_7_4_2_3_8_4_8_1_1_8_7_2_6_4_3_5_1_4_7_8_5_9_2_3_5_9_7_7_1_3_7_8_5_1_9_6_6_2_7_8_2_3_2_7_5_2_4_2_8_7_2_7_4_8_1_4_1_2_1_4_2_4_2_2_5_6_1_5_7_5_4_5_4_1_3_4_3_3_7_1_6_4_2_6_4_9_5_8_8_5_8_5_2_2_5_7_7_8_8_1_8_9_1_6_3_3_3_1_3_4_7_1_3_5_4_5_2_2_4_3_2_1_9_3_1_4_1_8_3_5_5_8_3_3_10_1_2_3_3_9_7_2_5_8_5_4_4_9_1_1_5_4_3_4_1_8_9_4_5_1_2_2_4_1_8_7_6_1_4_7_6_3_3_3_9_5_1_6_3_4_5_3_1_4_7_9_2_2_7_9_5_2_6_3_6_5_6_2_2_4_2_5_9_4_1_9_4_4_6_3_1_5_4_6_6_2_10_7_5_4_6_9_5_3_6_9_6_7_4_7_3_8_3_6_4_6_2_9_6_10_4_8_1_8_9_7_5_7_2_10_1_8_2_5_8_2_6_9_3_5_1_3_4_5_8_7_10_3_8_2_2_2_5_2_8_2_8_4_5_2_3_3_6_8_1_2_7_4_1_2_1_8_4_3_7_7_1_3_5_1_1_7_7_3_5_8_2_2_2_1_5_3_9_3_1_7_4_1_10_7_6_2_8_7_4_1_9_2_7_2_6_4_1_5_3_1_8_4_1_3_6_9_1_4_1_9_3_2_2_4_4_6_3_1_2_1_6_1_7_7_5_8_4_5_1_8_7</t>
   </si>
   <si>
-    <t>6_4_4_3_2_2_1_3_3_1_1_2_6_3_3_3_4_3_1_1_7_1_2_7_2_3_2_2_2_1_4_3_3_2_2_6_3_5_1_7_6_6_4_8_6_6_6_7_2_2_1_5_8_5_1_5_5_5_5_7_5_6_7_3_6_2_3_6_6_1_1_1_5_5_5_3_4_3_2_2_3_3_2_2_5_1_4_1_5_1_4_1_2_7_1_4_3_5_2_2_1_2_1_4_5_3_2_3_3_3_1_1_2_2_5_2_2_2_3_5_3_6_6_2_1_2_2_1_2_5_3_8_2_2_3_7_3_8_1_3_3_2_3_6_6_8_6_4_4_2_4_4_2_6_3_4_4_2_5_1_6_1_8_2_7_3_8_1_1_2_3_7_5_4_4_6_4_1_3_2_2_3_3_4_4_1_1_5_1_1_1_4_2_8_5_3_3_3_1_2_2_7_3_2_1_1_1_1_7_7_1_4_8_2_8_1_8_3_6_3_6_6_1_1_2_2_2_2_1_2_2_4_4_2_2_2_8_3_8_6_6_1_1_2_1_6_1_4_2_1_7_6_1_4_3_5_7_1_3_4_4_4_3_3_1_1_1_1_2_4_4_7_5_6_4_2_1_6_6_3_1_3_1_3_5_4_2_4_1_1_2_2_3_6_2_2_2_2_8_4_7_6_3_3_7_1_1_2_1_1_2_2_8_2_2_1_3_1_2_7_3_2_7_3_3_1_1_4_2_4_2_2_8_4_3_7_3_7_3_3_6_6_2_2_8_3_1_7_1_3_6_3_2_2_2_2_3_3_5_1_1_4_8_5_4_7_2_5_2_6_2_1_4_3_3_5_3_2_3_3_4_5_7_7_4_4_2_5_3_6_1_8_5_6_1_2_3_5_3_1_5_2_5_8_3_2_7_4_6_3_1_1_6_1_4_4_4_1_2_2_7_2_1_5_8_4_8_3_6_4_1_2_7_3_6_3_3_6_8_5_1_5_4_2_3_6_7_2_2_7_4_4_4_2_3_2_7_5_1_1_3_1_8_7_3_5_2_7_1_1_7_1_1_1_8_1_5_6_3_1_7_7_7_1_1_6_2_3_3_8_8_2_4_3_3_4_4_3_2_1</t>
+    <t>3_3_2_3_2_5_4_3_4_6_7_2_2_2_4_6_7_1_1_7_6_1_4_4_6_6_6_6_1_1_2_7_1_1_6_5_1_6_5_5_1_1_2_3_4_5_2_4_1_3_4_2_6_4_4_4_2_1_4_2_6_8_5_7_2_3_5_4_3_2_1_6_2_7_1_4_4_6_3_1_5_6_1_8_2_2_6_6_1_6_8_2_6_5_3_4_5_2_5_4_7_7_7_6_3_4_6_2_2_1_4_6_8_3_3_2_2_4_1_6_6_6_5_2_8_8_8_8_6_3_6_8_2_2_2_1_2_7_2_2_4_4_1_3_1_2_8_3_1_2_8_3_3_8_1_6_4_5_7_3_3_7_4_3_5_5_5_6_2_4_8_6_2_5_5_4_3_4_5_8_3_2_3_8_1_2_2_1_5_1_1_4_2_2_4_8_3_1_2_6_7_4_3_1_7_5_6_2_3_1_3_3_3_2_2_1_6_4_2_4_7_2_4_4_4_7_7_5_8_2_1_7_1_4_4_4_1_5_5_4_2_2_3_8_8_3_4_8_2_3_3_4_8_1_7_8_8_8_1_3_5_5_5_7_1_1_1_1_3_3_6_7_8_3_2_2_1_5_4_2_1_2_4_4_3_2_3_3_2_8_3_7_1_1_3_1_3_6_1_1_7_4_5_8_4_4_2_1_8_7_5_8_6_8_3_8_8_8_2_2_7_3_2_3_1_4_6_2_4_5_5_3_2_7_7_7_5_5_1_3_2_7_3_4_2_2_2_3_3_3_2_1_8_3_8_2_8_2_3_2_8_4_4_1_7_8_8_6_2_8_4_8_8_1_8_3_7_7_1_8_8_1_8_1_2_3_8_3_2_8_7_8_3_2_2_5_4_3_3_2_2_1_7_8_8_4_7_3_1_6_6_6_6_8_3_8_1_4_6_1_2_6_2_2_2_6_4_4_1_1_1_8_6_3_4_7_4_1_1_4_6_2_8_7_5_4_5_5_3_6_5_7_8_3_5_4_6_3_3_6_3_2_4_4_8_8_2_5_1_7_6_6_5_8_8_4_7_7_2_7_7_2_3_1_2_4_1_8_5_3_1_1_1_1_1_6_4_7_5_4</t>
   </si>
   <si>
     <t>6_6_2_4_1_1_7_3_2_4_1_4_9_6_4_8_9_6_3_7_9_9_8_1_7_10_5_10_3_6_1_3_5_3_2_5_1_5_5_6_3_8_6_5_4_3_6_8_3_2_7_1_2_8_10_2_5_9_2_8_5_6_3_6_10_4_5_4_5_7_2_10_7_6_4_3_3_3_5_2_5_1_5_8_3_1_1_5_4_9_9_2_6_2_8_4_6_4_2_3_1_9_1_7_4_6_6_9_2_7_3_5_7_2_3_10_1_4_7_2_1_9_1_8_1_2_2_4_3_5_1_1_7_2_3_4_5_6_10_5_3_5_3_9_7_9_6_1_3_7_5_6_1_1_4_9_8_6_5_1_9_7_1_2_4_3_9_1_1_7_5_5_2_6_9_3_2_3_9_1_10_6_4_3_7_6_6_1_1_4_1_3_4_6_8_1_5_5_7_9_6_1_9_3_7_2_3_1_1_5_6_1_6_2_3_7_1_2_9_4_9_9_8_8_8_6_8_4_2_3_2_4_3_7_6_1_2_4_6_5_9_2_2_6_2_3_5_6_6_5_10_7_8_5_8_2_5_3_1_7_4_1_6_2_7_2_9_9_9_3_5_2_5_2_9_2_1_6_2_3_5_5_10_2_2_2_7_9_4_4_9_4_8_2_5_3_7_5_6_8_5_2_10_5_4_6_3_9_1_6_2_6_3_7_8_6_1_8_3_6_5_7_5_4_2_8_3_8_4_1_7_2_9_3_6_6_3_8_6_7_1_2_3_8_3_1_7_4_9_4_8_2_2_1_9_4_1_9_9_3_1_1_9_9_10_5_2_1_5_2_7_2_5_1_8_2_2_6_6_9_6_8_2_3_6_2_3_4_4_10_2_6_4_10_1_4_3_2_9_4_1_9_6_4_7_5_9_6_3_8_4_7_2_4_5_2_1_2_4_8_4_8_6_1_7_5_1_1_5_1_8_8_4_7_4_6_1_2_6_3_4_10_6_3_1_5_7_3_9_1_1_10_6_7_6_3_5_7_8_5_4_2_4_10_5_3_2_8_8_3_7_7_9_5_3_6_9_2_2_2_3_7_1_3_3_2_6_2_6_1_3_3_2_1_1_9_1_5_4_9</t>
   </si>
   <si>
-    <t>1_2_4_1_6_3_5_4_4_6_2_5_3_6_3_3_5_3_1_2_2_6_2_1_3_3_3_3_6_5_7_2_4_6_4_6_5_2_2_6_2_1_5_4_2_2_3_7_7_1_1_3_6_4_4_2_1_4_8_7_1_3_6_7_3_2_3_7_1_4_3_8_5_3_7_5_7_2_2_7_8_4_7_7_7_3_3_4_3_3_4_6_1_3_3_5_6_1_1_8_1_7_8_2_2_2_1_5_3_3_8_4_5_2_4_4_7_7_7_2_2_4_3_2_5_1_1_2_2_1_1_5_5_5_4_8_7_3_7_5_4_1_2_3_1_5_5_2_4_8_8_3_3_1_1_4_4_5_4_3_5_4_4_2_2_2_4_8_2_1_2_7_2_1_3_2_2_3_1_3_6_4_4_4_6_1_2_1_1_2_2_3_6_6_3_4_4_4_2_2_2_1_1_5_3_5_1_2_2_1_1_7_3_6_8_1_7_2_4_1_5_5_2_1_7_1_8_3_3_3_4_4_4_2_2_4_4_4_1_2_2_1_5_3_6_8_4_3_8_7_7_7_3_1_6_5_5_1_1_5_3_2_5_7_8_5_3_6_3_3_5_3_3_3_3_4_4_2_2_6_7_1_5_1_3_2_2_5_5_5_3_1_1_7_4_7_1_2_2_8_3_5_1_7_1_5_7_7_2_4_2_7_7_4_1_2_2_3_8_7_8_8_6_4_5_1_6_3_1_1_8_7_6_2_2_7_7_5_3_4_1_4_1_6_5_7_3_4_1_6_3_8_8_4_4_4_7_3_3_2_6_1_8_5_5_4_3_1_1_3_1_3_5_8_6_1_2_5_2_1_8_8_3_4_1_6_7_3_8_3_3_4_4_4_4_4_2_1_3_5_3_1_1_7_1_1_2_6_7_1_6_5_3_2_4_4_4_4_5_3_7_2_4_2_2_2_6_6_1_3_6_1_4_4_4_4_7_4_1_4_3_3_2_7_1_5_5_1_1_6_3_1_2_2_2_7_2_4_5_3_3_3_1_1_1_4_3_2_4_1_7_7_3_2_3_7_3_2_5_2_7_7_3_1_1_4_2_4_3_2_8_5_1_7_2_4_8_3_1_1</t>
+    <t>7_5_3_3_5_4_1_2_3_7_7_6_5_2_1_6_1_7_4_4_1_3_7_7_7_3_1_4_1_4_4_8_3_5_5_7_8_2_5_8_2_2_7_5_6_1_6_3_5_1_7_1_7_3_3_7_6_2_5_4_7_2_2_5_3_5_5_1_2_3_5_3_3_2_1_4_3_8_6_7_7_7_8_3_8_2_5_2_2_2_6_3_2_1_8_6_4_2_2_2_7_4_1_2_1_2_8_8_5_8_7_4_4_5_2_1_5_2_5_8_4_4_6_6_2_1_2_8_3_7_3_3_1_8_1_1_4_4_4_4_4_3_1_3_4_4_4_2_1_1_4_7_6_8_8_4_1_1_2_8_5_8_8_8_8_1_4_5_1_2_2_7_4_7_7_8_4_5_1_3_1_8_2_3_4_5_1_8_2_1_1_3_7_4_7_4_3_7_1_7_5_6_4_7_8_8_1_6_7_7_1_2_4_8_2_2_8_1_3_2_2_7_2_2_2_8_8_3_3_4_2_5_6_7_1_6_5_2_3_8_2_2_1_1_5_7_1_1_2_5_5_5_8_1_7_5_8_2_1_7_7_8_4_4_4_7_6_5_5_7_2_6_5_1_1_6_8_2_4_8_2_7_2_3_2_2_4_4_8_6_4_8_1_1_5_4_1_3_2_4_4_5_2_8_2_7_2_1_8_2_7_5_3_3_3_2_4_2_7_4_2_5_2_4_4_7_7_4_5_7_1_4_4_4_4_2_6_8_4_4_7_7_3_3_1_3_3_5_5_6_5_2_1_5_1_7_4_5_1_4_8_4_5_3_4_4_8_3_3_4_2_4_8_8_5_4_5_7_7_7_2_8_7_3_4_4_4_3_3_5_7_2_4_6_2_2_1_8_5_7_4_6_5_5_4_4_6_6_6_1_2_5_1_4_7_5_8_4_8_5_6_6_6_7_7_2_1_2_3_1_1_1_5_8_4_3_7_8_5_5_5_2_3_2_3_2_8_1_1_8_1_6_6_4_4_4_4_2_7_5_7_1_7_5_5_4_4_4_2_1_1_8_2_2_4_5_3_2_3_3_8_3_3_3_8_4_4_3_4_1_5_3_4_1_4_5_6_2_2_1</t>
   </si>
   <si>
     <t>5_2_2_6_8_1_2_1_2_4_4_2_2_8_4_2_5_1_2_7_3_7_5_7_1_1_2_6_4_2_7_3_5_7_7_1_5_5_1_2_4_3_7_1_4_1_2_2_8_1_1_6_6_6_4_5_3_8_2_4_4_8_8_4_9_7_7_7_9_2_5_3_6_4_8_6_1_9_3_2_9_6_7_9_6_9_3_3_1_7_7_5_6_6_8_2_5_2_2_4_5_9_8_10_6_6_1_8_1_3_4_9_7_7_1_8_8_5_3_7_2_2_7_6_7_4_2_4_4_2_7_6_5_6_4_6_5_2_8_7_5_4_2_2_7_5_3_5_3_7_1_4_5_1_7_5_6_5_3_7_8_4_7_5_1_2_2_2_4_5_9_3_4_3_8_7_8_3_2_6_2_3_2_1_1_2_1_9_4_2_1_3_1_5_9_6_2_2_6_7_1_6_3_8_5_1_10_3_5_3_5_9_9_5_3_5_9_3_3_5_1_1_4_4_9_9_1_6_7_3_1_7_7_10_4_5_10_6_10_5_8_2_6_7_7_8_4_1_4_2_10_2_9_7_1_4_2_2_7_2_3_3_10_6_10_2_10_6_10_3_7_5_7_1_2_5_8_1_2_3_2_3_3_1_8_2_2_2_8_9_5_3_3_1_4_8_6_6_4_9_3_5_6_6_6_5_6_1_1_2_4_2_9_5_2_8_8_7_1_2_9_10_3_7_3_10_4_1_2_7_2_8_2_1_2_4_4_1_5_1_4_3_6_1_3_7_6_6_3_1_2_4_1_7_9_1_9_7_7_3_4_1_1_2_4_1_4_3_7_6_6_6_5_10_7_5_8_8_6_5_4_3_4_5_2_1_1_3_2_5_9_1_4_6_4_6_1_2_6_4_8_1_3_2_1_4_4_1_7_2_5_1_4_8_9_1_3_6_5_8_4_1_6_1_9_5_9_2_5_7_1_9_9_3_3_1_6_5_6_3_4_2_9_1_5_6_2_6_1_10_2_3_4_3_1_7_4_6_5_7_9_3_5_3_7_7_2_5_1_3_9_2_2_10_5_6_2_4_2_1_1_1_3_2_6_1_4_10_5_1_7_3_2_1_4_1_2_1_2_5</t>
   </si>
   <si>
-    <t>5_8_3_2_8_4_8_8_8_3_3_4_1_2_2_3_1_1_8_1_6_2_4_8_1_3_6_7_1_3_7_6_6_3_3_3_1_1_8_7_7_5_2_2_2_4_4_4_3_3_7_3_1_1_1_7_1_1_3_1_3_3_8_1_5_5_1_7_2_2_3_4_2_3_6_1_4_4_6_7_2_8_5_1_6_1_1_2_3_1_6_6_4_2_2_7_2_4_3_3_7_2_1_1_3_2_2_1_2_6_3_2_3_1_2_3_8_2_6_6_2_1_2_1_4_1_1_1_1_3_4_2_6_2_7_5_5_1_2_3_3_2_6_6_3_6_4_2_5_7_5_2_1_1_6_2_3_7_1_3_8_6_6_1_1_6_2_2_3_2_5_8_3_1_2_1_7_5_3_2_7_2_2_5_3_1_5_4_7_7_6_2_2_3_1_1_3_3_3_3_8_2_2_3_8_7_2_5_3_8_3_3_1_3_1_1_3_3_4_4_1_3_3_4_3_3_3_3_1_8_6_2_2_2_1_1_1_2_2_2_5_6_3_2_5_4_2_4_7_5_2_3_1_1_2_2_2_3_2_4_2_2_7_2_1_4_3_6_3_3_1_1_3_6_3_4_2_2_2_2_2_1_6_2_3_2_2_2_3_7_6_1_3_4_2_2_2_2_5_5_6_2_2_2_3_7_7_2_8_8_4_4_2_2_4_5_5_8_5_3_3_8_2_1_3_3_1_4_3_2_5_2_7_2_3_1_6_4_2_2_2_2_2_4_7_7_2_7_8_4_2_2_7_6_4_1_1_1_6_2_2_1_7_2_3_5_4_1_1_6_7_7_5_3_3_5_4_6_4_6_7_2_4_1_4_5_2_1_2_1_1_6_6_6_1_3_5_5_5_1_1_2_1_4_5_2_4_5_1_4_2_8_5_8_7_1_4_1_1_7_1_2_4_2_3_7_4_3_3_2_3_5_4_2_1_4_1_2_6_6_8_1_3_8_8_3_3_4_3_5_4_2_2_2_3_3_1_5_5_1_1_2_4_4_7_3_1_2_3_7_3_6_5_1_6_3_3_1_2_2_1_4_3_2_1_7_5_1_3_4_2_4_5_1_1_2_3_2_2_4</t>
+    <t>2_2_2_8_7_6_3_5_4_3_8_5_1_3_3_6_1_3_4_2_6_3_8_8_4_2_1_1_1_4_5_4_4_6_6_6_6_3_5_4_8_3_7_8_6_4_3_5_4_3_2_5_5_7_1_8_2_3_8_7_4_8_1_4_7_5_3_6_8_2_8_2_8_8_8_5_4_7_2_4_5_2_3_5_6_4_5_1_1_1_2_3_7_1_4_1_3_5_2_3_3_1_1_3_3_7_7_4_4_3_5_1_2_7_4_6_3_2_3_6_5_5_2_1_1_4_4_8_7_1_1_2_1_6_3_2_2_2_2_7_7_7_4_6_7_6_2_3_3_2_5_2_4_4_8_1_2_4_8_6_2_6_3_8_3_8_3_5_4_1_1_2_7_5_1_5_4_7_2_7_5_4_6_6_3_5_1_5_8_8_8_8_2_2_5_4_6_2_5_7_6_6_3_2_4_4_3_2_6_8_8_1_1_3_4_2_8_3_5_7_5_1_1_6_7_3_3_5_7_3_7_5_3_3_1_5_7_7_7_2_7_1_6_3_1_3_1_7_7_1_5_4_2_6_3_8_4_2_2_2_8_1_1_7_7_1_7_1_1_7_8_1_1_7_7_5_2_5_2_8_8_4_1_1_2_8_3_1_5_5_7_4_2_1_2_6_6_6_2_3_7_7_2_2_2_2_4_6_6_4_8_2_2_4_2_5_3_4_6_4_4_3_1_4_2_4_7_4_2_2_7_5_4_6_8_2_3_4_2_7_1_4_3_4_8_4_2_2_6_3_3_2_8_5_4_8_1_4_8_7_7_2_5_1_1_1_8_1_1_3_4_8_4_1_4_4_3_5_1_3_1_1_1_1_7_5_1_2_6_5_5_2_2_4_8_8_8_1_1_1_5_7_1_8_7_8_7_1_3_2_2_8_8_3_3_1_6_1_1_1_2_1_1_5_6_7_7_2_5_2_4_4_4_3_3_6_1_6_4_2_2_7_6_2_4_7_2_8_6_8_1_2_5_4_6_3_1_2_2_4_4_2_1_5_6_1_4_1_1_7_1_6_5_2_7_4_5_1_4_6_2_8_7_7_3_7_6_8_5_8_3_3_2_2_8_8_7_1_2_1</t>
   </si>
   <si>
     <t>4_3_1_6_7_8_10_6_4_6_2_3_3_2_3_1_2_5_6_2_7_4_2_9_1_4_3_6_5_3_5_6_10_6_9_9_2_1_2_2_4_6_10_7_10_7_6_4_8_1_8_10_4_3_8_3_2_6_8_6_2_4_3_2_1_2_2_1_10_4_3_9_1_8_4_2_4_2_6_6_1_2_4_5_1_3_1_4_4_7_6_4_1_5_3_10_6_7_8_1_9_7_3_7_3_10_7_5_1_6_4_9_7_2_4_4_6_4_6_8_1_1_2_9_10_7_3_2_6_4_1_7_4_10_3_3_5_7_9_4_2_4_1_6_1_6_1_10_4_2_5_2_6_8_6_8_2_8_1_5_1_2_1_3_8_5_1_3_9_5_3_2_3_2_3_9_5_1_7_5_5_3_6_1_4_7_2_10_4_4_1_8_4_6_1_2_8_9_9_6_4_9_1_3_6_3_6_4_10_5_5_9_7_4_3_2_8_1_8_7_7_3_1_2_9_3_6_5_6_4_2_7_5_5_7_6_8_8_5_6_2_5_4_9_4_8_7_5_6_1_7_7_2_4_4_8_1_2_1_8_1_7_4_5_7_2_6_10_4_2_2_5_8_4_2_3_8_2_5_3_1_6_5_3_8_8_4_4_4_6_2_2_1_8_2_3_9_5_5_1_4_4_8_4_2_1_10_1_8_10_3_2_4_5_5_5_2_4_2_10_6_1_6_2_6_6_3_6_5_1_2_2_2_9_10_7_4_7_1_9_1_4_4_4_9_1_8_4_7_1_8_8_4_3_6_9_7_10_6_1_3_3_5_1_3_8_9_2_6_1_7_5_2_1_7_6_5_7_2_8_6_6_8_1_10_6_1_6_5_2_3_8_5_8_4_2_2_4_6_9_7_8_8_5_9_7_4_5_3_2_4_8_6_6_5_7_4_7_7_8_1_9_3_6_2_5_8_4_8_4_7_1_5_8_8_5_1_5_9_4_7_10_7_1_7_8_2_2_8_5_2_1_8_4_4_2_4_1_3_1_3_5_7_3_2_4_4_2_9_2_10_5_1_4_4_6_2_10_7_8_4_2_1_7_4_9_2_9_5_8_6_10_6_4_2_2_5_7_1_4</t>
   </si>
   <si>
-    <t>5_7_6_1_1_1_1_6_1_1_4_4_2_2_2_2_6_4_1_3_2_4_2_2_2_6_3_1_2_2_1_1_4_4_2_1_2_4_4_7_3_4_5_2_2_2_2_6_3_7_2_1_3_3_2_1_2_6_5_2_1_7_7_1_8_8_6_3_6_2_4_3_1_5_3_6_8_8_3_1_8_1_3_3_1_3_8_8_3_1_1_1_7_7_3_3_2_6_6_4_3_2_3_1_2_3_3_4_2_2_6_6_1_1_3_7_1_8_1_1_6_6_4_5_1_6_1_1_1_3_3_6_6_2_3_1_4_5_2_8_3_5_2_3_2_3_1_8_2_2_3_1_1_5_8_2_7_2_5_2_1_3_6_6_6_3_3_7_2_3_8_1_2_1_3_3_2_6_7_2_1_1_4_6_5_4_4_7_7_1_2_5_6_1_7_8_6_2_2_8_3_1_1_5_3_2_2_1_2_3_3_1_4_3_2_2_6_2_6_6_5_6_2_4_7_6_1_3_8_4_4_2_5_3_3_4_4_4_2_4_3_4_8_8_6_2_2_2_1_8_1_4_4_5_3_3_4_4_4_6_3_4_1_4_4_6_2_5_4_4_2_1_4_2_3_5_5_1_4_7_5_5_5_5_5_5_2_1_2_6_7_7_7_2_7_3_7_1_1_2_5_5_5_8_3_1_3_1_1_3_3_4_4_7_7_4_4_5_5_7_7_3_3_5_6_5_4_1_1_1_7_1_6_4_6_6_6_3_1_6_2_3_1_7_1_1_1_4_2_2_2_4_2_1_1_8_3_3_3_4_6_3_3_3_4_7_7_2_2_8_1_1_1_5_1_6_6_6_6_4_4_4_6_2_5_1_2_2_3_3_6_4_4_5_3_3_7_2_4_7_6_4_1_4_4_8_2_4_3_6_2_5_2_5_2_1_1_2_3_4_7_8_4_1_7_6_7_1_6_3_8_8_7_8_5_1_2_6_4_1_3_3_3_2_2_8_4_2_7_1_1_4_8_4_5_4_6_1_1_7_7_1_2_1_1_2_1_1_5_8_2_5_8_3_2_7_4_4_2_4_4_6_1_3_4_1_1_3_4_6_5_4_6_5_2_8_2_2_8_2</t>
+    <t>2_5_5_4_5_4_2_1_4_2_8_5_7_6_7_2_2_8_8_5_4_6_1_5_4_7_2_4_3_3_2_6_8_8_8_4_8_7_6_7_2_6_1_8_4_2_3_2_3_4_1_4_2_3_5_8_1_4_4_3_1_2_3_3_5_8_7_5_8_8_6_4_1_5_8_4_3_3_1_1_1_6_6_7_2_3_1_1_2_1_8_8_3_2_4_5_7_8_2_7_5_5_3_4_7_4_8_4_6_3_6_4_7_8_6_4_4_3_4_3_1_4_3_8_8_7_5_2_2_2_1_8_8_3_3_8_4_2_6_3_1_5_3_3_2_1_6_6_7_4_6_5_2_1_3_3_3_4_8_5_5_7_6_2_2_2_2_7_7_4_3_1_3_5_1_6_1_7_5_5_2_2_8_7_1_1_1_4_3_3_3_4_5_5_2_1_1_1_5_5_3_3_6_2_8_1_7_3_2_2_2_5_6_7_8_7_8_1_3_8_2_3_2_2_7_2_2_7_4_4_1_2_6_1_7_2_1_5_2_3_3_1_1_1_2_7_1_4_8_5_5_2_4_7_4_4_6_1_7_2_3_7_8_1_4_1_7_7_2_3_8_8_1_1_5_6_8_7_3_6_6_1_3_2_2_6_6_5_6_2_2_3_3_8_6_1_4_3_8_8_1_5_2_2_2_8_2_7_2_3_8_4_2_4_2_3_4_4_2_8_1_1_2_8_3_7_5_3_3_2_2_8_1_3_3_3_6_6_1_8_3_3_7_4_1_4_7_6_7_5_4_2_5_1_7_2_8_4_4_4_2_1_6_6_4_3_4_8_6_8_1_1_3_1_3_4_4_3_8_6_5_4_4_4_4_1_5_7_2_2_5_1_3_3_3_1_3_7_4_2_1_5_5_2_2_5_5_4_2_1_7_7_1_1_3_1_3_3_7_3_1_6_7_1_7_5_1_3_3_7_1_1_7_2_4_4_1_2_4_3_6_3_4_2_1_1_1_8_2_4_5_8_2_7_5_2_2_2_6_5_2_5_3_6_2_8_2_3_3_6_8_3_6_6_7_2_6_3_3_1_8_5_5_6_2_7_8_7_7_1_2_1_1_1_3_3_7_3_7_7</t>
   </si>
   <si>
     <t>2_6_6_6_7_6_7_6_3_1_7_6_1_4_7_1_2_1_6_2_8_9_1_1_6_7_8_4_10_3_9_9_6_10_3_1_7_7_5_7_7_8_3_3_3_3_6_2_8_8_5_3_5_9_4_2_10_6_10_3_1_2_8_7_7_2_6_6_10_6_4_7_6_2_1_6_8_1_2_1_8_4_5_6_3_9_5_5_2_1_5_10_3_1_1_8_5_8_3_1_1_7_3_2_2_10_6_6_6_2_4_2_8_2_8_2_5_2_4_1_3_10_4_8_5_1_4_8_10_6_2_8_1_9_1_6_10_6_6_4_5_7_3_4_1_9_9_2_1_1_3_8_3_6_3_5_2_4_5_4_2_8_1_6_7_6_9_6_5_5_1_5_3_4_6_4_2_6_7_2_7_5_6_5_7_6_4_6_8_8_1_3_1_1_1_8_2_5_1_7_1_6_6_6_6_9_5_3_4_4_3_3_4_4_2_6_6_2_4_6_2_9_1_3_6_7_6_9_6_1_1_1_8_4_4_3_9_7_4_7_8_2_9_6_5_6_10_5_9_10_4_1_6_1_2_10_7_3_6_4_3_5_1_7_9_4_7_3_6_1_5_5_6_2_1_1_2_8_8_7_7_9_5_9_2_5_5_2_6_6_4_7_7_7_9_4_7_2_7_7_3_3_9_1_5_6_2_4_1_8_4_1_1_3_3_2_1_5_4_5_1_2_1_2_4_3_5_2_4_3_3_4_2_8_9_4_4_2_7_9_2_4_2_9_1_4_4_5_8_2_7_5_2_2_9_5_9_3_4_7_4_3_3_1_3_5_2_7_6_3_2_7_8_8_5_4_9_1_1_9_2_1_7_2_3_8_5_1_7_8_1_6_5_8_4_5_3_1_4_6_3_4_2_1_3_8_9_2_4_1_2_6_1_7_5_3_1_4_1_1_4_1_8_2_2_1_5_8_1_1_6_4_2_2_1_9_1_5_4_8_1_10_5_3_5_2_1_3_3_5_2_8_1_4_2_2_9_6_10_3_1_2_1_9_9_1_6_1_6_2_7_1_9_7_2_7_4_2_1_2_2_10_2_4_6_3_5_6_8_8_2_7_3_3_2_2_1_1_4_3</t>
   </si>
   <si>
-    <t>2_4_4_3_3_3_7_4_1_3_8_1_1_5_5_3_2_3_2_7_3_3_6_8_3_1_2_1_1_2_5_8_3_4_1_1_3_1_1_4_8_8_3_3_6_4_7_4_4_5_1_3_7_4_6_2_2_5_4_1_1_4_2_5_1_4_4_3_2_7_1_7_6_5_6_1_2_2_7_1_2_5_1_4_3_4_4_8_6_2_6_4_3_4_2_5_2_4_4_4_4_3_7_7_1_4_5_4_4_4_5_1_7_2_1_5_1_2_4_8_2_7_1_3_1_2_1_2_2_2_2_7_4_5_5_8_6_4_1_2_6_1_1_3_2_3_7_1_3_1_3_4_4_7_1_3_3_6_6_2_5_2_3_1_1_1_5_2_1_2_1_1_1_7_7_6_4_3_1_1_1_2_5_2_2_2_4_2_2_2_2_1_4_2_2_5_1_1_1_3_1_3_3_1_5_5_4_2_4_3_1_2_6_7_6_6_8_8_8_3_5_3_2_3_3_6_3_5_5_7_1_3_3_6_2_2_2_5_1_3_2_5_5_4_8_2_2_6_2_3_4_6_3_1_4_3_1_1_3_4_3_4_2_4_1_1_6_1_3_1_5_7_7_7_2_4_1_1_8_1_2_6_5_6_5_1_3_3_3_4_2_7_2_2_2_2_3_4_4_2_5_5_4_5_1_5_6_1_2_2_1_1_3_6_3_2_8_4_8_7_7_4_4_4_6_7_4_3_2_1_3_3_6_6_8_7_3_1_4_3_4_4_2_1_1_2_7_4_1_2_7_2_2_1_1_7_2_2_2_1_3_3_6_1_1_2_4_2_4_3_2_3_6_4_5_1_1_5_3_8_3_4_4_4_2_2_4_5_3_2_3_5_5_1_4_5_2_2_2_2_3_3_1_4_7_3_3_1_7_7_2_2_1_8_1_5_4_4_4_2_3_4_8_1_2_3_1_1_2_3_6_1_2_2_5_8_1_3_8_4_3_5_1_3_7_7_3_3_8_1_2_2_2_1_2_2_1_1_1_1_1_2_6_6_2_1_3_5_3_1_7_1_3_7_2_3_2_2_2_4_4_4_1_2_3_7_2_3_2_2_3_3_3_4_2_1_1_6_8_1</t>
+    <t>6_8_6_1_3_2_2_2_2_4_1_1_1_3_6_2_4_8_8_7_6_2_3_1_4_6_2_6_5_5_2_5_1_4_5_4_1_3_3_1_1_1_4_6_4_6_1_3_4_1_7_2_3_7_3_5_1_6_8_5_7_3_1_8_1_7_1_5_4_4_4_8_3_1_5_5_8_5_1_1_4_2_2_6_7_3_4_4_3_5_2_7_1_8_4_4_4_3_2_8_4_6_8_4_4_4_2_1_3_7_7_2_2_2_2_2_5_5_2_2_2_5_1_4_6_4_2_2_5_2_2_8_2_5_3_5_5_1_1_4_4_1_1_3_8_7_2_1_7_8_3_2_2_8_5_2_1_1_7_5_3_1_4_1_5_7_4_4_4_6_3_3_3_2_5_2_2_7_7_6_4_8_2_7_2_2_7_7_7_2_2_1_1_7_5_4_4_1_1_6_7_7_2_1_4_1_8_8_8_8_2_1_1_1_7_7_8_8_1_6_4_6_2_2_2_7_8_3_4_5_5_5_2_1_4_4_3_1_1_7_1_1_7_1_6_1_7_6_2_6_4_6_5_5_3_2_8_4_8_3_1_1_5_1_3_5_3_4_2_1_3_6_3_1_3_1_5_6_2_1_1_3_5_4_8_3_2_3_3_5_1_1_8_1_1_1_1_4_6_6_3_1_4_3_1_5_3_6_8_8_3_2_6_8_3_3_3_1_3_3_1_7_2_1_4_1_2_8_1_4_1_1_5_2_8_8_3_7_7_8_6_5_7_7_4_4_8_3_3_2_5_2_3_3_1_1_4_1_4_4_1_6_5_8_8_6_2_8_7_7_2_2_2_1_4_4_5_2_1_2_3_6_8_8_1_6_4_6_2_6_7_3_3_1_7_6_6_3_2_8_4_2_4_8_5_3_1_3_5_4_6_1_3_1_5_2_3_7_7_3_3_1_4_2_4_5_8_3_1_5_6_4_4_3_7_1_1_5_5_5_2_2_7_3_6_3_1_2_2_8_2_6_1_6_4_4_1_1_5_5_3_3_2_2_1_4_3_7_4_6_1_1_8_2_1_8_6_4_2_1_2_5_5_5_1_8_1_2_2_4_4_5_5_7_1_7_7_7_8_8</t>
   </si>
   <si>
     <t>1_3_5_6_1_2_8_5_7_2_1_4_6_1_2_2_7_9_1_1_2_4_4_1_2_3_1_7_1_5_6_6_5_3_9_5_5_1_6_9_9_10_4_7_5_10_4_6_4_5_9_3_6_3_8_8_5_5_8_8_4_9_3_4_7_9_6_7_9_3_9_3_1_7_6_5_6_1_8_7_5_2_5_7_6_7_4_3_4_3_9_6_7_3_5_6_10_7_5_7_1_6_1_1_4_6_1_6_6_8_10_6_2_8_2_1_4_3_4_8_7_1_10_6_5_2_8_4_4_6_6_8_5_4_6_6_6_7_6_4_4_9_9_4_8_3_5_2_9_3_1_2_7_9_8_9_9_9_2_1_7_6_1_5_3_4_7_5_2_4_10_5_7_2_1_4_5_1_8_1_4_2_8_6_1_3_2_8_3_2_3_4_3_7_5_10_6_3_6_8_7_2_2_2_10_6_4_2_10_5_2_2_8_5_3_1_3_3_6_6_3_6_1_3_2_3_4_2_8_2_7_2_2_2_5_2_3_6_7_1_2_4_8_2_3_3_2_2_2_5_6_3_5_5_7_8_9_1_4_3_4_6_3_2_7_7_9_7_6_5_1_6_3_6_5_1_2_1_8_8_1_7_2_5_8_2_3_6_5_5_2_7_4_2_2_1_3_3_9_5_5_7_2_5_4_3_8_1_5_1_2_6_1_2_6_2_6_7_3_6_1_1_5_1_9_6_5_7_1_2_5_7_3_7_6_4_4_6_10_4_3_4_2_1_6_10_7_9_9_1_4_4_1_2_9_4_3_1_3_4_8_2_1_5_4_2_6_3_3_4_1_9_3_5_5_3_5_4_8_5_6_1_8_8_9_8_4_5_6_9_5_5_2_4_8_7_6_1_5_2_1_8_5_4_1_4_1_2_9_5_1_7_9_1_7_5_9_5_4_2_2_1_3_2_4_1_8_1_3_4_1_3_4_3_2_1_1_3_6_1_4_5_5_9_7_9_1_4_4_8_3_9_5_9_3_7_8_3_1_8_4_9_6_4_7_3_4_1_1_5_1_8_8_6_3_1_4_2_2_1_4_2_9_4_2_9_5_5_6_4_8_3_2_3_4_1_2_6_1_3</t>
@@ -843,64 +848,79 @@
     <t>4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_3_4_4_4_4_4_6_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_6_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_5_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_1_1_1_1_1_2_2_2_2_2_2_3_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3_4_4_4_4_4_5_5_5_5_5_6_6_1_1_1_1_1_2_2_2_2_2_3_3_3_3_3</t>
   </si>
   <si>
+    <t>1_3_9_9_1_1_1_2_10_10_1_5_5_8_3_3_9_6_2_2_1_1_1_1_7_4_3_5_9_5_3_4_4_8_8_9_5_5_7_4_4_8_3_6_9_3_5_7_7_1_1_1_5_6_8_6_4_4_6_1_6_1_1_1_2_2_1_5_7_10_1_7_7_8_8_2_8_3_5_3_2_5_5_3_4_3_9_10_4_8_8_3_3_3_8_8_6_7_3_9_8_1_9_3_4_6_1_4_2_8_10_5_6_4_4_5_4_1_2_9_2_6_6_10_6_6_4_10_10_3_5_2_1_2_7_3_10_6_5_7_7_2_3_2_7_2_9_5_1_3_2_2_10_2_2_9_1_1_9_3_10_2_5_4_1_7_5_4_4_4_7_3_6_1_1_7_8_7_4_2_5_7_8_7_1_5_7_7_2_2_5_5_1_2_2_4_4_5_8_7_5_3_4_4_1_7_3_10_10_2_5_5_3_5_4_4_5_5_9_2_7_9_5_7_4_2_1_9_5_7_7_3_6_8_5_2_2_9_8_3_8_5_8_1_7_5_6_3_6_6_2_6_9_5_10_4_7_7_9_1_1_10_6_2_8_10_5_5_9_2_2_7_9_1_6_5_3_7_1_9_8_6_2_8_6_10_2_3_3_6_2_2_8_6_3_3_3_2_10_2_3_10_3_1_3_6_6_6_4_6_5_9_3_8_4_1_1_8_8_8_2_4_6_4_5_5_5_2_6_6_8_3_3_1_6_6_6_10_7_1_7_10_9_7_1_3_6_7_7_1_3_8_8_2_7_7_7_5_9_3_6_7_4_10_2_9_4_2_7_6_3_10_4_10_1_10_4_8_7_6_6_1_4_3_4_1_4_4_8_6_3_7_5_4_5_10_6_8_8_8_3_3_4_1_1_3_8_3_1_1_5_2_7_7_1_5_4_7_8_4_1_1_8_1_1_8_2_2_2_8_5_9_9_5_2_5_8_9_9_1_7_5_8_3_4_3_2_5_1_7_3_6_2_3_8_8_10_2_1_7_6_1_5_5_5_1_1_6_4_6_2_2_6_1_5_3_2_8_3_3_4_1_6_5_9_5_3_4_7_9_6_6_10_2_9_5_2_4_3_6</t>
+  </si>
+  <si>
+    <t>6_6_11_4_1_5_1_8_3_3_8_9_5_6_10_4_4_9_2_8_10_5_9_11_1_7_1_3_10_6_8_9_1_5_10_4_1_4_4_2_10_7_1_10_6_10_5_10_7_2_7_10_7_2_4_5_3_2_6_6_11_5_10_5_7_5_3_7_10_2_1_9_5_3_5_6_5_3_5_1_4_9_1_3_6_6_10_6_2_2_3_10_7_2_7_5_6_3_1_5_3_2_4_6_4_1_1_4_10_7_6_4_2_5_6_2_5_1_5_4_9_7_6_5_9_3_4_10_7_6_4_6_10_3_4_1_2_2_2_1_9_4_6_3_11_3_10_5_10_6_5_5_6_6_9_1_1_5_1_5_10_6_3_7_7_2_10_6_2_5_11_4_3_9_4_7_4_3_8_2_2_9_3_10_2_1_4_2_3_9_11_7_5_10_6_3_2_4_8_3_3_2_1_3_1_2_6_4_8_3_3_10_4_3_8_4_1_4_9_10_1_2_2_10_5_4_1_3_9_6_8_1_5_3_8_1_8_6_10_2_3_7_3_5_7_2_9_2_8_2_4_11_3_4_8_4_6_9_1_9_6_8_5_10_6_3_6_10_5_2_7_6_6_3_6_2_3_1_9_1_6_1_2_9_3_2_8_1_4_8_3_4_10_2_6_5_4_2_11_4_4_4_2_2_2_1_1_1_3_3_1_1_9_3_1_5_5_4_2_4_11_6_6_8_5_3_1_6_10_3_2_2_1_2_2_2_4_1_3_7_9_8_5_8_4_5_2_3_1_3_9_2_4_2_1_4_4_7_3_9_4_10_2_2_2_7_7_5_5_4_10_7_10_4_4_11_7_4_7_1_1_4_1_8_4_7_3_2_6_2_6_3_7_3_1_4_1_7_1_7_4_1_4_8_9_2_8_4_11_3_2_4_11_6_6_3_8_4_9_8_8_10_6_3_6_7_4_6_7_1_4_9_10_5_11_6_1_10_4_11_4_4_2_2_1_3_3_11_6_6_4_2_2_1_8_1_7_5_6_3_8_1_3_4_5_6_9_2_4_7_5_4_1_4_4_2_5_6_3_4_5_2_3_10_7_8_8_4_10_2_2_6_9_2_6_5_10_3_3_5</t>
+  </si>
+  <si>
+    <t>5_1_9_9_9_1_3_3_3_1_1_4_4_9_1_3_5_9_1_1_9_2_2_6_1_10_8_1_7_2_2_1_2_4_8_5_5_10_2_3_6_10_7_3_8_8_5_3_2_4_2_2_1_9_1_8_7_4_3_5_3_7_5_9_9_7_8_8_7_1_4_1_3_1_10_1_5_4_4_4_5_10_10_4_4_10_6_4_2_8_2_6_5_10_6_4_8_6_1_6_4_10_2_10_1_8_6_4_4_1_3_8_8_6_4_1_9_4_4_3_5_2_2_6_3_1_8_9_7_1_9_9_7_4_3_10_6_2_2_7_8_4_5_7_4_6_2_2_7_6_1_3_1_10_8_8_3_1_3_10_7_6_3_7_7_3_1_5_3_5_5_1_5_9_1_6_5_4_4_6_1_2_6_4_1_2_7_2_2_6_8_8_8_4_6_1_1_2_2_2_2_9_1_3_2_7_5_5_5_5_5_5_1_6_1_4_8_3_6_1_10_4_4_4_4_4_7_1_10_10_5_9_6_7_3_6_1_1_6_3_3_7_6_6_9_2_10_10_1_2_2_10_4_2_7_9_9_9_4_9_3_4_10_9_8_5_3_1_2_3_3_6_1_3_5_2_7_8_8_1_1_9_2_1_8_5_7_7_7_8_5_3_9_2_3_9_3_1_1_9_9_1_7_5_5_4_4_7_9_9_3_9_5_6_7_2_7_7_3_1_1_6_9_9_2_2_2_1_1_9_5_2_2_2_10_2_1_4_7_5_4_10_9_9_9_3_3_10_8_6_7_2_3_10_3_3_3_8_9_7_7_7_7_5_5_2_2_9_9_1_1_1_8_7_8_8_5_10_3_10_4_4_2_2_1_1_4_4_4_1_10_9_8_8_6_2_1_9_10_4_2_10_5_6_1_8_2_2_10_4_6_10_1_3_6_8_8_7_5_7_2_6_9_5_6_2_7_1_10_2_5_5_5_10_2_10_2_6_7_6_3_9_5_5_2_7_2_2_8_8_6_1_1_9_9_5_5_5_3_5_4_4_7_3_10_3_8_3_1_10_9_6_6_6_7_7_3_3_10_8_8_10_5_3_6_4_5_7_3_10_4_5_5_7_2_10_7_3_4_7</t>
+  </si>
+  <si>
+    <t>8_2_1_10_4_4_11_4_8_2_6_1_6_6_7_1_2_3_3_6_7_1_8_1_6_11_6_4_7_1_7_8_6_2_9_3_4_1_8_10_5_3_4_4_11_4_3_1_8_9_1_8_7_5_2_10_3_11_3_2_10_7_1_10_3_10_3_2_9_4_10_6_6_1_6_1_8_5_5_7_5_8_5_6_2_8_2_3_4_5_5_9_7_4_2_3_7_3_1_4_3_10_6_2_5_2_10_5_10_6_9_5_7_4_3_5_5_5_7_5_1_8_5_5_4_8_9_8_4_8_6_2_2_5_2_5_10_6_11_4_9_3_4_4_1_5_2_4_5_4_10_2_1_6_5_6_3_9_1_6_9_11_3_10_2_3_2_7_2_4_10_4_6_4_4_2_10_2_4_1_7_10_7_8_2_6_10_3_6_2_10_4_5_7_1_2_4_5_4_9_3_6_6_5_5_1_4_3_4_7_7_3_10_5_2_11_6_5_5_5_2_3_2_1_4_2_1_6_3_9_9_4_8_3_5_6_5_2_4_4_5_7_9_5_2_1_4_4_6_4_3_3_8_3_5_1_7_3_5_5_3_7_1_5_4_6_2_9_1_1_1_2_10_3_8_1_4_11_6_4_1_10_6_4_1_10_5_4_1_4_5_6_10_1_7_2_4_6_4_5_3_4_2_5_4_1_1_8_10_4_6_5_5_6_10_3_6_10_6_3_5_7_4_7_7_11_4_8_4_1_8_3_5_1_10_7_7_6_1_9_1_1_8_4_8_1_2_6_8_9_6_9_3_7_6_5_2_4_2_1_2_10_6_1_4_4_8_7_3_3_3_8_9_7_3_4_6_4_6_10_4_5_10_7_1_1_3_11_5_6_10_4_1_4_7_10_6_2_5_10_6_2_3_4_1_1_3_10_5_2_5_1_6_5_3_3_8_10_6_3_3_2_2_10_5_4_9_3_1_11_4_6_2_6_2_4_4_8_4_4_8_6_8_7_7_1_4_11_5_1_8_1_4_1_4_11_4_4_5_9_4_3_4_9_6_6_5_10_7_8_5_2_3_2_8_2_6_3_5_1_6_2_7_8_2_3_5_5_1_2_9_11_6_2_6_6_5_5_8_8</t>
+  </si>
+  <si>
+    <t>7_9_3_6_3_4_10_4_2_3_6_8_10_3_1_1_9_9_9_9_8_5_1_4_8_8_4_6_4_10_8_9_4_9_9_9_10_8_8_8_10_6_4_4_2_2_2_3_5_1_1_1_1_1_9_9_1_1_4_4_9_4_4_2_1_5_7_6_5_6_7_5_2_5_8_3_3_2_8_1_7_6_6_1_2_6_4_8_3_5_10_3_3_2_8_1_6_7_10_2_3_5_8_5_1_1_8_8_5_4_4_4_4_5_1_8_5_5_7_7_7_4_2_2_9_2_4_4_1_8_5_8_8_8_1_4_2_5_3_1_7_2_2_10_7_8_7_2_3_10_5_7_5_5_2_7_4_2_3_2_4_10_5_5_5_3_1_6_7_3_10_1_5_5_2_8_1_1_5_8_1_10_10_4_2_5_5_3_9_4_8_6_2_3_8_6_7_4_4_4_9_1_10_10_7_7_6_5_6_4_2_10_6_6_6_8_1_9_9_2_1_8_2_3_8_1_4_8_9_5_3_6_6_8_8_3_6_9_8_4_4_9_9_3_2_2_8_8_8_7_6_6_1_10_7_7_5_1_5_8_6_3_2_9_7_7_7_1_10_2_3_3_4_6_4_4_1_5_4_10_9_8_5_5_1_1_6_3_2_4_4_10_5_7_2_7_2_2_8_2_8_4_4_4_4_10_3_6_3_4_5_7_10_2_1_7_1_3_6_6_6_1_3_5_2_5_7_6_10_5_8_6_7_10_10_7_3_3_1_6_6_4_5_9_9_8_2_5_8_4_3_2_7_3_6_1_9_5_4_9_10_5_6_2_8_4_3_10_3_3_2_4_2_2_9_8_5_5_1_2_8_2_9_7_9_2_2_2_2_7_5_8_9_7_7_3_9_5_9_6_6_8_3_7_5_6_3_8_5_5_3_10_1_2_3_10_1_7_1_2_8_7_8_2_1_4_1_4_4_10_10_7_1_5_5_5_9_5_2_1_3_1_1_5_9_8_9_10_2_4_10_3_4_4_2_10_9_7_8_7_1_6_2_10_10_3_4_3_3_2_2_2_5_7_6_2_6_4_8_8_10_9_5_6_10_10_8_4_8_5_10_6_6_4_10_7_6_4_1_4</t>
+  </si>
+  <si>
+    <t>9_9_6_9_4_6_6_7_1_5_2_6_5_1_1_10_3_4_9_10_3_6_1_1_5_3_1_1_9_1_2_2_8_9_1_1_1_1_1_7_6_8_2_9_9_5_1_1_1_5_5_4_3_5_6_9_9_2_2_7_5_4_2_8_7_8_8_3_4_4_3_9_6_7_5_7_3_2_7_3_6_5_9_2_7_10_4_6_5_2_6_4_4_8_2_2_1_1_4_7_3_2_11_4_7_7_4_5_1_3_2_11_5_6_5_1_3_2_1_6_6_7_10_7_4_9_9_1_1_4_8_1_3_2_6_8_11_6_1_7_1_6_11_6_6_9_10_7_6_10_7_2_7_2_8_4_9_6_9_8_10_6_10_7_6_2_6_10_5_2_7_7_5_6_5_2_4_7_11_3_4_7_4_7_4_2_4_6_6_6_1_6_3_1_3_3_2_3_5_1_3_4_2_3_7_4_5_3_3_2_5_2_3_8_1_10_6_3_8_9_5_9_4_11_7_10_3_1_8_2_9_4_5_4_2_2_2_6_11_7_7_6_9_4_4_4_5_1_10_6_1_1_3_3_10_6_4_3_5_9_3_6_3_2_8_4_4_1_8_10_3_9_8_6_2_7_8_1_6_9_3_4_9_5_2_2_1_8_8_8_8_8_1_4_1_6_4_4_2_6_6_4_2_8_2_8_9_5_2_2_4_6_9_8_10_3_1_1_2_4_2_8_5_6_6_6_7_3_1_1_8_4_7_2_2_1_3_7_8_10_5_6_3_10_1_4_6_5_7_1_1_1_6_3_3_7_5_6_8_4_2_3_5_5_5_7_9_1_3_4_8_3_2_3_2_1_5_2_4_10_7_7_1_10_5_3_5_7_3_8_1_2_2_1_8_8_7_5_1_6_2_2_6_10_3_1_2_10_3_5_8_6_1_11_2_8_8_8_5_8_6_5_10_7_1_3_2_7_3_5_6_8_10_2_6_3_4_3_1_3_7_4_3_1_5_10_3_3_1_8_2_6_10_2_6_4_8_3_3_9_10_6_4_7_6_10_7_9_3_2_6_3_4_4_8_3_5_7_3_5_9_8_3_6_5_4_2_4_4_10_7_9_2_5_2_4_5_3_1_2</t>
+  </si>
+  <si>
+    <t>3_3_9_7_6_10_10_6_5_5_7_1_5_9_1_4_4_3_6_7_6_7_1_1_9_9_4_1_6_3_8_5_1_7_8_10_10_2_4_3_2_2_2_2_3_3_2_4_5_5_4_4_1_4_6_1_6_6_3_4_3_9_1_4_9_5_9_4_5_10_1_9_6_5_5_5_3_5_6_6_9_6_8_7_7_1_8_2_2_2_3_7_3_3_5_1_1_6_5_3_2_2_2_6_9_3_3_6_5_6_10_3_8_7_7_2_4_2_10_8_5_3_7_1_8_9_5_2_7_7_8_7_1_7_4_1_3_5_6_6_6_9_1_6_8_3_2_1_1_3_6_4_5_2_2_6_1_2_10_5_2_2_4_8_5_3_3_10_10_10_8_2_7_8_3_9_5_1_1_5_9_9_7_4_4_4_4_1_5_1_1_1_5_2_7_7_3_8_1_1_1_2_3_1_9_10_6_4_1_4_4_3_8_2_9_10_1_3_4_1_8_1_8_7_5_8_9_8_6_10_10_7_8_3_4_3_3_6_1_3_1_9_1_2_2_4_5_7_2_3_5_3_6_1_6_6_7_4_9_2_5_2_9_9_10_3_6_5_8_3_10_2_4_1_4_4_8_10_7_6_9_5_10_1_2_9_2_3_10_5_10_3_1_6_6_5_5_8_5_5_5_1_3_7_5_8_7_6_1_5_6_7_7_6_6_8_9_1_2_7_7_7_8_7_6_2_6_6_9_4_7_7_1_7_1_10_8_2_10_8_1_9_4_1_4_2_3_6_6_6_8_1_1_9_2_3_2_5_4_10_1_1_1_3_5_5_5_3_10_3_7_7_5_5_5_9_8_1_5_5_1_4_7_4_1_10_7_7_4_4_10_2_2_1_6_5_2_9_3_3_8_5_6_1_6_4_7_5_7_5_2_1_4_4_3_3_3_3_5_1_5_1_1_2_8_10_7_8_6_7_8_2_10_9_9_6_3_5_5_4_4_5_9_8_6_1_10_3_4_2_10_7_8_2_3_6_3_8_2_1_1_7_7_7_5_9_4_7_10_6_8_4_6_7_1_5_6_6_6_6_4_7_5_7_8_3_6_10_1_5_10_10_7_10_2_6_4_7_1_7</t>
+  </si>
+  <si>
+    <t>3_5_4_9_1_10_7_3_2_6_7_6_4_6_1_2_10_7_11_6_5_1_10_7_6_4_3_2_2_1_1_5_7_5_10_7_6_7_3_2_7_6_3_9_7_1_1_1_8_4_8_5_8_1_10_7_2_2_10_3_10_5_3_2_8_7_10_7_5_7_7_9_6_2_11_7_9_4_7_7_8_3_4_9_1_9_7_2_5_7_4_5_10_5_1_6_8_2_9_7_2_9_4_8_7_4_1_5_4_2_8_3_8_1_3_2_9_9_2_5_6_6_8_7_3_5_8_4_1_7_5_3_10_6_2_7_6_9_9_6_2_2_1_8_7_3_1_7_2_4_1_4_7_4_5_6_2_2_2_5_6_4_8_2_10_6_11_3_3_10_2_2_9_8_3_7_6_7_11_2_7_7_1_8_5_4_10_5_1_4_9_5_1_9_8_6_6_6_5_6_4_7_10_7_7_3_8_6_5_1_9_3_5_6_9_11_4_8_3_4_3_3_1_2_9_5_5_2_9_5_6_2_8_2_3_2_9_3_2_3_4_4_4_5_3_10_4_6_8_5_6_1_1_10_3_1_5_2_5_1_4_3_7_8_4_2_2_1_2_4_1_7_8_8_2_1_1_2_8_5_1_1_8_2_5_5_6_1_7_6_5_1_9_4_4_10_5_2_5_1_5_5_3_8_1_4_6_8_2_1_1_6_1_11_6_2_2_4_4_10_3_6_3_10_2_2_4_7_3_2_7_7_3_2_1_8_8_4_3_8_4_2_9_7_4_5_8_9_1_3_4_3_5_1_4_7_9_2_4_10_7_3_4_8_8_6_1_4_8_2_4_5_1_6_2_3_8_6_5_2_4_4_1_10_3_10_7_10_5_3_1_5_6_7_5_7_9_6_10_4_1_3_3_1_2_4_5_8_6_9_4_8_4_5_2_6_5_7_6_1_2_1_7_3_5_4_6_8_3_8_6_2_1_7_8_5_4_8_10_2_6_8_7_4_7_1_3_4_7_1_8_9_9_7_5_5_5_2_8_7_1_4_5_3_9_8_7_6_3_1_9_9_7_8_3_1_1_1_9_3_8_3_6_6_3_3_10_5_3_8_4_2_1_2_2_6_2_6_11_6</t>
+  </si>
+  <si>
+    <t>11_11_11</t>
+  </si>
+  <si>
+    <t>3_10_2_8_2_3_9_2_3_9_1_3_1_9_9_9_5_5_8_3_9_9_7_10_5_8_4_8_2_2_9_10_1_2_6_4_4_3_8_7_1_1_5_3_8_4_1_8_5_10_1_1_2_5_1_10_8_2_2_5_2_10_6_1_3_6_2_2_4_3_7_4_8_8_5_3_8_9_3_7_3_1_6_10_1_10_2_2_2_2_2_6_10_6_6_7_2_8_8_10_6_10_1_1_2_2_9_8_3_3_6_2_8_7_7_7_5_6_4_6_2_5_2_9_10_5_8_8_8_8_8_4_2_3_3_1_10_4_9_9_1_1_1_6_6_1_8_2_5_2_10_10_3_5_7_10_3_7_1_2_8_4_3_4_4_4_6_1_4_5_10_2_2_1_3_2_4_10_2_2_8_4_6_2_8_2_5_2_10_10_9_9_3_2_1_4_1_2_10_8_8_2_3_6_7_2_7_5_4_1_2_2_2_9_6_5_10_9_3_3_5_7_7_3_4_1_5_10_6_5_6_5_4_6_5_7_4_1_6_1_3_8_10_7_8_4_3_1_2_2_9_7_4_3_3_9_1_1_2_5_5_2_2_8_3_5_8_2_7_1_1_6_7_2_5_6_9_6_10_5_7_10_10_9_2_3_4_10_9_10_2_2_6_10_3_3_8_7_3_1_8_8_1_4_1_7_7_10_8_3_5_2_5_4_2_2_2_1_3_1_7_5_8_4_9_4_1_2_2_1_7_5_2_8_3_10_3_10_7_10_1_9_9_7_3_2_8_9_9_1_7_6_3_6_3_3_8_3_5_3_10_4_1_5_5_5_5_10_2_5_3_2_3_1_8_5_2_6_8_4_2_7_7_4_4_2_1_2_4_7_5_3_3_3_6_6_6_6_1_3_2_2_4_6_10_10_5_1_1_7_9_2_5_9_8_2_2_6_5_5_2_3_10_2_1_1_3_8_2_4_3_4_5_1_6_8_2_7_6_6_8_4_8_4_2_4_8_9_1_2_6_6_7_1_10_6_6_10_4_7_1_3_3_7_6_4_1_8_1_5_1_2_7_6_10_1_6_1_8_1_8_5_5_2_1_10_10_6_6_7_2_4_4_3_5_8_9_2_2_5</t>
+  </si>
+  <si>
+    <t>2_6_4_1_1_5_10_6_2_5_3_4_1_4_10_7_3_7_3_3_9_10_7_10_4_3_6_11_7_8_2_9_9_2_4_1_3_5_5_10_7_4_9_1_2_8_2_3_1_6_5_3_8_8_6_5_11_4_1_4_10_5_1_1_3_2_2_2_5_9_3_4_2_1_4_10_5_6_3_6_2_1_10_7_5_2_3_9_11_4_6_7_1_4_5_5_3_2_5_9_7_2_6_1_1_3_6_1_5_7_7_11_7_7_11_6_4_6_5_3_5_3_2_3_8_9_10_4_4_8_3_2_7_6_5_8_3_9_9_8_2_10_5_6_3_7_6_4_4_1_1_4_8_2_4_8_3_11_6_4_2_8_6_1_3_5_2_11_7_2_9_8_9_3_1_5_9_9_1_1_4_3_4_2_10_3_2_1_2_3_4_1_5_1_7_2_6_8_4_5_8_3_5_5_2_1_5_10_6_3_1_3_8_10_7_2_1_10_2_7_1_4_2_8_1_7_3_6_4_5_1_11_4_10_4_11_5_5_3_8_2_4_2_11_2_4_3_2_9_1_1_8_2_1_4_1_8_2_4_9_3_3_1_7_9_9_8_6_2_10_3_6_1_4_1_4_4_1_1_11_5_8_9_1_5_4_1_9_9_1_9_1_1_3_6_1_4_1_10_5_6_1_11_6_11_5_2_4_1_1_5_6_4_8_3_6_2_5_9_2_5_11_7_9_4_6_1_1_9_6_7_7_3_9_1_7_2_9_5_9_6_10_5_4_6_7_8_3_7_10_4_11_7_7_5_3_6_6_7_8_3_4_9_4_3_2_5_3_3_8_4_4_7_1_9_1_8_1_4_6_5_1_8_1_7_3_7_2_2_6_11_7_1_9_4_7_9_6_8_2_6_1_2_1_7_7_2_8_4_6_11_7_1_5_1_5_7_3_5_4_4_6_3_3_9_10_2_2_2_6_9_4_1_2_3_6_10_6_7_10_4_4_4_9_3_2_5_3_2_6_10_5_2_9_6_3_1_4_7_7_5_2_5_6_6_6_9_1_11_5_5_8_3_1_1_4_8_5_2_2_2_5_2_7_6_10_4_1_8_1_2_4_6_5_5_2_2_10_2_4</t>
+  </si>
+  <si>
     <t>3_5_3_1_1_2_1_2_4_1_1_2_4_5_7_6_5_8_8_6_3_3_3_6_6_4_6_2_1_2_5_4_3_3_3_6_3_5_2_1_2_7_10_4_1_7_2_5_4_8_8_1_4_4_4_4_9_5_1_5_1_5_5_4_8_9_2_9_9_5_5_4_6_7_2_7_1_9_9_1_1_5_10_8_4_1_3_1_4_7_7_2_5_2_2_2_2_1_1_6_9_1_7_1_6_2_5_1_1_3_3_6_2_8_1_1_1_4_8_8_8_4_3_3_7_7_9_9_7_6_5_10_1_3_3_7_5_1_9_2_2_2_4_2_2_2_3_5_1_4_9_5_3_2_2_3_10_7_1_4_2_6_9_8_8_6_1_7_5_8_7_5_5_10_10_1_5_3_7_8_3_8_7_3_6_7_1_8_4_8_9_9_9_5_5_1_7_7_3_3_3_1_4_7_5_1_4_6_4_9_1_2_6_5_1_2_8_2_5_2_3_3_6_1_4_4_5_5_7_9_8_10_3_1_3_2_5_8_2_4_2_3_5_2_2_2_4_6_8_4_2_2_1_8_6_8_1_3_9_5_5_5_1_1_5_10_10_4_5_6_1_5_5_5_4_9_10_2_2_1_2_7_1_2_3_6_5_5_4_3_4_1_1_4_3_3_5_6_1_1_6_6_1_1_4_1_3_1_1_6_4_2_5_7_6_1_4_1_8_4_1_1_3_5_5_2_3_7_7_7_7_7_1_6_6_8_10_1_4_2_9_2_6_6_5_2_9_3_1_4_3_3_2_1_1_7_2_4_1_6_5_3_1_9_3_8_8_10_5_3_1_5_1_2_1_2_2_4_9_2_3_1_8_9_9_1_8_6_2_4_9_1_4_4_6_5_7_2_6_6_4_4_2_6_4_9_4_5_2_5_9_9_10_8_2_6_1_1_9_3_5_5_3_4_3_5_2_1_1_6_2_3_3_8_3_8_4_4_2_8_9_9_5_2_6_1_8_1_4_4_1_1_3_4_6_6_2_2_5_4_2_7_5_3_2_5_5_4_9_6_5_4_4_9_1_10_4_4_9_2_3_9_5_10_10_5_7_9_8_6_7_9_9_3_3_3_3_3_6_6</t>
   </si>
   <si>
-    <t>6_6_11_4_1_5_1_8_3_3_8_9_5_6_10_4_4_9_2_8_10_5_9_11_1_7_1_3_10_6_8_9_1_5_10_4_1_4_4_2_10_7_1_10_6_10_5_10_7_2_7_10_7_2_4_5_3_2_6_6_11_5_10_5_7_5_3_7_10_2_1_9_5_3_5_6_5_3_5_1_4_9_1_3_6_6_10_6_2_2_3_10_7_2_7_5_6_3_1_5_3_2_4_6_4_1_1_4_10_7_6_4_2_5_6_2_5_1_5_4_9_7_6_5_9_3_4_10_7_6_4_6_10_3_4_1_2_2_2_1_9_4_6_3_11_3_10_5_10_6_5_5_6_6_9_1_1_5_1_5_10_6_3_7_7_2_10_6_2_5_11_4_3_9_4_7_4_3_8_2_2_9_3_10_2_1_4_2_3_9_11_7_5_10_6_3_2_4_8_3_3_2_1_3_1_2_6_4_8_3_3_10_4_3_8_4_1_4_9_10_1_2_2_10_5_4_1_3_9_6_8_1_5_3_8_1_8_6_10_2_3_7_3_5_7_2_9_2_8_2_4_11_3_4_8_4_6_9_1_9_6_8_5_10_6_3_6_10_5_2_7_6_6_3_6_2_3_1_9_1_6_1_2_9_3_2_8_1_4_8_3_4_10_2_6_5_4_2_11_4_4_4_2_2_2_1_1_1_3_3_1_1_9_3_1_5_5_4_2_4_11_6_6_8_5_3_1_6_10_3_2_2_1_2_2_2_4_1_3_7_9_8_5_8_4_5_2_3_1_3_9_2_4_2_1_4_4_7_3_9_4_10_2_2_2_7_7_5_5_4_10_7_10_4_4_11_7_4_7_1_1_4_1_8_4_7_3_2_6_2_6_3_7_3_1_4_1_7_1_7_4_1_4_8_9_2_8_4_11_3_2_4_11_6_6_3_8_4_9_8_8_10_6_3_6_7_4_6_7_1_4_9_10_5_11_6_1_10_4_11_4_4_2_2_1_3_3_11_6_6_4_2_2_1_8_1_7_5_6_3_8_1_3_4_5_6_9_2_4_7_5_4_1_4_4_2_5_6_3_4_5_2_3_10_7_8_8_4_10_2_2_6_9_2_6_5_10_3_3_5</t>
-  </si>
-  <si>
     <t>4_4_5_5_4_2_1_2_4_4_1_1_5_2_3_5_8_9_2_3_4_3_6_1_3_3_3_1_1_4_4_4_4_2_6_7_5_3_3_4_2_3_9_6_6_1_4_4_1_4_3_8_9_7_9_8_2_1_4_3_1_6_5_4_2_8_1_5_4_6_1_5_7_8_5_3_2_4_1_4_7_2_5_4_10_10_4_2_1_7_7_9_5_4_5_8_4_4_7_6_6_3_2_6_2_2_8_4_4_1_3_1_8_2_2_1_8_8_7_5_6_6_9_5_4_4_6_2_1_9_9_9_9_1_6_5_3_2_3_6_5_5_5_5_3_3_2_3_1_4_4_6_2_2_5_4_5_2_1_1_2_5_2_2_1_1_7_7_2_3_5_1_1_3_6_8_5_2_2_2_3_9_1_10_5_8_8_2_6_4_8_4_3_3_1_7_7_7_1_5_6_4_5_4_4_6_2_5_6_5_5_3_4_3_9_1_3_5_2_7_3_6_7_3_6_6_6_6_6_7_7_4_4_4_2_3_3_8_4_2_4_1_1_1_5_8_5_5_2_7_7_8_2_7_3_2_5_7_5_7_9_4_2_2_9_6_1_2_5_1_3_6_9_1_3_5_3_4_6_8_7_3_7_10_4_1_8_7_9_3_3_7_8_5_7_9_1_2_7_5_1_5_2_3_4_6_2_6_2_1_8_9_4_2_2_7_1_2_2_5_3_6_3_8_6_2_2_1_1_9_9_1_5_1_1_10_9_4_3_2_10_2_2_8_5_9_1_7_9_3_9_9_1_5_3_2_7_4_8_2_8_3_4_4_1_7_8_9_1_5_5_5_4_4_6_1_7_1_8_8_3_4_5_6_6_2_1_10_9_9_9_1_4_4_7_2_2_2_9_4_4_4_9_9_9_1_3_8_9_6_4_2_6_5_7_1_4_8_2_6_6_3_2_1_5_2_6_4_1_3_3_8_4_3_6_6_5_1_10_6_4_3_1_4_2_1_6_6_1_5_5_10_4_7_3_1_3_8_7_1_3_7_10_2_1_3_2_3_8_3_7_1_2_6_9_4_8_9_3_10_10_4_1_3_8_5_3_2_2_2_5_5_1_6_9_3_2_6_4_2</t>
   </si>
   <si>
-    <t>8_2_1_10_4_4_11_4_8_2_6_1_6_6_7_1_2_3_3_6_7_1_8_1_6_11_6_4_7_1_7_8_6_2_9_3_4_1_8_10_5_3_4_4_11_4_3_1_8_9_1_8_7_5_2_10_3_11_3_2_10_7_1_10_3_10_3_2_9_4_10_6_6_1_6_1_8_5_5_7_5_8_5_6_2_8_2_3_4_5_5_9_7_4_2_3_7_3_1_4_3_10_6_2_5_2_10_5_10_6_9_5_7_4_3_5_5_5_7_5_1_8_5_5_4_8_9_8_4_8_6_2_2_5_2_5_10_6_11_4_9_3_4_4_1_5_2_4_5_4_10_2_1_6_5_6_3_9_1_6_9_11_3_10_2_3_2_7_2_4_10_4_6_4_4_2_10_2_4_1_7_10_7_8_2_6_10_3_6_2_10_4_5_7_1_2_4_5_4_9_3_6_6_5_5_1_4_3_4_7_7_3_10_5_2_11_6_5_5_5_2_3_2_1_4_2_1_6_3_9_9_4_8_3_5_6_5_2_4_4_5_7_9_5_2_1_4_4_6_4_3_3_8_3_5_1_7_3_5_5_3_7_1_5_4_6_2_9_1_1_1_2_10_3_8_1_4_11_6_4_1_10_6_4_1_10_5_4_1_4_5_6_10_1_7_2_4_6_4_5_3_4_2_5_4_1_1_8_10_4_6_5_5_6_10_3_6_10_6_3_5_7_4_7_7_11_4_8_4_1_8_3_5_1_10_7_7_6_1_9_1_1_8_4_8_1_2_6_8_9_6_9_3_7_6_5_2_4_2_1_2_10_6_1_4_4_8_7_3_3_3_8_9_7_3_4_6_4_6_10_4_5_10_7_1_1_3_11_5_6_10_4_1_4_7_10_6_2_5_10_6_2_3_4_1_1_3_10_5_2_5_1_6_5_3_3_8_10_6_3_3_2_2_10_5_4_9_3_1_11_4_6_2_6_2_4_4_8_4_4_8_6_8_7_7_1_4_11_5_1_8_1_4_1_4_11_4_4_5_9_4_3_4_9_6_6_5_10_7_8_5_2_3_2_8_2_6_3_5_1_6_2_7_8_2_3_5_5_1_2_9_11_6_2_6_6_5_5_8_8</t>
-  </si>
-  <si>
     <t>8_3_4_2_1_4_1_10_2_2_9_5_7_2_2_6_4_6_2_3_1_1_6_4_7_10_10_10_10_9_9_7_4_2_2_7_6_2_6_9_7_8_8_8_1_5_2_2_3_7_1_9_5_5_4_4_3_1_5_5_5_3_4_3_5_6_10_4_3_6_7_2_8_1_1_3_5_2_3_3_6_10_5_4_4_7_5_5_10_9_10_4_3_6_7_3_3_7_7_1_8_2_4_4_4_5_10_6_2_4_1_1_5_4_8_2_1_2_7_3_2_6_7_6_1_2_1_1_3_2_2_3_9_1_9_2_3_6_6_6_2_2_10_10_4_2_2_7_3_5_1_7_7_7_4_2_9_2_3_1_3_7_4_5_5_2_8_1_4_2_8_3_2_2_1_1_9_5_8_8_1_1_3_4_8_1_8_8_1_5_1_6_8_8_10_4_3_10_6_2_2_3_10_5_1_2_5_5_4_2_7_4_4_5_5_1_1_4_4_4_3_7_1_4_2_2_1_4_3_3_8_8_6_8_9_1_2_10_1_8_1_4_7_5_5_1_7_8_2_1_4_1_3_9_6_8_1_3_4_4_5_6_8_1_1_7_10_3_5_5_9_9_7_5_2_4_4_5_3_5_3_4_7_7_1_1_8_2_2_1_1_1_4_4_3_2_2_5_2_9_3_1_5_9_9_8_1_10_4_6_1_6_7_1_8_5_4_4_2_3_7_1_6_1_7_2_3_3_5_2_5_6_7_7_6_6_7_2_5_4_6_2_1_2_3_5_10_10_9_10_10_9_2_4_5_5_3_3_2_3_2_2_3_3_2_8_2_8_2_8_2_6_4_9_2_5_7_3_2_8_8_1_1_3_4_4_3_5_2_2_4_9_5_2_5_5_1_1_7_7_4_3_5_1_4_7_2_4_7_7_10_4_6_2_2_3_1_1_2_7_10_5_8_7_7_5_4_1_1_9_5_2_4_6_8_2_4_7_1_6_2_1_3_1_2_4_4_8_8_5_2_10_3_8_4_4_10_5_3_7_10_10_1_5_4_2_2_1_3_5_1_9_6_2_10_1_4_1_3_2_6_1_6_3_7_6_4_8_4_2_3_3_4_9_5_3_4_6_10_1</t>
   </si>
   <si>
-    <t>9_9_6_9_4_6_6_7_1_5_2_6_5_1_1_10_3_4_9_10_3_6_1_1_5_3_1_1_9_1_2_2_8_9_1_1_1_1_1_7_6_8_2_9_9_5_1_1_1_5_5_4_3_5_6_9_9_2_2_7_5_4_2_8_7_8_8_3_4_4_3_9_6_7_5_7_3_2_7_3_6_5_9_2_7_10_4_6_5_2_6_4_4_8_2_2_1_1_4_7_3_2_11_4_7_7_4_5_1_3_2_11_5_6_5_1_3_2_1_6_6_7_10_7_4_9_9_1_1_4_8_1_3_2_6_8_11_6_1_7_1_6_11_6_6_9_10_7_6_10_7_2_7_2_8_4_9_6_9_8_10_6_10_7_6_2_6_10_5_2_7_7_5_6_5_2_4_7_11_3_4_7_4_7_4_2_4_6_6_6_1_6_3_1_3_3_2_3_5_1_3_4_2_3_7_4_5_3_3_2_5_2_3_8_1_10_6_3_8_9_5_9_4_11_7_10_3_1_8_2_9_4_5_4_2_2_2_6_11_7_7_6_9_4_4_4_5_1_10_6_1_1_3_3_10_6_4_3_5_9_3_6_3_2_8_4_4_1_8_10_3_9_8_6_2_7_8_1_6_9_3_4_9_5_2_2_1_8_8_8_8_8_1_4_1_6_4_4_2_6_6_4_2_8_2_8_9_5_2_2_4_6_9_8_10_3_1_1_2_4_2_8_5_6_6_6_7_3_1_1_8_4_7_2_2_1_3_7_8_10_5_6_3_10_1_4_6_5_7_1_1_1_6_3_3_7_5_6_8_4_2_3_5_5_5_7_9_1_3_4_8_3_2_3_2_1_5_2_4_10_7_7_1_10_5_3_5_7_3_8_1_2_2_1_8_8_7_5_1_6_2_2_6_10_3_1_2_10_3_5_8_6_1_11_2_8_8_8_5_8_6_5_10_7_1_3_2_7_3_5_6_8_10_2_6_3_4_3_1_3_7_4_3_1_5_10_3_3_1_8_2_6_10_2_6_4_8_3_3_9_10_6_4_7_6_10_7_9_3_2_6_3_4_4_8_3_5_7_3_5_9_8_3_6_5_4_2_4_4_10_7_9_2_5_2_4_5_3_1_2</t>
-  </si>
-  <si>
     <t>4_6_7_7_1_1_2_3_5_1_8_1_3_4_1_1_1_7_10_2_2_1_1_1_10_5_7_7_3_8_1_3_4_1_5_8_6_8_1_8_4_2_4_4_6_2_1_4_2_1_4_1_9_4_4_9_6_4_3_5_2_5_5_3_9_3_10_8_5_8_6_5_6_6_2_3_4_5_6_2_6_6_7_4_3_6_8_9_4_5_1_8_8_5_8_5_5_2_8_3_9_9_2_3_4_4_6_8_4_5_6_8_2_2_6_8_10_2_4_2_6_9_3_2_3_1_5_9_7_9_3_3_8_6_7_2_1_1_3_1_4_4_7_7_7_2_3_2_9_1_1_2_3_3_4_1_6_6_4_3_2_5_9_6_9_2_3_4_2_8_2_4_9_7_7_5_1_7_4_6_6_4_3_3_7_1_4_1_3_4_4_3_2_9_7_4_8_3_3_9_3_1_7_6_3_1_2_6_7_8_2_2_4_8_4_2_1_2_6_4_2_6_8_3_1_5_9_1_7_10_1_2_2_8_9_10_9_4_5_3_7_5_3_3_6_9_4_4_3_10_5_6_1_1_2_8_6_6_1_6_5_3_3_9_1_1_5_1_1_4_9_1_3_2_2_5_5_9_3_4_2_4_1_1_1_10_3_1_1_8_1_6_6_6_5_2_3_8_8_5_4_3_6_6_4_4_6_6_1_4_4_1_1_2_2_5_3_10_2_4_7_4_4_2_3_2_1_4_1_2_8_8_6_8_2_1_1_8_6_7_3_4_2_4_4_3_8_4_9_5_2_1_1_3_3_3_3_8_8_8_4_4_3_7_2_7_2_1_7_10_3_4_4_5_2_2_1_1_2_6_4_3_3_2_1_5_6_6_6_6_9_6_2_1_2_1_7_6_8_3_3_2_1_1_7_1_2_9_9_2_4_3_6_5_4_10_5_5_4_3_5_1_5_7_5_10_1_3_1_8_4_2_1_5_8_9_2_2_9_6_7_9_6_1_9_4_1_8_2_4_7_3_2_5_7_8_3_1_2_5_7_9_9_4_4_2_6_6_9_1_1_4_4_2_9_9_6_3_5_5_2_3_10_10_10_4_3_2_6_3_3_5_1_5_7_4_8_4_4_5</t>
   </si>
   <si>
-    <t>3_5_4_9_1_10_7_3_2_6_7_6_4_6_1_2_10_7_11_6_5_1_10_7_6_4_3_2_2_1_1_5_7_5_10_7_6_7_3_2_7_6_3_9_7_1_1_1_8_4_8_5_8_1_10_7_2_2_10_3_10_5_3_2_8_7_10_7_5_7_7_9_6_2_11_7_9_4_7_7_8_3_4_9_1_9_7_2_5_7_4_5_10_5_1_6_8_2_9_7_2_9_4_8_7_4_1_5_4_2_8_3_8_1_3_2_9_9_2_5_6_6_8_7_3_5_8_4_1_7_5_3_10_6_2_7_6_9_9_6_2_2_1_8_7_3_1_7_2_4_1_4_7_4_5_6_2_2_2_5_6_4_8_2_10_6_11_3_3_10_2_2_9_8_3_7_6_7_11_2_7_7_1_8_5_4_10_5_1_4_9_5_1_9_8_6_6_6_5_6_4_7_10_7_7_3_8_6_5_1_9_3_5_6_9_11_4_8_3_4_3_3_1_2_9_5_5_2_9_5_6_2_8_2_3_2_9_3_2_3_4_4_4_5_3_10_4_6_8_5_6_1_1_10_3_1_5_2_5_1_4_3_7_8_4_2_2_1_2_4_1_7_8_8_2_1_1_2_8_5_1_1_8_2_5_5_6_1_7_6_5_1_9_4_4_10_5_2_5_1_5_5_3_8_1_4_6_8_2_1_1_6_1_11_6_2_2_4_4_10_3_6_3_10_2_2_4_7_3_2_7_7_3_2_1_8_8_4_3_8_4_2_9_7_4_5_8_9_1_3_4_3_5_1_4_7_9_2_4_10_7_3_4_8_8_6_1_4_8_2_4_5_1_6_2_3_8_6_5_2_4_4_1_10_3_10_7_10_5_3_1_5_6_7_5_7_9_6_10_4_1_3_3_1_2_4_5_8_6_9_4_8_4_5_2_6_5_7_6_1_2_1_7_3_5_4_6_8_3_8_6_2_1_7_8_5_4_8_10_2_6_8_7_4_7_1_3_4_7_1_8_9_9_7_5_5_5_2_8_7_1_4_5_3_9_8_7_6_3_1_9_9_7_8_3_1_1_1_9_3_8_3_6_6_3_3_10_5_3_8_4_2_1_2_2_6_2_6_11_6</t>
-  </si>
-  <si>
-    <t>11_11_11</t>
-  </si>
-  <si>
     <t>8_6_6_8_4_5_10_10_5_6_1_2_1_6_8_2_10_7_8_3_9_9_4_10_1_9_9_2_3_1_3_4_5_4_4_1_5_5_5_5_1_10_9_9_2_3_3_3_2_8_5_3_1_4_1_4_6_5_6_4_5_5_3_1_7_7_7_6_2_10_1_2_2_2_2_3_3_3_8_5_2_3_9_5_7_1_4_4_2_5_1_1_3_8_6_3_1_5_1_2_3_7_2_5_3_8_2_5_10_10_4_1_4_1_4_3_8_5_6_9_1_1_3_9_6_6_5_10_3_3_2_9_6_1_1_1_1_8_1_8_9_3_8_8_3_2_2_4_5_7_7_2_1_1_6_1_2_4_7_7_8_1_1_2_9_3_9_2_9_7_7_2_2_2_10_6_4_6_6_9_1_6_4_8_5_7_6_4_10_3_7_4_9_6_1_2_2_1_1_1_5_1_5_1_3_3_5_1_1_5_8_1_6_4_7_6_2_1_2_5_1_7_5_9_3_10_5_3_2_4_6_3_9_9_1_3_1_4_10_3_3_2_5_5_5_3_5_4_3_1_4_4_8_8_1_8_3_3_2_5_4_1_7_3_1_4_4_2_1_3_5_1_2_2_9_4_4_3_2_4_9_1_5_5_1_2_5_5_2_8_9_7_9_2_2_1_1_2_2_8_4_4_8_8_8_6_8_8_8_4_1_1_3_8_4_4_10_6_2_8_9_9_6_2_2_6_4_4_4_8_2_2_1_1_4_8_1_2_3_9_8_1_4_2_4_3_7_3_5_2_1_1_4_6_6_5_3_3_2_1_3_10_5_4_1_1_7_1_8_2_2_3_4_4_8_6_4_2_3_7_2_3_5_8_2_6_6_7_1_1_6_4_3_5_5_1_8_4_5_2_10_3_4_3_4_7_4_6_10_7_7_9_1_2_7_2_9_2_5_5_7_2_7_5_3_1_3_3_5_2_3_4_3_3_2_10_10_7_4_5_3_8_8_5_2_1_6_2_6_4_5_4_2_4_5_2_3_8_5_5_10_2_6_3_5_2_7_4_5_8_5_6_4_1_1_4_4_1_3_1_1_8_6_2_5_6_6_5_8_9_1_1_3_10_6_8_4_7_10_1</t>
   </si>
   <si>
-    <t>2_6_4_1_1_5_10_6_2_5_3_4_1_4_10_7_3_7_3_3_9_10_7_10_4_3_6_11_7_8_2_9_9_2_4_1_3_5_5_10_7_4_9_1_2_8_2_3_1_6_5_3_8_8_6_5_11_4_1_4_10_5_1_1_3_2_2_2_5_9_3_4_2_1_4_10_5_6_3_6_2_1_10_7_5_2_3_9_11_4_6_7_1_4_5_5_3_2_5_9_7_2_6_1_1_3_6_1_5_7_7_11_7_7_11_6_4_6_5_3_5_3_2_3_8_9_10_4_4_8_3_2_7_6_5_8_3_9_9_8_2_10_5_6_3_7_6_4_4_1_1_4_8_2_4_8_3_11_6_4_2_8_6_1_3_5_2_11_7_2_9_8_9_3_1_5_9_9_1_1_4_3_4_2_10_3_2_1_2_3_4_1_5_1_7_2_6_8_4_5_8_3_5_5_2_1_5_10_6_3_1_3_8_10_7_2_1_10_2_7_1_4_2_8_1_7_3_6_4_5_1_11_4_10_4_11_5_5_3_8_2_4_2_11_2_4_3_2_9_1_1_8_2_1_4_1_8_2_4_9_3_3_1_7_9_9_8_6_2_10_3_6_1_4_1_4_4_1_1_11_5_8_9_1_5_4_1_9_9_1_9_1_1_3_6_1_4_1_10_5_6_1_11_6_11_5_2_4_1_1_5_6_4_8_3_6_2_5_9_2_5_11_7_9_4_6_1_1_9_6_7_7_3_9_1_7_2_9_5_9_6_10_5_4_6_7_8_3_7_10_4_11_7_7_5_3_6_6_7_8_3_4_9_4_3_2_5_3_3_8_4_4_7_1_9_1_8_1_4_6_5_1_8_1_7_3_7_2_2_6_11_7_1_9_4_7_9_6_8_2_6_1_2_1_7_7_2_8_4_6_11_7_1_5_1_5_7_3_5_4_4_6_3_3_9_10_2_2_2_6_9_4_1_2_3_6_10_6_7_10_4_4_4_9_3_2_5_3_2_6_10_5_2_9_6_3_1_4_7_7_5_2_5_6_6_6_9_1_11_5_5_8_3_1_1_4_8_5_2_2_2_5_2_7_6_10_4_1_8_1_2_4_6_5_5_2_2_10_2_4</t>
-  </si>
-  <si>
-    <t>1_2_2_4_2_2_2_3_3_3_8_7_7_1_5_1_1_6_2_1_2_8_7_2_3_3_1_4_6_7_6_3_3_8_8_8_2_2_1_1_4_4_7_3_2_7_7_7_7_2_7_4_4_2_7_7_7_8_8_8_2_4_8_4_8_8_7_7_1_4_7_5_2_2_8_8_8_1_2_1_1_7_7_4_2_2_2_2_2_8_5_2_6_6_1_8_4_1_3_3_3_2_3_3_6_4_1_1_1_4_4_1_2_1_1_2_3_8_8_8_8_2_8_4_3_4_3_5_1_2_4_4_7_2_7_2_5_8_8_5_6_1_5_3_1_5_5_4_4_1_1_1_6_8_6_2_2_7_8_1_2_1_1_2_1_1_1_2_4_4_2_4_5_4_8_3_1_1_6_3_1_2_1_1_8_2_2_2_3_4_7_8_2_6_4_2_2_4_4_5_6_6_5_5_3_1_8_8_2_2_4_2_3_3_1_5_2_3_1_2_1_1_1_8_8_4_4_1_1_7_4_4_1_5_6_4_4_8_8_6_6_6_8_7_6_7_5_5_5_6_3_3_5_8_3_2_4_3_8_3_6_7_1_3_4_8_3_2_1_8_8_8_8_8_4_2_7_1_4_4_4_7_1_1_3_3_3_8_1_4_3_2_7_1_8_4_8_4_8_2_1_8_7_4_4_4_4_2_3_1_8_7_3_3_2_2_8_8_4_4_2_6_6_2_2_4_8_4_3_6_4_8_7_3_2_2_1_7_2_2_2_7_1_1_1_1_1_8_8_7_3_2_2_2_1_3_8_7_4_6_3_4_6_3_2_8_6_6_6_6_3_1_7_3_2_7_2_7_1_8_1_4_1_2_1_7_1_1_1_4_1_2_2_4_6_1_5_1_3_7_5_3_3_3_1_8_2_2_6_2_1_7_6_1_3_1_4_7_7_7_7_5_8_4_8_7_2_1_7_4_4_2_2_8_8_8_3_1_1_2_6_1_7_2_2_4_7_8_1_6_2_5_2_7_2_2_8_1_1_5_7_2_4_1_7_1_2_4_3_3_3_7_2_1_3_3_4_7_1_7_4_7_1_7_4_2_5_5_3_4_7_3_8_7_3_3_1_2_6_2</t>
+    <t>1_3_5_2_4_7_5_8_5_4_3_1_8_2_2_7_1_1_3_2_2_2_2_1_1_5_5_1_2_4_4_2_3_2_2_7_1_2_1_4_3_4_4_5_7_6_8_3_1_1_5_3_7_8_4_3_8_6_4_2_2_2_1_6_3_4_4_8_4_6_3_8_4_4_5_4_5_7_6_1_3_2_2_7_2_1_3_3_5_7_5_8_3_1_1_4_1_1_1_4_2_1_4_7_7_1_8_6_4_7_1_1_1_1_1_5_5_1_4_1_3_8_4_3_3_8_8_1_7_8_7_2_2_2_6_4_4_1_4_1_3_1_1_6_4_3_6_8_1_3_6_1_3_8_8_2_3_6_2_2_7_5_6_4_4_8_1_7_4_3_3_3_3_4_1_5_3_2_8_8_2_8_2_1_4_4_2_5_3_2_5_3_3_3_4_1_7_8_8_6_7_1_7_7_4_2_2_7_5_4_1_1_3_8_5_5_1_8_8_8_6_2_3_2_4_2_1_1_5_8_1_3_3_4_3_7_7_3_2_3_4_1_7_1_7_7_2_8_6_5_7_3_8_5_3_1_2_4_3_1_1_2_7_4_3_1_1_4_2_2_1_7_8_4_4_7_7_8_1_7_4_4_4_4_4_2_1_3_7_7_2_5_2_3_7_2_1_1_3_1_5_7_6_2_4_1_3_8_6_6_6_1_1_6_6_7_6_3_3_5_4_2_1_7_1_3_1_8_8_8_4_3_3_1_1_8_5_8_3_3_1_3_2_5_1_6_7_6_7_2_5_1_1_2_7_2_2_1_3_7_7_2_8_8_5_2_2_5_8_2_3_8_6_4_4_5_1_1_1_7_1_3_7_3_7_8_8_8_4_3_4_4_4_7_3_6_6_7_4_5_7_3_7_1_6_7_5_4_4_4_7_1_6_5_7_2_2_7_3_7_1_4_7_4_6_4_1_1_4_4_5_2_5_5_4_2_6_2_4_1_2_4_1_4_3_5_8_7_7_5_7_7_3_8_6_4_8_1_4_8_7_3_2_8_7_2_3_2_6_3_1_1_1_7_2_3_7_1_1_7_4_1_4_4_3_1_1_1_2_7_3_8_8_1_4_1_1_7_2_7</t>
   </si>
   <si>
     <t>4_2_7_5_8_7_6_7_3_6_7_8_7_6_2_3_7_4_8_4_3_1_5_7_2_6_6_7_8_2_7_5_1_7_4_1_6_4_4_7_5_2_5_1_3_6_2_3_2_1_2_9_3_6_6_7_2_8_3_2_7_4_2_4_8_2_3_1_4_2_6_6_6_8_4_3_8_1_4_2_5_4_2_3_5_7_6_3_1_4_1_5_7_4_6_3_3_4_2_1_6_1_4_9_2_3_7_3_7_1_2_7_8_9_1_4_2_7_3_5_1_4_4_1_8_8_6_8_9_2_1_3_1_3_2_1_7_8_7_5_7_6_9_3_3_3_1_4_3_3_6_2_3_4_1_7_1_7_9_7_6_7_2_1_8_2_7_2_6_6_3_4_2_1_3_1_2_4_1_4_5_8_7_3_6_8_7_3_2_9_2_8_7_3_5_2_4_3_1_9_9_8_5_2_7_9_5_4_3_3_9_8_5_2_1_4_4_7_6_3_1_9_4_7_8_5_6_9_5_3_4_2_8_8_8_3_3_3_2_1_3_6_3_6_5_1_4_8_4_9_2_3_5_1_1_8_3_3_1_5_2_3_9_6_1_5_2_2_9_7_6_5_1_1_1_2_6_5_6_1_3_4_4_5_1_6_6_4_8_7_6_2_4_1_4_8_9_2_1_3_7_6_1_2_3_8_2_1_2_4_6_3_6_4_1_3_9_6_4_4_2_5_1_2_1_4_4_2_1_2_1_8_1_6_6_2_5_6_2_3_5_4_3_5_9_8_8_5_9_8_1_5_5_2_1_6_3_8_4_1_6_4_6_9_2_8_1_6_5_8_8_7_6_1_2_7_7_1_8_7_5_7_3_1_1_9_5_7_7_3_8_6_2_8_4_6_7_5_7_5_6_5_2_3_3_3_7_1_4_1_4_4_1_3_1_2_1_8_5_3_5_9_5_4_3_2_1_3_6_8_2_8_7_2_2_7_2_7_1_3_3_8_4_6_1_5_5_6_1_6_2_3_4_7_5_9_3_5_7_2_8_3_5_4_7_9_8_6_5_1_3_7_5_2_8_4_1_3_4_1_2_7_6_1_4_1_8_3_8_1_7_4_4_5_1_3_7_1_2_1</t>
   </si>
   <si>
-    <t>8_4_1_4_1_1_1_3_8_4_2_4_4_3_2_1_8_5_1_3_3_6_6_4_2_7_2_2_5_5_1_6_6_4_5_2_7_6_6_7_7_6_3_5_8_2_2_4_6_6_3_8_1_8_4_3_3_3_3_3_1_8_8_1_4_3_1_3_1_1_1_1_4_1_1_4_2_1_2_2_2_1_1_1_4_5_3_4_7_2_2_1_1_8_8_8_8_8_2_2_2_3_3_7_7_2_5_3_4_1_1_8_3_7_4_4_4_2_7_7_1_3_7_1_1_4_7_1_3_3_1_1_4_7_7_3_1_8_8_4_5_5_6_8_1_4_3_2_6_1_3_4_1_7_2_3_1_4_6_4_4_4_2_8_3_2_3_1_8_4_4_1_1_6_3_1_6_1_2_7_1_1_6_6_6_6_6_3_1_4_1_8_5_5_2_3_3_7_3_3_2_2_8_8_2_8_7_1_2_2_2_2_8_8_2_2_1_7_8_8_4_7_3_1_1_1_6_8_3_3_5_2_1_2_8_3_6_8_1_6_6_1_4_1_7_8_8_1_2_7_8_2_1_3_7_1_8_8_8_4_4_2_8_3_7_3_6_2_2_1_2_1_1_3_3_1_3_8_3_2_2_2_2_4_3_3_6_5_2_1_4_8_4_2_5_7_8_3_1_5_2_2_6_6_1_3_3_4_7_7_7_6_2_3_1_5_8_8_2_2_5_7_2_5_7_4_4_1_7_7_7_4_8_8_2_8_1_7_2_8_8_2_2_2_1_7_1_2_2_5_4_4_7_1_1_6_7_7_2_4_6_4_4_3_3_1_5_1_7_1_2_4_1_1_8_4_4_8_4_7_1_7_6_7_7_6_2_2_1_4_5_8_4_2_6_7_2_4_3_3_7_7_5_2_5_1_1_1_1_2_8_3_3_1_4_4_7_2_1_2_2_2_1_1_7_4_5_8_8_8_2_1_2_1_1_1_3_7_1_7_7_3_3_2_6_4_4_1_4_6_1_1_2_8_3_4_1_4_1_1_8_6_7_1_1_5_1_7_3_7_2_1_2_1_3_3_1_1_2_3_3_1_1_3_2_2_2_3_7_8_6_6_2_1_1_8_2_2_4_3</t>
+    <t>4_2_1_1_8_2_4_5_1_6_6_3_4_2_4_4_1_1_8_4_2_2_7_2_7_8_2_2_3_1_1_1_1_2_5_5_1_2_2_1_2_1_2_2_2_2_4_3_2_1_1_1_3_2_2_8_2_1_3_3_7_4_7_1_8_1_2_4_2_8_5_5_5_7_8_8_2_3_1_5_4_5_3_8_7_8_2_2_4_2_2_5_7_5_7_3_1_2_1_4_5_2_2_3_1_7_1_6_1_8_6_8_3_3_1_6_2_2_2_8_1_2_2_3_1_1_1_1_6_3_5_3_8_2_6_1_4_4_7_1_1_6_1_2_7_1_2_8_7_2_8_5_3_3_5_8_7_7_3_6_4_4_4_8_5_5_1_8_3_4_2_7_7_7_5_2_2_2_8_1_8_4_8_5_3_1_7_4_2_2_4_1_8_2_6_6_4_4_4_4_2_1_1_1_6_4_7_7_3_3_2_2_3_8_8_8_7_8_8_6_1_4_2_3_4_1_1_7_4_7_7_7_1_1_6_2_4_4_3_1_1_4_2_1_4_6_6_3_1_7_7_3_1_7_3_3_1_1_3_3_7_8_8_4_1_7_1_8_1_2_5_1_1_3_2_2_1_1_8_8_8_2_4_1_5_3_1_5_1_4_3_3_3_3_5_6_2_2_8_1_1_1_5_2_2_2_4_4_7_1_5_7_1_8_5_7_6_3_3_7_6_4_4_4_4_8_8_1_2_3_5_4_4_8_7_4_4_3_3_7_6_1_4_2_2_1_1_7_2_6_6_3_2_6_4_1_1_6_4_1_5_5_8_8_1_5_4_7_7_1_7_5_5_3_7_1_8_8_8_2_4_3_7_5_2_2_5_4_1_3_4_4_6_1_5_8_8_8_2_2_7_2_5_6_4_4_4_8_2_3_8_1_5_1_3_1_5_8_1_2_4_2_8_2_2_8_4_6_3_3_3_8_3_3_4_5_1_4_1_3_4_1_1_6_6_1_6_1_4_4_4_5_6_4_3_1_2_4_1_1_5_5_5_6_3_7_1_4_4_2_6_2_8_4_4_7_3_2_8_3_6_3_4_1_1_6_1_1_4_2_1_1_4_3_1_3_3_3_1_7</t>
   </si>
   <si>
     <t>2_2_9_8_2_1_7_2_9_4_8_8_1_1_2_1_6_4_1_2_3_2_4_3_3_3_7_2_6_4_6_4_5_4_1_4_3_2_2_4_4_1_3_6_8_8_7_8_1_3_6_3_3_4_5_5_2_6_8_4_1_1_8_1_6_1_1_6_3_4_4_4_7_1_7_6_5_4_9_3_2_2_4_6_7_6_6_1_3_4_3_7_3_5_1_5_9_1_1_5_1_2_6_1_6_2_2_3_6_4_6_3_6_8_4_2_7_8_3_1_7_8_2_8_2_4_3_2_5_7_1_6_3_9_9_2_7_6_4_3_8_2_2_8_6_8_1_9_9_4_3_7_1_1_4_8_1_6_2_1_7_4_4_9_7_5_7_3_3_2_1_7_4_5_6_3_1_3_4_2_1_3_2_1_7_7_8_8_9_2_7_1_4_4_1_8_7_3_4_6_1_6_1_5_6_9_8_7_3_2_4_2_2_8_5_3_3_8_1_4_3_8_3_7_4_3_5_2_1_3_2_2_2_2_3_8_3_6_6_3_2_1_6_1_2_9_2_4_6_5_7_9_7_1_1_1_4_1_9_3_3_6_8_2_4_1_8_2_8_7_1_4_1_2_4_4_2_3_9_9_6_1_2_3_1_7_8_9_7_1_9_2_8_2_7_4_5_5_6_6_8_4_8_2_3_4_4_1_4_3_5_8_4_4_7_7_2_6_5_2_5_1_4_2_4_1_5_3_9_2_1_1_1_4_2_7_4_4_7_5_4_6_8_8_4_1_4_4_2_1_6_3_6_9_2_5_7_4_1_4_6_3_6_1_9_2_2_2_3_5_4_8_5_9_3_9_1_3_6_4_8_8_3_6_3_7_1_7_1_3_9_7_4_1_4_3_3_3_6_5_6_7_8_7_2_4_3_8_7_9_6_7_6_7_3_7_8_2_9_5_8_3_4_7_3_2_1_5_5_5_3_1_4_1_7_5_5_7_5_6_4_1_4_5_5_1_4_2_3_2_4_9_2_6_3_1_8_2_2_8_9_3_8_3_5_2_2_6_5_4_6_1_1_7_4_9_9_1_4_7_3_3_7_6_8_3_2_9_5_6_1_8_6_4_4_3_2_5_1_5</t>
   </si>
   <si>
-    <t>7_7_8_4_3_4_3_3_2_3_1_2_2_8_1_2_1_4_4_7_7_1_8_8_1_4_1_2_2_1_1_1_3_5_8_2_1_1_1_7_6_6_5_2_2_8_8_1_4_5_5_7_7_7_7_7_4_3_2_8_1_1_5_8_1_1_3_2_2_7_8_1_3_7_4_4_3_3_4_1_4_4_6_2_4_7_1_8_8_7_4_4_7_4_4_7_6_3_2_3_2_3_7_7_3_6_2_2_5_3_7_2_6_2_8_2_1_7_5_3_7_3_8_1_8_6_1_6_5_7_2_8_8_2_4_8_8_8_8_8_8_8_3_1_8_3_6_2_2_7_1_4_5_2_8_1_3_7_5_3_3_5_3_4_4_1_8_7_3_2_1_7_7_3_5_4_7_3_1_1_1_3_1_8_8_4_4_1_8_1_3_6_1_1_1_3_8_3_2_8_3_1_3_1_1_4_5_8_4_7_7_7_6_4_2_2_2_4_4_1_6_8_7_7_6_3_8_8_2_3_4_1_1_8_8_2_2_8_2_8_4_2_2_1_7_1_8_7_5_8_8_3_6_4_2_8_2_3_2_7_1_1_8_6_1_7_7_2_6_1_3_4_4_8_1_6_4_4_8_8_7_1_6_1_5_5_1_5_7_2_7_8_8_3_7_8_5_1_6_2_1_4_4_8_2_1_2_6_1_6_7_4_4_4_2_1_1_5_6_3_7_8_1_6_3_4_2_7_7_1_1_5_1_2_2_2_5_5_5_4_1_1_1_6_1_1_4_3_2_2_4_4_2_2_4_6_6_4_8_5_1_8_5_3_5_7_1_7_1_8_6_3_6_5_8_3_5_6_1_5_1_3_1_8_1_1_4_1_4_1_2_4_8_1_7_1_5_6_6_6_2_8_3_7_1_4_2_3_4_8_5_6_3_2_6_6_2_8_6_5_2_2_3_3_6_3_1_2_8_6_6_3_3_4_8_5_4_1_4_1_1_1_2_2_2_7_1_1_3_2_6_1_3_8_7_1_1_8_8_8_2_7_3_7_1_7_7_8_2_3_4_4_4_6_7_4_2_6_2_2_3_3_6_4_6_8_8_5_5_2_2_3_7_1_7_7_2_3_1_3</t>
+    <t>8_5_8_8_2_4_4_2_2_1_2_3_3_1_8_5_1_3_1_4_2_7_5_3_7_3_8_2_5_2_8_4_3_4_8_1_6_5_8_8_4_6_4_8_4_1_1_1_2_2_4_8_3_6_1_2_4_4_4_3_3_1_8_8_8_4_8_4_1_6_6_1_8_3_4_7_2_6_4_4_7_4_7_1_1_6_2_7_3_2_1_1_8_3_1_1_4_4_4_1_2_6_6_6_1_3_2_8_6_4_4_4_2_6_5_2_3_1_7_7_8_6_1_5_5_1_4_1_2_7_1_8_2_6_5_6_3_1_1_8_1_2_7_6_4_7_5_2_5_8_2_5_7_7_4_6_2_4_2_5_5_6_5_8_8_7_2_4_4_4_8_8_8_4_7_8_7_7_8_2_8_8_5_6_1_5_4_1_5_4_4_6_3_1_3_1_4_2_1_7_2_2_2_6_2_6_2_2_5_8_8_4_7_5_2_7_2_1_7_7_3_4_4_4_8_6_5_5_7_8_3_2_5_5_5_5_4_4_8_5_2_2_1_1_2_7_8_3_2_2_2_4_4_2_7_7_7_8_5_4_4_4_1_4_6_3_1_1_2_2_2_2_8_1_1_5_7_2_5_3_2_5_5_1_1_1_4_4_5_8_3_4_4_4_4_5_1_1_6_5_4_1_5_8_3_7_4_2_8_1_6_4_3_3_2_8_8_3_8_3_6_5_8_2_3_3_3_3_5_4_1_7_6_4_8_7_3_3_1_3_3_2_4_8_1_4_2_2_3_8_6_3_6_7_5_2_2_6_4_4_8_3_2_4_1_2_4_5_6_4_2_1_7_6_6_1_6_8_3_6_2_3_5_5_5_2_3_3_3_4_4_8_5_4_3_1_6_4_1_2_3_2_8_1_1_8_8_4_4_3_3_8_2_2_2_3_1_1_2_2_2_7_2_1_4_6_3_6_8_8_2_2_1_3_6_4_1_1_4_4_4_5_5_1_1_7_6_6_8_5_3_3_4_3_7_3_3_3_8_1_4_1_3_3_2_2_1_3_2_8_4_1_4_1_3_3_6_3_3_7_4_8_2_5_4_7_7_1_3_2_3_2_1_8_1_7_7_6_6_6</t>
   </si>
   <si>
     <t>6_7_2_3_7_3_7_6_8_4_8_4_1_7_5_3_3_4_9_2_6_5_5_4_8_2_6_5_4_4_2_2_2_9_5_5_2_7_1_5_8_5_2_8_2_6_2_2_1_8_8_6_1_7_4_3_3_8_4_3_7_7_1_5_3_4_8_8_6_7_2_2_3_3_4_4_1_3_8_1_9_2_2_3_5_4_8_4_6_2_3_2_4_6_3_7_8_6_3_2_6_2_1_4_8_3_6_5_7_5_8_8_3_2_2_6_1_5_6_9_8_4_1_3_2_4_4_5_2_1_5_2_5_3_9_6_8_6_4_9_7_3_6_6_2_6_5_7_8_2_2_7_5_3_4_1_2_1_3_1_6_3_1_3_3_7_2_2_5_1_2_2_4_3_6_3_4_9_2_3_2_8_3_3_2_1_7_2_5_2_5_6_3_2_4_3_2_4_1_4_1_5_4_5_6_3_7_5_2_8_5_3_1_7_4_4_3_2_1_8_7_4_5_5_5_1_5_3_1_6_3_7_1_8_4_3_2_6_7_5_6_3_2_3_2_3_3_4_8_8_8_3_2_9_9_2_8_2_2_7_4_4_2_4_3_2_9_4_6_3_8_6_8_3_3_2_7_4_8_2_1_5_5_2_1_2_7_6_8_4_4_1_2_3_8_7_1_9_9_4_6_2_8_1_8_5_6_2_5_1_9_1_7_7_6_4_9_8_4_2_3_1_1_1_7_4_5_4_5_1_2_4_9_7_3_9_1_9_3_8_3_3_9_5_4_2_2_5_8_4_4_8_5_7_4_4_3_2_8_9_3_5_3_7_2_7_1_8_6_3_3_3_4_1_7_2_8_2_2_8_2_8_2_1_2_2_2_2_8_5_3_3_7_9_9_8_6_8_2_4_2_7_7_1_6_6_2_2_7_5_1_6_1_1_1_6_8_9_1_4_9_4_8_1_6_8_6_7_5_8_2_5_2_2_2_9_5_6_8_2_5_2_7_6_8_1_6_8_1_2_2_2_7_8_5_3_5_8_9_6_6_3_5_4_2_2_8_4_2_3_5_1_1_4_9_1_1_4_4_5_3_6_3_1_4_7_6_4_3_2_2_1_4_5_4_3_6_5_4_5</t>
   </si>
   <si>
-    <t>6_1_8_2_8_4_6_3_3_6_8_6_7_8_8_8_6_8_6_7_8_2_7_3_1_2_3_3_1_3_2_6_2_3_3_7_7_4_6_1_1_2_2_1_7_3_8_4_2_2_2_5_8_6_4_4_4_1_6_6_7_2_2_3_6_5_6_5_4_4_1_6_8_5_6_7_6_6_1_1_6_8_4_1_7_4_1_8_1_2_1_4_3_3_6_4_5_7_1_1_7_2_8_1_7_1_5_1_3_6_3_1_8_1_1_8_2_6_1_1_5_3_1_1_8_4_4_2_3_4_3_2_2_1_5_3_5_5_5_6_2_5_2_1_3_2_2_2_7_7_7_1_8_3_1_4_1_1_7_7_6_5_3_4_4_5_6_2_1_8_1_4_4_2_3_3_3_6_8_6_7_8_8_1_2_4_1_6_8_1_4_3_5_8_4_1_1_3_4_4_4_4_5_5_4_4_6_2_8_4_3_6_7_1_7_3_4_6_7_7_7_3_1_5_2_7_4_8_1_2_2_1_5_4_4_8_8_6_1_2_1_2_4_4_3_3_1_7_4_1_4_1_4_1_7_7_1_3_6_1_1_4_3_1_5_5_6_8_1_4_8_2_1_3_5_8_1_7_2_4_5_1_4_1_5_5_7_2_8_7_1_2_2_7_7_2_5_5_1_6_1_1_1_4_8_8_1_2_2_4_7_2_7_3_3_3_3_6_7_7_1_4_6_2_4_4_3_4_1_1_1_3_7_3_3_4_5_2_6_2_2_8_2_4_1_2_6_5_2_8_8_8_1_4_2_3_4_7_7_6_1_7_2_2_7_7_7_1_2_6_2_7_6_8_2_1_7_2_2_8_6_8_5_1_6_2_7_2_2_7_8_4_4_4_2_6_8_1_7_3_1_7_7_1_3_6_1_8_8_1_8_1_1_4_6_2_2_2_3_8_7_7_4_4_4_5_3_1_1_3_1_1_1_7_4_4_3_8_1_3_1_1_2_1_2_3_3_3_5_7_7_7_7_8_2_2_2_2_6_2_3_2_1_2_3_6_3_3_2_4_5_4_1_8_2_1_1_3_4_2_7_5_3_8_3_3_4_5_5_5_8_2_7_8_7_6_4_2_2_4</t>
+    <t>3_3_4_2_2_8_1_5_5_2_1_2_8_8_1_8_6_3_2_7_8_8_4_2_1_2_4_1_6_6_1_7_2_2_6_3_2_7_8_5_4_2_2_1_2_4_1_1_1_3_1_1_8_1_2_2_2_1_4_1_2_1_4_5_5_4_3_7_4_4_4_3_2_5_3_3_4_1_8_7_8_5_4_4_1_2_2_1_1_7_6_4_4_1_4_7_8_5_1_1_1_2_2_7_7_6_8_7_7_1_7_6_6_6_1_1_1_3_4_4_2_1_3_3_2_1_3_6_2_2_2_8_3_3_3_3_5_5_5_5_1_5_2_2_7_2_2_5_4_4_3_1_8_3_4_3_7_2_7_3_5_1_6_2_3_6_2_3_7_3_5_2_1_6_1_8_2_2_6_2_2_2_4_1_8_2_7_7_4_1_6_4_4_1_6_6_6_2_2_7_8_1_4_5_8_8_2_2_4_7_5_4_8_1_1_3_5_1_5_7_1_8_1_6_6_3_1_7_7_6_1_3_4_8_1_7_3_3_1_1_4_1_1_2_2_5_2_5_4_7_7_7_8_2_1_4_4_4_8_4_6_6_2_1_1_8_4_3_5_5_2_2_1_4_2_2_8_6_6_2_4_4_6_8_5_5_3_3_4_1_4_4_1_8_7_7_7_7_2_6_8_3_8_7_1_1_8_2_1_1_7_3_7_2_1_1_1_4_4_8_8_8_5_6_3_8_4_3_7_4_4_5_7_2_3_8_5_3_3_3_4_3_3_8_3_2_2_6_4_7_5_2_5_8_1_6_6_4_4_4_3_2_2_4_4_7_4_4_8_2_1_1_6_4_8_3_4_4_1_6_3_3_7_3_3_2_2_4_6_2_7_5_3_6_6_1_2_2_2_2_2_4_5_8_4_1_3_1_1_5_5_4_5_1_1_2_2_8_1_5_1_3_2_4_7_1_2_4_7_4_3_3_3_3_6_3_3_5_7_7_5_5_3_8_1_1_8_3_6_1_3_1_3_1_2_8_5_1_2_4_8_8_4_2_3_4_2_2_1_2_5_1_7_1_1_4_2_3_5_7_7_4_1_5_5_2_2_2_3_8_8_5_8_4_4_6_3_3_1_3</t>
   </si>
   <si>
     <t>6_8_1_2_6_8_3_6_5_9_4_3_7_6_3_7_7_6_9_7_5_6_2_8_3_5_9_1_2_5_2_5_2_4_6_2_3_3_2_3_8_3_1_8_2_4_2_1_1_4_9_3_1_8_8_7_3_5_6_5_1_4_2_6_3_5_3_8_3_6_1_2_9_7_5_3_8_9_2_3_7_2_2_5_3_6_1_3_3_5_8_1_9_9_2_1_8_1_3_9_2_9_4_6_2_5_7_7_9_1_2_8_3_8_2_5_2_6_8_7_1_8_1_1_9_8_4_6_9_1_5_4_1_8_9_9_3_7_1_6_7_3_2_7_3_2_9_4_6_2_1_3_8_8_7_6_7_5_1_5_4_9_2_7_7_1_5_7_7_7_3_4_2_1_5_5_3_3_5_1_1_5_3_1_6_1_3_1_1_4_1_1_3_7_2_2_6_1_2_5_5_3_1_7_3_4_2_4_7_2_7_2_4_2_8_8_4_5_6_8_2_5_1_1_7_3_1_7_4_3_8_9_8_2_7_2_1_1_2_2_5_4_6_2_5_9_4_7_3_7_7_8_3_2_3_4_6_9_3_4_1_4_3_2_1_3_2_1_4_1_6_5_1_9_1_3_4_2_6_2_4_8_7_2_9_6_5_4_8_3_9_8_4_3_3_1_5_8_6_3_1_1_5_1_2_2_1_9_3_8_1_4_5_6_9_5_7_2_2_1_4_3_8_1_9_7_9_7_3_5_8_5_8_9_7_4_6_3_1_8_1_4_8_3_1_9_5_2_1_6_2_7_2_3_2_1_7_4_5_2_6_6_8_2_3_2_8_4_2_4_6_4_1_7_5_3_2_8_3_5_4_7_1_6_2_7_1_8_4_6_1_5_1_2_6_3_4_4_3_8_5_8_7_3_1_4_9_6_8_3_1_2_3_4_2_9_1_7_3_1_8_8_2_1_2_1_5_4_5_1_5_7_1_3_9_7_7_2_2_1_3_7_4_9_1_2_2_1_1_9_4_6_4_1_4_3_3_6_6_3_6_5_7_1_7_8_6_9_1_6_5_4_2_5_2_3_3_9_8_6_2_5_1_3_2_6_7_3_9_6_7_9_6_1_1_6_5_2_4_6</t>
   </si>
   <si>
-    <t>1_3_3_4_2_5_4_2_1_8_7_8_8_8_2_3_2_7_4_3_7_7_7_6_1_1_5_2_8_8_8_2_1_2_8_8_2_2_2_2_1_3_3_7_1_2_4_4_2_4_4_6_3_3_5_5_4_1_7_1_1_7_8_4_2_7_3_8_3_8_8_8_4_3_1_5_2_7_3_7_8_8_5_7_3_3_2_2_3_8_3_7_8_3_3_1_1_3_4_8_1_3_1_4_8_7_4_1_1_1_2_7_8_8_1_7_4_3_1_3_2_2_7_6_3_4_6_6_2_1_1_6_7_1_4_1_7_1_1_2_2_1_3_6_6_2_1_1_2_8_2_1_1_1_3_2_7_4_4_8_3_7_1_3_2_7_3_1_7_8_4_7_4_2_4_4_4_6_2_6_4_1_5_8_2_6_4_1_6_7_1_6_4_1_8_8_1_2_1_6_1_1_3_1_4_8_3_2_2_7_1_1_2_1_7_7_7_4_4_2_4_2_2_3_4_4_7_3_2_1_8_3_8_8_8_8_6_2_8_7_2_6_1_3_8_1_2_2_8_2_2_4_4_2_7_7_2_6_7_2_2_1_5_3_5_2_6_6_1_8_4_7_2_7_2_1_1_1_5_1_1_3_1_1_6_2_3_4_4_7_2_3_1_1_4_3_7_6_6_2_2_4_1_1_5_5_8_2_4_1_4_2_2_1_1_4_2_4_7_1_1_1_1_1_6_8_2_2_1_8_8_1_1_8_1_8_7_4_8_8_1_5_2_1_1_6_4_4_4_4_1_5_3_1_1_4_5_8_3_4_1_5_2_2_5_7_2_2_3_1_7_6_4_1_1_7_7_7_4_7_3_4_2_6_3_1_2_8_7_6_4_2_4_5_4_4_2_1_7_7_1_1_1_4_1_3_3_7_1_6_2_1_3_3_3_4_5_1_7_8_2_1_8_3_1_6_6_2_2_5_4_3_1_1_1_4_6_6_5_2_3_7_3_1_2_8_1_5_5_4_1_1_2_1_2_5_1_6_2_1_1_1_1_6_7_2_4_5_1_5_4_6_1_3_2_1_6_4_3_3_3_3_4_1_2_3_3_4_2_6_5_7_3_2_1_6_1_7_1_1</t>
+    <t>3_3_1_7_6_6_8_7_1_8_2_3_4_6_2_8_4_7_6_2_5_2_1_3_7_7_7_3_3_2_4_8_1_6_7_4_3_8_8_2_2_7_2_4_5_4_1_4_2_5_6_7_3_8_5_1_8_3_3_4_4_5_7_1_7_6_3_5_5_7_2_1_1_2_1_3_1_4_4_7_4_4_7_1_7_7_7_4_3_2_8_8_2_2_1_8_8_7_8_1_8_2_1_2_3_4_7_2_3_3_2_6_2_1_4_4_2_2_6_6_7_8_1_5_5_1_2_7_7_1_7_1_1_4_6_1_5_1_8_7_7_7_8_7_3_6_2_5_2_7_4_4_2_1_4_4_3_4_4_5_4_2_2_1_1_5_3_2_7_8_6_1_1_1_3_3_3_8_1_6_4_5_4_2_2_7_7_1_2_3_3_3_8_8_4_4_1_4_3_3_2_8_4_4_4_6_2_7_7_1_1_3_3_3_2_2_1_1_1_1_8_6_5_1_5_8_6_1_8_2_8_7_7_1_1_8_1_1_4_7_8_8_8_2_1_6_2_6_4_4_7_8_4_1_1_7_7_4_3_1_2_6_4_6_1_2_3_6_6_4_3_1_8_7_6_5_3_2_1_5_1_3_6_2_3_2_2_2_1_8_3_8_2_2_1_2_4_8_2_3_4_7_7_6_6_6_4_1_1_1_1_1_2_2_1_1_1_1_5_5_5_7_3_3_1_8_4_4_2_7_3_6_3_5_2_8_6_7_3_5_1_1_2_7_5_4_4_7_3_4_1_1_1_3_3_5_4_3_2_8_4_5_7_4_4_6_3_5_8_8_6_2_2_3_4_8_8_6_1_1_7_1_4_4_7_7_4_4_4_8_6_6_2_6_7_4_2_2_8_8_2_1_1_4_7_7_7_7_4_2_2_3_1_3_1_8_3_4_4_1_2_3_2_5_1_3_4_2_8_7_1_1_2_2_3_3_2_7_5_8_3_4_5_3_6_3_4_4_3_1_3_3_7_1_2_3_5_3_5_4_8_8_2_1_1_2_4_1_1_7_1_5_3_3_1_3_7_2_6_5_5_4_2_5_4_1_5_3_4_3_2_4_7_7_3_4_7_5_7_3</t>
   </si>
   <si>
     <t>2_9_2_1_2_8_1_1_8_3_1_4_7_3_2_1_5_3_4_3_2_7_6_2_7_7_3_2_5_6_6_8_1_1_5_8_6_7_3_1_9_8_4_1_1_2_2_5_5_2_1_8_4_1_1_3_4_1_1_2_8_8_3_9_9_2_6_7_9_4_9_8_2_1_1_9_8_7_7_5_8_4_1_1_5_2_8_5_1_1_3_2_4_8_8_3_3_2_9_2_3_2_9_9_6_6_7_2_4_1_2_1_2_3_6_7_1_9_1_4_4_6_4_3_1_4_6_8_5_3_5_2_9_4_1_2_2_9_8_8_1_7_3_2_6_8_6_5_1_9_6_4_1_2_9_4_6_2_9_8_9_5_4_2_1_8_8_3_3_2_1_7_1_3_9_8_3_1_6_2_3_6_1_2_4_5_6_4_3_7_8_7_1_4_7_6_8_1_3_3_1_4_9_8_5_9_3_3_4_4_2_4_3_6_1_3_5_3_4_3_3_5_2_1_1_3_5_3_1_4_3_2_9_6_2_2_7_2_1_8_6_6_7_4_7_7_3_6_4_4_9_4_5_7_5_5_6_1_7_1_8_9_3_4_2_4_2_1_8_4_2_1_4_5_7_1_5_8_6_6_3_3_7_5_2_6_9_3_5_9_8_6_2_4_6_1_4_7_2_1_8_8_4_2_4_5_2_6_5_7_9_1_8_1_2_1_7_3_5_2_5_4_3_8_4_8_6_5_7_5_1_8_3_3_4_2_2_2_5_2_6_9_3_6_2_5_2_4_5_4_5_6_4_9_7_6_6_6_2_1_8_5_1_3_6_2_2_4_6_3_9_3_5_1_9_1_7_7_2_9_6_1_9_7_2_4_4_6_6_6_8_8_6_3_3_1_7_5_2_1_3_7_8_1_7_5_4_2_7_1_2_4_4_9_5_2_2_9_2_1_2_6_8_8_1_6_6_2_6_3_9_8_4_1_5_4_5_1_2_2_9_3_1_3_4_8_5_1_2_7_3_1_5_8_5_2_3_1_5_4_2_3_6_3_7_4_1_7_8_6_4_3_4_8_6_4_8_3_2_6_3_5_2_1_8_3_4_6_8_6_6_6_6_4_2_1_6_2_1_7</t>
@@ -8441,7 +8461,7 @@
         <v>20</v>
       </c>
       <c r="G189" s="17" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>20</v>
@@ -8472,7 +8492,7 @@
         <v>20</v>
       </c>
       <c r="G190" s="17" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>20</v>
@@ -8503,7 +8523,7 @@
         <v>20</v>
       </c>
       <c r="G191" s="17" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>20</v>
@@ -8534,7 +8554,7 @@
         <v>20</v>
       </c>
       <c r="G192" s="17" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>20</v>
@@ -8565,7 +8585,7 @@
         <v>20</v>
       </c>
       <c r="G193" s="17" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>20</v>
@@ -8596,13 +8616,13 @@
         <v>20</v>
       </c>
       <c r="G194" s="17" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I194" s="17" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J194" s="18"/>
     </row>
@@ -8627,13 +8647,13 @@
         <v>20</v>
       </c>
       <c r="G195" s="17" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I195" s="17" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J195" s="18"/>
     </row>
@@ -8658,13 +8678,13 @@
         <v>20</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I196" s="17" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J196" s="18"/>
     </row>
@@ -8689,13 +8709,13 @@
         <v>20</v>
       </c>
       <c r="G197" s="17" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I197" s="17" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J197" s="18"/>
     </row>
@@ -8720,13 +8740,13 @@
         <v>20</v>
       </c>
       <c r="G198" s="17" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I198" s="17" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J198" s="18"/>
     </row>
@@ -8745,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="E199" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F199" s="17" t="s">
         <v>20</v>
@@ -8776,7 +8796,7 @@
         <v>2</v>
       </c>
       <c r="E200" s="19" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F200" s="17" t="s">
         <v>20</v>
@@ -8807,7 +8827,7 @@
         <v>3</v>
       </c>
       <c r="E201" s="19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F201" s="17" t="s">
         <v>20</v>
@@ -8838,7 +8858,7 @@
         <v>4</v>
       </c>
       <c r="E202" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F202" s="17" t="s">
         <v>20</v>
@@ -8869,7 +8889,7 @@
         <v>5</v>
       </c>
       <c r="E203" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F203" s="17" t="s">
         <v>20</v>
@@ -8900,7 +8920,7 @@
         <v>6</v>
       </c>
       <c r="E204" s="19" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F204" s="17" t="s">
         <v>20</v>
@@ -8937,13 +8957,13 @@
         <v>20</v>
       </c>
       <c r="G205" s="17" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I205" s="17" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J205" s="18"/>
     </row>
@@ -8968,13 +8988,13 @@
         <v>20</v>
       </c>
       <c r="G206" s="17" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I206" s="17" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="J206" s="18"/>
     </row>
@@ -8999,13 +9019,13 @@
         <v>20</v>
       </c>
       <c r="G207" s="17" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I207" s="17" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J207" s="18"/>
     </row>
@@ -9030,13 +9050,13 @@
         <v>20</v>
       </c>
       <c r="G208" s="17" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I208" s="17" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J208" s="18"/>
     </row>
@@ -9055,19 +9075,19 @@
         <v>5</v>
       </c>
       <c r="E209" s="19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F209" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G209" s="17" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I209" s="17" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J209" s="18"/>
     </row>
@@ -9092,13 +9112,13 @@
         <v>20</v>
       </c>
       <c r="G210" s="17" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I210" s="17" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J210" s="18"/>
     </row>
@@ -9123,13 +9143,13 @@
         <v>20</v>
       </c>
       <c r="G211" s="17" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I211" s="17" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J211" s="18"/>
     </row>
@@ -9154,13 +9174,13 @@
         <v>20</v>
       </c>
       <c r="G212" s="17" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I212" s="17" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J212" s="18"/>
     </row>
@@ -9185,13 +9205,13 @@
         <v>20</v>
       </c>
       <c r="G213" s="17" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I213" s="17" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J213" s="18"/>
     </row>
@@ -9210,19 +9230,19 @@
         <v>5</v>
       </c>
       <c r="E214" s="19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F214" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G214" s="17" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I214" s="17" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J214" s="18"/>
     </row>
@@ -9402,13 +9422,13 @@
         <v>20</v>
       </c>
       <c r="G220" s="17" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I220" s="17" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J220" s="18"/>
     </row>
@@ -9427,19 +9447,19 @@
         <v>7</v>
       </c>
       <c r="E221" s="19" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F221" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G221" s="17" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I221" s="17" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J221" s="18"/>
     </row>
@@ -9457,19 +9477,19 @@
         <v>1</v>
       </c>
       <c r="E222" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F222" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G222" s="17" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I222" s="17" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J222" s="18"/>
       <c r="K222" s="18"/>
@@ -9488,19 +9508,19 @@
         <v>2</v>
       </c>
       <c r="E223" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G223" s="17" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I223" s="17" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K223" s="9"/>
     </row>
@@ -9518,19 +9538,19 @@
         <v>3</v>
       </c>
       <c r="E224" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F224" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G224" s="17" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I224" s="17" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K224" s="9"/>
     </row>
@@ -9548,19 +9568,19 @@
         <v>4</v>
       </c>
       <c r="E225" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F225" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G225" s="17" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I225" s="17" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K225" s="9"/>
     </row>
@@ -9578,19 +9598,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F226" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G226" s="17" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I226" s="17" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K226" s="9"/>
     </row>
@@ -9614,13 +9634,13 @@
         <v>20</v>
       </c>
       <c r="G227" s="17" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I227" s="17" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K227" s="9"/>
     </row>
@@ -9644,13 +9664,13 @@
         <v>20</v>
       </c>
       <c r="G228" s="19" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I228" s="17" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J228" s="9"/>
       <c r="K228" s="9"/>
@@ -9675,13 +9695,13 @@
         <v>20</v>
       </c>
       <c r="G229" s="19" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I229" s="19" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J229"/>
       <c r="K229"/>
@@ -9700,19 +9720,19 @@
         <v>2</v>
       </c>
       <c r="E230" s="19" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F230" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G230" s="19" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I230" s="19" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J230"/>
       <c r="K230"/>
@@ -9731,19 +9751,19 @@
         <v>3</v>
       </c>
       <c r="E231" s="19" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F231" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G231" s="19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I231" s="19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J231"/>
       <c r="K231"/>
@@ -9768,13 +9788,13 @@
         <v>20</v>
       </c>
       <c r="G232" s="19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I232" s="19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J232"/>
       <c r="K232"/>
@@ -9793,19 +9813,19 @@
         <v>1</v>
       </c>
       <c r="E233" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F233" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G233" s="19" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I233" s="19" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J233"/>
       <c r="K233"/>
@@ -9824,19 +9844,19 @@
         <v>2</v>
       </c>
       <c r="E234" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F234" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G234" s="19" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I234" s="19" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J234"/>
       <c r="K234"/>
@@ -9855,19 +9875,19 @@
         <v>3</v>
       </c>
       <c r="E235" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F235" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G235" s="19" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I235" s="19" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J235"/>
       <c r="K235"/>
@@ -9886,19 +9906,19 @@
         <v>4</v>
       </c>
       <c r="E236" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F236" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G236" s="19" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I236" s="19" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J236"/>
       <c r="K236"/>
@@ -9917,19 +9937,19 @@
         <v>5</v>
       </c>
       <c r="E237" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F237" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G237" s="19" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I237" s="19" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J237"/>
       <c r="K237"/>
@@ -9948,19 +9968,19 @@
         <v>1</v>
       </c>
       <c r="E238" s="19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F238" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G238" s="19" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I238" s="19" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J238"/>
       <c r="K238"/>
@@ -9979,19 +9999,19 @@
         <v>2</v>
       </c>
       <c r="E239" s="19" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F239" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G239" s="19" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I239" s="19" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J239"/>
       <c r="K239"/>
@@ -10010,19 +10030,19 @@
         <v>3</v>
       </c>
       <c r="E240" s="19" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F240" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G240" s="19" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I240" s="19" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J240"/>
       <c r="K240"/>
@@ -10041,19 +10061,19 @@
         <v>4</v>
       </c>
       <c r="E241" s="19" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F241" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G241" s="19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I241" s="19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J241"/>
       <c r="K241"/>
@@ -10072,19 +10092,19 @@
         <v>5</v>
       </c>
       <c r="E242" s="19" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F242" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G242" s="19" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I242" s="19" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J242"/>
       <c r="K242"/>
@@ -10103,19 +10123,19 @@
         <v>6</v>
       </c>
       <c r="E243" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F243" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G243" s="19" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I243" s="19" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J243"/>
       <c r="K243"/>
@@ -10134,19 +10154,19 @@
         <v>1</v>
       </c>
       <c r="E244" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F244" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G244" s="19" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I244" s="17" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J244" s="9"/>
       <c r="K244" s="9"/>
@@ -10165,19 +10185,19 @@
         <v>2</v>
       </c>
       <c r="E245" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F245" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G245" s="19" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I245" s="17" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J245" s="9"/>
       <c r="K245" s="9"/>
@@ -10196,19 +10216,19 @@
         <v>3</v>
       </c>
       <c r="E246" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F246" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G246" s="19" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I246" s="17" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J246" s="9"/>
       <c r="K246" s="9"/>
@@ -10227,19 +10247,19 @@
         <v>4</v>
       </c>
       <c r="E247" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F247" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G247" s="19" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I247" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J247" s="9"/>
       <c r="K247" s="9"/>
@@ -10258,19 +10278,19 @@
         <v>5</v>
       </c>
       <c r="E248" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F248" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G248" s="19" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I248" s="17" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J248" s="9"/>
       <c r="K248" s="9"/>
@@ -10295,13 +10315,13 @@
         <v>20</v>
       </c>
       <c r="G249" s="19" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I249" s="17" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J249" s="9"/>
       <c r="K249" s="9"/>
@@ -10326,13 +10346,13 @@
         <v>20</v>
       </c>
       <c r="G250" s="19" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I250" s="19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="251" s="5" customFormat="1" ht="16.5" spans="1:11">
@@ -10505,13 +10525,13 @@
         <v>20</v>
       </c>
       <c r="G256" s="17" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I256" s="17" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J256" s="18"/>
     </row>
@@ -10529,19 +10549,19 @@
         <v>7</v>
       </c>
       <c r="E257" s="19" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F257" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G257" s="17" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I257" s="17" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J257" s="18"/>
     </row>
@@ -10559,7 +10579,7 @@
         <v>1</v>
       </c>
       <c r="E258" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F258" s="17" t="s">
         <v>20</v>
@@ -10590,7 +10610,7 @@
         <v>2</v>
       </c>
       <c r="E259" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F259" s="17" t="s">
         <v>20</v>
@@ -10621,7 +10641,7 @@
         <v>3</v>
       </c>
       <c r="E260" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F260" s="17" t="s">
         <v>20</v>
@@ -10652,7 +10672,7 @@
         <v>4</v>
       </c>
       <c r="E261" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F261" s="17" t="s">
         <v>20</v>
@@ -10683,7 +10703,7 @@
         <v>5</v>
       </c>
       <c r="E262" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F262" s="17" t="s">
         <v>20</v>
@@ -10714,19 +10734,19 @@
         <v>1</v>
       </c>
       <c r="E263" s="19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F263" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G263" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I263" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K263" s="9"/>
     </row>
@@ -10744,19 +10764,19 @@
         <v>2</v>
       </c>
       <c r="E264" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F264" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G264" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I264" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K264" s="9"/>
     </row>
@@ -10774,19 +10794,19 @@
         <v>3</v>
       </c>
       <c r="E265" s="19" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F265" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G265" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I265" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K265" s="9"/>
     </row>
@@ -10804,19 +10824,19 @@
         <v>4</v>
       </c>
       <c r="E266" s="19" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F266" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G266" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I266" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K266" s="9"/>
     </row>
@@ -10834,19 +10854,19 @@
         <v>5</v>
       </c>
       <c r="E267" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F267" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G267" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I267" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K267" s="9"/>
     </row>
@@ -10870,13 +10890,13 @@
         <v>20</v>
       </c>
       <c r="G268" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I268" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K268" s="9"/>
     </row>
@@ -10894,19 +10914,19 @@
         <v>1</v>
       </c>
       <c r="E269" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G269" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I269" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J269" s="33"/>
       <c r="K269" s="33"/>
@@ -10925,19 +10945,19 @@
         <v>2</v>
       </c>
       <c r="E270" s="19" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G270" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I270" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J270" s="33"/>
       <c r="K270" s="33"/>
@@ -10956,19 +10976,19 @@
         <v>3</v>
       </c>
       <c r="E271" s="19" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G271" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I271" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J271" s="33"/>
       <c r="K271" s="33"/>
@@ -10987,19 +11007,19 @@
         <v>4</v>
       </c>
       <c r="E272" s="19" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G272" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I272" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J272" s="33"/>
       <c r="K272" s="33"/>
@@ -11018,19 +11038,19 @@
         <v>5</v>
       </c>
       <c r="E273" s="19" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G273" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I273" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J273" s="33"/>
       <c r="K273" s="33"/>
@@ -11049,19 +11069,19 @@
         <v>6</v>
       </c>
       <c r="E274" s="19" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G274" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I274" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J274" s="33"/>
       <c r="K274" s="33"/>
@@ -11080,19 +11100,19 @@
         <v>7</v>
       </c>
       <c r="E275" s="19" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I275" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J275" s="33"/>
       <c r="K275" s="33"/>
@@ -11117,13 +11137,13 @@
         <v>20</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J276" s="33"/>
     </row>
@@ -11147,13 +11167,13 @@
         <v>20</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J277" s="33"/>
     </row>
@@ -11177,13 +11197,13 @@
         <v>20</v>
       </c>
       <c r="G278" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J278" s="33"/>
     </row>
@@ -11201,19 +11221,19 @@
         <v>4</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J279" s="33"/>
     </row>
@@ -11231,19 +11251,19 @@
         <v>1</v>
       </c>
       <c r="E280" s="19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F280" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G280" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I280" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="J280" s="33"/>
       <c r="K280" s="33"/>
@@ -11262,19 +11282,19 @@
         <v>2</v>
       </c>
       <c r="E281" s="19" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F281" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G281" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I281" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J281" s="33"/>
       <c r="K281" s="33"/>
@@ -11293,19 +11313,19 @@
         <v>3</v>
       </c>
       <c r="E282" s="19" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F282" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G282" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I282" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J282" s="33"/>
       <c r="K282" s="33"/>
@@ -11324,19 +11344,19 @@
         <v>4</v>
       </c>
       <c r="E283" s="19" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F283" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G283" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I283" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J283" s="33"/>
       <c r="K283" s="33"/>
@@ -11355,19 +11375,19 @@
         <v>5</v>
       </c>
       <c r="E284" s="19" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F284" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G284" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I284" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J284" s="33"/>
       <c r="K284" s="33"/>
@@ -11386,19 +11406,19 @@
         <v>6</v>
       </c>
       <c r="E285" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F285" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G285" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I285" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J285" s="33"/>
       <c r="K285" s="33"/>
@@ -11423,13 +11443,13 @@
         <v>20</v>
       </c>
       <c r="G286" s="5" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J286" s="33"/>
     </row>
@@ -11453,13 +11473,13 @@
         <v>20</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I287" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J287" s="33"/>
     </row>
@@ -11483,13 +11503,13 @@
         <v>20</v>
       </c>
       <c r="G288" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J288" s="33"/>
     </row>
@@ -11507,19 +11527,19 @@
         <v>4</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J289" s="33"/>
     </row>
@@ -11543,13 +11563,13 @@
         <v>20</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I290" s="5" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J290" s="33"/>
     </row>
@@ -11573,13 +11593,13 @@
         <v>20</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J291" s="33"/>
     </row>
@@ -11603,13 +11623,13 @@
         <v>20</v>
       </c>
       <c r="G292" s="5" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I292" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="J292" s="33"/>
     </row>
@@ -11627,19 +11647,19 @@
         <v>4</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I293" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J293" s="33"/>
     </row>
@@ -11657,19 +11677,19 @@
         <v>1</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G294" s="39" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H294" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I294" s="39" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J294" s="40"/>
       <c r="K294" s="40"/>
@@ -11688,13 +11708,13 @@
         <v>2</v>
       </c>
       <c r="E295" s="34" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F295" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G295" s="39" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H295" s="35" t="s">
         <v>20</v>
@@ -11719,13 +11739,13 @@
         <v>3</v>
       </c>
       <c r="E296" s="34" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F296" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G296" s="39" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H296" s="35" t="s">
         <v>20</v>
@@ -11756,7 +11776,7 @@
         <v>20</v>
       </c>
       <c r="G297" s="39" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H297" s="35" t="s">
         <v>20</v>
@@ -11787,7 +11807,7 @@
         <v>20</v>
       </c>
       <c r="G298" s="39" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H298" s="35" t="s">
         <v>20</v>
@@ -11812,19 +11832,19 @@
         <v>1</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G299" s="39" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H299" s="35" t="s">
         <v>20</v>
       </c>
       <c r="I299" s="39" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J299" s="40"/>
       <c r="K299" s="40"/>
@@ -11843,13 +11863,13 @@
         <v>2</v>
       </c>
       <c r="E300" s="34" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F300" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G300" s="39" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H300" s="35" t="s">
         <v>20</v>
@@ -11873,13 +11893,13 @@
         <v>3</v>
       </c>
       <c r="E301" s="34" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F301" s="35" t="s">
         <v>20</v>
       </c>
       <c r="G301" s="39" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H301" s="35" t="s">
         <v>20</v>
@@ -11909,7 +11929,7 @@
         <v>20</v>
       </c>
       <c r="G302" s="39" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H302" s="35" t="s">
         <v>20</v>
@@ -11939,7 +11959,7 @@
         <v>20</v>
       </c>
       <c r="G303" s="39" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H303" s="35" t="s">
         <v>20</v>
